--- a/Översikt GNOSJÖ.xlsx
+++ b/Översikt GNOSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44757</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46030</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44711</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 38355-2023</t>
+          <t>A 28312-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -919,14 +919,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45161</v>
+        <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -939,23 +939,23 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
@@ -963,51 +963,51 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 38355-2023 artfynd.xlsx", "A 38355-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 28312-2025 artfynd.xlsx", "A 28312-2025")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 38355-2023 karta.png", "A 38355-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 28312-2025 karta.png", "A 28312-2025")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 38355-2023 georefererad karta.tif", "A 38355-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 28312-2025 georefererad karta.tif", "A 28312-2025")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 38355-2023 FSC-klagomål.docx", "A 38355-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 28312-2025 FSC-klagomål.docx", "A 28312-2025")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 38355-2023 FSC-klagomål mail.docx", "A 38355-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 28312-2025 FSC-klagomål mail.docx", "A 28312-2025")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 38355-2023 tillsynsbegäran.docx", "A 38355-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 28312-2025 tillsynsbegäran.docx", "A 28312-2025")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 38355-2023 tillsynsbegäran mail.docx", "A 38355-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 28312-2025 tillsynsbegäran mail.docx", "A 28312-2025")</f>
         <v/>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
         <v>44721</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 28312-2025</t>
+          <t>A 38355-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45818</v>
+        <v>45161</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1173,51 +1173,51 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 28312-2025 artfynd.xlsx", "A 28312-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 38355-2023 artfynd.xlsx", "A 38355-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 28312-2025 karta.png", "A 28312-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 38355-2023 karta.png", "A 38355-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 28312-2025 georefererad karta.tif", "A 28312-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 38355-2023 georefererad karta.tif", "A 38355-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 28312-2025 FSC-klagomål.docx", "A 28312-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 38355-2023 FSC-klagomål.docx", "A 38355-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 28312-2025 FSC-klagomål mail.docx", "A 28312-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 38355-2023 FSC-klagomål mail.docx", "A 38355-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 28312-2025 tillsynsbegäran.docx", "A 28312-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 38355-2023 tillsynsbegäran.docx", "A 38355-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 28312-2025 tillsynsbegäran mail.docx", "A 28312-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 38355-2023 tillsynsbegäran mail.docx", "A 38355-2023")</f>
         <v/>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
         <v>44530</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>44837</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>44482</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>44456</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>44474</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 50444-2022</t>
+          <t>A 3418-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44866</v>
+        <v>44585</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1618,8 +1618,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1662,7 +1667,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 3418-2022</t>
+          <t>A 50444-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1676,10 +1681,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44585</v>
+        <v>44866</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1691,13 +1696,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1757,7 +1757,7 @@
         <v>44468</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>44503</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 20077-2022</t>
+          <t>A 59855-2021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44698</v>
+        <v>44494</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1959,7 +1959,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 59855-2021</t>
+          <t>A 20077-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44494</v>
+        <v>44698</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2049,7 +2049,7 @@
         <v>44470</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>44698</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>44467</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>44568</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>44804</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>44855</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>44747</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>44588</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>44858</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>44470</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 16243-2025</t>
+          <t>A 13352-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45749</v>
+        <v>45387</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2789,11 +2789,6 @@
       <c r="G29" t="inlineStr">
         <is>
           <t>GNOSJÖ</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -2840,7 +2835,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 43758-2023</t>
+          <t>A 42280-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2854,10 +2849,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45187</v>
+        <v>45180</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2870,7 +2865,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2913,7 +2908,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 43784-2023</t>
+          <t>A 46657-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2927,10 +2922,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45187</v>
+        <v>44850</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2943,7 +2938,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.8</v>
+        <v>7.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2986,7 +2981,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33575-2022</t>
+          <t>A 20948-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3000,10 +2995,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44789</v>
+        <v>45439</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3016,7 +3011,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.4</v>
+        <v>6.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3059,7 +3054,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 47454-2023</t>
+          <t>A 5089-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3073,10 +3068,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45202</v>
+        <v>45330</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3089,7 +3084,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3132,7 +3127,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 59026-2023</t>
+          <t>A 62053-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3146,10 +3141,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45252</v>
+        <v>44918</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3162,7 +3157,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3205,7 +3200,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 23254-2023</t>
+          <t>A 49725-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3219,10 +3214,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45075</v>
+        <v>44455</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3235,7 +3230,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3278,7 +3273,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 49720-2021</t>
+          <t>A 39668-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3292,10 +3287,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44455</v>
+        <v>45167</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3308,7 +3303,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.1</v>
+        <v>0.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3351,7 +3346,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 64718-2023</t>
+          <t>A 48188-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3365,10 +3360,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45281</v>
+        <v>44853</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3381,7 +3376,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3424,7 +3419,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 53078-2021</t>
+          <t>A 25837-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3438,10 +3433,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44467</v>
+        <v>45090</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3454,7 +3449,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3497,7 +3492,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 46657-2022</t>
+          <t>A 57730-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3511,10 +3506,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44850</v>
+        <v>45246</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3527,7 +3522,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>7.9</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3570,7 +3565,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 3504-2023</t>
+          <t>A 49720-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3584,10 +3579,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44950</v>
+        <v>44455</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3600,7 +3595,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3643,7 +3638,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 5082-2024</t>
+          <t>A 30961-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3657,10 +3652,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45330</v>
+        <v>45113</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3673,7 +3668,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3716,7 +3711,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 41347-2023</t>
+          <t>A 13610-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3730,10 +3725,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45174</v>
+        <v>45390</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3746,7 +3741,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>6.2</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3789,7 +3784,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 30091-2024</t>
+          <t>A 61677-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3799,14 +3794,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45489</v>
+        <v>46002</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3819,7 +3814,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3862,7 +3857,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 50440-2022</t>
+          <t>A 49758-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3876,10 +3871,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44866</v>
+        <v>45597</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3892,7 +3887,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>8.699999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3935,7 +3930,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 5707-2022</t>
+          <t>A 8698-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3949,10 +3944,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44596</v>
+        <v>45712</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3965,7 +3960,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4008,7 +4003,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 55909-2022</t>
+          <t>A 24861-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4022,10 +4017,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44889</v>
+        <v>45799</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4038,7 +4033,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.9</v>
+        <v>5.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4081,7 +4076,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 56625-2022</t>
+          <t>A 25482-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4095,10 +4090,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44893</v>
+        <v>45802</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4111,7 +4106,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4154,7 +4149,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 30101-2024</t>
+          <t>A 63511-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4164,14 +4159,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45489</v>
+        <v>46013</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4184,7 +4179,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4227,7 +4222,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 27264-2023</t>
+          <t>A 63220-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4241,10 +4236,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45096</v>
+        <v>46010</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4257,7 +4252,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4300,7 +4295,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 15776-2023</t>
+          <t>A 38510-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4314,10 +4309,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45021</v>
+        <v>45884</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4330,7 +4325,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4373,7 +4368,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 9641-2026</t>
+          <t>A 15436-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4387,10 +4382,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46070</v>
+        <v>45401</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4402,13 +4397,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4451,7 +4441,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 9624-2026</t>
+          <t>A 48229-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4465,10 +4455,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46070</v>
+        <v>44858</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4480,13 +4470,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4529,7 +4514,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 9627-2026</t>
+          <t>A 6415-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4543,10 +4528,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46070</v>
+        <v>45699</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4558,13 +4543,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4607,7 +4587,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 62053-2022</t>
+          <t>A 1664-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4621,10 +4601,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44918</v>
+        <v>46034</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4637,7 +4617,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4680,7 +4660,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 30669-2025</t>
+          <t>A 40863-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4694,10 +4674,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45831</v>
+        <v>45897</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4710,7 +4690,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4753,7 +4733,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 30654-2025</t>
+          <t>A 7316-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4767,10 +4747,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45831</v>
+        <v>45345</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4783,7 +4763,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4826,7 +4806,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 31235-2025</t>
+          <t>A 40552-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4840,10 +4820,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45832</v>
+        <v>45896</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4856,7 +4836,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4899,7 +4879,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 4293-2022</t>
+          <t>A 21080-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4913,10 +4893,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44588</v>
+        <v>45777</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4929,7 +4909,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4972,7 +4952,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 31228-2025</t>
+          <t>A 42615-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4986,10 +4966,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45832</v>
+        <v>45905</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5002,7 +4982,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5045,7 +5025,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 6415-2025</t>
+          <t>A 30654-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5059,10 +5039,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45699</v>
+        <v>45831</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5075,7 +5055,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5118,7 +5098,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 8698-2025</t>
+          <t>A 30669-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5132,10 +5112,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45712</v>
+        <v>45831</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5148,7 +5128,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5191,7 +5171,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 40552-2025</t>
+          <t>A 31228-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5205,10 +5185,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45896</v>
+        <v>45832</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5221,7 +5201,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5264,7 +5244,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 40863-2025</t>
+          <t>A 31235-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5278,10 +5258,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45897</v>
+        <v>45832</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5294,7 +5274,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5337,7 +5317,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 27675-2025</t>
+          <t>A 43637-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5351,10 +5331,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45813</v>
+        <v>45911</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5367,7 +5347,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5410,7 +5390,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 36508-2022</t>
+          <t>A 43656-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5424,10 +5404,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44804</v>
+        <v>45912</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5440,7 +5420,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5483,7 +5463,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 21080-2025</t>
+          <t>A 44383-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5497,10 +5477,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45777</v>
+        <v>45916</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5513,7 +5493,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5556,7 +5536,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 50304-2024</t>
+          <t>A 44394-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5570,10 +5550,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45600</v>
+        <v>45916</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5586,7 +5566,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5629,7 +5609,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 8747-2024</t>
+          <t>A 27675-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5643,10 +5623,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45356</v>
+        <v>45813</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5659,7 +5639,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5702,7 +5682,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 42615-2025</t>
+          <t>A 16243-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5716,10 +5696,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45905</v>
+        <v>45749</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5731,8 +5711,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5775,7 +5760,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 43637-2025</t>
+          <t>A 58779-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5789,10 +5774,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45911</v>
+        <v>45986</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5805,7 +5790,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.6</v>
+        <v>1.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5848,7 +5833,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 43656-2025</t>
+          <t>A 36508-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5862,10 +5847,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45912</v>
+        <v>44804</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5878,7 +5863,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5921,7 +5906,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 44383-2025</t>
+          <t>A 9641-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5935,10 +5920,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45916</v>
+        <v>46070</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5950,8 +5935,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5994,7 +5984,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 44394-2025</t>
+          <t>A 9624-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6008,10 +5998,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45916</v>
+        <v>46070</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6023,8 +6013,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6067,7 +6062,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 37198-2025</t>
+          <t>A 9627-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6081,10 +6076,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45875</v>
+        <v>46070</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6096,8 +6091,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6140,7 +6140,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 4992-2023</t>
+          <t>A 5082-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44958</v>
+        <v>45330</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6213,7 +6213,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 58249-2021</t>
+          <t>A 37198-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6227,10 +6227,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44487</v>
+        <v>45875</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6286,7 +6286,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 38510-2025</t>
+          <t>A 50728-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6300,10 +6300,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45884</v>
+        <v>45946</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6316,7 +6316,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.1</v>
+        <v>15.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6359,7 +6359,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 19307-2023</t>
+          <t>A 11667-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6373,10 +6373,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45049</v>
+        <v>46084</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6432,7 +6432,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 25487-2022</t>
+          <t>A 6781-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44732</v>
+        <v>44602</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>7.1</v>
+        <v>3.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6505,7 +6505,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 58970-2024</t>
+          <t>A 41347-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45636</v>
+        <v>45174</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.5</v>
+        <v>6.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6578,7 +6578,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 11667-2026</t>
+          <t>A 50440-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6592,10 +6592,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46084</v>
+        <v>44866</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6651,7 +6651,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 29066-2022</t>
+          <t>A 4992-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6665,10 +6665,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44750</v>
+        <v>44958</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6724,7 +6724,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 34083-2023</t>
+          <t>A 13600-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6738,10 +6738,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45125</v>
+        <v>46097</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6753,8 +6753,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6797,7 +6802,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 49758-2024</t>
+          <t>A 30101-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6807,14 +6812,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45597</v>
+        <v>45489</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6827,7 +6832,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6870,7 +6875,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 25837-2023</t>
+          <t>A 17402-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6884,10 +6889,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45090</v>
+        <v>46120</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6943,7 +6948,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 50728-2025</t>
+          <t>A 55918-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6957,10 +6962,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45946</v>
+        <v>45973</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6973,7 +6978,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>15.2</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7016,7 +7021,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 13600-2026</t>
+          <t>A 18473-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7030,10 +7035,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46097</v>
+        <v>46127</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7045,13 +7050,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7094,7 +7094,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 23625-2022</t>
+          <t>A 19171-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7108,10 +7108,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44721</v>
+        <v>46132</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>22.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7167,7 +7167,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 47856-2022</t>
+          <t>A 56240-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7181,10 +7181,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44855</v>
+        <v>45974</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.1</v>
+        <v>3.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7240,7 +7240,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 41323-2022</t>
+          <t>A 56554-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7254,10 +7254,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44826</v>
+        <v>45975</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.1</v>
+        <v>7.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7313,7 +7313,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 16303-2023</t>
+          <t>A 37864-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7327,10 +7327,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45028</v>
+        <v>45881</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>6.3</v>
+        <v>3.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7386,7 +7386,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 51901-2022</t>
+          <t>A 57012-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7400,10 +7400,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44872</v>
+        <v>45978</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>7.3</v>
+        <v>0.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7459,7 +7459,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 56240-2025</t>
+          <t>A 18337-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45974</v>
+        <v>46125</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 55918-2025</t>
+          <t>A 54833-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7546,10 +7546,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45973</v>
+        <v>45618</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7561,8 +7561,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7605,7 +7610,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 41918-2022</t>
+          <t>A 27036-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7619,10 +7624,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44830</v>
+        <v>45095</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7635,7 +7640,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7678,7 +7683,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 56554-2025</t>
+          <t>A 33575-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7692,10 +7697,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45975</v>
+        <v>44789</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7708,7 +7713,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>7.2</v>
+        <v>2.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7751,7 +7756,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 17402-2026</t>
+          <t>A 61532-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7761,14 +7766,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46120</v>
+        <v>45265</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7780,8 +7785,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7824,7 +7834,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 57730-2023</t>
+          <t>A 58780-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7838,10 +7848,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45246</v>
+        <v>45986</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7854,7 +7864,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7897,7 +7907,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 6763-2025</t>
+          <t>A 36905-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7911,10 +7921,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45700</v>
+        <v>45538</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7927,7 +7937,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7970,7 +7980,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 57012-2025</t>
+          <t>A 21076-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7984,10 +7994,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45978</v>
+        <v>45777</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8000,7 +8010,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8043,7 +8053,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 52813-2021</t>
+          <t>A 11157-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8057,10 +8067,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44467</v>
+        <v>45371</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8073,7 +8083,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8116,7 +8126,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 18473-2026</t>
+          <t>A 11163-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8130,10 +8140,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46127</v>
+        <v>45371</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8146,7 +8156,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8189,7 +8199,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 42280-2023</t>
+          <t>A 37963-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8203,10 +8213,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45180</v>
+        <v>45544</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8219,7 +8229,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.9</v>
+        <v>5.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8262,7 +8272,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 58780-2025</t>
+          <t>A 61411-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8276,10 +8286,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45986</v>
+        <v>46000</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8292,7 +8302,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8335,7 +8345,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 19171-2026</t>
+          <t>A 3987-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8349,10 +8359,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46132</v>
+        <v>45322</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8365,7 +8375,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>22.2</v>
+        <v>2.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8408,7 +8418,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 27258-2023</t>
+          <t>A 61792-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8422,10 +8432,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45096</v>
+        <v>46002</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8438,7 +8448,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.5</v>
+        <v>10.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8481,7 +8491,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 61411-2025</t>
+          <t>A 31772-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8495,10 +8505,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46000</v>
+        <v>45118</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8511,7 +8521,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8554,7 +8564,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 61677-2025</t>
+          <t>A 61682-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8571,7 +8581,7 @@
         <v>46002</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8584,7 +8594,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8627,7 +8637,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 61682-2025</t>
+          <t>A 42618-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8641,10 +8651,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46002</v>
+        <v>45905</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8657,7 +8667,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8700,7 +8710,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 48188-2022</t>
+          <t>A 30314-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8714,10 +8724,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44853</v>
+        <v>45490</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8730,7 +8740,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8773,7 +8783,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 61792-2025</t>
+          <t>A 64481-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8787,10 +8797,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46002</v>
+        <v>45280</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8803,7 +8813,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>10.6</v>
+        <v>5.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8846,7 +8856,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 18337-2026</t>
+          <t>A 32177-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8860,10 +8870,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46125</v>
+        <v>45511</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8876,7 +8886,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8919,7 +8929,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 26746-2023</t>
+          <t>A 60859-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8933,10 +8943,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45093</v>
+        <v>45644</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8949,7 +8959,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -8992,7 +9002,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 54833-2024</t>
+          <t>A 55074-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9006,10 +9016,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45618</v>
+        <v>45237</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9021,13 +9031,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9070,7 +9075,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 63220-2025</t>
+          <t>A 5818-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9084,10 +9089,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46010</v>
+        <v>44963</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9100,7 +9105,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9143,7 +9148,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 63511-2025</t>
+          <t>A 62045-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9157,10 +9162,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46013</v>
+        <v>44918</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9173,7 +9178,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9216,7 +9221,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 21076-2025</t>
+          <t>A 40244-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9230,10 +9235,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45777</v>
+        <v>45554</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9246,7 +9251,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9289,7 +9294,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 11157-2024</t>
+          <t>A 41323-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9303,10 +9308,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45371</v>
+        <v>44826</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9319,7 +9324,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9362,7 +9367,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 11163-2024</t>
+          <t>A 4293-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9376,10 +9381,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45371</v>
+        <v>44588</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9392,7 +9397,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9435,7 +9440,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 1664-2026</t>
+          <t>A 23132-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9449,10 +9454,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46034</v>
+        <v>46161</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9465,7 +9470,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9508,7 +9513,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 37963-2024</t>
+          <t>A 23138-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9522,10 +9527,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45544</v>
+        <v>46161</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9538,7 +9543,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>5.3</v>
+        <v>2.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9581,7 +9586,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 36905-2024</t>
+          <t>A 27264-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9595,10 +9600,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45538</v>
+        <v>45096</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9611,7 +9616,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9654,7 +9659,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 3987-2024</t>
+          <t>A 27952-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9668,10 +9673,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45322</v>
+        <v>46193</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9683,8 +9688,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9727,7 +9737,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 22650-2024</t>
+          <t>A 27954-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9741,10 +9751,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45447</v>
+        <v>46193</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9757,7 +9767,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>7.9</v>
+        <v>2.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9800,7 +9810,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 61532-2023</t>
+          <t>A 27951-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9810,14 +9820,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45265</v>
+        <v>46193</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9831,11 +9841,11 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9878,7 +9888,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 42618-2025</t>
+          <t>A 27953-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9892,10 +9902,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45905</v>
+        <v>46193</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9907,8 +9917,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9951,7 +9966,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 26210-2024</t>
+          <t>A 27729-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9961,14 +9976,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45468</v>
+        <v>46191</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -9981,7 +9996,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.3</v>
+        <v>5.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10024,7 +10039,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 37864-2025</t>
+          <t>A 28026-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10038,10 +10053,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45881</v>
+        <v>46195</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10054,7 +10069,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10097,7 +10112,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 58779-2025</t>
+          <t>A 28018-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10111,10 +10126,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45986</v>
+        <v>46195</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10127,7 +10142,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10170,7 +10185,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 60859-2024</t>
+          <t>A 28058-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10184,10 +10199,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45644</v>
+        <v>46195</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10200,7 +10215,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10243,7 +10258,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 43787-2023</t>
+          <t>A 53077-2021</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10257,10 +10272,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45187</v>
+        <v>44467</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10273,7 +10288,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10316,7 +10331,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 43760-2023</t>
+          <t>A 32913-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10330,10 +10345,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45187</v>
+        <v>46244</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10346,7 +10361,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10389,7 +10404,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 43790-2023</t>
+          <t>A 32903-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10403,10 +10418,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45187</v>
+        <v>46244</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10419,7 +10434,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10462,7 +10477,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 35325-2023</t>
+          <t>A 30160-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10476,10 +10491,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45146</v>
+        <v>46206</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10492,7 +10507,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10535,7 +10550,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 10996-2024</t>
+          <t>A 58356-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10549,10 +10564,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45370</v>
+        <v>44893</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10565,7 +10580,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>5.9</v>
+        <v>2.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10608,7 +10623,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 40067-2023</t>
+          <t>A 20078-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10622,10 +10637,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45168</v>
+        <v>44698</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10638,7 +10653,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10681,7 +10696,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 73961-2021</t>
+          <t>A 35325-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10695,10 +10710,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44553</v>
+        <v>45146</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10710,13 +10725,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>5.1</v>
+        <v>0.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10759,7 +10769,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 20078-2022</t>
+          <t>A 73961-2021</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10773,10 +10783,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44698</v>
+        <v>44553</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10788,8 +10798,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>1.7</v>
+        <v>5.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10832,7 +10847,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 6781-2022</t>
+          <t>A 27258-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10846,10 +10861,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44602</v>
+        <v>45096</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10862,7 +10877,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10905,7 +10920,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 36406-2022</t>
+          <t>A 29066-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10919,10 +10934,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44803</v>
+        <v>44750</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10935,7 +10950,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -10978,7 +10993,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 27036-2023</t>
+          <t>A 3504-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10992,10 +11007,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45095</v>
+        <v>44950</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11008,7 +11023,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11068,7 +11083,7 @@
         <v>45716</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11124,7 +11139,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 43786-2023</t>
+          <t>A 36653-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11134,14 +11149,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45187</v>
+        <v>44804</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11154,7 +11169,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11197,7 +11212,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 23132-2026</t>
+          <t>A 23254-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11211,10 +11226,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46161</v>
+        <v>45075</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11227,7 +11242,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11270,7 +11285,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 23138-2026</t>
+          <t>A 27498-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11284,10 +11299,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46161</v>
+        <v>46185</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11299,8 +11314,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>2.3</v>
+        <v>38</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11343,7 +11363,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 6747-2025</t>
+          <t>A 64718-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11357,10 +11377,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45700</v>
+        <v>45281</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11373,7 +11393,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.5</v>
+        <v>4.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11416,7 +11436,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 6789-2025</t>
+          <t>A 31983-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11430,10 +11450,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45700</v>
+        <v>46232</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11446,7 +11466,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11489,7 +11509,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 59727-2024</t>
+          <t>A 37630-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11503,10 +11523,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45639</v>
+        <v>46276</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11518,8 +11538,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>2.3</v>
+        <v>13.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11562,7 +11587,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 30961-2023</t>
+          <t>A 52813-2021</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11576,10 +11601,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45113</v>
+        <v>44467</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11592,7 +11617,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11635,7 +11660,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 16244-2025</t>
+          <t>A 47454-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11649,10 +11674,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45749</v>
+        <v>45202</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11664,13 +11689,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11713,7 +11733,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 48227-2022</t>
+          <t>A 34083-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11727,10 +11747,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44858</v>
+        <v>45125</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11743,7 +11763,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11786,7 +11806,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 22846-2024</t>
+          <t>A 6785-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11800,10 +11820,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45448</v>
+        <v>45700</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11816,7 +11836,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11859,7 +11879,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 27729-2026</t>
+          <t>A 6793-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11869,14 +11889,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46191</v>
+        <v>45700</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11889,7 +11909,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>5.6</v>
+        <v>0.9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11932,7 +11952,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 61531-2023</t>
+          <t>A 59727-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11942,14 +11962,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45265</v>
+        <v>45639</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11961,13 +11981,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12010,7 +12025,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 28018-2026</t>
+          <t>A 15434-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12024,10 +12039,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46195</v>
+        <v>45020</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12040,7 +12055,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12083,7 +12098,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 27952-2026</t>
+          <t>A 41918-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12097,10 +12112,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46193</v>
+        <v>44830</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12112,13 +12127,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12161,7 +12171,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 27954-2026</t>
+          <t>A 61531-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12171,14 +12181,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46193</v>
+        <v>45265</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12190,8 +12200,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12234,7 +12249,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 27951-2026</t>
+          <t>A 26746-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12248,10 +12263,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46193</v>
+        <v>45093</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12263,13 +12278,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12312,7 +12322,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 28058-2026</t>
+          <t>A 15776-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12326,10 +12336,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46195</v>
+        <v>45021</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12342,7 +12352,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12385,7 +12395,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 27953-2026</t>
+          <t>A 51901-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12399,10 +12409,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46193</v>
+        <v>44872</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12414,13 +12424,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>5.7</v>
+        <v>7.3</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12463,7 +12468,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 28026-2026</t>
+          <t>A 26210-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12477,10 +12482,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46195</v>
+        <v>45468</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12493,7 +12498,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12536,7 +12541,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 39668-2023</t>
+          <t>A 16244-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12550,10 +12555,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45167</v>
+        <v>45749</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12565,8 +12570,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>0.3</v>
+        <v>2.3</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12609,7 +12619,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 5818-2023</t>
+          <t>A 41357-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12623,10 +12633,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44963</v>
+        <v>45174</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12639,7 +12649,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12682,7 +12692,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 32913-2026</t>
+          <t>A 6662-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12696,10 +12706,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46244</v>
+        <v>45341</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12712,7 +12722,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2.7</v>
+        <v>0.2</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12755,7 +12765,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 5030-2022</t>
+          <t>A 8747-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12769,10 +12779,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44593</v>
+        <v>45356</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12785,7 +12795,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12828,7 +12838,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 40244-2024</t>
+          <t>A 56393-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12842,10 +12852,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45554</v>
+        <v>45243</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12858,7 +12868,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12901,7 +12911,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 64481-2023</t>
+          <t>A 32826-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12915,10 +12925,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45280</v>
+        <v>45124</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12931,7 +12941,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>5.5</v>
+        <v>0.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -12974,7 +12984,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 32903-2026</t>
+          <t>A 1450-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -12988,10 +12998,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46244</v>
+        <v>45303</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13047,7 +13057,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 55074-2023</t>
+          <t>A 53078-2021</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13061,10 +13071,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45237</v>
+        <v>44467</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13077,7 +13087,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13120,7 +13130,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 58356-2022</t>
+          <t>A 36406-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13134,10 +13144,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44893</v>
+        <v>44803</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13150,7 +13160,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13193,7 +13203,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 14355-2023</t>
+          <t>A 10996-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13207,10 +13217,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45012</v>
+        <v>45370</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13223,7 +13233,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.6</v>
+        <v>5.9</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13266,7 +13276,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 13913-2024</t>
+          <t>A 22846-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13280,10 +13290,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45391</v>
+        <v>45448</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13296,7 +13306,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13339,7 +13349,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 49725-2021</t>
+          <t>A 30091-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13349,14 +13359,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44455</v>
+        <v>45489</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13369,7 +13379,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13412,7 +13422,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 46254-2024</t>
+          <t>A 48227-2022</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13426,10 +13436,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45581</v>
+        <v>44858</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13442,7 +13452,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13485,7 +13495,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 30160-2026</t>
+          <t>A 43758-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13499,10 +13509,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46206</v>
+        <v>45187</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13515,7 +13525,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13558,7 +13568,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 13352-2024</t>
+          <t>A 6747-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13572,10 +13582,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45387</v>
+        <v>45700</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13588,7 +13598,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13631,7 +13641,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 13610-2024</t>
+          <t>A 50304-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13645,10 +13655,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45390</v>
+        <v>45600</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13661,7 +13671,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13704,7 +13714,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 56393-2023</t>
+          <t>A 43786-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13718,10 +13728,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45243</v>
+        <v>45187</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13734,7 +13744,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13777,7 +13787,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 36653-2022</t>
+          <t>A 43787-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13787,14 +13797,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44804</v>
+        <v>45187</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13807,7 +13817,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -13850,7 +13860,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 48229-2022</t>
+          <t>A 46254-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13864,10 +13874,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44858</v>
+        <v>45581</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13880,7 +13890,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13923,7 +13933,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 5089-2024</t>
+          <t>A 47856-2022</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13937,10 +13947,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45330</v>
+        <v>44855</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -13953,7 +13963,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -13996,7 +14006,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 58247-2021</t>
+          <t>A 19307-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14010,10 +14020,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44487</v>
+        <v>45049</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14026,7 +14036,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>8.9</v>
+        <v>0.4</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14069,7 +14079,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 31772-2023</t>
+          <t>A 56625-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14083,10 +14093,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45118</v>
+        <v>44893</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14099,7 +14109,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14142,7 +14152,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 6662-2024</t>
+          <t>A 43790-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14156,10 +14166,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45341</v>
+        <v>45187</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14172,7 +14182,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14215,7 +14225,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 53077-2021</t>
+          <t>A 59026-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14229,10 +14239,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44467</v>
+        <v>45252</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14245,7 +14255,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14288,7 +14298,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 1450-2024</t>
+          <t>A 58970-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14302,10 +14312,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45303</v>
+        <v>45636</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14318,7 +14328,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14361,7 +14371,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 6785-2025</t>
+          <t>A 23259-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14375,10 +14385,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45700</v>
+        <v>45075</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14391,7 +14401,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14434,7 +14444,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 6793-2025</t>
+          <t>A 5030-2022</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14448,10 +14458,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45700</v>
+        <v>44593</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14464,7 +14474,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14507,7 +14517,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 32826-2023</t>
+          <t>A 6789-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14521,10 +14531,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45124</v>
+        <v>45700</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14537,7 +14547,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14580,7 +14590,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 27498-2026</t>
+          <t>A 58247-2021</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14594,10 +14604,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46185</v>
+        <v>44487</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14609,13 +14619,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>38</v>
+        <v>8.9</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14658,7 +14663,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 32177-2024</t>
+          <t>A 58249-2021</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14672,10 +14677,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45511</v>
+        <v>44487</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14688,7 +14693,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14731,7 +14736,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 41357-2023</t>
+          <t>A 25487-2022</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14745,10 +14750,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45174</v>
+        <v>44732</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14761,7 +14766,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>4.1</v>
+        <v>7.1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -14804,7 +14809,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 62045-2022</t>
+          <t>A 6763-2025</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14818,10 +14823,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44918</v>
+        <v>45700</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14834,7 +14839,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -14877,7 +14882,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 15434-2023</t>
+          <t>A 13913-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14891,10 +14896,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45020</v>
+        <v>45391</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14907,7 +14912,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -14950,7 +14955,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 23259-2023</t>
+          <t>A 43760-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -14964,10 +14969,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45075</v>
+        <v>45187</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -14980,7 +14985,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15023,7 +15028,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 31983-2026</t>
+          <t>A 43784-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15037,10 +15042,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46232</v>
+        <v>45187</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15053,7 +15058,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15096,7 +15101,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 30314-2024</t>
+          <t>A 55909-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15110,10 +15115,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45490</v>
+        <v>44889</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15126,7 +15131,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15169,7 +15174,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 20948-2024</t>
+          <t>A 14355-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15183,10 +15188,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45439</v>
+        <v>45012</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15199,7 +15204,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>6.4</v>
+        <v>1.6</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15242,7 +15247,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 37630-2026</t>
+          <t>A 40067-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15256,10 +15261,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46276</v>
+        <v>45168</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15271,13 +15276,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I199" t="n">
-        <v>13.6</v>
+        <v>0.6</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15320,7 +15320,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 8119-2025</t>
+          <t>A 22650-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15334,10 +15334,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45707</v>
+        <v>45447</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.8</v>
+        <v>7.9</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15393,7 +15393,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 270-2023</t>
+          <t>A 23625-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15407,10 +15407,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44928</v>
+        <v>44721</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15466,7 +15466,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 29707-2024</t>
+          <t>A 16303-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15476,14 +15476,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45485</v>
+        <v>45028</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15496,7 +15496,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>7.7</v>
+        <v>6.3</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15539,7 +15539,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 18314-2024</t>
+          <t>A 5707-2022</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15553,10 +15553,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45422</v>
+        <v>44596</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15612,7 +15612,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 24861-2025</t>
+          <t>A 8119-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15626,10 +15626,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45799</v>
+        <v>45707</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15685,7 +15685,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 25482-2025</t>
+          <t>A 270-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15699,10 +15699,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45802</v>
+        <v>44928</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>8.300000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -15758,7 +15758,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 15436-2024</t>
+          <t>A 18314-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -15772,10 +15772,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45401</v>
+        <v>45422</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -15831,7 +15831,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 7316-2024</t>
+          <t>A 29707-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15841,14 +15841,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45345</v>
+        <v>45485</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.1</v>
+        <v>7.7</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -15921,7 +15921,7 @@
         <v>44166</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         <v>44712</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
         <v>44711</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>45763</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>45798</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>46160</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>

--- a/Översikt GNOSJÖ.xlsx
+++ b/Översikt GNOSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44757</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46030</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44711</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 28312-2025</t>
+          <t>A 23612-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -919,14 +919,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45818</v>
+        <v>44721</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -954,7 +954,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -963,264 +963,264 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 23612-2022 artfynd.xlsx", "A 23612-2022")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 23612-2022 karta.png", "A 23612-2022")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 23612-2022 georefererad karta.tif", "A 23612-2022")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 23612-2022 FSC-klagomål.docx", "A 23612-2022")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 23612-2022 FSC-klagomål mail.docx", "A 23612-2022")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 23612-2022 tillsynsbegäran.docx", "A 23612-2022")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 23612-2022 tillsynsbegäran mail.docx", "A 23612-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 38355-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45161</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>GNOSJÖ</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 38355-2023 artfynd.xlsx", "A 38355-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 38355-2023 karta.png", "A 38355-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 38355-2023 georefererad karta.tif", "A 38355-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 38355-2023 FSC-klagomål.docx", "A 38355-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 38355-2023 FSC-klagomål mail.docx", "A 38355-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 38355-2023 tillsynsbegäran.docx", "A 38355-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 38355-2023 tillsynsbegäran mail.docx", "A 38355-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 28312-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45818</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>GNOSJÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
         <v>3</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 28312-2025 artfynd.xlsx", "A 28312-2025")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 28312-2025 karta.png", "A 28312-2025")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 28312-2025 georefererad karta.tif", "A 28312-2025")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 28312-2025 FSC-klagomål.docx", "A 28312-2025")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 28312-2025 FSC-klagomål mail.docx", "A 28312-2025")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 28312-2025 tillsynsbegäran.docx", "A 28312-2025")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 28312-2025 tillsynsbegäran mail.docx", "A 28312-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 23612-2022</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>44721</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>GNOSJÖ</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 23612-2022 artfynd.xlsx", "A 23612-2022")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 23612-2022 karta.png", "A 23612-2022")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 23612-2022 georefererad karta.tif", "A 23612-2022")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 23612-2022 FSC-klagomål.docx", "A 23612-2022")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 23612-2022 FSC-klagomål mail.docx", "A 23612-2022")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 23612-2022 tillsynsbegäran.docx", "A 23612-2022")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 23612-2022 tillsynsbegäran mail.docx", "A 23612-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 38355-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45161</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>GNOSJÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Mattlummer</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 38355-2023 artfynd.xlsx", "A 38355-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 38355-2023 karta.png", "A 38355-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 38355-2023 georefererad karta.tif", "A 38355-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 38355-2023 FSC-klagomål.docx", "A 38355-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 38355-2023 FSC-klagomål mail.docx", "A 38355-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 38355-2023 tillsynsbegäran.docx", "A 38355-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 38355-2023 tillsynsbegäran mail.docx", "A 38355-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>44530</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>44837</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>44482</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>44456</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>44474</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 3418-2022</t>
+          <t>A 50444-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44585</v>
+        <v>44866</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1618,13 +1618,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1667,7 +1662,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 50444-2022</t>
+          <t>A 3418-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1681,10 +1676,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44866</v>
+        <v>44585</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1696,8 +1691,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1757,7 +1757,7 @@
         <v>44468</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>44503</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>44494</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>44698</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>44470</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>44698</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>44467</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>44568</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>44804</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>44855</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 28372-2022</t>
+          <t>A 4298-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44747</v>
+        <v>44588</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 4298-2022</t>
+          <t>A 47454-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44588</v>
+        <v>45202</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2616,7 +2616,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 48480-2022</t>
+          <t>A 30961-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2630,10 +2630,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44858</v>
+        <v>45113</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 54362-2021</t>
+          <t>A 33575-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44470</v>
+        <v>44789</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2762,7 +2762,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 13352-2024</t>
+          <t>A 48480-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45387</v>
+        <v>44858</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 42280-2023</t>
+          <t>A 54362-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45180</v>
+        <v>44470</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2908,7 +2908,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 46657-2022</t>
+          <t>A 59026-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44850</v>
+        <v>45252</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>7.9</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2981,7 +2981,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 20948-2024</t>
+          <t>A 16244-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2995,10 +2995,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45439</v>
+        <v>45749</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3010,8 +3010,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>6.4</v>
+        <v>2.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3054,7 +3059,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 5089-2024</t>
+          <t>A 28372-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3068,10 +3073,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45330</v>
+        <v>44747</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3084,7 +3089,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>4.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3127,7 +3132,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 62053-2022</t>
+          <t>A 16243-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3141,10 +3146,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44918</v>
+        <v>45749</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3156,8 +3161,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3200,7 +3210,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 49725-2021</t>
+          <t>A 37198-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3214,10 +3224,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44455</v>
+        <v>45875</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3230,7 +3240,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3273,7 +3283,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 39668-2023</t>
+          <t>A 43758-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3287,10 +3297,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45167</v>
+        <v>45187</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3303,7 +3313,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3346,7 +3356,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 48188-2022</t>
+          <t>A 43784-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3360,10 +3370,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44853</v>
+        <v>45187</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3376,7 +3386,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3419,7 +3429,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 25837-2023</t>
+          <t>A 38510-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3433,10 +3443,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45090</v>
+        <v>45884</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3449,7 +3459,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3492,7 +3502,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 57730-2023</t>
+          <t>A 23254-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3506,10 +3516,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45246</v>
+        <v>45075</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3522,7 +3532,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3582,7 +3592,7 @@
         <v>44455</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3638,7 +3648,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 30961-2023</t>
+          <t>A 48227-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3652,10 +3662,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45113</v>
+        <v>44858</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3668,7 +3678,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3711,7 +3721,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 13610-2024</t>
+          <t>A 53078-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3725,10 +3735,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45390</v>
+        <v>44467</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3741,7 +3751,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3784,7 +3794,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 61677-2025</t>
+          <t>A 64718-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3798,10 +3808,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46002</v>
+        <v>45281</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3814,7 +3824,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3857,7 +3867,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 49758-2024</t>
+          <t>A 22846-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3871,10 +3881,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45597</v>
+        <v>45448</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3887,7 +3897,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3930,7 +3940,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 8698-2025</t>
+          <t>A 46657-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3944,10 +3954,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45712</v>
+        <v>44850</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3960,7 +3970,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.5</v>
+        <v>7.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4003,7 +4013,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 24861-2025</t>
+          <t>A 3504-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4017,10 +4027,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45799</v>
+        <v>44950</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4033,7 +4043,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5.6</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4076,7 +4086,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 25482-2025</t>
+          <t>A 27264-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4090,10 +4100,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45802</v>
+        <v>45096</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4106,7 +4116,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>8.300000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4149,7 +4159,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 63511-2025</t>
+          <t>A 15776-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4163,10 +4173,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46013</v>
+        <v>45021</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4179,7 +4189,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4222,7 +4232,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 63220-2025</t>
+          <t>A 11667-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4236,10 +4246,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46010</v>
+        <v>46084</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4252,7 +4262,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4295,7 +4305,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 38510-2025</t>
+          <t>A 5082-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4309,10 +4319,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45884</v>
+        <v>45330</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4325,7 +4335,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4368,7 +4378,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 15436-2024</t>
+          <t>A 6415-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4382,10 +4392,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45401</v>
+        <v>45699</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4398,7 +4408,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4441,7 +4451,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 48229-2022</t>
+          <t>A 8698-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4455,10 +4465,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44858</v>
+        <v>45712</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4471,7 +4481,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4514,7 +4524,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 6415-2025</t>
+          <t>A 41347-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4528,10 +4538,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45699</v>
+        <v>45174</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4544,7 +4554,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.7</v>
+        <v>6.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4587,7 +4597,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 1664-2026</t>
+          <t>A 30091-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4597,14 +4607,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46034</v>
+        <v>45489</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4617,7 +4627,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4660,7 +4670,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 40863-2025</t>
+          <t>A 50440-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4674,10 +4684,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45897</v>
+        <v>44866</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4690,7 +4700,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4733,7 +4743,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 7316-2024</t>
+          <t>A 5707-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4747,10 +4757,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45345</v>
+        <v>44596</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4763,7 +4773,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4823,7 +4833,7 @@
         <v>45896</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4879,7 +4889,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 21080-2025</t>
+          <t>A 40863-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4893,10 +4903,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45777</v>
+        <v>45897</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4909,7 +4919,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4952,7 +4962,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 42615-2025</t>
+          <t>A 61531-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4962,14 +4972,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45905</v>
+        <v>45265</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4981,8 +4991,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5025,7 +5040,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 30654-2025</t>
+          <t>A 13600-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5039,10 +5054,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45831</v>
+        <v>46097</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5054,8 +5069,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5098,7 +5118,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 30669-2025</t>
+          <t>A 21080-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5112,10 +5132,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45831</v>
+        <v>45777</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5128,7 +5148,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5171,7 +5191,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 31228-2025</t>
+          <t>A 42615-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5185,10 +5205,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45832</v>
+        <v>45905</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5201,7 +5221,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5244,7 +5264,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 31235-2025</t>
+          <t>A 43637-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5258,10 +5278,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45832</v>
+        <v>45911</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5274,7 +5294,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5317,7 +5337,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 43637-2025</t>
+          <t>A 43656-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5331,10 +5351,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5347,7 +5367,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5390,7 +5410,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 43656-2025</t>
+          <t>A 56625-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5404,10 +5424,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45912</v>
+        <v>44893</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5420,7 +5440,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5463,7 +5483,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 44383-2025</t>
+          <t>A 55909-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5477,10 +5497,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45916</v>
+        <v>44889</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5493,7 +5513,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5536,7 +5556,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 44394-2025</t>
+          <t>A 44383-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5553,7 +5573,7 @@
         <v>45916</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5566,7 +5586,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5609,7 +5629,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 27675-2025</t>
+          <t>A 44394-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5623,10 +5643,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45813</v>
+        <v>45916</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5639,7 +5659,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5682,7 +5702,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 16243-2025</t>
+          <t>A 30101-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5692,14 +5712,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45749</v>
+        <v>45489</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5711,13 +5731,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5760,7 +5775,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 58779-2025</t>
+          <t>A 17402-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5774,10 +5789,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45986</v>
+        <v>46120</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5790,7 +5805,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5833,7 +5848,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 36508-2022</t>
+          <t>A 18473-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5847,10 +5862,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44804</v>
+        <v>46127</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5863,7 +5878,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5906,7 +5921,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 9641-2026</t>
+          <t>A 39668-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5920,10 +5935,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46070</v>
+        <v>45167</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5935,13 +5950,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5984,7 +5994,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 9624-2026</t>
+          <t>A 19171-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5998,10 +6008,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46070</v>
+        <v>46132</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6013,13 +6023,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>1.3</v>
+        <v>22.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6062,7 +6067,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 9627-2026</t>
+          <t>A 62053-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6076,10 +6081,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46070</v>
+        <v>44918</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6091,13 +6096,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6140,7 +6140,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 5082-2024</t>
+          <t>A 4293-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45330</v>
+        <v>44588</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6213,7 +6213,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 37198-2025</t>
+          <t>A 18337-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6227,10 +6227,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45875</v>
+        <v>46125</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6303,7 +6303,7 @@
         <v>45946</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 11667-2026</t>
+          <t>A 54833-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6373,10 +6373,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46084</v>
+        <v>45618</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6388,8 +6388,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6432,7 +6437,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 6781-2022</t>
+          <t>A 21076-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6446,10 +6451,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44602</v>
+        <v>45777</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6462,7 +6467,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6505,7 +6510,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 41347-2023</t>
+          <t>A 50304-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6519,10 +6524,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45174</v>
+        <v>45600</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6535,7 +6540,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>6.2</v>
+        <v>1.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6578,7 +6583,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 50440-2022</t>
+          <t>A 8747-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6592,10 +6597,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44866</v>
+        <v>45356</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6608,7 +6613,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>8.699999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6651,7 +6656,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 4992-2023</t>
+          <t>A 5818-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6665,10 +6670,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44958</v>
+        <v>44963</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6681,7 +6686,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6724,7 +6729,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 13600-2026</t>
+          <t>A 37963-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6738,10 +6743,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46097</v>
+        <v>45544</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6753,13 +6758,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>2.9</v>
+        <v>5.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6802,7 +6802,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 30101-2024</t>
+          <t>A 36905-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6812,14 +6812,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45489</v>
+        <v>45538</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6875,7 +6875,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 17402-2026</t>
+          <t>A 4992-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6889,10 +6889,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46120</v>
+        <v>44958</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6948,7 +6948,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 55918-2025</t>
+          <t>A 3987-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45973</v>
+        <v>45322</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7021,7 +7021,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 18473-2026</t>
+          <t>A 56240-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7035,10 +7035,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46127</v>
+        <v>45974</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7094,7 +7094,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 19171-2026</t>
+          <t>A 61532-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7104,14 +7104,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46132</v>
+        <v>45265</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7123,8 +7123,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>22.2</v>
+        <v>1.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7167,7 +7172,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 56240-2025</t>
+          <t>A 55918-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7181,10 +7186,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45974</v>
+        <v>45973</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7197,7 +7202,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7257,7 +7262,7 @@
         <v>45975</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7313,7 +7318,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 37864-2025</t>
+          <t>A 58249-2021</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7327,10 +7332,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45881</v>
+        <v>44487</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7343,7 +7348,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7386,7 +7391,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 57012-2025</t>
+          <t>A 42618-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7400,10 +7405,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45978</v>
+        <v>45905</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7416,7 +7421,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7459,7 +7464,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 18337-2026</t>
+          <t>A 19307-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7473,10 +7478,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46125</v>
+        <v>45049</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7489,7 +7494,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.1</v>
+        <v>0.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7532,7 +7537,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 54833-2024</t>
+          <t>A 57012-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7546,10 +7551,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45618</v>
+        <v>45978</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7561,13 +7566,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7610,7 +7610,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 27036-2023</t>
+          <t>A 37864-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7624,10 +7624,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45095</v>
+        <v>45881</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7683,7 +7683,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 33575-2022</t>
+          <t>A 5030-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7697,10 +7697,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44789</v>
+        <v>44593</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7756,7 +7756,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 61532-2023</t>
+          <t>A 40244-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7766,14 +7766,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45265</v>
+        <v>45554</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7785,13 +7785,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7834,7 +7829,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 58780-2025</t>
+          <t>A 25487-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7848,10 +7843,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45986</v>
+        <v>44732</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7864,7 +7859,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.1</v>
+        <v>7.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7907,7 +7902,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 36905-2024</t>
+          <t>A 64481-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7921,10 +7916,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45538</v>
+        <v>45280</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7937,7 +7932,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7980,7 +7975,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 21076-2025</t>
+          <t>A 58970-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7994,10 +7989,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45777</v>
+        <v>45636</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8010,7 +8005,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8053,7 +8048,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 11157-2024</t>
+          <t>A 29066-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8067,10 +8062,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45371</v>
+        <v>44750</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8083,7 +8078,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8126,7 +8121,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 11163-2024</t>
+          <t>A 58780-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8140,10 +8135,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45371</v>
+        <v>45986</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8156,7 +8151,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8199,7 +8194,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 37963-2024</t>
+          <t>A 34083-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8213,10 +8208,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45544</v>
+        <v>45125</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8229,7 +8224,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8272,7 +8267,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 61411-2025</t>
+          <t>A 49758-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8286,10 +8281,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46000</v>
+        <v>45597</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8302,7 +8297,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8345,7 +8340,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 3987-2024</t>
+          <t>A 25837-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8359,10 +8354,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45322</v>
+        <v>45090</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8375,7 +8370,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8418,7 +8413,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 61792-2025</t>
+          <t>A 23625-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8432,10 +8427,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46002</v>
+        <v>44721</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8448,7 +8443,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>10.6</v>
+        <v>1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8491,7 +8486,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 31772-2023</t>
+          <t>A 61411-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8505,10 +8500,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45118</v>
+        <v>46000</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8521,7 +8516,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8564,7 +8559,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 61682-2025</t>
+          <t>A 47856-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8578,10 +8573,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46002</v>
+        <v>44855</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8594,7 +8589,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8637,7 +8632,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 42618-2025</t>
+          <t>A 41323-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8651,10 +8646,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45905</v>
+        <v>44826</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8710,7 +8705,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 30314-2024</t>
+          <t>A 61677-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8724,10 +8719,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45490</v>
+        <v>46002</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8740,7 +8735,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8783,7 +8778,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 64481-2023</t>
+          <t>A 61682-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8797,10 +8792,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45280</v>
+        <v>46002</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8813,7 +8808,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8856,7 +8851,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 32177-2024</t>
+          <t>A 61792-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8870,10 +8865,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45511</v>
+        <v>46002</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8886,7 +8881,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.9</v>
+        <v>10.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8929,7 +8924,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 60859-2024</t>
+          <t>A 16303-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8943,10 +8938,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45644</v>
+        <v>45028</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8959,7 +8954,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3.1</v>
+        <v>6.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9002,7 +8997,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 55074-2023</t>
+          <t>A 63220-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9016,10 +9011,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45237</v>
+        <v>46010</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9032,7 +9027,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9075,7 +9070,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 5818-2023</t>
+          <t>A 51901-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9089,10 +9084,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44963</v>
+        <v>44872</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9105,7 +9100,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.7</v>
+        <v>7.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9148,7 +9143,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 62045-2022</t>
+          <t>A 63511-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9162,10 +9157,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44918</v>
+        <v>46013</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9178,7 +9173,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9221,7 +9216,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 40244-2024</t>
+          <t>A 55074-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9235,10 +9230,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45554</v>
+        <v>45237</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9294,7 +9289,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 41323-2022</t>
+          <t>A 41918-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9308,10 +9303,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44826</v>
+        <v>44830</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9324,7 +9319,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9367,7 +9362,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 4293-2022</t>
+          <t>A 58356-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9381,10 +9376,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44588</v>
+        <v>44893</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9397,7 +9392,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9440,7 +9435,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 23132-2026</t>
+          <t>A 57730-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9454,10 +9449,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46161</v>
+        <v>45246</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9470,7 +9465,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9513,7 +9508,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 23138-2026</t>
+          <t>A 6763-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9527,10 +9522,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46161</v>
+        <v>45700</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9543,7 +9538,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9586,7 +9581,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 27264-2023</t>
+          <t>A 23132-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9600,10 +9595,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45096</v>
+        <v>46161</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9616,7 +9611,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9659,7 +9654,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 27952-2026</t>
+          <t>A 23138-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9673,10 +9668,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46193</v>
+        <v>46161</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9688,13 +9683,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>8.5</v>
+        <v>2.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9737,7 +9727,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 27954-2026</t>
+          <t>A 1664-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9751,10 +9741,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46193</v>
+        <v>46034</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9767,7 +9757,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9810,7 +9800,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 27951-2026</t>
+          <t>A 52813-2021</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9824,10 +9814,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46193</v>
+        <v>44467</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9839,13 +9829,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9888,7 +9873,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 27953-2026</t>
+          <t>A 42280-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9902,10 +9887,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46193</v>
+        <v>45180</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9917,13 +9902,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>5.7</v>
+        <v>1.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9966,7 +9946,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 27729-2026</t>
+          <t>A 14355-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9976,14 +9956,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46191</v>
+        <v>45012</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -9996,7 +9976,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>5.6</v>
+        <v>1.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10039,7 +10019,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 28026-2026</t>
+          <t>A 27258-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10053,10 +10033,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46195</v>
+        <v>45096</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10069,7 +10049,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10112,7 +10092,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 28018-2026</t>
+          <t>A 13913-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10126,10 +10106,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46195</v>
+        <v>45391</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10142,7 +10122,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10185,7 +10165,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 28058-2026</t>
+          <t>A 49725-2021</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10199,10 +10179,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46195</v>
+        <v>44455</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10215,7 +10195,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10258,7 +10238,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 53077-2021</t>
+          <t>A 48188-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10272,10 +10252,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44467</v>
+        <v>44853</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10288,7 +10268,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10331,7 +10311,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 32913-2026</t>
+          <t>A 46254-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10345,10 +10325,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46244</v>
+        <v>45581</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10361,7 +10341,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10404,7 +10384,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 32903-2026</t>
+          <t>A 26746-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10418,10 +10398,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46244</v>
+        <v>45093</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10434,7 +10414,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10477,7 +10457,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 30160-2026</t>
+          <t>A 13352-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10491,10 +10471,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46206</v>
+        <v>45387</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10507,7 +10487,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10550,7 +10530,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 58356-2022</t>
+          <t>A 13610-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10564,10 +10544,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44893</v>
+        <v>45390</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10580,7 +10560,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10623,7 +10603,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 20078-2022</t>
+          <t>A 58779-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10637,10 +10617,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44698</v>
+        <v>45986</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10696,7 +10676,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 35325-2023</t>
+          <t>A 56393-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10710,10 +10690,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45146</v>
+        <v>45243</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10726,7 +10706,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10769,7 +10749,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 73961-2021</t>
+          <t>A 11157-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10783,10 +10763,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44553</v>
+        <v>45371</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10798,13 +10778,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10847,7 +10822,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 27258-2023</t>
+          <t>A 11163-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10861,10 +10836,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45096</v>
+        <v>45371</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10877,7 +10852,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10920,7 +10895,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 29066-2022</t>
+          <t>A 9641-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10934,10 +10909,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44750</v>
+        <v>46070</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10949,8 +10924,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -10993,7 +10973,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 3504-2023</t>
+          <t>A 9624-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11007,10 +10987,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44950</v>
+        <v>46070</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11022,8 +11002,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11066,7 +11051,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 9828-2025</t>
+          <t>A 9627-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11080,10 +11065,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45716</v>
+        <v>46070</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11095,8 +11080,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11156,7 +11146,7 @@
         <v>44804</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11212,7 +11202,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 23254-2023</t>
+          <t>A 27729-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11222,14 +11212,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45075</v>
+        <v>46191</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11242,7 +11232,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.4</v>
+        <v>5.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11285,7 +11275,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 27498-2026</t>
+          <t>A 48229-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11299,10 +11289,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46185</v>
+        <v>44858</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11314,13 +11304,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>38</v>
+        <v>3.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11363,7 +11348,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 64718-2023</t>
+          <t>A 28018-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11377,10 +11362,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45281</v>
+        <v>46195</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11393,7 +11378,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11436,7 +11421,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 31983-2026</t>
+          <t>A 22650-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11450,10 +11435,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46232</v>
+        <v>45447</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11466,7 +11451,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1</v>
+        <v>7.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11509,7 +11494,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 37630-2026</t>
+          <t>A 27952-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11523,10 +11508,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46276</v>
+        <v>46193</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11540,11 +11525,11 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>13.6</v>
+        <v>8.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11587,7 +11572,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 52813-2021</t>
+          <t>A 27954-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11601,10 +11586,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44467</v>
+        <v>46193</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11617,7 +11602,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11660,7 +11645,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 47454-2023</t>
+          <t>A 27951-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11674,10 +11659,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45202</v>
+        <v>46193</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11689,8 +11674,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11733,7 +11723,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 34083-2023</t>
+          <t>A 28058-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11747,10 +11737,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45125</v>
+        <v>46195</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11763,7 +11753,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11806,7 +11796,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 6785-2025</t>
+          <t>A 27953-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11820,10 +11810,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45700</v>
+        <v>46193</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11835,8 +11825,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>0.5</v>
+        <v>5.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11879,7 +11874,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 6793-2025</t>
+          <t>A 28026-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11893,10 +11888,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45700</v>
+        <v>46195</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11909,7 +11904,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11952,7 +11947,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 59727-2024</t>
+          <t>A 5089-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11966,10 +11961,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45639</v>
+        <v>45330</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11982,7 +11977,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12025,7 +12020,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 15434-2023</t>
+          <t>A 58247-2021</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12039,10 +12034,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45020</v>
+        <v>44487</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12055,7 +12050,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.5</v>
+        <v>8.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12098,7 +12093,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 41918-2022</t>
+          <t>A 26210-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12112,10 +12107,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44830</v>
+        <v>45468</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12128,7 +12123,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12171,7 +12166,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 61531-2023</t>
+          <t>A 31772-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12181,14 +12176,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45265</v>
+        <v>45118</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12200,13 +12195,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12249,7 +12239,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 26746-2023</t>
+          <t>A 6662-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12263,10 +12253,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45093</v>
+        <v>45341</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12279,7 +12269,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12322,7 +12312,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 15776-2023</t>
+          <t>A 53077-2021</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12336,10 +12326,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45021</v>
+        <v>44467</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12352,7 +12342,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12395,7 +12385,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 51901-2022</t>
+          <t>A 60859-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12409,10 +12399,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44872</v>
+        <v>45644</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12425,7 +12415,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>7.3</v>
+        <v>3.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12468,7 +12458,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 26210-2024</t>
+          <t>A 1450-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12482,10 +12472,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45468</v>
+        <v>45303</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12498,7 +12488,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12541,7 +12531,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 16244-2025</t>
+          <t>A 32913-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12555,10 +12545,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45749</v>
+        <v>46244</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12570,13 +12560,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12619,7 +12604,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 41357-2023</t>
+          <t>A 43787-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12633,10 +12618,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45174</v>
+        <v>45187</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12649,7 +12634,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12692,7 +12677,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 6662-2024</t>
+          <t>A 43760-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12706,10 +12691,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45341</v>
+        <v>45187</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12722,7 +12707,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12765,7 +12750,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 8747-2024</t>
+          <t>A 43790-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12779,10 +12764,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45356</v>
+        <v>45187</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12795,7 +12780,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12838,7 +12823,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 56393-2023</t>
+          <t>A 32903-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12852,10 +12837,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45243</v>
+        <v>46244</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12868,7 +12853,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12911,7 +12896,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 32826-2023</t>
+          <t>A 35325-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12925,10 +12910,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45124</v>
+        <v>45146</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12941,7 +12926,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -12984,7 +12969,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 1450-2024</t>
+          <t>A 10996-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -12998,10 +12983,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45303</v>
+        <v>45370</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13014,7 +12999,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.9</v>
+        <v>5.9</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13057,7 +13042,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 53078-2021</t>
+          <t>A 40067-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13071,10 +13056,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44467</v>
+        <v>45168</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13087,7 +13072,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13130,7 +13115,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 36406-2022</t>
+          <t>A 73961-2021</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13144,10 +13129,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44803</v>
+        <v>44553</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13159,8 +13144,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>2.1</v>
+        <v>5.1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13203,7 +13193,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 10996-2024</t>
+          <t>A 20078-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13217,10 +13207,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45370</v>
+        <v>44698</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13233,7 +13223,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>5.9</v>
+        <v>1.7</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13276,7 +13266,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 22846-2024</t>
+          <t>A 6781-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13290,10 +13280,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45448</v>
+        <v>44602</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13306,7 +13296,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13349,7 +13339,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 30091-2024</t>
+          <t>A 30160-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13359,14 +13349,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45489</v>
+        <v>46206</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13379,7 +13369,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13422,7 +13412,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 48227-2022</t>
+          <t>A 36406-2022</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13436,10 +13426,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44858</v>
+        <v>44803</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13452,7 +13442,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13495,7 +13485,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 43758-2023</t>
+          <t>A 6785-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13509,10 +13499,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45187</v>
+        <v>45700</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13525,7 +13515,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13568,7 +13558,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 6747-2025</t>
+          <t>A 6793-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13585,7 +13575,7 @@
         <v>45700</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13598,7 +13588,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13641,7 +13631,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 50304-2024</t>
+          <t>A 27036-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13655,10 +13645,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45600</v>
+        <v>45095</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13714,7 +13704,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 43786-2023</t>
+          <t>A 9828-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13728,10 +13718,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45187</v>
+        <v>45716</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13744,7 +13734,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13787,7 +13777,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 43787-2023</t>
+          <t>A 43786-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13804,7 +13794,7 @@
         <v>45187</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13817,7 +13807,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -13860,7 +13850,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 46254-2024</t>
+          <t>A 32826-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13874,10 +13864,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45581</v>
+        <v>45124</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13890,7 +13880,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13933,7 +13923,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 47856-2022</t>
+          <t>A 6747-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13947,10 +13937,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44855</v>
+        <v>45700</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -13963,7 +13953,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14006,7 +13996,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 19307-2023</t>
+          <t>A 6789-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14020,10 +14010,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45049</v>
+        <v>45700</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14036,7 +14026,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14079,7 +14069,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 56625-2022</t>
+          <t>A 59727-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14093,10 +14083,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44893</v>
+        <v>45639</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14109,7 +14099,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14152,7 +14142,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 43790-2023</t>
+          <t>A 32177-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14166,10 +14156,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45187</v>
+        <v>45511</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14182,7 +14172,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14225,7 +14215,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 59026-2023</t>
+          <t>A 41357-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14239,10 +14229,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45252</v>
+        <v>45174</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14255,7 +14245,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14298,7 +14288,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 58970-2024</t>
+          <t>A 27498-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14312,10 +14302,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45636</v>
+        <v>46185</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14327,8 +14317,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>1.5</v>
+        <v>38</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14371,7 +14366,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 23259-2023</t>
+          <t>A 62045-2022</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14385,10 +14380,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45075</v>
+        <v>44918</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14401,7 +14396,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14444,7 +14439,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 5030-2022</t>
+          <t>A 15434-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14458,10 +14453,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44593</v>
+        <v>45020</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14474,7 +14469,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14517,7 +14512,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 6789-2025</t>
+          <t>A 23259-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14531,10 +14526,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45700</v>
+        <v>45075</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14547,7 +14542,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14590,7 +14585,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 58247-2021</t>
+          <t>A 30314-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14604,10 +14599,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44487</v>
+        <v>45490</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14620,7 +14615,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>8.9</v>
+        <v>1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14663,7 +14658,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 58249-2021</t>
+          <t>A 20948-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14677,10 +14672,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44487</v>
+        <v>45439</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14693,7 +14688,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>3.3</v>
+        <v>6.4</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14736,7 +14731,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 25487-2022</t>
+          <t>A 31983-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14750,10 +14745,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44732</v>
+        <v>46232</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14766,7 +14761,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>7.1</v>
+        <v>1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -14809,7 +14804,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 6763-2025</t>
+          <t>A 37630-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14823,10 +14818,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45700</v>
+        <v>46276</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14838,8 +14833,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>1.6</v>
+        <v>13.6</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -14882,7 +14882,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 13913-2024</t>
+          <t>A 8119-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14896,10 +14896,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45391</v>
+        <v>45707</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -14955,7 +14955,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 43760-2023</t>
+          <t>A 270-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -14969,10 +14969,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45187</v>
+        <v>44928</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15028,7 +15028,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 43784-2023</t>
+          <t>A 29707-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15038,14 +15038,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45187</v>
+        <v>45485</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>3.8</v>
+        <v>7.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15101,7 +15101,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 55909-2022</t>
+          <t>A 18314-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15115,10 +15115,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44889</v>
+        <v>45422</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15174,7 +15174,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 14355-2023</t>
+          <t>A 24861-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15188,10 +15188,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45012</v>
+        <v>45799</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.6</v>
+        <v>5.6</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15247,7 +15247,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 40067-2023</t>
+          <t>A 25482-2025</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15261,10 +15261,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45168</v>
+        <v>45802</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15320,7 +15320,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 22650-2024</t>
+          <t>A 15436-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15334,10 +15334,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45447</v>
+        <v>45401</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>7.9</v>
+        <v>2.2</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15393,7 +15393,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 23625-2022</t>
+          <t>A 7316-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15407,10 +15407,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44721</v>
+        <v>45345</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15466,7 +15466,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 16303-2023</t>
+          <t>A 30669-2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15480,10 +15480,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45028</v>
+        <v>45831</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15496,7 +15496,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>6.3</v>
+        <v>0.7</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15539,7 +15539,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 5707-2022</t>
+          <t>A 30654-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15553,10 +15553,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44596</v>
+        <v>45831</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15612,7 +15612,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 8119-2025</t>
+          <t>A 31235-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15626,10 +15626,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45707</v>
+        <v>45832</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15685,7 +15685,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 270-2023</t>
+          <t>A 31228-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15699,10 +15699,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44928</v>
+        <v>45832</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -15758,7 +15758,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 18314-2024</t>
+          <t>A 27675-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -15772,10 +15772,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45422</v>
+        <v>45813</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -15831,7 +15831,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 29707-2024</t>
+          <t>A 36508-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15841,14 +15841,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45485</v>
+        <v>44804</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>7.7</v>
+        <v>2.7</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -15921,7 +15921,7 @@
         <v>44166</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         <v>44712</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
         <v>44711</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>45763</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>45798</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>46160</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>

--- a/Översikt GNOSJÖ.xlsx
+++ b/Översikt GNOSJÖ.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE213"/>
+  <dimension ref="A1:AE211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44757</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46030</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44711</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>44721</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>45161</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>45818</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>44530</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>44837</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>44482</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>44456</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 55069-2021</t>
+          <t>A 3418-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44474</v>
+        <v>44585</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1545,8 +1545,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1589,7 +1594,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 50444-2022</t>
+          <t>A 55069-2021</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1603,10 +1608,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44866</v>
+        <v>44474</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1619,7 +1624,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1662,7 +1667,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 3418-2022</t>
+          <t>A 50444-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1676,10 +1681,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44585</v>
+        <v>44866</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1691,13 +1696,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1757,7 +1757,7 @@
         <v>44468</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>44503</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>44494</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>44698</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>44470</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>44698</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>44467</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>44568</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>44804</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>44855</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 4298-2022</t>
+          <t>A 28372-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44588</v>
+        <v>44747</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.8</v>
+        <v>4.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 47454-2023</t>
+          <t>A 4298-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45202</v>
+        <v>44588</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2616,7 +2616,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 30961-2023</t>
+          <t>A 48480-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2630,10 +2630,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45113</v>
+        <v>44858</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33575-2022</t>
+          <t>A 54362-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44789</v>
+        <v>44470</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2762,7 +2762,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 48480-2022</t>
+          <t>A 13352-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44858</v>
+        <v>45387</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 54362-2021</t>
+          <t>A 20948-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44470</v>
+        <v>45439</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>6.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2908,7 +2908,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 59026-2023</t>
+          <t>A 5089-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45252</v>
+        <v>45330</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2981,7 +2981,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 16244-2025</t>
+          <t>A 62053-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2995,10 +2995,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45749</v>
+        <v>44918</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3010,13 +3010,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3059,7 +3054,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 28372-2022</t>
+          <t>A 39668-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3073,10 +3068,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44747</v>
+        <v>45167</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3089,7 +3084,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.3</v>
+        <v>0.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3132,7 +3127,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 16243-2025</t>
+          <t>A 48188-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3146,10 +3141,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45749</v>
+        <v>44853</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3161,13 +3156,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3210,7 +3200,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 37198-2025</t>
+          <t>A 25837-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3224,10 +3214,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45875</v>
+        <v>45090</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3240,7 +3230,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3283,7 +3273,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 43758-2023</t>
+          <t>A 42280-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3297,10 +3287,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45187</v>
+        <v>45180</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3313,7 +3303,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3356,7 +3346,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 43784-2023</t>
+          <t>A 46657-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3370,10 +3360,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45187</v>
+        <v>44850</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3386,7 +3376,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.8</v>
+        <v>7.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3429,7 +3419,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 38510-2025</t>
+          <t>A 57730-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3443,10 +3433,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45884</v>
+        <v>45246</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3459,7 +3449,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3502,7 +3492,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 23254-2023</t>
+          <t>A 30961-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3516,10 +3506,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45075</v>
+        <v>45113</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3532,7 +3522,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3575,7 +3565,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 49720-2021</t>
+          <t>A 49758-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3589,10 +3579,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44455</v>
+        <v>45597</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3605,7 +3595,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3648,7 +3638,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 48227-2022</t>
+          <t>A 13610-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3662,10 +3652,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44858</v>
+        <v>45390</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3678,7 +3668,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3721,7 +3711,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 53078-2021</t>
+          <t>A 24861-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3735,10 +3725,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44467</v>
+        <v>45799</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3751,7 +3741,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>5.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3794,7 +3784,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 64718-2023</t>
+          <t>A 8698-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3808,10 +3798,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45281</v>
+        <v>45712</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3824,7 +3814,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3867,7 +3857,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 22846-2024</t>
+          <t>A 48229-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3881,10 +3871,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45448</v>
+        <v>44858</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3897,7 +3887,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3940,7 +3930,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 46657-2022</t>
+          <t>A 25482-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3954,10 +3944,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44850</v>
+        <v>45802</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3970,7 +3960,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>7.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4013,7 +4003,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 3504-2023</t>
+          <t>A 38510-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4027,10 +4017,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44950</v>
+        <v>45884</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4043,7 +4033,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4086,7 +4076,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 27264-2023</t>
+          <t>A 15436-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4100,10 +4090,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45096</v>
+        <v>45401</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4116,7 +4106,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4159,7 +4149,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 15776-2023</t>
+          <t>A 1664-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4173,10 +4163,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45021</v>
+        <v>46034</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4189,7 +4179,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4232,7 +4222,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11667-2026</t>
+          <t>A 6415-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4246,10 +4236,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46084</v>
+        <v>45699</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4262,7 +4252,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4305,7 +4295,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 5082-2024</t>
+          <t>A 7316-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4319,10 +4309,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45330</v>
+        <v>45345</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4335,7 +4325,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4378,7 +4368,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 6415-2025</t>
+          <t>A 40863-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4392,10 +4382,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45699</v>
+        <v>45897</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4408,7 +4398,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4451,7 +4441,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 8698-2025</t>
+          <t>A 40552-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4465,10 +4455,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45712</v>
+        <v>45896</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4481,7 +4471,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4524,7 +4514,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 41347-2023</t>
+          <t>A 21080-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4538,10 +4528,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45174</v>
+        <v>45777</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4554,7 +4544,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>6.2</v>
+        <v>1.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4597,7 +4587,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 30091-2024</t>
+          <t>A 16243-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4607,14 +4597,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45489</v>
+        <v>45749</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4626,8 +4616,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4670,7 +4665,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 50440-2022</t>
+          <t>A 30654-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4684,10 +4679,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44866</v>
+        <v>45831</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4700,7 +4695,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>8.699999999999999</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4743,7 +4738,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 5707-2022</t>
+          <t>A 30669-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4757,10 +4752,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44596</v>
+        <v>45831</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4773,7 +4768,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4816,7 +4811,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 40552-2025</t>
+          <t>A 42615-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4830,10 +4825,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45896</v>
+        <v>45905</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4846,7 +4841,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4889,7 +4884,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 40863-2025</t>
+          <t>A 31228-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4903,10 +4898,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45897</v>
+        <v>45832</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4919,7 +4914,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4962,7 +4957,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 61531-2023</t>
+          <t>A 31235-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4972,14 +4967,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45265</v>
+        <v>45832</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4991,13 +4986,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>0.9</v>
+        <v>4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5040,7 +5030,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 13600-2026</t>
+          <t>A 43637-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5054,10 +5044,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46097</v>
+        <v>45911</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5069,13 +5059,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5118,7 +5103,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 21080-2025</t>
+          <t>A 43656-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5132,10 +5117,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45777</v>
+        <v>45912</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5148,7 +5133,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5191,7 +5176,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 42615-2025</t>
+          <t>A 44383-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5205,10 +5190,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45905</v>
+        <v>45916</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5221,7 +5206,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5264,7 +5249,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 43637-2025</t>
+          <t>A 44394-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5278,10 +5263,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45911</v>
+        <v>45916</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5294,7 +5279,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5337,7 +5322,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 43656-2025</t>
+          <t>A 5082-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5351,10 +5336,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45912</v>
+        <v>45330</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5367,7 +5352,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5410,7 +5395,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 56625-2022</t>
+          <t>A 27675-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5424,10 +5409,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44893</v>
+        <v>45813</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5440,7 +5425,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5483,7 +5468,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 55909-2022</t>
+          <t>A 36508-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5497,10 +5482,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44889</v>
+        <v>44804</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5513,7 +5498,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5556,7 +5541,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 44383-2025</t>
+          <t>A 6781-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5570,10 +5555,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45916</v>
+        <v>44602</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5586,7 +5571,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5629,7 +5614,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 44394-2025</t>
+          <t>A 41347-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5643,10 +5628,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45916</v>
+        <v>45174</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5659,7 +5644,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.2</v>
+        <v>6.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5702,7 +5687,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 30101-2024</t>
+          <t>A 50440-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5712,14 +5697,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45489</v>
+        <v>44866</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5732,7 +5717,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5775,7 +5760,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 17402-2026</t>
+          <t>A 4992-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5789,10 +5774,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46120</v>
+        <v>44958</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5805,7 +5790,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5848,7 +5833,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 18473-2026</t>
+          <t>A 37198-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5862,10 +5847,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46127</v>
+        <v>45875</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5878,7 +5863,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5921,7 +5906,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 39668-2023</t>
+          <t>A 50728-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5935,10 +5920,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45167</v>
+        <v>45946</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5951,7 +5936,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.3</v>
+        <v>15.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5994,7 +5979,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 19171-2026</t>
+          <t>A 30101-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6004,14 +5989,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46132</v>
+        <v>45489</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6024,7 +6009,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>22.2</v>
+        <v>1.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6067,7 +6052,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 62053-2022</t>
+          <t>A 58779-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6081,10 +6066,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44918</v>
+        <v>45986</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6097,7 +6082,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6140,7 +6125,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 4293-2022</t>
+          <t>A 55918-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6154,10 +6139,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44588</v>
+        <v>45973</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6170,7 +6155,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6213,7 +6198,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 18337-2026</t>
+          <t>A 56240-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6227,10 +6212,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46125</v>
+        <v>45974</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6243,7 +6228,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6286,7 +6271,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 50728-2025</t>
+          <t>A 27036-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6300,10 +6285,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45946</v>
+        <v>45095</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6316,7 +6301,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>15.2</v>
+        <v>1.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6359,7 +6344,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 54833-2024</t>
+          <t>A 33575-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6373,10 +6358,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45618</v>
+        <v>44789</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6388,13 +6373,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6437,7 +6417,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 21076-2025</t>
+          <t>A 56554-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6451,10 +6431,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45777</v>
+        <v>45975</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6467,7 +6447,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.6</v>
+        <v>7.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6510,7 +6490,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 50304-2024</t>
+          <t>A 9641-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6524,10 +6504,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45600</v>
+        <v>46070</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6539,8 +6519,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6583,7 +6568,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 8747-2024</t>
+          <t>A 57012-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6597,10 +6582,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45356</v>
+        <v>45978</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6613,7 +6598,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6656,7 +6641,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 5818-2023</t>
+          <t>A 9624-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6670,10 +6655,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44963</v>
+        <v>46070</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6685,8 +6670,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6729,7 +6719,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 37963-2024</t>
+          <t>A 9627-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6743,10 +6733,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45544</v>
+        <v>46070</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6758,8 +6748,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6802,7 +6797,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 36905-2024</t>
+          <t>A 11157-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6816,10 +6811,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45538</v>
+        <v>45371</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6832,7 +6827,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6875,7 +6870,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 4992-2023</t>
+          <t>A 11163-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6889,10 +6884,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44958</v>
+        <v>45371</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6905,7 +6900,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6948,7 +6943,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 3987-2024</t>
+          <t>A 58780-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6962,10 +6957,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45322</v>
+        <v>45986</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6978,7 +6973,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7021,7 +7016,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 56240-2025</t>
+          <t>A 11667-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7035,10 +7030,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45974</v>
+        <v>46084</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7051,7 +7046,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7094,7 +7089,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 61532-2023</t>
+          <t>A 31772-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7104,14 +7099,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45265</v>
+        <v>45118</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7123,13 +7118,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7172,7 +7162,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 55918-2025</t>
+          <t>A 30314-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7186,10 +7176,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45973</v>
+        <v>45490</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7202,7 +7192,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7245,7 +7235,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 56554-2025</t>
+          <t>A 64481-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7259,10 +7249,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45975</v>
+        <v>45280</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7275,7 +7265,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7318,7 +7308,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 58249-2021</t>
+          <t>A 61411-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7332,10 +7322,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44487</v>
+        <v>46000</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7348,7 +7338,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7391,7 +7381,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 42618-2025</t>
+          <t>A 32177-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7405,10 +7395,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45905</v>
+        <v>45511</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7421,7 +7411,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7464,7 +7454,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 19307-2023</t>
+          <t>A 61792-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7478,10 +7468,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45049</v>
+        <v>46002</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7494,7 +7484,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.4</v>
+        <v>10.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7537,7 +7527,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 57012-2025</t>
+          <t>A 61682-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7551,10 +7541,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45978</v>
+        <v>46002</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7567,7 +7557,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7610,7 +7600,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 37864-2025</t>
+          <t>A 61677-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7624,10 +7614,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45881</v>
+        <v>46002</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7640,7 +7630,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7683,7 +7673,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 5030-2022</t>
+          <t>A 60859-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7697,10 +7687,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44593</v>
+        <v>45644</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7713,7 +7703,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7756,7 +7746,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 40244-2024</t>
+          <t>A 63511-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7770,10 +7760,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45554</v>
+        <v>46013</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7786,7 +7776,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.9</v>
+        <v>4.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7829,7 +7819,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 25487-2022</t>
+          <t>A 63220-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7843,10 +7833,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44732</v>
+        <v>46010</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7859,7 +7849,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>7.1</v>
+        <v>1.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7902,7 +7892,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 64481-2023</t>
+          <t>A 13600-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7916,10 +7906,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45280</v>
+        <v>46097</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7931,8 +7921,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7975,7 +7970,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 58970-2024</t>
+          <t>A 55074-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7989,10 +7984,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45636</v>
+        <v>45237</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8005,7 +8000,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8048,7 +8043,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 29066-2022</t>
+          <t>A 5818-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8062,10 +8057,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44750</v>
+        <v>44963</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8078,7 +8073,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8121,7 +8116,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 58780-2025</t>
+          <t>A 62045-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8135,10 +8130,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45986</v>
+        <v>44918</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8151,7 +8146,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8194,7 +8189,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 34083-2023</t>
+          <t>A 40244-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8208,10 +8203,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45125</v>
+        <v>45554</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8224,7 +8219,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8267,7 +8262,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 49758-2024</t>
+          <t>A 41323-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8281,10 +8276,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45597</v>
+        <v>44826</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8297,7 +8292,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8340,7 +8335,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 25837-2023</t>
+          <t>A 4293-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8354,10 +8349,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45090</v>
+        <v>44588</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8370,7 +8365,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8413,7 +8408,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 23625-2022</t>
+          <t>A 17402-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8427,10 +8422,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44721</v>
+        <v>46120</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8443,7 +8438,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8486,7 +8481,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 61411-2025</t>
+          <t>A 27264-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8500,10 +8495,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46000</v>
+        <v>45096</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8516,7 +8511,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8559,7 +8554,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 47856-2022</t>
+          <t>A 18473-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8573,10 +8568,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44855</v>
+        <v>46127</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8589,7 +8584,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8632,7 +8627,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 41323-2022</t>
+          <t>A 19171-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8646,10 +8641,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44826</v>
+        <v>46132</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8662,7 +8657,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.1</v>
+        <v>22.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8705,7 +8700,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 61677-2025</t>
+          <t>A 53077-2021</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8719,10 +8714,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46002</v>
+        <v>44467</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8735,7 +8730,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8778,7 +8773,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 61682-2025</t>
+          <t>A 37864-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8792,10 +8787,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46002</v>
+        <v>45881</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8808,7 +8803,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8851,7 +8846,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 61792-2025</t>
+          <t>A 58356-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8865,10 +8860,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46002</v>
+        <v>44893</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8881,7 +8876,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>10.6</v>
+        <v>2.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8924,7 +8919,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 16303-2023</t>
+          <t>A 18337-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8938,10 +8933,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45028</v>
+        <v>46125</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8954,7 +8949,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>6.3</v>
+        <v>4.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -8997,7 +8992,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 63220-2025</t>
+          <t>A 54833-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9011,10 +9006,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46010</v>
+        <v>45618</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9026,8 +9021,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9070,7 +9070,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 51901-2022</t>
+          <t>A 20078-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9084,10 +9084,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44872</v>
+        <v>44698</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>7.3</v>
+        <v>1.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9143,7 +9143,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 63511-2025</t>
+          <t>A 61532-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9153,14 +9153,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46013</v>
+        <v>45265</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9172,8 +9172,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9216,7 +9221,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 55074-2023</t>
+          <t>A 35325-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9230,10 +9235,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45237</v>
+        <v>45146</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9246,7 +9251,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9289,7 +9294,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 41918-2022</t>
+          <t>A 73961-2021</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9303,10 +9308,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44830</v>
+        <v>44553</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9318,8 +9323,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>2</v>
+        <v>5.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9362,7 +9372,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 58356-2022</t>
+          <t>A 36905-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9376,10 +9386,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44893</v>
+        <v>45538</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9392,7 +9402,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9435,7 +9445,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 57730-2023</t>
+          <t>A 21076-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9449,10 +9459,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45246</v>
+        <v>45777</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9465,7 +9475,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9508,7 +9518,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 6763-2025</t>
+          <t>A 27258-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9522,10 +9532,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45700</v>
+        <v>45096</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9538,7 +9548,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9581,7 +9591,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 23132-2026</t>
+          <t>A 29066-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9595,10 +9605,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46161</v>
+        <v>44750</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9611,7 +9621,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9654,7 +9664,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 23138-2026</t>
+          <t>A 3504-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9668,10 +9678,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46161</v>
+        <v>44950</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9684,7 +9694,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9727,7 +9737,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 1664-2026</t>
+          <t>A 37963-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9741,10 +9751,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46034</v>
+        <v>45544</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9757,7 +9767,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.7</v>
+        <v>5.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9800,7 +9810,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 52813-2021</t>
+          <t>A 3987-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9814,10 +9824,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44467</v>
+        <v>45322</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9830,7 +9840,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9873,7 +9883,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 42280-2023</t>
+          <t>A 42618-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9887,10 +9897,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45180</v>
+        <v>45905</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9903,7 +9913,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9946,7 +9956,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 14355-2023</t>
+          <t>A 9828-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9960,10 +9970,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45012</v>
+        <v>45716</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -9976,7 +9986,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10019,7 +10029,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 27258-2023</t>
+          <t>A 36653-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10029,14 +10039,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45096</v>
+        <v>44804</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10049,7 +10059,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10092,7 +10102,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 13913-2024</t>
+          <t>A 23254-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10106,10 +10116,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45391</v>
+        <v>45075</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10122,7 +10132,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10165,7 +10175,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 49725-2021</t>
+          <t>A 64718-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10179,10 +10189,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44455</v>
+        <v>45281</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10195,7 +10205,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10238,7 +10248,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 48188-2022</t>
+          <t>A 52813-2021</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10252,10 +10262,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44853</v>
+        <v>44467</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10268,7 +10278,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10311,7 +10321,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 46254-2024</t>
+          <t>A 47454-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10325,10 +10335,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45581</v>
+        <v>45202</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10341,7 +10351,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10384,7 +10394,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 26746-2023</t>
+          <t>A 34083-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10398,10 +10408,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45093</v>
+        <v>45125</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10414,7 +10424,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10457,7 +10467,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 13352-2024</t>
+          <t>A 6785-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10471,10 +10481,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45387</v>
+        <v>45700</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10487,7 +10497,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10530,7 +10540,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 13610-2024</t>
+          <t>A 6793-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10544,10 +10554,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45390</v>
+        <v>45700</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10560,7 +10570,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10603,7 +10613,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 58779-2025</t>
+          <t>A 59727-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10617,10 +10627,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45986</v>
+        <v>45639</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10633,7 +10643,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10676,7 +10686,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 56393-2023</t>
+          <t>A 15434-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10690,10 +10700,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45243</v>
+        <v>45020</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10706,7 +10716,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10749,7 +10759,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 11157-2024</t>
+          <t>A 41918-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10763,10 +10773,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45371</v>
+        <v>44830</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10779,7 +10789,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10822,7 +10832,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 11163-2024</t>
+          <t>A 61531-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10832,14 +10842,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45371</v>
+        <v>45265</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10851,8 +10861,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10895,7 +10910,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 9641-2026</t>
+          <t>A 26746-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10909,10 +10924,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46070</v>
+        <v>45093</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10924,13 +10939,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -10973,7 +10983,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 9624-2026</t>
+          <t>A 23132-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10987,10 +10997,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46070</v>
+        <v>46161</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11002,13 +11012,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11051,7 +11056,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 9627-2026</t>
+          <t>A 23138-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11065,10 +11070,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46070</v>
+        <v>46161</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11080,13 +11085,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11129,7 +11129,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 36653-2022</t>
+          <t>A 15776-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11139,14 +11139,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44804</v>
+        <v>45021</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11159,7 +11159,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11202,7 +11202,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 27729-2026</t>
+          <t>A 51901-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11212,14 +11212,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46191</v>
+        <v>44872</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>5.6</v>
+        <v>7.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11275,7 +11275,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 48229-2022</t>
+          <t>A 26210-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11289,10 +11289,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44858</v>
+        <v>45468</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11348,7 +11348,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 28018-2026</t>
+          <t>A 16244-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11362,10 +11362,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46195</v>
+        <v>45749</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11377,8 +11377,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11421,7 +11426,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 22650-2024</t>
+          <t>A 41357-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11435,10 +11440,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45447</v>
+        <v>45174</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11451,7 +11456,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>7.9</v>
+        <v>4.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11494,7 +11499,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 27952-2026</t>
+          <t>A 6662-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11508,10 +11513,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46193</v>
+        <v>45341</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11523,13 +11528,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>8.5</v>
+        <v>0.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11572,7 +11572,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 27954-2026</t>
+          <t>A 8747-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11586,10 +11586,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46193</v>
+        <v>45356</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11645,7 +11645,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 27951-2026</t>
+          <t>A 56393-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11659,10 +11659,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46193</v>
+        <v>45243</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11674,13 +11674,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>1.6</v>
+        <v>4.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11723,7 +11718,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 28058-2026</t>
+          <t>A 32826-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11737,10 +11732,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46195</v>
+        <v>45124</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11753,7 +11748,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11796,7 +11791,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 27953-2026</t>
+          <t>A 1450-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11810,10 +11805,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46193</v>
+        <v>45303</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11825,13 +11820,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>5.7</v>
+        <v>0.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11874,7 +11864,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 28026-2026</t>
+          <t>A 27954-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11888,10 +11878,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46195</v>
+        <v>46193</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11904,7 +11894,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11947,7 +11937,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 5089-2024</t>
+          <t>A 27951-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11961,10 +11951,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45330</v>
+        <v>46193</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11976,8 +11966,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12020,7 +12015,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 58247-2021</t>
+          <t>A 27953-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12034,10 +12029,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44487</v>
+        <v>46193</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12049,8 +12044,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>8.9</v>
+        <v>5.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12093,7 +12093,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 26210-2024</t>
+          <t>A 27729-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12103,14 +12103,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45468</v>
+        <v>46191</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.3</v>
+        <v>5.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 31772-2023</t>
+          <t>A 28026-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12180,10 +12180,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45118</v>
+        <v>46195</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12239,7 +12239,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 6662-2024</t>
+          <t>A 28018-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12253,10 +12253,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45341</v>
+        <v>46195</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.2</v>
+        <v>3.2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12312,7 +12312,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 53077-2021</t>
+          <t>A 28058-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12326,10 +12326,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44467</v>
+        <v>46195</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12385,7 +12385,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 60859-2024</t>
+          <t>A 53078-2021</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12399,10 +12399,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45644</v>
+        <v>44467</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12458,7 +12458,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 1450-2024</t>
+          <t>A 36406-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12472,10 +12472,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45303</v>
+        <v>44803</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12548,7 +12548,7 @@
         <v>46244</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 43787-2023</t>
+          <t>A 10996-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12618,10 +12618,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45187</v>
+        <v>45370</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.5</v>
+        <v>5.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12677,7 +12677,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 43760-2023</t>
+          <t>A 32903-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12691,10 +12691,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45187</v>
+        <v>46244</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 43790-2023</t>
+          <t>A 22846-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12764,10 +12764,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45187</v>
+        <v>45448</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12823,7 +12823,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 32903-2026</t>
+          <t>A 30091-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12833,14 +12833,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46244</v>
+        <v>45489</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12896,7 +12896,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 35325-2023</t>
+          <t>A 48227-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12910,10 +12910,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45146</v>
+        <v>44858</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -12969,7 +12969,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 10996-2024</t>
+          <t>A 30160-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -12983,10 +12983,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45370</v>
+        <v>46206</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>5.9</v>
+        <v>1.6</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13042,7 +13042,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 40067-2023</t>
+          <t>A 43758-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13056,10 +13056,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45168</v>
+        <v>45187</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13115,7 +13115,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 73961-2021</t>
+          <t>A 6747-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13129,10 +13129,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44553</v>
+        <v>45700</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13144,13 +13144,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>5.1</v>
+        <v>0.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13193,7 +13188,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 20078-2022</t>
+          <t>A 50304-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13207,10 +13202,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44698</v>
+        <v>45600</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13223,7 +13218,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13266,7 +13261,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 6781-2022</t>
+          <t>A 43786-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13280,10 +13275,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44602</v>
+        <v>45187</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13296,7 +13291,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13339,7 +13334,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 30160-2026</t>
+          <t>A 43787-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13353,10 +13348,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46206</v>
+        <v>45187</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13369,7 +13364,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13412,7 +13407,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 36406-2022</t>
+          <t>A 46254-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13426,10 +13421,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44803</v>
+        <v>45581</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13442,7 +13437,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13485,7 +13480,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 6785-2025</t>
+          <t>A 47856-2022</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13499,10 +13494,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45700</v>
+        <v>44855</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13515,7 +13510,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13558,7 +13553,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 6793-2025</t>
+          <t>A 19307-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13572,10 +13567,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45700</v>
+        <v>45049</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13588,7 +13583,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13631,7 +13626,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 27036-2023</t>
+          <t>A 56625-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13645,10 +13640,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45095</v>
+        <v>44893</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13661,7 +13656,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13704,7 +13699,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 9828-2025</t>
+          <t>A 43790-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13718,10 +13713,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45716</v>
+        <v>45187</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13734,7 +13729,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13777,7 +13772,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 43786-2023</t>
+          <t>A 59026-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13791,10 +13786,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45187</v>
+        <v>45252</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13807,7 +13802,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -13850,7 +13845,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 32826-2023</t>
+          <t>A 58970-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13864,10 +13859,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45124</v>
+        <v>45636</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13880,7 +13875,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13923,7 +13918,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 6747-2025</t>
+          <t>A 23259-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13937,10 +13932,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45700</v>
+        <v>45075</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -13953,7 +13948,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -13996,7 +13991,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 6789-2025</t>
+          <t>A 5030-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14010,10 +14005,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45700</v>
+        <v>44593</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14026,7 +14021,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14069,7 +14064,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 59727-2024</t>
+          <t>A 6789-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14083,10 +14078,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45639</v>
+        <v>45700</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14099,7 +14094,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14142,7 +14137,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 32177-2024</t>
+          <t>A 58247-2021</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14156,10 +14151,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45511</v>
+        <v>44487</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14172,7 +14167,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.9</v>
+        <v>8.9</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14215,7 +14210,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 41357-2023</t>
+          <t>A 58249-2021</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14229,10 +14224,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45174</v>
+        <v>44487</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14245,7 +14240,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14288,7 +14283,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 27498-2026</t>
+          <t>A 25487-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14302,10 +14297,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46185</v>
+        <v>44732</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14317,13 +14312,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>38</v>
+        <v>7.1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14366,7 +14356,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 62045-2022</t>
+          <t>A 6763-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14380,10 +14370,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44918</v>
+        <v>45700</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14396,7 +14386,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14439,7 +14429,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 15434-2023</t>
+          <t>A 13913-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14453,10 +14443,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45020</v>
+        <v>45391</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14469,7 +14459,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14512,7 +14502,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 23259-2023</t>
+          <t>A 43760-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14526,10 +14516,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45075</v>
+        <v>45187</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14542,7 +14532,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14585,7 +14575,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 30314-2024</t>
+          <t>A 43784-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14599,10 +14589,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45490</v>
+        <v>45187</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14615,7 +14605,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14658,7 +14648,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 20948-2024</t>
+          <t>A 55909-2022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14672,10 +14662,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45439</v>
+        <v>44889</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14688,7 +14678,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>6.4</v>
+        <v>1.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14731,7 +14721,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 31983-2026</t>
+          <t>A 14355-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14745,10 +14735,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46232</v>
+        <v>45012</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14761,7 +14751,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -14804,7 +14794,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 37630-2026</t>
+          <t>A 27498-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14818,10 +14808,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46276</v>
+        <v>46185</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14835,11 +14825,11 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I193" t="n">
-        <v>13.6</v>
+        <v>38</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -14882,7 +14872,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 8119-2025</t>
+          <t>A 40067-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14896,10 +14886,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45707</v>
+        <v>45168</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14912,7 +14902,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -14955,7 +14945,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 270-2023</t>
+          <t>A 22650-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -14969,10 +14959,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44928</v>
+        <v>45447</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -14985,7 +14975,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.9</v>
+        <v>7.9</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15028,7 +15018,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 29707-2024</t>
+          <t>A 31983-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15038,14 +15028,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45485</v>
+        <v>46232</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15058,7 +15048,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>7.7</v>
+        <v>1</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15101,7 +15091,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 18314-2024</t>
+          <t>A 23625-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15115,10 +15105,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45422</v>
+        <v>44721</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15131,7 +15121,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15174,7 +15164,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 24861-2025</t>
+          <t>A 16303-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15188,10 +15178,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45799</v>
+        <v>45028</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15204,7 +15194,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>5.6</v>
+        <v>6.3</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15247,7 +15237,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 25482-2025</t>
+          <t>A 5707-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15261,10 +15251,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45802</v>
+        <v>44596</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15277,7 +15267,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>8.300000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15320,7 +15310,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 15436-2024</t>
+          <t>A 37630-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15334,10 +15324,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45401</v>
+        <v>46276</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15349,8 +15339,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>2.2</v>
+        <v>13.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15393,7 +15388,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 7316-2024</t>
+          <t>A 8119-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15407,10 +15402,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45345</v>
+        <v>45707</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15423,7 +15418,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15466,7 +15461,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 30669-2025</t>
+          <t>A 270-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15480,10 +15475,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45831</v>
+        <v>44928</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15496,7 +15491,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15539,7 +15534,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 30654-2025</t>
+          <t>A 27952-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15553,10 +15548,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45831</v>
+        <v>46193</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15568,8 +15563,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I203" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15612,7 +15612,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 31235-2025</t>
+          <t>A 18314-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15626,10 +15626,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45832</v>
+        <v>45422</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15685,7 +15685,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 31228-2025</t>
+          <t>A 29707-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15695,14 +15695,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45832</v>
+        <v>45485</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.5</v>
+        <v>7.7</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -15758,24 +15758,24 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 27675-2025</t>
+          <t>S 2580-2020</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45813</v>
+        <v>44166</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>3.1</v>
+        <v>0.1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -15831,24 +15831,24 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 36508-2022</t>
+          <t>S 2956-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44804</v>
+        <v>44712</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15860,8 +15860,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I207" t="n">
-        <v>2.7</v>
+        <v>42.7</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -15904,7 +15909,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>S 2580-2020</t>
+          <t>S 2912-2022</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -15914,14 +15919,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44166</v>
+        <v>44711</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15933,8 +15938,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>0.1</v>
+        <v>33.4</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -15977,7 +15987,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>S 2956-2022</t>
+          <t>S 1256-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -15991,10 +16001,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44712</v>
+        <v>45763</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16006,13 +16016,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I209" t="n">
-        <v>42.7</v>
+        <v>9</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16055,7 +16060,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>S 2912-2022</t>
+          <t>S 1619-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16069,10 +16074,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44711</v>
+        <v>45798</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16090,7 +16095,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>33.4</v>
+        <v>43.9</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16130,10 +16135,10 @@
       </c>
       <c r="V210" s="2" t="inlineStr"/>
     </row>
-    <row r="211" ht="15" customHeight="1">
+    <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>S 1256-2025</t>
+          <t>S 1452-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16147,10 +16152,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45763</v>
+        <v>46160</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16162,8 +16167,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I211" t="n">
-        <v>9</v>
+        <v>43.3</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16202,162 +16212,6 @@
         <v>0</v>
       </c>
       <c r="V211" s="2" t="inlineStr"/>
-    </row>
-    <row r="212" ht="15" customHeight="1">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>S 1619-2025</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D212" s="1" t="n">
-        <v>45798</v>
-      </c>
-      <c r="E212" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>GNOSJÖ</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I212" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="J212" t="n">
-        <v>0</v>
-      </c>
-      <c r="K212" t="n">
-        <v>0</v>
-      </c>
-      <c r="L212" t="n">
-        <v>0</v>
-      </c>
-      <c r="M212" t="n">
-        <v>0</v>
-      </c>
-      <c r="N212" t="n">
-        <v>0</v>
-      </c>
-      <c r="O212" t="n">
-        <v>0</v>
-      </c>
-      <c r="P212" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
-      <c r="R212" t="n">
-        <v>0</v>
-      </c>
-      <c r="S212" t="n">
-        <v>0</v>
-      </c>
-      <c r="T212" t="n">
-        <v>0</v>
-      </c>
-      <c r="U212" t="n">
-        <v>0</v>
-      </c>
-      <c r="V212" s="2" t="inlineStr"/>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>S 1452-2026</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D213" s="1" t="n">
-        <v>46160</v>
-      </c>
-      <c r="E213" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>GNOSJÖ</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I213" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="J213" t="n">
-        <v>0</v>
-      </c>
-      <c r="K213" t="n">
-        <v>0</v>
-      </c>
-      <c r="L213" t="n">
-        <v>0</v>
-      </c>
-      <c r="M213" t="n">
-        <v>0</v>
-      </c>
-      <c r="N213" t="n">
-        <v>0</v>
-      </c>
-      <c r="O213" t="n">
-        <v>0</v>
-      </c>
-      <c r="P213" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
-      <c r="R213" t="n">
-        <v>0</v>
-      </c>
-      <c r="S213" t="n">
-        <v>0</v>
-      </c>
-      <c r="T213" t="n">
-        <v>0</v>
-      </c>
-      <c r="U213" t="n">
-        <v>0</v>
-      </c>
-      <c r="V213" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt GNOSJÖ.xlsx
+++ b/Översikt GNOSJÖ.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE211"/>
+  <dimension ref="A1:AE210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44757</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46030</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44711</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 23612-2022</t>
+          <t>A 38355-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44721</v>
+        <v>45161</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.4</v>
+        <v>11.4</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -979,143 +979,143 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 38355-2023 artfynd.xlsx", "A 38355-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 38355-2023 karta.png", "A 38355-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 38355-2023 georefererad karta.tif", "A 38355-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 38355-2023 FSC-klagomål.docx", "A 38355-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 38355-2023 FSC-klagomål mail.docx", "A 38355-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 38355-2023 tillsynsbegäran.docx", "A 38355-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 38355-2023 tillsynsbegäran mail.docx", "A 38355-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 23612-2022</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>44721</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>GNOSJÖ</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
           <t>Kungsfågel</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 23612-2022 artfynd.xlsx", "A 23612-2022")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 23612-2022 karta.png", "A 23612-2022")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 23612-2022 georefererad karta.tif", "A 23612-2022")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 23612-2022 FSC-klagomål.docx", "A 23612-2022")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 23612-2022 FSC-klagomål mail.docx", "A 23612-2022")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 23612-2022 tillsynsbegäran.docx", "A 23612-2022")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 23612-2022 tillsynsbegäran mail.docx", "A 23612-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 38355-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45161</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>GNOSJÖ</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Mattlummer</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 38355-2023 artfynd.xlsx", "A 38355-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 38355-2023 karta.png", "A 38355-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 38355-2023 georefererad karta.tif", "A 38355-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 38355-2023 FSC-klagomål.docx", "A 38355-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 38355-2023 FSC-klagomål mail.docx", "A 38355-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 38355-2023 tillsynsbegäran.docx", "A 38355-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 38355-2023 tillsynsbegäran mail.docx", "A 38355-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>45818</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>44530</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>44837</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>44482</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 50154-2021</t>
+          <t>A 3418-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44456</v>
+        <v>44585</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1472,8 +1472,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1516,7 +1521,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 3418-2022</t>
+          <t>A 55069-2021</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1530,10 +1535,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44585</v>
+        <v>44474</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1545,13 +1550,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1594,7 +1594,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 55069-2021</t>
+          <t>A 50444-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44474</v>
+        <v>44866</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1667,7 +1667,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 50444-2022</t>
+          <t>A 53196-2021</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44866</v>
+        <v>44468</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1740,7 +1740,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 53196-2021</t>
+          <t>A 62615-2021</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44468</v>
+        <v>44503</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 62615-2021</t>
+          <t>A 59855-2021</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1827,10 +1827,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44503</v>
+        <v>44494</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1886,7 +1886,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 59855-2021</t>
+          <t>A 20077-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44494</v>
+        <v>44698</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1959,7 +1959,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 20077-2022</t>
+          <t>A 54376-2021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44698</v>
+        <v>44470</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2032,7 +2032,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 54376-2021</t>
+          <t>A 20080-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44470</v>
+        <v>44698</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2105,7 +2105,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 20080-2022</t>
+          <t>A 53064-2021</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44698</v>
+        <v>44467</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2178,7 +2178,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 53064-2021</t>
+          <t>A 704-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2192,10 +2192,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44467</v>
+        <v>44568</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2251,7 +2251,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 704-2022</t>
+          <t>A 36525-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44568</v>
+        <v>44804</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2324,7 +2324,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 36525-2022</t>
+          <t>A 47858-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44804</v>
+        <v>44855</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2397,7 +2397,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 47858-2022</t>
+          <t>A 28372-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44855</v>
+        <v>44747</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2470,7 +2470,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 28372-2022</t>
+          <t>A 4298-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44747</v>
+        <v>44588</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 4298-2022</t>
+          <t>A 48480-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44588</v>
+        <v>44858</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2616,7 +2616,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 48480-2022</t>
+          <t>A 54362-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2630,10 +2630,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44858</v>
+        <v>44470</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 54362-2021</t>
+          <t>A 16243-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44470</v>
+        <v>45749</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2718,8 +2718,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2762,7 +2767,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 13352-2024</t>
+          <t>A 43758-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2776,10 +2781,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45387</v>
+        <v>45187</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2792,7 +2797,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2835,7 +2840,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 20948-2024</t>
+          <t>A 43784-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2849,10 +2854,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45439</v>
+        <v>45187</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2865,7 +2870,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>6.4</v>
+        <v>3.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2908,7 +2913,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 5089-2024</t>
+          <t>A 47454-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2922,10 +2927,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45330</v>
+        <v>45202</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2938,7 +2943,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2981,7 +2986,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 62053-2022</t>
+          <t>A 59026-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2995,10 +3000,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44918</v>
+        <v>45252</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3011,7 +3016,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3054,7 +3059,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 39668-2023</t>
+          <t>A 23254-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3068,10 +3073,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45167</v>
+        <v>45075</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3084,7 +3089,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3127,7 +3132,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 48188-2022</t>
+          <t>A 53078-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3141,10 +3146,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44853</v>
+        <v>44467</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3157,7 +3162,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3200,7 +3205,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 25837-2023</t>
+          <t>A 64718-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3214,10 +3219,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45090</v>
+        <v>45281</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3230,7 +3235,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3273,7 +3278,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 42280-2023</t>
+          <t>A 46657-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3287,10 +3292,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45180</v>
+        <v>44850</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3303,7 +3308,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.9</v>
+        <v>7.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3346,7 +3351,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 46657-2022</t>
+          <t>A 3504-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3360,10 +3365,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44850</v>
+        <v>44950</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3376,7 +3381,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>7.9</v>
+        <v>0.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3419,7 +3424,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 57730-2023</t>
+          <t>A 33575-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3433,10 +3438,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45246</v>
+        <v>44789</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3449,7 +3454,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3492,7 +3497,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 30961-2023</t>
+          <t>A 5082-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3506,10 +3511,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45113</v>
+        <v>45330</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3522,7 +3527,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3565,7 +3570,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 49758-2024</t>
+          <t>A 27264-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3579,10 +3584,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45597</v>
+        <v>45096</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3595,7 +3600,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3638,7 +3643,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 13610-2024</t>
+          <t>A 41347-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3652,10 +3657,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45390</v>
+        <v>45174</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3668,7 +3673,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>6.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3711,7 +3716,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 24861-2025</t>
+          <t>A 30091-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3721,14 +3726,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45799</v>
+        <v>45489</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3741,7 +3746,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5.6</v>
+        <v>1.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3784,7 +3789,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 8698-2025</t>
+          <t>A 50440-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3798,10 +3803,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45712</v>
+        <v>44866</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3814,7 +3819,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3857,7 +3862,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 48229-2022</t>
+          <t>A 5707-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3871,10 +3876,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44858</v>
+        <v>44596</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3887,7 +3892,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3930,7 +3935,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 25482-2025</t>
+          <t>A 15776-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3944,10 +3949,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45802</v>
+        <v>45021</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3960,7 +3965,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>8.300000000000001</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4003,7 +4008,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 38510-2025</t>
+          <t>A 55909-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4017,10 +4022,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45884</v>
+        <v>44889</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4033,7 +4038,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4076,7 +4081,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 15436-2024</t>
+          <t>A 56625-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4090,10 +4095,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45401</v>
+        <v>44893</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4106,7 +4111,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4149,7 +4154,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 1664-2026</t>
+          <t>A 30101-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4159,14 +4164,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46034</v>
+        <v>45489</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4222,7 +4227,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 6415-2025</t>
+          <t>A 9641-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4236,10 +4241,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45699</v>
+        <v>46070</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4251,8 +4256,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4295,7 +4305,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 7316-2024</t>
+          <t>A 9624-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4309,10 +4319,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45345</v>
+        <v>46070</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4324,8 +4334,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4368,7 +4383,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 40863-2025</t>
+          <t>A 9627-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4382,10 +4397,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45897</v>
+        <v>46070</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4397,8 +4412,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4441,7 +4461,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 40552-2025</t>
+          <t>A 62053-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4455,10 +4475,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45896</v>
+        <v>44918</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4471,7 +4491,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4514,7 +4534,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 21080-2025</t>
+          <t>A 4293-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4528,10 +4548,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45777</v>
+        <v>44588</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4544,7 +4564,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4587,7 +4607,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 16243-2025</t>
+          <t>A 30669-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4601,10 +4621,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45749</v>
+        <v>45831</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4616,13 +4636,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4682,7 +4697,7 @@
         <v>45831</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4738,7 +4753,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 30669-2025</t>
+          <t>A 31235-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4752,10 +4767,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45831</v>
+        <v>45832</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4768,7 +4783,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4811,7 +4826,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 42615-2025</t>
+          <t>A 31228-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4825,10 +4840,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45905</v>
+        <v>45832</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4841,7 +4856,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4884,7 +4899,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 31228-2025</t>
+          <t>A 11667-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4898,10 +4913,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45832</v>
+        <v>46084</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4914,7 +4929,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4957,7 +4972,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 31235-2025</t>
+          <t>A 6415-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4971,10 +4986,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45832</v>
+        <v>45699</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4987,7 +5002,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5030,7 +5045,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 43637-2025</t>
+          <t>A 8698-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5044,10 +5059,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45911</v>
+        <v>45712</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5060,7 +5075,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.6</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5103,7 +5118,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 43656-2025</t>
+          <t>A 50304-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5117,10 +5132,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45912</v>
+        <v>45600</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5133,7 +5148,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5176,7 +5191,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 44383-2025</t>
+          <t>A 8747-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5190,10 +5205,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45916</v>
+        <v>45356</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5206,7 +5221,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5249,7 +5264,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 44394-2025</t>
+          <t>A 13600-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5263,10 +5278,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45916</v>
+        <v>46097</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5278,8 +5293,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5322,7 +5342,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 5082-2024</t>
+          <t>A 27675-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5336,10 +5356,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45330</v>
+        <v>45813</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5352,7 +5372,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5395,7 +5415,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 27675-2025</t>
+          <t>A 36508-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5409,10 +5429,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45813</v>
+        <v>44804</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5425,7 +5445,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5468,7 +5488,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 36508-2022</t>
+          <t>A 4992-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5482,10 +5502,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44804</v>
+        <v>44958</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5498,7 +5518,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5541,7 +5561,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 6781-2022</t>
+          <t>A 58249-2021</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5555,10 +5575,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44602</v>
+        <v>44487</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5571,7 +5591,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5614,7 +5634,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 41347-2023</t>
+          <t>A 19307-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5628,10 +5648,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45174</v>
+        <v>45049</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5644,7 +5664,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>6.2</v>
+        <v>0.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5687,7 +5707,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 50440-2022</t>
+          <t>A 40552-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5701,10 +5721,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44866</v>
+        <v>45896</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5717,7 +5737,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>8.699999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5760,7 +5780,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 4992-2023</t>
+          <t>A 17402-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5774,10 +5794,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44958</v>
+        <v>46120</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5790,7 +5810,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5850,7 +5870,7 @@
         <v>45875</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5906,7 +5926,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 50728-2025</t>
+          <t>A 25487-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5920,10 +5940,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45946</v>
+        <v>44732</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5936,7 +5956,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>15.2</v>
+        <v>7.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5979,7 +5999,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 30101-2024</t>
+          <t>A 40863-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5989,14 +6009,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45489</v>
+        <v>45897</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6009,7 +6029,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6052,7 +6072,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 58779-2025</t>
+          <t>A 18473-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6066,10 +6086,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45986</v>
+        <v>46127</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6082,7 +6102,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6125,7 +6145,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 55918-2025</t>
+          <t>A 58970-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6139,10 +6159,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45973</v>
+        <v>45636</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6155,7 +6175,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6198,7 +6218,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 56240-2025</t>
+          <t>A 29066-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6212,10 +6232,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45974</v>
+        <v>44750</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6228,7 +6248,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6271,7 +6291,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 27036-2023</t>
+          <t>A 34083-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6285,10 +6305,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45095</v>
+        <v>45125</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6301,7 +6321,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6344,7 +6364,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 33575-2022</t>
+          <t>A 38510-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6358,10 +6378,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44789</v>
+        <v>45884</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6374,7 +6394,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6417,7 +6437,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 56554-2025</t>
+          <t>A 19171-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6431,10 +6451,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45975</v>
+        <v>46132</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6447,7 +6467,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>7.2</v>
+        <v>22.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6490,7 +6510,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 9641-2026</t>
+          <t>A 21080-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6504,10 +6524,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46070</v>
+        <v>45777</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6519,13 +6539,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6568,7 +6583,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 57012-2025</t>
+          <t>A 49758-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6582,10 +6597,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45978</v>
+        <v>45597</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6598,7 +6613,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6641,7 +6656,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 9624-2026</t>
+          <t>A 25837-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6655,10 +6670,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46070</v>
+        <v>45090</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6670,13 +6685,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6719,7 +6729,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 9627-2026</t>
+          <t>A 23625-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6733,10 +6743,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46070</v>
+        <v>44721</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6748,13 +6758,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6797,7 +6802,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 11157-2024</t>
+          <t>A 42615-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6811,10 +6816,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45371</v>
+        <v>45905</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6827,7 +6832,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6870,7 +6875,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 11163-2024</t>
+          <t>A 18337-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6884,10 +6889,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45371</v>
+        <v>46125</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6900,7 +6905,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6943,7 +6948,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 58780-2025</t>
+          <t>A 54833-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6957,10 +6962,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45986</v>
+        <v>45618</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6972,8 +6977,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7016,7 +7026,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 11667-2026</t>
+          <t>A 43637-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7030,10 +7040,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46084</v>
+        <v>45911</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7046,7 +7056,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7089,7 +7099,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 31772-2023</t>
+          <t>A 43656-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7103,10 +7113,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45118</v>
+        <v>45912</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7119,7 +7129,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7162,7 +7172,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 30314-2024</t>
+          <t>A 47856-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7176,10 +7186,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45490</v>
+        <v>44855</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7192,7 +7202,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7235,7 +7245,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 64481-2023</t>
+          <t>A 44383-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7249,10 +7259,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45280</v>
+        <v>45916</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7265,7 +7275,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7308,7 +7318,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 61411-2025</t>
+          <t>A 44394-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7322,10 +7332,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46000</v>
+        <v>45916</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7338,7 +7348,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7381,7 +7391,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 32177-2024</t>
+          <t>A 41323-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7395,10 +7405,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45511</v>
+        <v>44826</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7411,7 +7421,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7454,7 +7464,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 61792-2025</t>
+          <t>A 21076-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7468,10 +7478,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46002</v>
+        <v>45777</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7484,7 +7494,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>10.6</v>
+        <v>2.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7527,7 +7537,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 61682-2025</t>
+          <t>A 16303-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7541,10 +7551,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46002</v>
+        <v>45028</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7557,7 +7567,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.9</v>
+        <v>6.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7600,7 +7610,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 61677-2025</t>
+          <t>A 51901-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7614,10 +7624,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46002</v>
+        <v>44872</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7630,7 +7640,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.8</v>
+        <v>7.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7673,7 +7683,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 60859-2024</t>
+          <t>A 37963-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7687,10 +7697,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45644</v>
+        <v>45544</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7703,7 +7713,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.1</v>
+        <v>5.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7746,7 +7756,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 63511-2025</t>
+          <t>A 41918-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7760,10 +7770,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46013</v>
+        <v>44830</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7776,7 +7786,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7819,7 +7829,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 63220-2025</t>
+          <t>A 36905-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7833,10 +7843,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46010</v>
+        <v>45538</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7849,7 +7859,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7892,7 +7902,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 13600-2026</t>
+          <t>A 57730-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7906,10 +7916,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46097</v>
+        <v>45246</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7921,13 +7931,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7970,7 +7975,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 55074-2023</t>
+          <t>A 6763-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7984,10 +7989,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45237</v>
+        <v>45700</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8000,7 +8005,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8043,7 +8048,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 5818-2023</t>
+          <t>A 3987-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8057,10 +8062,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44963</v>
+        <v>45322</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8073,7 +8078,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8116,7 +8121,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 62045-2022</t>
+          <t>A 61532-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8126,14 +8131,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44918</v>
+        <v>45265</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8145,8 +8150,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8189,7 +8199,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 40244-2024</t>
+          <t>A 42618-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8203,10 +8213,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45554</v>
+        <v>45905</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8219,7 +8229,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8262,7 +8272,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 41323-2022</t>
+          <t>A 52813-2021</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8276,10 +8286,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44826</v>
+        <v>44467</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8335,7 +8345,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 4293-2022</t>
+          <t>A 42280-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8349,10 +8359,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44588</v>
+        <v>45180</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8365,7 +8375,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8408,7 +8418,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 17402-2026</t>
+          <t>A 37864-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8422,10 +8432,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46120</v>
+        <v>45881</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8438,7 +8448,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8481,7 +8491,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 27264-2023</t>
+          <t>A 27258-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8498,7 +8508,7 @@
         <v>45096</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8511,7 +8521,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8554,7 +8564,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 18473-2026</t>
+          <t>A 48188-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8568,10 +8578,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46127</v>
+        <v>44853</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8584,7 +8594,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8627,7 +8637,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 19171-2026</t>
+          <t>A 26746-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8641,10 +8651,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46132</v>
+        <v>45093</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8657,7 +8667,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>22.2</v>
+        <v>2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8700,7 +8710,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 53077-2021</t>
+          <t>A 11157-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8714,10 +8724,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44467</v>
+        <v>45371</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8730,7 +8740,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8773,7 +8783,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 37864-2025</t>
+          <t>A 11163-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8787,10 +8797,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45881</v>
+        <v>45371</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8803,7 +8813,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8846,7 +8856,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 58356-2022</t>
+          <t>A 23132-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8860,10 +8870,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44893</v>
+        <v>46161</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8876,7 +8886,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8919,7 +8929,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 18337-2026</t>
+          <t>A 23138-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8933,10 +8943,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46125</v>
+        <v>46161</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8949,7 +8959,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -8992,7 +9002,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 54833-2024</t>
+          <t>A 22650-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9006,10 +9016,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45618</v>
+        <v>45447</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9021,13 +9031,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>1.6</v>
+        <v>7.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9070,7 +9075,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 20078-2022</t>
+          <t>A 50728-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9084,10 +9089,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44698</v>
+        <v>45946</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9100,7 +9105,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.7</v>
+        <v>15.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9143,7 +9148,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 61532-2023</t>
+          <t>A 26210-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9153,14 +9158,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45265</v>
+        <v>45468</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9172,13 +9177,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9221,7 +9221,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 35325-2023</t>
+          <t>A 60859-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9235,10 +9235,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45146</v>
+        <v>45644</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9294,7 +9294,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 73961-2021</t>
+          <t>A 43787-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9308,10 +9308,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44553</v>
+        <v>45187</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9323,13 +9323,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>5.1</v>
+        <v>0.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9372,7 +9367,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 36905-2024</t>
+          <t>A 43760-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9386,10 +9381,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45538</v>
+        <v>45187</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9402,7 +9397,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9445,7 +9440,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 21076-2025</t>
+          <t>A 43790-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9459,10 +9454,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45777</v>
+        <v>45187</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9475,7 +9470,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9518,7 +9513,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 27258-2023</t>
+          <t>A 35325-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9532,10 +9527,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45096</v>
+        <v>45146</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9548,7 +9543,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9591,7 +9586,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 29066-2022</t>
+          <t>A 10996-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9605,10 +9600,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44750</v>
+        <v>45370</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9621,7 +9616,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9664,7 +9659,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 3504-2023</t>
+          <t>A 40067-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9678,10 +9673,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44950</v>
+        <v>45168</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9737,7 +9732,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 37963-2024</t>
+          <t>A 73961-2021</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9751,10 +9746,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45544</v>
+        <v>44553</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9766,8 +9761,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9810,7 +9810,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 3987-2024</t>
+          <t>A 27729-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9820,14 +9820,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45322</v>
+        <v>46191</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.5</v>
+        <v>5.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9883,7 +9883,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 42618-2025</t>
+          <t>A 28018-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9897,10 +9897,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45905</v>
+        <v>46195</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9956,7 +9956,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 9828-2025</t>
+          <t>A 27954-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9970,10 +9970,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45716</v>
+        <v>46193</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10029,7 +10029,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 36653-2022</t>
+          <t>A 20078-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10039,14 +10039,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44804</v>
+        <v>44698</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10102,7 +10102,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 23254-2023</t>
+          <t>A 27951-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10116,10 +10116,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45075</v>
+        <v>46193</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10131,8 +10131,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10175,7 +10180,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 64718-2023</t>
+          <t>A 6781-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10189,10 +10194,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45281</v>
+        <v>44602</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10205,7 +10210,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10248,7 +10253,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 52813-2021</t>
+          <t>A 28058-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10262,10 +10267,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44467</v>
+        <v>46195</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10278,7 +10283,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10321,7 +10326,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 47454-2023</t>
+          <t>A 27953-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10335,10 +10340,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45202</v>
+        <v>46193</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10350,8 +10355,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>0.5</v>
+        <v>5.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10394,7 +10404,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 34083-2023</t>
+          <t>A 28026-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10408,10 +10418,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45125</v>
+        <v>46195</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10424,7 +10434,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10467,7 +10477,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 6785-2025</t>
+          <t>A 36406-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10481,10 +10491,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45700</v>
+        <v>44803</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10497,7 +10507,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10540,7 +10550,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 6793-2025</t>
+          <t>A 27036-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10554,10 +10564,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45700</v>
+        <v>45095</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10570,7 +10580,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10613,7 +10623,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 59727-2024</t>
+          <t>A 56240-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10627,10 +10637,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45639</v>
+        <v>45974</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10643,7 +10653,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10686,7 +10696,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 15434-2023</t>
+          <t>A 9828-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10700,10 +10710,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45020</v>
+        <v>45716</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10716,7 +10726,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10759,7 +10769,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 41918-2022</t>
+          <t>A 55918-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10773,10 +10783,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44830</v>
+        <v>45973</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10789,7 +10799,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10832,7 +10842,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 61531-2023</t>
+          <t>A 56554-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10842,14 +10852,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45265</v>
+        <v>45975</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10861,13 +10871,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>0.9</v>
+        <v>7.2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10910,7 +10915,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 26746-2023</t>
+          <t>A 43786-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10924,10 +10929,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45093</v>
+        <v>45187</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10940,7 +10945,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -10983,7 +10988,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 23132-2026</t>
+          <t>A 32913-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10997,10 +11002,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46161</v>
+        <v>46244</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11013,7 +11018,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11056,7 +11061,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 23138-2026</t>
+          <t>A 57012-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11070,10 +11075,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46161</v>
+        <v>45978</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11086,7 +11091,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11129,7 +11134,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 15776-2023</t>
+          <t>A 32903-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11143,10 +11148,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45021</v>
+        <v>46244</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11159,7 +11164,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11202,7 +11207,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 51901-2022</t>
+          <t>A 6747-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11216,10 +11221,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44872</v>
+        <v>45700</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11232,7 +11237,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>7.3</v>
+        <v>0.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11275,7 +11280,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 26210-2024</t>
+          <t>A 6789-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11289,10 +11294,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45468</v>
+        <v>45700</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11305,7 +11310,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11348,7 +11353,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 16244-2025</t>
+          <t>A 59727-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11362,10 +11367,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45749</v>
+        <v>45639</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11375,11 +11380,6 @@
       <c r="G146" t="inlineStr">
         <is>
           <t>GNOSJÖ</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I146" t="n">
@@ -11426,7 +11426,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 41357-2023</t>
+          <t>A 58780-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11440,10 +11440,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45174</v>
+        <v>45986</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11499,7 +11499,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 6662-2024</t>
+          <t>A 30961-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11513,10 +11513,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45341</v>
+        <v>45113</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.2</v>
+        <v>2.7</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11572,7 +11572,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 8747-2024</t>
+          <t>A 30160-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11586,10 +11586,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45356</v>
+        <v>46206</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11645,7 +11645,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 56393-2023</t>
+          <t>A 16244-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11659,10 +11659,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45243</v>
+        <v>45749</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11674,8 +11674,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11718,7 +11723,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 32826-2023</t>
+          <t>A 48227-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11732,10 +11737,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45124</v>
+        <v>44858</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11748,7 +11753,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11791,7 +11796,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 1450-2024</t>
+          <t>A 61411-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11805,10 +11810,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45303</v>
+        <v>46000</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11821,7 +11826,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11864,7 +11869,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 27954-2026</t>
+          <t>A 22846-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11878,10 +11883,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46193</v>
+        <v>45448</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11894,7 +11899,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11937,7 +11942,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 27951-2026</t>
+          <t>A 61677-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11951,10 +11956,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46193</v>
+        <v>46002</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11966,13 +11971,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12015,7 +12015,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 27953-2026</t>
+          <t>A 61682-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12029,10 +12029,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46193</v>
+        <v>46002</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12044,13 +12044,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>5.7</v>
+        <v>0.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12093,7 +12088,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 27729-2026</t>
+          <t>A 61792-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12103,14 +12098,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46191</v>
+        <v>46002</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12123,7 +12118,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>5.6</v>
+        <v>10.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12166,7 +12161,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 28026-2026</t>
+          <t>A 61531-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12176,14 +12171,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46195</v>
+        <v>45265</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12195,8 +12190,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12239,7 +12239,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 28018-2026</t>
+          <t>A 27498-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12253,10 +12253,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46195</v>
+        <v>46185</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12268,8 +12268,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>3.2</v>
+        <v>38</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12312,7 +12317,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 28058-2026</t>
+          <t>A 63220-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12326,10 +12331,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46195</v>
+        <v>46010</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12342,7 +12347,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12385,7 +12390,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 53078-2021</t>
+          <t>A 63511-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12399,10 +12404,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44467</v>
+        <v>46013</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12415,7 +12420,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12458,7 +12463,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 36406-2022</t>
+          <t>A 39668-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12472,10 +12477,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44803</v>
+        <v>45167</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12488,7 +12493,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.1</v>
+        <v>0.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12531,7 +12536,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 32913-2026</t>
+          <t>A 31983-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12545,10 +12550,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46244</v>
+        <v>46232</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12561,7 +12566,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12604,7 +12609,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 10996-2024</t>
+          <t>A 37630-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12618,10 +12623,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45370</v>
+        <v>46276</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12633,8 +12638,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>5.9</v>
+        <v>13.6</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12677,7 +12687,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 32903-2026</t>
+          <t>A 5818-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12691,10 +12701,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46244</v>
+        <v>44963</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12707,7 +12717,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12750,7 +12760,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 22846-2024</t>
+          <t>A 5030-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12764,10 +12774,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45448</v>
+        <v>44593</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12780,7 +12790,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12823,7 +12833,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 30091-2024</t>
+          <t>A 40244-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12833,14 +12843,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45489</v>
+        <v>45554</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12853,7 +12863,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12896,7 +12906,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 48227-2022</t>
+          <t>A 64481-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12910,10 +12920,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44858</v>
+        <v>45280</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12926,7 +12936,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -12969,7 +12979,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 30160-2026</t>
+          <t>A 1664-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -12983,10 +12993,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46206</v>
+        <v>46034</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -12999,7 +13009,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13042,7 +13052,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 43758-2023</t>
+          <t>A 27952-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13056,10 +13066,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45187</v>
+        <v>46193</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13071,8 +13081,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I169" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13115,7 +13130,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 6747-2025</t>
+          <t>A 55074-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13129,10 +13144,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45700</v>
+        <v>45237</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13145,7 +13160,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13188,7 +13203,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 50304-2024</t>
+          <t>A 58356-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13202,10 +13217,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45600</v>
+        <v>44893</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13218,7 +13233,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13261,7 +13276,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 43786-2023</t>
+          <t>A 14355-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13275,10 +13290,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45187</v>
+        <v>45012</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13291,7 +13306,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13334,7 +13349,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 43787-2023</t>
+          <t>A 13913-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13348,10 +13363,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45187</v>
+        <v>45391</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13364,7 +13379,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13424,7 +13439,7 @@
         <v>45581</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13480,7 +13495,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 47856-2022</t>
+          <t>A 13352-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13494,10 +13509,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44855</v>
+        <v>45387</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13510,7 +13525,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.1</v>
+        <v>2.1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13553,7 +13568,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 19307-2023</t>
+          <t>A 13610-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13567,10 +13582,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45049</v>
+        <v>45390</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13583,7 +13598,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13626,7 +13641,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 56625-2022</t>
+          <t>A 56393-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13640,10 +13655,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44893</v>
+        <v>45243</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13656,7 +13671,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13699,7 +13714,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 43790-2023</t>
+          <t>A 36653-2022</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13709,14 +13724,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45187</v>
+        <v>44804</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13729,7 +13744,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13772,7 +13787,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 59026-2023</t>
+          <t>A 48229-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13786,10 +13801,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45252</v>
+        <v>44858</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13802,7 +13817,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -13845,7 +13860,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 58970-2024</t>
+          <t>A 5089-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13859,10 +13874,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45636</v>
+        <v>45330</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13875,7 +13890,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13918,7 +13933,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 23259-2023</t>
+          <t>A 58247-2021</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13932,10 +13947,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45075</v>
+        <v>44487</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -13948,7 +13963,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.8</v>
+        <v>8.9</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -13991,7 +14006,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 5030-2022</t>
+          <t>A 58779-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14005,10 +14020,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44593</v>
+        <v>45986</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14021,7 +14036,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14064,7 +14079,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 6789-2025</t>
+          <t>A 31772-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14078,10 +14093,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45700</v>
+        <v>45118</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14094,7 +14109,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14137,7 +14152,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 58247-2021</t>
+          <t>A 6662-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14151,10 +14166,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44487</v>
+        <v>45341</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14167,7 +14182,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>8.9</v>
+        <v>0.2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14210,7 +14225,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 58249-2021</t>
+          <t>A 53077-2021</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14224,10 +14239,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44487</v>
+        <v>44467</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14240,7 +14255,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14283,7 +14298,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 25487-2022</t>
+          <t>A 1450-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14297,10 +14312,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44732</v>
+        <v>45303</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14313,7 +14328,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>7.1</v>
+        <v>0.9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14356,7 +14371,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 6763-2025</t>
+          <t>A 6785-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14373,7 +14388,7 @@
         <v>45700</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14386,7 +14401,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14429,7 +14444,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 13913-2024</t>
+          <t>A 6793-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14443,10 +14458,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45391</v>
+        <v>45700</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14459,7 +14474,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14502,7 +14517,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 43760-2023</t>
+          <t>A 32826-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14516,10 +14531,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45187</v>
+        <v>45124</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14532,7 +14547,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14575,7 +14590,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 43784-2023</t>
+          <t>A 32177-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14589,10 +14604,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45187</v>
+        <v>45511</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14605,7 +14620,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14648,7 +14663,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 55909-2022</t>
+          <t>A 41357-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14662,10 +14677,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44889</v>
+        <v>45174</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14678,7 +14693,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14721,7 +14736,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 14355-2023</t>
+          <t>A 62045-2022</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14735,10 +14750,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45012</v>
+        <v>44918</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14751,7 +14766,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -14794,7 +14809,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 27498-2026</t>
+          <t>A 15434-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14808,10 +14823,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46185</v>
+        <v>45020</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14823,13 +14838,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>38</v>
+        <v>0.5</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -14872,7 +14882,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 40067-2023</t>
+          <t>A 23259-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14886,10 +14896,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45168</v>
+        <v>45075</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14902,7 +14912,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -14945,7 +14955,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 22650-2024</t>
+          <t>A 30314-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -14959,10 +14969,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45447</v>
+        <v>45490</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -14975,7 +14985,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>7.9</v>
+        <v>1</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15018,7 +15028,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 31983-2026</t>
+          <t>A 20948-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15032,10 +15042,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46232</v>
+        <v>45439</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15048,7 +15058,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1</v>
+        <v>6.4</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15091,7 +15101,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 23625-2022</t>
+          <t>A 8119-2025</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15105,10 +15115,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44721</v>
+        <v>45707</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15121,7 +15131,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15164,7 +15174,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 16303-2023</t>
+          <t>A 270-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15178,10 +15188,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45028</v>
+        <v>44928</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15194,7 +15204,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>6.3</v>
+        <v>1.9</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15237,7 +15247,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 5707-2022</t>
+          <t>A 29707-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15247,14 +15257,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44596</v>
+        <v>45485</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15267,7 +15277,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.5</v>
+        <v>7.7</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15310,7 +15320,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 37630-2026</t>
+          <t>A 18314-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15324,10 +15334,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46276</v>
+        <v>45422</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15339,13 +15349,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>13.6</v>
+        <v>1.3</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15388,7 +15393,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 8119-2025</t>
+          <t>A 24861-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15402,10 +15407,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45707</v>
+        <v>45799</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15418,7 +15423,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15461,7 +15466,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 270-2023</t>
+          <t>A 25482-2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15475,10 +15480,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44928</v>
+        <v>45802</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15491,7 +15496,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15534,7 +15539,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 27952-2026</t>
+          <t>A 15436-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15548,10 +15553,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46193</v>
+        <v>45401</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15563,13 +15568,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I203" t="n">
-        <v>8.5</v>
+        <v>2.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15612,7 +15612,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 18314-2024</t>
+          <t>A 7316-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15626,10 +15626,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45422</v>
+        <v>45345</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15685,24 +15685,24 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 29707-2024</t>
+          <t>S 2580-2020</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45485</v>
+        <v>44166</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>7.7</v>
+        <v>0.1</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -15758,7 +15758,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>S 2580-2020</t>
+          <t>S 2956-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -15768,14 +15768,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44166</v>
+        <v>44712</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15787,8 +15787,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>0.1</v>
+        <v>42.7</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -15831,7 +15836,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>S 2956-2022</t>
+          <t>S 2912-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15845,10 +15850,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44712</v>
+        <v>44711</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15866,7 +15871,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>42.7</v>
+        <v>33.4</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -15909,7 +15914,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>S 2912-2022</t>
+          <t>S 1256-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -15923,10 +15928,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44711</v>
+        <v>45763</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15938,13 +15943,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I208" t="n">
-        <v>33.4</v>
+        <v>9</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -15987,7 +15987,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>S 1256-2025</t>
+          <t>S 1619-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16001,10 +16001,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45763</v>
+        <v>45798</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16016,8 +16016,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I209" t="n">
-        <v>9</v>
+        <v>43.9</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16057,10 +16062,10 @@
       </c>
       <c r="V209" s="2" t="inlineStr"/>
     </row>
-    <row r="210" ht="15" customHeight="1">
+    <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>S 1619-2025</t>
+          <t>S 1452-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16074,10 +16079,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45798</v>
+        <v>46160</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16095,7 +16100,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>43.9</v>
+        <v>43.3</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16134,84 +16139,6 @@
         <v>0</v>
       </c>
       <c r="V210" s="2" t="inlineStr"/>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>S 1452-2026</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D211" s="1" t="n">
-        <v>46160</v>
-      </c>
-      <c r="E211" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>GNOSJÖ</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I211" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="J211" t="n">
-        <v>0</v>
-      </c>
-      <c r="K211" t="n">
-        <v>0</v>
-      </c>
-      <c r="L211" t="n">
-        <v>0</v>
-      </c>
-      <c r="M211" t="n">
-        <v>0</v>
-      </c>
-      <c r="N211" t="n">
-        <v>0</v>
-      </c>
-      <c r="O211" t="n">
-        <v>0</v>
-      </c>
-      <c r="P211" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
-      <c r="R211" t="n">
-        <v>0</v>
-      </c>
-      <c r="S211" t="n">
-        <v>0</v>
-      </c>
-      <c r="T211" t="n">
-        <v>0</v>
-      </c>
-      <c r="U211" t="n">
-        <v>0</v>
-      </c>
-      <c r="V211" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt GNOSJÖ.xlsx
+++ b/Översikt GNOSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44757</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46030</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44711</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 38355-2023</t>
+          <t>A 23612-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45161</v>
+        <v>44721</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>11.4</v>
+        <v>4.4</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -979,143 +979,143 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 23612-2022 artfynd.xlsx", "A 23612-2022")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 23612-2022 karta.png", "A 23612-2022")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 23612-2022 georefererad karta.tif", "A 23612-2022")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 23612-2022 FSC-klagomål.docx", "A 23612-2022")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 23612-2022 FSC-klagomål mail.docx", "A 23612-2022")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 23612-2022 tillsynsbegäran.docx", "A 23612-2022")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 23612-2022 tillsynsbegäran mail.docx", "A 23612-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 38355-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45161</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>GNOSJÖ</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
           <t>Mattlummer</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 38355-2023 artfynd.xlsx", "A 38355-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 38355-2023 karta.png", "A 38355-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 38355-2023 georefererad karta.tif", "A 38355-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 38355-2023 FSC-klagomål.docx", "A 38355-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 38355-2023 FSC-klagomål mail.docx", "A 38355-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 38355-2023 tillsynsbegäran.docx", "A 38355-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 38355-2023 tillsynsbegäran mail.docx", "A 38355-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 23612-2022</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>44721</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>GNOSJÖ</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 23612-2022 artfynd.xlsx", "A 23612-2022")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 23612-2022 karta.png", "A 23612-2022")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 23612-2022 georefererad karta.tif", "A 23612-2022")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 23612-2022 FSC-klagomål.docx", "A 23612-2022")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 23612-2022 FSC-klagomål mail.docx", "A 23612-2022")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 23612-2022 tillsynsbegäran.docx", "A 23612-2022")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 23612-2022 tillsynsbegäran mail.docx", "A 23612-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>45818</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>44530</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>44837</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>44482</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 3418-2022</t>
+          <t>A 55069-2021</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44585</v>
+        <v>44474</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1472,13 +1472,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1521,7 +1516,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 55069-2021</t>
+          <t>A 50444-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1535,10 +1530,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44474</v>
+        <v>44866</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1546,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1594,7 +1589,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 50444-2022</t>
+          <t>A 3418-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1608,10 +1603,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44866</v>
+        <v>44585</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1623,8 +1618,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1684,7 +1684,7 @@
         <v>44468</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>44503</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>44494</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>44698</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>44470</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>44698</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>44467</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>44568</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>44804</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>44855</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>44747</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>44588</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>44858</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>44470</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16243-2025</t>
+          <t>A 13352-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45749</v>
+        <v>45387</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2716,11 +2716,6 @@
       <c r="G28" t="inlineStr">
         <is>
           <t>GNOSJÖ</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -2767,7 +2762,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 43758-2023</t>
+          <t>A 42280-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2781,10 +2776,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45187</v>
+        <v>45180</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2797,7 +2792,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2840,7 +2835,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 43784-2023</t>
+          <t>A 46657-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2854,10 +2849,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45187</v>
+        <v>44850</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2870,7 +2865,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.8</v>
+        <v>7.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2913,7 +2908,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 47454-2023</t>
+          <t>A 20948-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2927,10 +2922,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45202</v>
+        <v>45439</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2943,7 +2938,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>6.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2986,7 +2981,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 59026-2023</t>
+          <t>A 5089-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3000,10 +2995,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45252</v>
+        <v>45330</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3016,7 +3011,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3059,7 +3054,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 23254-2023</t>
+          <t>A 62053-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3073,10 +3068,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45075</v>
+        <v>44918</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3089,7 +3084,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3132,7 +3127,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 53078-2021</t>
+          <t>A 39668-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3146,10 +3141,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44467</v>
+        <v>45167</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3162,7 +3157,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3205,7 +3200,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 64718-2023</t>
+          <t>A 48188-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3219,10 +3214,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45281</v>
+        <v>44853</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3235,7 +3230,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3278,7 +3273,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 46657-2022</t>
+          <t>A 57730-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3292,10 +3287,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44850</v>
+        <v>45246</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3308,7 +3303,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>7.9</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3351,7 +3346,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 3504-2023</t>
+          <t>A 49758-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3365,10 +3360,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44950</v>
+        <v>45597</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3381,7 +3376,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3424,7 +3419,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 33575-2022</t>
+          <t>A 25837-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3438,10 +3433,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44789</v>
+        <v>45090</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3454,7 +3449,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3497,7 +3492,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 5082-2024</t>
+          <t>A 30961-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3511,10 +3506,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45330</v>
+        <v>45113</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3527,7 +3522,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3570,7 +3565,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 27264-2023</t>
+          <t>A 48229-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3584,10 +3579,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45096</v>
+        <v>44858</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3600,7 +3595,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3643,7 +3638,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 41347-2023</t>
+          <t>A 13610-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3657,10 +3652,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45174</v>
+        <v>45390</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3673,7 +3668,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>6.2</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3716,7 +3711,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 30091-2024</t>
+          <t>A 16243-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3726,14 +3721,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45489</v>
+        <v>45749</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3745,8 +3740,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3789,7 +3789,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 50440-2022</t>
+          <t>A 5082-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44866</v>
+        <v>45330</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>8.699999999999999</v>
+        <v>2.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3862,7 +3862,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 5707-2022</t>
+          <t>A 6781-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3876,10 +3876,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44596</v>
+        <v>44602</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3935,7 +3935,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 15776-2023</t>
+          <t>A 41347-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3949,10 +3949,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45021</v>
+        <v>45174</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>6.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4008,7 +4008,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 55909-2022</t>
+          <t>A 50440-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4022,10 +4022,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44889</v>
+        <v>44866</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 56625-2022</t>
+          <t>A 4992-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44893</v>
+        <v>44958</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4171,7 +4171,7 @@
         <v>45489</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 9641-2026</t>
+          <t>A 61532-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4237,14 +4237,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46070</v>
+        <v>45265</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4258,11 +4258,11 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4305,7 +4305,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 9624-2026</t>
+          <t>A 27036-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46070</v>
+        <v>45095</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4334,13 +4334,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4383,7 +4378,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 9627-2026</t>
+          <t>A 33575-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4397,10 +4392,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46070</v>
+        <v>44789</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4412,13 +4407,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4461,7 +4451,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 62053-2022</t>
+          <t>A 38510-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4475,10 +4465,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44918</v>
+        <v>45884</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4491,7 +4481,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4534,7 +4524,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 4293-2022</t>
+          <t>A 36905-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4548,10 +4538,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44588</v>
+        <v>45538</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4564,7 +4554,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4607,7 +4597,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 30669-2025</t>
+          <t>A 21076-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4621,10 +4611,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45831</v>
+        <v>45777</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4637,7 +4627,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4680,7 +4670,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 30654-2025</t>
+          <t>A 6415-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4694,10 +4684,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45831</v>
+        <v>45699</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4710,7 +4700,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4753,7 +4743,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 31235-2025</t>
+          <t>A 11157-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4767,10 +4757,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45832</v>
+        <v>45371</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4783,7 +4773,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4826,7 +4816,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 31228-2025</t>
+          <t>A 11163-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4840,10 +4830,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45832</v>
+        <v>45371</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4856,7 +4846,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4899,7 +4889,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11667-2026</t>
+          <t>A 37963-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4913,10 +4903,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46084</v>
+        <v>45544</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4929,7 +4919,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4972,7 +4962,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 6415-2025</t>
+          <t>A 31772-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4986,10 +4976,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45699</v>
+        <v>45118</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5002,7 +4992,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5045,7 +5035,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 8698-2025</t>
+          <t>A 40863-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5059,10 +5049,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45712</v>
+        <v>45897</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5075,7 +5065,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5118,7 +5108,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 50304-2024</t>
+          <t>A 3987-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5132,10 +5122,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45600</v>
+        <v>45322</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5148,7 +5138,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5191,7 +5181,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 8747-2024</t>
+          <t>A 30314-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5205,10 +5195,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45356</v>
+        <v>45490</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5221,7 +5211,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5264,7 +5254,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 13600-2026</t>
+          <t>A 40552-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5278,10 +5268,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46097</v>
+        <v>45896</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5293,13 +5283,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5342,7 +5327,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 27675-2025</t>
+          <t>A 8698-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5356,10 +5341,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45813</v>
+        <v>45712</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5372,7 +5357,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5415,7 +5400,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 36508-2022</t>
+          <t>A 64481-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5429,10 +5414,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44804</v>
+        <v>45280</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5445,7 +5430,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.7</v>
+        <v>5.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5488,7 +5473,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 4992-2023</t>
+          <t>A 42618-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5502,10 +5487,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44958</v>
+        <v>45905</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5518,7 +5503,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5561,7 +5546,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 58249-2021</t>
+          <t>A 21080-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5575,10 +5560,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44487</v>
+        <v>45777</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5591,7 +5576,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5634,7 +5619,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 19307-2023</t>
+          <t>A 32177-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5648,10 +5633,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45049</v>
+        <v>45511</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5664,7 +5649,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5707,7 +5692,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 40552-2025</t>
+          <t>A 42615-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5721,10 +5706,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45896</v>
+        <v>45905</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5737,7 +5722,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5780,7 +5765,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 17402-2026</t>
+          <t>A 43637-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5794,10 +5779,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46120</v>
+        <v>45911</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5810,7 +5795,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.3</v>
+        <v>4.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5853,7 +5838,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 37198-2025</t>
+          <t>A 43656-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5867,10 +5852,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45875</v>
+        <v>45912</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5883,7 +5868,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5926,7 +5911,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 25487-2022</t>
+          <t>A 44383-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5940,10 +5925,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44732</v>
+        <v>45916</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5956,7 +5941,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>7.1</v>
+        <v>2.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5999,7 +5984,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 40863-2025</t>
+          <t>A 44394-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6013,10 +5998,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45897</v>
+        <v>45916</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6029,7 +6014,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6072,7 +6057,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 18473-2026</t>
+          <t>A 60859-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6086,10 +6071,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46127</v>
+        <v>45644</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6102,7 +6087,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6145,7 +6130,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 58970-2024</t>
+          <t>A 55074-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6159,10 +6144,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45636</v>
+        <v>45237</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6175,7 +6160,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6218,7 +6203,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 29066-2022</t>
+          <t>A 5818-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6232,10 +6217,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44750</v>
+        <v>44963</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6248,7 +6233,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6291,7 +6276,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 34083-2023</t>
+          <t>A 62045-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6305,10 +6290,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45125</v>
+        <v>44918</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6321,7 +6306,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6364,7 +6349,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 38510-2025</t>
+          <t>A 40244-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6378,10 +6363,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45884</v>
+        <v>45554</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6394,7 +6379,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6437,7 +6422,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 19171-2026</t>
+          <t>A 41323-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6451,10 +6436,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46132</v>
+        <v>44826</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6467,7 +6452,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>22.2</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6510,7 +6495,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 21080-2025</t>
+          <t>A 4293-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6524,10 +6509,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45777</v>
+        <v>44588</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6540,7 +6525,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6583,7 +6568,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 49758-2024</t>
+          <t>A 27264-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6597,10 +6582,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45597</v>
+        <v>45096</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6613,7 +6598,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6656,7 +6641,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 25837-2023</t>
+          <t>A 50728-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6670,10 +6655,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45090</v>
+        <v>45946</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6686,7 +6671,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.3</v>
+        <v>15.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6729,7 +6714,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 23625-2022</t>
+          <t>A 53077-2021</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6743,10 +6728,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44721</v>
+        <v>44467</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6759,7 +6744,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6802,7 +6787,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 42615-2025</t>
+          <t>A 58356-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6816,10 +6801,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45905</v>
+        <v>44893</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6832,7 +6817,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6875,7 +6860,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 18337-2026</t>
+          <t>A 20078-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6889,10 +6874,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46125</v>
+        <v>44698</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6905,7 +6890,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6948,7 +6933,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 54833-2024</t>
+          <t>A 55918-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6962,10 +6947,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45618</v>
+        <v>45973</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6977,13 +6962,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7026,7 +7006,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 43637-2025</t>
+          <t>A 35325-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7040,10 +7020,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45911</v>
+        <v>45146</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7056,7 +7036,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.6</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7099,7 +7079,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 43656-2025</t>
+          <t>A 73961-2021</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7113,10 +7093,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45912</v>
+        <v>44553</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7128,8 +7108,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>3.2</v>
+        <v>5.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7172,7 +7157,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 47856-2022</t>
+          <t>A 56240-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7186,10 +7171,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44855</v>
+        <v>45974</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7202,7 +7187,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.1</v>
+        <v>3.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7245,7 +7230,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 44383-2025</t>
+          <t>A 56554-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7259,10 +7244,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45916</v>
+        <v>45975</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7275,7 +7260,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.3</v>
+        <v>7.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7318,7 +7303,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 44394-2025</t>
+          <t>A 27258-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7332,10 +7317,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45916</v>
+        <v>45096</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7348,7 +7333,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7391,7 +7376,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 41323-2022</t>
+          <t>A 29066-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7405,10 +7390,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44826</v>
+        <v>44750</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7421,7 +7406,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7464,7 +7449,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 21076-2025</t>
+          <t>A 57012-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7478,10 +7463,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45777</v>
+        <v>45978</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7494,7 +7479,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7537,7 +7522,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 16303-2023</t>
+          <t>A 3504-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7551,10 +7536,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45028</v>
+        <v>44950</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7567,7 +7552,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>6.3</v>
+        <v>0.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7610,7 +7595,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 51901-2022</t>
+          <t>A 9828-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7624,10 +7609,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44872</v>
+        <v>45716</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7640,7 +7625,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>7.3</v>
+        <v>0.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7683,7 +7668,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 37963-2024</t>
+          <t>A 58780-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7697,10 +7682,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45544</v>
+        <v>45986</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7713,7 +7698,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>5.3</v>
+        <v>1.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7756,7 +7741,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 41918-2022</t>
+          <t>A 23132-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7770,10 +7755,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44830</v>
+        <v>46161</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7786,7 +7771,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7829,7 +7814,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 36905-2024</t>
+          <t>A 36653-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7839,14 +7824,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45538</v>
+        <v>44804</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7859,7 +7844,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7902,7 +7887,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 57730-2023</t>
+          <t>A 23138-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7916,10 +7901,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45246</v>
+        <v>46161</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7932,7 +7917,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7975,7 +7960,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 6763-2025</t>
+          <t>A 23254-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7989,10 +7974,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45700</v>
+        <v>45075</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8005,7 +7990,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8048,7 +8033,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 3987-2024</t>
+          <t>A 64718-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8062,10 +8047,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45322</v>
+        <v>45281</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8078,7 +8063,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8121,7 +8106,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 61532-2023</t>
+          <t>A 61411-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8131,14 +8116,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45265</v>
+        <v>46000</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8150,13 +8135,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8199,7 +8179,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 42618-2025</t>
+          <t>A 61792-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8213,10 +8193,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45905</v>
+        <v>46002</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8229,7 +8209,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.1</v>
+        <v>10.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8272,7 +8252,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 52813-2021</t>
+          <t>A 61682-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8286,10 +8266,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44467</v>
+        <v>46002</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8302,7 +8282,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8345,7 +8325,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 42280-2023</t>
+          <t>A 61677-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8359,10 +8339,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45180</v>
+        <v>46002</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8375,7 +8355,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8418,7 +8398,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 37864-2025</t>
+          <t>A 52813-2021</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8432,10 +8412,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45881</v>
+        <v>44467</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8448,7 +8428,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8491,7 +8471,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 27258-2023</t>
+          <t>A 47454-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8505,10 +8485,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45096</v>
+        <v>45202</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8521,7 +8501,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8564,7 +8544,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 48188-2022</t>
+          <t>A 34083-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8578,10 +8558,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44853</v>
+        <v>45125</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8594,7 +8574,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8637,7 +8617,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 26746-2023</t>
+          <t>A 63511-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8651,10 +8631,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45093</v>
+        <v>46013</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8667,7 +8647,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8710,7 +8690,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 11157-2024</t>
+          <t>A 63220-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8724,10 +8704,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45371</v>
+        <v>46010</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8740,7 +8720,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8783,7 +8763,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 11163-2024</t>
+          <t>A 6785-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8797,10 +8777,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45371</v>
+        <v>45700</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8813,7 +8793,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8856,7 +8836,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 23132-2026</t>
+          <t>A 6793-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8870,10 +8850,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46161</v>
+        <v>45700</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8886,7 +8866,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8929,7 +8909,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 23138-2026</t>
+          <t>A 59727-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8943,10 +8923,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46161</v>
+        <v>45639</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9002,7 +8982,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 22650-2024</t>
+          <t>A 15434-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9016,10 +8996,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45447</v>
+        <v>45020</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9032,7 +9012,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>7.9</v>
+        <v>0.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9075,7 +9055,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 50728-2025</t>
+          <t>A 41918-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9089,10 +9069,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45946</v>
+        <v>44830</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9105,7 +9085,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>15.2</v>
+        <v>2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9148,7 +9128,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 26210-2024</t>
+          <t>A 61531-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9158,14 +9138,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45468</v>
+        <v>45265</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9177,8 +9157,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9221,7 +9206,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 60859-2024</t>
+          <t>A 26746-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9235,10 +9220,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45644</v>
+        <v>45093</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9251,7 +9236,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9294,7 +9279,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 43787-2023</t>
+          <t>A 1664-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9308,10 +9293,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45187</v>
+        <v>46034</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9324,7 +9309,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9367,7 +9352,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 43760-2023</t>
+          <t>A 15776-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9381,10 +9366,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45187</v>
+        <v>45021</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9397,7 +9382,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9440,7 +9425,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 43790-2023</t>
+          <t>A 51901-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9454,10 +9439,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45187</v>
+        <v>44872</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9470,7 +9455,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>3</v>
+        <v>7.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9513,7 +9498,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 35325-2023</t>
+          <t>A 26210-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9527,10 +9512,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45146</v>
+        <v>45468</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9543,7 +9528,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9586,7 +9571,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 10996-2024</t>
+          <t>A 16244-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9600,10 +9585,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45370</v>
+        <v>45749</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9615,8 +9600,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>5.9</v>
+        <v>2.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9659,7 +9649,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 40067-2023</t>
+          <t>A 41357-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9673,10 +9663,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45168</v>
+        <v>45174</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9689,7 +9679,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9732,7 +9722,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 73961-2021</t>
+          <t>A 6662-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9746,10 +9736,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44553</v>
+        <v>45341</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9761,13 +9751,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>5.1</v>
+        <v>0.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9810,7 +9795,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 27729-2026</t>
+          <t>A 58779-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9820,14 +9805,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46191</v>
+        <v>45986</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9840,7 +9825,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>5.6</v>
+        <v>1.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9883,7 +9868,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 28018-2026</t>
+          <t>A 8747-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9897,10 +9882,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46195</v>
+        <v>45356</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9913,7 +9898,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9956,7 +9941,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 27954-2026</t>
+          <t>A 9641-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9970,10 +9955,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46193</v>
+        <v>46070</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -9985,8 +9970,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10029,7 +10019,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 20078-2022</t>
+          <t>A 9624-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10043,10 +10033,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44698</v>
+        <v>46070</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10058,8 +10048,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10102,7 +10097,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 27951-2026</t>
+          <t>A 9627-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10116,10 +10111,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46193</v>
+        <v>46070</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10133,7 +10128,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I129" t="n">
@@ -10180,7 +10175,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 6781-2022</t>
+          <t>A 56393-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10194,10 +10189,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44602</v>
+        <v>45243</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10210,7 +10205,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10253,7 +10248,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 28058-2026</t>
+          <t>A 11667-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10267,10 +10262,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46195</v>
+        <v>46084</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10283,7 +10278,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10326,7 +10321,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 27953-2026</t>
+          <t>A 32826-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10340,10 +10335,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46193</v>
+        <v>45124</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10355,13 +10350,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>5.7</v>
+        <v>0.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10404,7 +10394,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 28026-2026</t>
+          <t>A 1450-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10418,10 +10408,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46195</v>
+        <v>45303</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10434,7 +10424,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10477,7 +10467,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 36406-2022</t>
+          <t>A 27954-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10491,10 +10481,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44803</v>
+        <v>46193</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10507,7 +10497,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10550,7 +10540,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 27036-2023</t>
+          <t>A 13600-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10564,10 +10554,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45095</v>
+        <v>46097</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10579,8 +10569,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10623,7 +10618,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 56240-2025</t>
+          <t>A 27951-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10637,10 +10632,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45974</v>
+        <v>46193</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10652,8 +10647,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10696,7 +10696,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 9828-2025</t>
+          <t>A 27953-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10710,10 +10710,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45716</v>
+        <v>46193</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10725,8 +10725,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>0.4</v>
+        <v>5.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10769,7 +10774,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 55918-2025</t>
+          <t>A 27729-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10779,14 +10784,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45973</v>
+        <v>46191</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10799,7 +10804,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.1</v>
+        <v>5.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10842,7 +10847,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 56554-2025</t>
+          <t>A 28026-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10856,10 +10861,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45975</v>
+        <v>46195</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10872,7 +10877,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>7.2</v>
+        <v>1.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10915,7 +10920,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 43786-2023</t>
+          <t>A 28018-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10929,10 +10934,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45187</v>
+        <v>46195</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10945,7 +10950,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -10988,7 +10993,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 32913-2026</t>
+          <t>A 28058-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11002,10 +11007,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46244</v>
+        <v>46195</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11018,7 +11023,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11061,7 +11066,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 57012-2025</t>
+          <t>A 53078-2021</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11075,10 +11080,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45978</v>
+        <v>44467</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11091,7 +11096,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11134,7 +11139,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 32903-2026</t>
+          <t>A 36406-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11148,10 +11153,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46244</v>
+        <v>44803</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11164,7 +11169,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11207,7 +11212,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 6747-2025</t>
+          <t>A 32913-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11221,10 +11226,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45700</v>
+        <v>46244</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11237,7 +11242,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11280,7 +11285,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 6789-2025</t>
+          <t>A 17402-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11294,10 +11299,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45700</v>
+        <v>46120</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11310,7 +11315,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11353,7 +11358,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 59727-2024</t>
+          <t>A 10996-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11367,10 +11372,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45639</v>
+        <v>45370</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11383,7 +11388,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.3</v>
+        <v>5.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11426,7 +11431,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 58780-2025</t>
+          <t>A 22846-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11440,10 +11445,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45986</v>
+        <v>45448</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11456,7 +11461,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11499,7 +11504,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 30961-2023</t>
+          <t>A 30091-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11509,14 +11514,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45113</v>
+        <v>45489</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11529,7 +11534,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11572,7 +11577,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 30160-2026</t>
+          <t>A 18473-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11586,10 +11591,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46206</v>
+        <v>46127</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11602,7 +11607,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11645,7 +11650,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 16244-2025</t>
+          <t>A 19171-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11659,10 +11664,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45749</v>
+        <v>46132</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11674,13 +11679,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>2.3</v>
+        <v>22.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11740,7 +11740,7 @@
         <v>44858</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 61411-2025</t>
+          <t>A 43758-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11810,10 +11810,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46000</v>
+        <v>45187</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11869,7 +11869,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 22846-2024</t>
+          <t>A 6747-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11883,10 +11883,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45448</v>
+        <v>45700</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11942,7 +11942,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 61677-2025</t>
+          <t>A 50304-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11956,10 +11956,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46002</v>
+        <v>45600</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11972,7 +11972,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12015,7 +12015,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 61682-2025</t>
+          <t>A 37864-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12029,10 +12029,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46002</v>
+        <v>45881</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12088,7 +12088,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 61792-2025</t>
+          <t>A 43786-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12102,10 +12102,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46002</v>
+        <v>45187</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>10.6</v>
+        <v>0.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12161,7 +12161,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 61531-2023</t>
+          <t>A 43787-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12171,14 +12171,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45265</v>
+        <v>45187</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12190,13 +12190,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12239,7 +12234,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 27498-2026</t>
+          <t>A 32903-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12253,10 +12248,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46185</v>
+        <v>46244</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12268,13 +12263,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>38</v>
+        <v>0.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12317,7 +12307,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 63220-2025</t>
+          <t>A 18337-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12331,10 +12321,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46010</v>
+        <v>46125</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12347,7 +12337,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12390,7 +12380,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 63511-2025</t>
+          <t>A 54833-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12404,10 +12394,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46013</v>
+        <v>45618</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12419,8 +12409,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12463,7 +12458,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 39668-2023</t>
+          <t>A 46254-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12477,10 +12472,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45167</v>
+        <v>45581</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12493,7 +12488,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12536,7 +12531,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 31983-2026</t>
+          <t>A 47856-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12550,10 +12545,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46232</v>
+        <v>44855</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12566,7 +12561,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12609,7 +12604,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 37630-2026</t>
+          <t>A 19307-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12623,10 +12618,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46276</v>
+        <v>45049</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12638,13 +12633,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>13.6</v>
+        <v>0.4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12687,7 +12677,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 5818-2023</t>
+          <t>A 56625-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12701,10 +12691,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44963</v>
+        <v>44893</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12760,7 +12750,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 5030-2022</t>
+          <t>A 30160-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12774,10 +12764,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44593</v>
+        <v>46206</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12790,7 +12780,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12833,7 +12823,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 40244-2024</t>
+          <t>A 43790-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12847,10 +12837,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45554</v>
+        <v>45187</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12863,7 +12853,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12906,7 +12896,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 64481-2023</t>
+          <t>A 59026-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12920,10 +12910,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45280</v>
+        <v>45252</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12936,7 +12926,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>5.5</v>
+        <v>2.1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -12979,7 +12969,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 1664-2026</t>
+          <t>A 58970-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -12993,10 +12983,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46034</v>
+        <v>45636</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13009,7 +12999,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13052,7 +13042,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 27952-2026</t>
+          <t>A 23259-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13066,10 +13056,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46193</v>
+        <v>45075</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13081,13 +13071,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>8.5</v>
+        <v>2.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13130,7 +13115,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 55074-2023</t>
+          <t>A 5030-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13144,10 +13129,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45237</v>
+        <v>44593</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13160,7 +13145,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13203,7 +13188,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 58356-2022</t>
+          <t>A 6789-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13217,10 +13202,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44893</v>
+        <v>45700</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13233,7 +13218,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13276,7 +13261,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 14355-2023</t>
+          <t>A 58247-2021</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13290,10 +13275,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45012</v>
+        <v>44487</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13306,7 +13291,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.6</v>
+        <v>8.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13349,7 +13334,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 13913-2024</t>
+          <t>A 58249-2021</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13363,10 +13348,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45391</v>
+        <v>44487</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13379,7 +13364,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13422,7 +13407,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 46254-2024</t>
+          <t>A 25487-2022</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13436,10 +13421,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45581</v>
+        <v>44732</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13452,7 +13437,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.3</v>
+        <v>7.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13495,7 +13480,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 13352-2024</t>
+          <t>A 6763-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13509,10 +13494,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45387</v>
+        <v>45700</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13525,7 +13510,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13568,7 +13553,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 13610-2024</t>
+          <t>A 13913-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13582,10 +13567,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45390</v>
+        <v>45391</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13598,7 +13583,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13641,7 +13626,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 56393-2023</t>
+          <t>A 43760-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13655,10 +13640,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45243</v>
+        <v>45187</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13671,7 +13656,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13714,7 +13699,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 36653-2022</t>
+          <t>A 43784-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13724,14 +13709,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44804</v>
+        <v>45187</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13744,7 +13729,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13787,7 +13772,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 48229-2022</t>
+          <t>A 55909-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13801,10 +13786,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44858</v>
+        <v>44889</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13817,7 +13802,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -13860,7 +13845,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 5089-2024</t>
+          <t>A 14355-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13874,10 +13859,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45330</v>
+        <v>45012</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13890,7 +13875,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13933,7 +13918,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 58247-2021</t>
+          <t>A 40067-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13947,10 +13932,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44487</v>
+        <v>45168</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -13963,7 +13948,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>8.9</v>
+        <v>0.6</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14006,7 +13991,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 58779-2025</t>
+          <t>A 22650-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14020,10 +14005,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45986</v>
+        <v>45447</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14036,7 +14021,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.7</v>
+        <v>7.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14079,7 +14064,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 31772-2023</t>
+          <t>A 23625-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14093,10 +14078,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45118</v>
+        <v>44721</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14109,7 +14094,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14152,7 +14137,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 6662-2024</t>
+          <t>A 16303-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14166,10 +14151,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45341</v>
+        <v>45028</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14182,7 +14167,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.2</v>
+        <v>6.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14225,7 +14210,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 53077-2021</t>
+          <t>A 5707-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14239,10 +14224,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44467</v>
+        <v>44596</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14255,7 +14240,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14298,7 +14283,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 1450-2024</t>
+          <t>A 8119-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14312,10 +14297,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45303</v>
+        <v>45707</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14328,7 +14313,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14371,7 +14356,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 6785-2025</t>
+          <t>A 27498-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14385,10 +14370,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45700</v>
+        <v>46185</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14400,8 +14385,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>0.5</v>
+        <v>38</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14444,7 +14434,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 6793-2025</t>
+          <t>A 31983-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14458,10 +14448,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45700</v>
+        <v>46232</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14474,7 +14464,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14517,7 +14507,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 32826-2023</t>
+          <t>A 270-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14531,10 +14521,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45124</v>
+        <v>44928</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14547,7 +14537,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14590,7 +14580,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 32177-2024</t>
+          <t>A 37630-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14604,10 +14594,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45511</v>
+        <v>46276</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14619,8 +14609,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>0.9</v>
+        <v>13.6</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14663,7 +14658,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 41357-2023</t>
+          <t>A 18314-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14677,10 +14672,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45174</v>
+        <v>45422</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14693,7 +14688,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14736,7 +14731,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 62045-2022</t>
+          <t>A 29707-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14746,14 +14741,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44918</v>
+        <v>45485</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14766,7 +14761,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>2.4</v>
+        <v>7.7</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -14809,7 +14804,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 15434-2023</t>
+          <t>A 27952-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14823,10 +14818,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45020</v>
+        <v>46193</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14838,8 +14833,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>0.5</v>
+        <v>8.5</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -14882,7 +14882,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 23259-2023</t>
+          <t>A 24861-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14896,10 +14896,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45075</v>
+        <v>45799</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -14955,7 +14955,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 30314-2024</t>
+          <t>A 25482-2025</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -14969,10 +14969,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45490</v>
+        <v>45802</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15028,7 +15028,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 20948-2024</t>
+          <t>A 15436-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15042,10 +15042,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45439</v>
+        <v>45401</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>6.4</v>
+        <v>2.2</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15101,7 +15101,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 8119-2025</t>
+          <t>A 7316-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15115,10 +15115,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45707</v>
+        <v>45345</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15174,7 +15174,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 270-2023</t>
+          <t>A 30654-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15188,10 +15188,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44928</v>
+        <v>45831</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15247,7 +15247,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 29707-2024</t>
+          <t>A 30669-2025</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15257,14 +15257,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45485</v>
+        <v>45831</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15320,7 +15320,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 18314-2024</t>
+          <t>A 31228-2025</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15334,10 +15334,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45422</v>
+        <v>45832</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15393,7 +15393,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 24861-2025</t>
+          <t>A 31235-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15407,10 +15407,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45799</v>
+        <v>45832</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15466,7 +15466,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 25482-2025</t>
+          <t>A 27675-2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15480,10 +15480,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45802</v>
+        <v>45813</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15496,7 +15496,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>8.300000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15539,7 +15539,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 15436-2024</t>
+          <t>A 36508-2022</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15553,10 +15553,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45401</v>
+        <v>44804</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15612,7 +15612,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 7316-2024</t>
+          <t>A 37198-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15626,10 +15626,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45345</v>
+        <v>45875</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15702,7 +15702,7 @@
         <v>44166</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>44712</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>44711</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>45763</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>45798</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>46160</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>

--- a/Översikt GNOSJÖ.xlsx
+++ b/Översikt GNOSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44757</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46030</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44711</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>44721</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>45161</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>45818</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>44530</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>44837</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>44482</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>44474</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>44866</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>44585</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>44468</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>44503</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>44494</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>44698</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>44470</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>44698</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>44467</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>44568</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>44804</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>44855</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>44747</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>44588</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>44858</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>44470</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>45387</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>45180</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>44850</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>45439</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>45330</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>44918</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>45167</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>44853</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>45246</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>45597</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>45090</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>45113</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>44858</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>45390</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>45749</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         <v>45330</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>44602</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>45174</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>44866</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>44958</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>45489</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>45265</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>45095</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>44789</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>45884</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>45538</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>45777</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>45699</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>45371</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>45371</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>45544</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>45118</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>45897</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>45322</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>45490</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>45896</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>45712</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>45280</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>45905</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>45777</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>45511</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>45905</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>45911</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>45912</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>45916</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>45916</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>45644</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>45237</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>44963</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44918</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>45554</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>44826</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>44588</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>45096</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>45946</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>44467</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>44893</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         <v>44698</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>45973</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>45146</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>44553</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>45974</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>45975</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>45096</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>44750</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>45978</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44950</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>45716</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>45986</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>46161</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>44804</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>46161</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>45075</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>45281</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         <v>46000</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>46002</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>46002</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>46002</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>44467</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>45202</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>45125</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>46013</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>46010</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>45700</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>45700</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>45639</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>45020</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>44830</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>45265</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>45093</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>46034</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>45021</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44872</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>45468</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>45749</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>45174</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>45341</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>45986</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         <v>45356</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>46070</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>46070</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>46070</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         <v>45243</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         <v>46084</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>45124</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>45303</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>46193</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>46097</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>46193</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>46193</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>46191</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>46195</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>46195</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>46195</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11083,7 +11083,7 @@
         <v>44467</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>44803</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>46244</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>46120</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>45370</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>45448</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>45489</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>46127</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>46132</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>44858</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>45187</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11886,7 +11886,7 @@
         <v>45700</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>45600</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>45881</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12105,7 +12105,7 @@
         <v>45187</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12178,7 +12178,7 @@
         <v>45187</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v>46244</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>46125</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>45618</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>45581</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>44855</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>45049</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>44893</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>46206</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12840,7 +12840,7 @@
         <v>45187</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>45252</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>45636</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13059,7 +13059,7 @@
         <v>45075</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>44593</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>45700</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         <v>44487</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13351,7 +13351,7 @@
         <v>44487</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13424,7 +13424,7 @@
         <v>44732</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13497,7 +13497,7 @@
         <v>45700</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>45391</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>45187</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13716,7 +13716,7 @@
         <v>45187</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13789,7 +13789,7 @@
         <v>44889</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13862,7 +13862,7 @@
         <v>45012</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13935,7 +13935,7 @@
         <v>45168</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14008,7 +14008,7 @@
         <v>45447</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14081,7 +14081,7 @@
         <v>44721</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14154,7 +14154,7 @@
         <v>45028</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>44596</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14300,7 +14300,7 @@
         <v>45707</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>46185</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>46232</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>44928</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>46276</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>45422</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>45485</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>46193</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14899,7 +14899,7 @@
         <v>45799</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>45802</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>45401</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>45345</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>45831</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15264,7 +15264,7 @@
         <v>45831</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>45832</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15410,7 +15410,7 @@
         <v>45832</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         <v>45813</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>44804</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15629,7 +15629,7 @@
         <v>45875</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>44166</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>44712</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>44711</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>45763</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>45798</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>46160</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>

--- a/Översikt GNOSJÖ.xlsx
+++ b/Översikt GNOSJÖ.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE210"/>
+  <dimension ref="A1:AE213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44757</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46030</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44711</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>44721</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>45161</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>45818</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>44530</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>44837</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>44482</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>44474</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>44866</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>44585</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>44468</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>44503</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>44494</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>44698</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>44470</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>44698</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>44467</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>44568</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>44804</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>44855</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>44747</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>44588</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>44858</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>44470</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>45387</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 42280-2023</t>
+          <t>A 20948-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45180</v>
+        <v>45439</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>6.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 46657-2022</t>
+          <t>A 5089-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44850</v>
+        <v>45330</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>7.9</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2908,7 +2908,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 20948-2024</t>
+          <t>A 62053-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45439</v>
+        <v>44918</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>6.4</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2981,7 +2981,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 5089-2024</t>
+          <t>A 39668-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2995,10 +2995,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45330</v>
+        <v>45167</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 62053-2022</t>
+          <t>A 48188-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44918</v>
+        <v>44853</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3127,7 +3127,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 39668-2023</t>
+          <t>A 25837-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45167</v>
+        <v>45090</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.3</v>
+        <v>2.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3200,7 +3200,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 48188-2022</t>
+          <t>A 57730-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3214,10 +3214,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44853</v>
+        <v>45246</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3273,7 +3273,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 57730-2023</t>
+          <t>A 42280-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45246</v>
+        <v>45180</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3346,7 +3346,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 49758-2024</t>
+          <t>A 46657-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45597</v>
+        <v>44850</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.5</v>
+        <v>7.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3419,7 +3419,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 25837-2023</t>
+          <t>A 49758-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3433,10 +3433,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45090</v>
+        <v>45597</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3509,7 +3509,7 @@
         <v>45113</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 48229-2022</t>
+          <t>A 13610-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44858</v>
+        <v>45390</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3638,7 +3638,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 13610-2024</t>
+          <t>A 48229-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3652,10 +3652,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45390</v>
+        <v>44858</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3728,7 +3728,7 @@
         <v>45749</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         <v>45330</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>44602</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>45174</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>44866</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>44958</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 30101-2024</t>
+          <t>A 37198-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4164,14 +4164,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45489</v>
+        <v>45875</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4227,7 +4227,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 61532-2023</t>
+          <t>A 38510-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4237,14 +4237,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45265</v>
+        <v>45884</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4256,13 +4256,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4305,7 +4300,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 27036-2023</t>
+          <t>A 37864-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4319,10 +4314,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45095</v>
+        <v>45881</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4335,7 +4330,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4378,7 +4373,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 33575-2022</t>
+          <t>A 6415-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4392,10 +4387,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44789</v>
+        <v>45699</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4408,7 +4403,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4451,7 +4446,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 38510-2025</t>
+          <t>A 30101-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4461,14 +4456,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45884</v>
+        <v>45489</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4481,7 +4476,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4524,7 +4519,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 36905-2024</t>
+          <t>A 18337-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4538,10 +4533,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45538</v>
+        <v>46125</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4554,7 +4549,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4597,7 +4592,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 21076-2025</t>
+          <t>A 54833-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4611,10 +4606,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45777</v>
+        <v>45618</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4626,8 +4621,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4670,7 +4670,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 6415-2025</t>
+          <t>A 61532-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4680,14 +4680,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45699</v>
+        <v>45265</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4699,8 +4699,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4743,7 +4748,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 11157-2024</t>
+          <t>A 40863-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4757,10 +4762,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45371</v>
+        <v>45897</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4773,7 +4778,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4816,7 +4821,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 11163-2024</t>
+          <t>A 36905-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4830,10 +4835,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45371</v>
+        <v>45538</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4846,7 +4851,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4889,7 +4894,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 37963-2024</t>
+          <t>A 21076-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4903,10 +4908,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45544</v>
+        <v>45777</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4919,7 +4924,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4962,7 +4967,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 31772-2023</t>
+          <t>A 40552-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4976,10 +4981,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45118</v>
+        <v>45896</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4992,7 +4997,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5035,7 +5040,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 40863-2025</t>
+          <t>A 21080-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5049,10 +5054,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45897</v>
+        <v>45777</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5065,7 +5070,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5108,7 +5113,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 3987-2024</t>
+          <t>A 27036-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5122,10 +5127,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45322</v>
+        <v>45095</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5138,7 +5143,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5181,7 +5186,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 30314-2024</t>
+          <t>A 33575-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5195,10 +5200,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45490</v>
+        <v>44789</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5211,7 +5216,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5254,7 +5259,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 40552-2025</t>
+          <t>A 37963-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5268,10 +5273,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45896</v>
+        <v>45544</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5284,7 +5289,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.7</v>
+        <v>5.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5327,7 +5332,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 8698-2025</t>
+          <t>A 42615-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5341,10 +5346,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45712</v>
+        <v>45905</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5357,7 +5362,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5400,7 +5405,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 64481-2023</t>
+          <t>A 8698-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5414,10 +5419,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45280</v>
+        <v>45712</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5430,7 +5435,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5473,7 +5478,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 42618-2025</t>
+          <t>A 3987-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5487,10 +5492,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45905</v>
+        <v>45322</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5503,7 +5508,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5546,7 +5551,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 21080-2025</t>
+          <t>A 43637-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5560,10 +5565,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45777</v>
+        <v>45911</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5576,7 +5581,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5619,7 +5624,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 32177-2024</t>
+          <t>A 43656-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5633,10 +5638,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45511</v>
+        <v>45912</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5649,7 +5654,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5692,7 +5697,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 42615-2025</t>
+          <t>A 42618-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5709,7 +5714,7 @@
         <v>45905</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5722,7 +5727,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5765,7 +5770,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 43637-2025</t>
+          <t>A 44383-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5779,10 +5784,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45911</v>
+        <v>45916</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5795,7 +5800,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5838,7 +5843,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 43656-2025</t>
+          <t>A 44394-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5852,10 +5857,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45912</v>
+        <v>45916</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5868,7 +5873,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5911,7 +5916,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 44383-2025</t>
+          <t>A 11157-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5925,10 +5930,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45916</v>
+        <v>45371</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5941,7 +5946,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5984,7 +5989,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 44394-2025</t>
+          <t>A 11163-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5998,10 +6003,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45916</v>
+        <v>45371</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6014,7 +6019,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6057,7 +6062,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 60859-2024</t>
+          <t>A 31772-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6071,10 +6076,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45644</v>
+        <v>45118</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6087,7 +6092,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6130,7 +6135,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 55074-2023</t>
+          <t>A 30314-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6144,10 +6149,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45237</v>
+        <v>45490</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6160,7 +6165,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6203,7 +6208,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 5818-2023</t>
+          <t>A 64481-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6217,10 +6222,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44963</v>
+        <v>45280</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6233,7 +6238,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.7</v>
+        <v>5.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6276,7 +6281,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 62045-2022</t>
+          <t>A 32177-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6290,10 +6295,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44918</v>
+        <v>45511</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6306,7 +6311,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6349,7 +6354,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 40244-2024</t>
+          <t>A 60859-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6363,10 +6368,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45554</v>
+        <v>45644</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6379,7 +6384,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6422,7 +6427,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 41323-2022</t>
+          <t>A 50728-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6436,10 +6441,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44826</v>
+        <v>45946</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6452,7 +6457,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>15.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6495,7 +6500,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 4293-2022</t>
+          <t>A 23132-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6509,10 +6514,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44588</v>
+        <v>46161</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6525,7 +6530,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6568,7 +6573,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 27264-2023</t>
+          <t>A 55074-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6582,10 +6587,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45096</v>
+        <v>45237</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6598,7 +6603,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6641,7 +6646,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 50728-2025</t>
+          <t>A 5818-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6655,10 +6660,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45946</v>
+        <v>44963</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6671,7 +6676,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>15.2</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6714,7 +6719,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 53077-2021</t>
+          <t>A 62045-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6728,10 +6733,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44467</v>
+        <v>44918</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6744,7 +6749,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6787,7 +6792,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 58356-2022</t>
+          <t>A 40244-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6801,10 +6806,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44893</v>
+        <v>45554</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6817,7 +6822,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6860,7 +6865,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 20078-2022</t>
+          <t>A 55918-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6874,10 +6879,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44698</v>
+        <v>45973</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6890,7 +6895,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6933,7 +6938,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 55918-2025</t>
+          <t>A 41323-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6947,10 +6952,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45973</v>
+        <v>44826</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7006,7 +7011,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 35325-2023</t>
+          <t>A 56240-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7020,10 +7025,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45146</v>
+        <v>45974</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7036,7 +7041,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7079,7 +7084,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 73961-2021</t>
+          <t>A 56554-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7093,10 +7098,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44553</v>
+        <v>45975</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7108,13 +7113,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7157,7 +7157,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 56240-2025</t>
+          <t>A 4293-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7171,10 +7171,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45974</v>
+        <v>44588</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7230,7 +7230,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 56554-2025</t>
+          <t>A 57012-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>7.2</v>
+        <v>0.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7303,7 +7303,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 27258-2023</t>
+          <t>A 27264-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7320,7 +7320,7 @@
         <v>45096</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7376,7 +7376,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 29066-2022</t>
+          <t>A 58780-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44750</v>
+        <v>45986</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7449,7 +7449,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 57012-2025</t>
+          <t>A 53077-2021</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7463,10 +7463,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45978</v>
+        <v>44467</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7522,7 +7522,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 3504-2023</t>
+          <t>A 61411-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7536,10 +7536,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44950</v>
+        <v>46000</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7595,7 +7595,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 9828-2025</t>
+          <t>A 61792-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7609,10 +7609,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45716</v>
+        <v>46002</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.4</v>
+        <v>10.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7668,7 +7668,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 58780-2025</t>
+          <t>A 58356-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7682,10 +7682,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45986</v>
+        <v>44893</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7698,7 +7698,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7741,7 +7741,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 23132-2026</t>
+          <t>A 61682-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7755,10 +7755,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46161</v>
+        <v>46002</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7814,7 +7814,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 36653-2022</t>
+          <t>A 61677-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7824,14 +7824,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44804</v>
+        <v>46002</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7887,7 +7887,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 23138-2026</t>
+          <t>A 20078-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7901,10 +7901,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46161</v>
+        <v>44698</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7960,7 +7960,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 23254-2023</t>
+          <t>A 35325-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7974,10 +7974,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45075</v>
+        <v>45146</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8033,7 +8033,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 64718-2023</t>
+          <t>A 73961-2021</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8047,10 +8047,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45281</v>
+        <v>44553</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8062,8 +8062,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8106,7 +8111,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 61411-2025</t>
+          <t>A 63511-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8120,10 +8125,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46000</v>
+        <v>46013</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8136,7 +8141,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8179,7 +8184,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 61792-2025</t>
+          <t>A 63220-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8193,10 +8198,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46002</v>
+        <v>46010</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8209,7 +8214,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>10.6</v>
+        <v>1.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8252,7 +8257,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 61682-2025</t>
+          <t>A 27258-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8266,10 +8271,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46002</v>
+        <v>45096</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8282,7 +8287,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8325,7 +8330,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 61677-2025</t>
+          <t>A 29066-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8339,10 +8344,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46002</v>
+        <v>44750</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8355,7 +8360,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.8</v>
+        <v>4.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8398,7 +8403,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 52813-2021</t>
+          <t>A 3504-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8412,10 +8417,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44467</v>
+        <v>44950</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8428,7 +8433,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8471,7 +8476,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 47454-2023</t>
+          <t>A 1664-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8485,10 +8490,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45202</v>
+        <v>46034</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8501,7 +8506,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8544,7 +8549,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 34083-2023</t>
+          <t>A 9828-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8558,10 +8563,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45125</v>
+        <v>45716</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8574,7 +8579,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8617,7 +8622,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 63511-2025</t>
+          <t>A 36653-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8627,14 +8632,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46013</v>
+        <v>44804</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8647,7 +8652,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8690,7 +8695,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 63220-2025</t>
+          <t>A 23254-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8704,10 +8709,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46010</v>
+        <v>45075</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8720,7 +8725,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8763,7 +8768,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 6785-2025</t>
+          <t>A 64718-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8777,10 +8782,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45700</v>
+        <v>45281</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8793,7 +8798,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.5</v>
+        <v>4.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8836,7 +8841,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 6793-2025</t>
+          <t>A 27954-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8850,10 +8855,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45700</v>
+        <v>46193</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8866,7 +8871,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8909,7 +8914,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 59727-2024</t>
+          <t>A 27951-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8923,10 +8928,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45639</v>
+        <v>46193</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8938,8 +8943,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -8982,7 +8992,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 15434-2023</t>
+          <t>A 27953-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -8996,10 +9006,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45020</v>
+        <v>46193</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9011,8 +9021,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>0.5</v>
+        <v>5.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9055,7 +9070,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 41918-2022</t>
+          <t>A 27729-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9065,14 +9080,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44830</v>
+        <v>46191</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9085,7 +9100,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2</v>
+        <v>5.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9128,7 +9143,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 61531-2023</t>
+          <t>A 28026-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9138,14 +9153,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45265</v>
+        <v>46195</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9157,13 +9172,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9206,7 +9216,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 26746-2023</t>
+          <t>A 28018-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9220,10 +9230,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45093</v>
+        <v>46195</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9236,7 +9246,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9279,7 +9289,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 1664-2026</t>
+          <t>A 28058-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9293,10 +9303,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46034</v>
+        <v>46195</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9309,7 +9319,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9352,7 +9362,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 15776-2023</t>
+          <t>A 58779-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9366,10 +9376,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45021</v>
+        <v>45986</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9382,7 +9392,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9425,7 +9435,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 51901-2022</t>
+          <t>A 52813-2021</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9439,10 +9449,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44872</v>
+        <v>44467</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9455,7 +9465,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>7.3</v>
+        <v>1.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9498,7 +9508,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 26210-2024</t>
+          <t>A 47454-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9512,10 +9522,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45468</v>
+        <v>45202</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9528,7 +9538,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9571,7 +9581,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 16244-2025</t>
+          <t>A 9641-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9585,10 +9595,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45749</v>
+        <v>46070</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9606,7 +9616,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9649,7 +9659,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 41357-2023</t>
+          <t>A 9624-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9663,10 +9673,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45174</v>
+        <v>46070</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9678,8 +9688,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9722,7 +9737,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 6662-2024</t>
+          <t>A 9627-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9736,10 +9751,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45341</v>
+        <v>46070</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9751,8 +9766,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9795,7 +9815,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 58779-2025</t>
+          <t>A 34083-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9809,10 +9829,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45986</v>
+        <v>45125</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9825,7 +9845,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9868,7 +9888,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 8747-2024</t>
+          <t>A 11667-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9882,10 +9902,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45356</v>
+        <v>46084</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9898,7 +9918,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9941,7 +9961,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 9641-2026</t>
+          <t>A 6785-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9955,10 +9975,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46070</v>
+        <v>45700</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -9970,13 +9990,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10019,7 +10034,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 9624-2026</t>
+          <t>A 6793-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10033,10 +10048,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46070</v>
+        <v>45700</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10048,13 +10063,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10097,7 +10107,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 9627-2026</t>
+          <t>A 59727-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10111,10 +10121,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46070</v>
+        <v>45639</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10126,13 +10136,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10175,7 +10180,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 56393-2023</t>
+          <t>A 15434-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10189,10 +10194,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45243</v>
+        <v>45020</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10205,7 +10210,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10248,7 +10253,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 11667-2026</t>
+          <t>A 41918-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10262,10 +10267,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46084</v>
+        <v>44830</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10278,7 +10283,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10321,7 +10326,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 32826-2023</t>
+          <t>A 61531-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10331,14 +10336,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45124</v>
+        <v>45265</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10350,8 +10355,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10394,7 +10404,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 1450-2024</t>
+          <t>A 26746-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10408,10 +10418,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45303</v>
+        <v>45093</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10424,7 +10434,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10467,7 +10477,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 27954-2026</t>
+          <t>A 13600-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10481,10 +10491,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46193</v>
+        <v>46097</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10496,8 +10506,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10540,7 +10555,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 13600-2026</t>
+          <t>A 15776-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10554,10 +10569,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46097</v>
+        <v>45021</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10569,13 +10584,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10618,7 +10628,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 27951-2026</t>
+          <t>A 51901-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10632,10 +10642,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46193</v>
+        <v>44872</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10647,13 +10657,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>1.6</v>
+        <v>7.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10696,7 +10701,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 27953-2026</t>
+          <t>A 26210-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10710,10 +10715,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46193</v>
+        <v>45468</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10725,13 +10730,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>5.7</v>
+        <v>1.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10774,7 +10774,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 27729-2026</t>
+          <t>A 16244-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10784,14 +10784,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46191</v>
+        <v>45749</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10803,8 +10803,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>5.6</v>
+        <v>2.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10847,7 +10852,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 28026-2026</t>
+          <t>A 41357-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10861,10 +10866,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46195</v>
+        <v>45174</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10877,7 +10882,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10920,7 +10925,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 28018-2026</t>
+          <t>A 17402-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10934,10 +10939,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46195</v>
+        <v>46120</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10950,7 +10955,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -10993,7 +10998,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 28058-2026</t>
+          <t>A 6662-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11007,10 +11012,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46195</v>
+        <v>45341</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11023,7 +11028,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11066,7 +11071,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 53078-2021</t>
+          <t>A 8747-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11080,10 +11085,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44467</v>
+        <v>45356</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11096,7 +11101,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11139,7 +11144,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 36406-2022</t>
+          <t>A 18473-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11153,10 +11158,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44803</v>
+        <v>46127</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11169,7 +11174,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11212,7 +11217,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 32913-2026</t>
+          <t>A 19171-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11226,10 +11231,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46244</v>
+        <v>46132</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11242,7 +11247,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.7</v>
+        <v>22.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11285,7 +11290,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 17402-2026</t>
+          <t>A 30160-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11299,10 +11304,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46120</v>
+        <v>46206</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11315,7 +11320,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11358,7 +11363,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 10996-2024</t>
+          <t>A 56393-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11372,10 +11377,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45370</v>
+        <v>45243</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11388,7 +11393,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>5.9</v>
+        <v>4.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11431,7 +11436,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 22846-2024</t>
+          <t>A 32826-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11445,10 +11450,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45448</v>
+        <v>45124</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11461,7 +11466,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11504,7 +11509,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 30091-2024</t>
+          <t>A 1450-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11514,14 +11519,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45489</v>
+        <v>45303</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11534,7 +11539,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11577,7 +11582,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 18473-2026</t>
+          <t>A 53078-2021</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11591,10 +11596,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46127</v>
+        <v>44467</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11607,7 +11612,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11650,7 +11655,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 19171-2026</t>
+          <t>A 36406-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11664,10 +11669,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46132</v>
+        <v>44803</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11680,7 +11685,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>22.2</v>
+        <v>2.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11723,7 +11728,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 48227-2022</t>
+          <t>A 10996-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11737,10 +11742,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44858</v>
+        <v>45370</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11753,7 +11758,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.3</v>
+        <v>5.9</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11796,7 +11801,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 43758-2023</t>
+          <t>A 22846-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11810,10 +11815,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45187</v>
+        <v>45448</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11826,7 +11831,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11869,7 +11874,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 6747-2025</t>
+          <t>A 30091-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11879,14 +11884,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45700</v>
+        <v>45489</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11899,7 +11904,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11942,7 +11947,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 50304-2024</t>
+          <t>A 48227-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11956,10 +11961,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45600</v>
+        <v>44858</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11972,7 +11977,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12015,7 +12020,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 37864-2025</t>
+          <t>A 43758-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12029,10 +12034,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45881</v>
+        <v>45187</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12045,7 +12050,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12088,7 +12093,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 43786-2023</t>
+          <t>A 6747-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12102,10 +12107,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45187</v>
+        <v>45700</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12118,7 +12123,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12161,7 +12166,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 43787-2023</t>
+          <t>A 50304-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12175,10 +12180,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45187</v>
+        <v>45600</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12191,7 +12196,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12234,7 +12239,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 32903-2026</t>
+          <t>A 43786-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12248,10 +12253,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46244</v>
+        <v>45187</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12264,7 +12269,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12307,7 +12312,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 18337-2026</t>
+          <t>A 43787-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12321,10 +12326,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46125</v>
+        <v>45187</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12337,7 +12342,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12380,7 +12385,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 54833-2024</t>
+          <t>A 27498-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12394,10 +12399,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45618</v>
+        <v>46185</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12415,7 +12420,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.6</v>
+        <v>38</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12475,7 +12480,7 @@
         <v>45581</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12548,7 +12553,7 @@
         <v>44855</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12621,7 +12626,7 @@
         <v>45049</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12694,7 +12699,7 @@
         <v>44893</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12750,7 +12755,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 30160-2026</t>
+          <t>A 31983-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12764,10 +12769,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46206</v>
+        <v>46232</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12780,7 +12785,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12823,7 +12828,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 43790-2023</t>
+          <t>A 37630-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12837,10 +12842,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45187</v>
+        <v>46276</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12852,8 +12857,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>3</v>
+        <v>13.6</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12896,7 +12906,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 59026-2023</t>
+          <t>A 43790-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12910,10 +12920,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45252</v>
+        <v>45187</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12926,7 +12936,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -12969,7 +12979,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 58970-2024</t>
+          <t>A 59026-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -12983,10 +12993,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45636</v>
+        <v>45252</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -12999,7 +13009,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13042,7 +13052,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 23259-2023</t>
+          <t>A 58970-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13056,10 +13066,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45075</v>
+        <v>45636</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13072,7 +13082,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13115,7 +13125,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 5030-2022</t>
+          <t>A 23259-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13129,10 +13139,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44593</v>
+        <v>45075</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13145,7 +13155,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13188,7 +13198,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 6789-2025</t>
+          <t>A 5030-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13202,10 +13212,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45700</v>
+        <v>44593</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13218,7 +13228,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13261,7 +13271,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 58247-2021</t>
+          <t>A 27952-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13275,10 +13285,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44487</v>
+        <v>46193</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13290,8 +13300,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13334,7 +13349,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 58249-2021</t>
+          <t>A 6789-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13348,10 +13363,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44487</v>
+        <v>45700</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13364,7 +13379,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13407,7 +13422,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 25487-2022</t>
+          <t>A 58247-2021</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13421,10 +13436,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44732</v>
+        <v>44487</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13437,7 +13452,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13480,7 +13495,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 6763-2025</t>
+          <t>A 58249-2021</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13494,10 +13509,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45700</v>
+        <v>44487</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13510,7 +13525,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13553,7 +13568,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 13913-2024</t>
+          <t>A 25487-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13567,10 +13582,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45391</v>
+        <v>44732</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13583,7 +13598,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2.2</v>
+        <v>7.1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13626,7 +13641,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 43760-2023</t>
+          <t>A 6763-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13640,10 +13655,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45187</v>
+        <v>45700</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13656,7 +13671,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13699,7 +13714,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 43784-2023</t>
+          <t>A 39094-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13713,10 +13728,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45187</v>
+        <v>46283</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13728,8 +13743,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13772,7 +13792,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 55909-2022</t>
+          <t>A 38885-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13786,10 +13806,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44889</v>
+        <v>46286</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13802,7 +13822,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -13845,7 +13865,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 14355-2023</t>
+          <t>A 13913-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13859,10 +13879,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45012</v>
+        <v>45391</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13875,7 +13895,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13918,7 +13938,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 40067-2023</t>
+          <t>A 23138-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13932,10 +13952,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45168</v>
+        <v>46161</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -13948,7 +13968,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -13991,7 +14011,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 22650-2024</t>
+          <t>A 43760-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14005,10 +14025,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45447</v>
+        <v>45187</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14021,7 +14041,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>7.9</v>
+        <v>0.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14064,7 +14084,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 23625-2022</t>
+          <t>A 43784-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14078,10 +14098,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44721</v>
+        <v>45187</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14094,7 +14114,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14137,7 +14157,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 16303-2023</t>
+          <t>A 55909-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14151,10 +14171,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45028</v>
+        <v>44889</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14167,7 +14187,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>6.3</v>
+        <v>1.9</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14210,7 +14230,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 5707-2022</t>
+          <t>A 14355-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14224,10 +14244,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44596</v>
+        <v>45012</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14240,7 +14260,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14283,7 +14303,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 8119-2025</t>
+          <t>A 38886-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14297,10 +14317,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45707</v>
+        <v>46286</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14313,7 +14333,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14356,7 +14376,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 27498-2026</t>
+          <t>A 32913-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14370,10 +14390,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46185</v>
+        <v>46244</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14385,13 +14405,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>38</v>
+        <v>2.7</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14434,7 +14449,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 31983-2026</t>
+          <t>A 32903-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14448,10 +14463,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46232</v>
+        <v>46244</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14464,7 +14479,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14507,7 +14522,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 270-2023</t>
+          <t>A 40067-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14521,10 +14536,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44928</v>
+        <v>45168</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14537,7 +14552,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14580,7 +14595,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 37630-2026</t>
+          <t>A 22650-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14594,10 +14609,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46276</v>
+        <v>45447</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14609,13 +14624,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>13.6</v>
+        <v>7.9</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14658,7 +14668,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 18314-2024</t>
+          <t>A 23625-2022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14672,10 +14682,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45422</v>
+        <v>44721</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14688,7 +14698,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14731,7 +14741,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 29707-2024</t>
+          <t>A 16303-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14741,14 +14751,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45485</v>
+        <v>45028</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14761,7 +14771,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>7.7</v>
+        <v>6.3</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -14804,7 +14814,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 27952-2026</t>
+          <t>A 5707-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14818,10 +14828,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46193</v>
+        <v>44596</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14833,13 +14843,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>8.5</v>
+        <v>0.5</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -14882,7 +14887,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 24861-2025</t>
+          <t>A 8119-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14896,10 +14901,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45799</v>
+        <v>45707</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14912,7 +14917,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -14955,7 +14960,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 25482-2025</t>
+          <t>A 270-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -14969,10 +14974,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45802</v>
+        <v>44928</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -14985,7 +14990,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>8.300000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15028,7 +15033,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 15436-2024</t>
+          <t>A 18314-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15042,10 +15047,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45401</v>
+        <v>45422</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15058,7 +15063,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15101,7 +15106,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 7316-2024</t>
+          <t>A 29707-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15111,14 +15116,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45345</v>
+        <v>45485</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15131,7 +15136,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.1</v>
+        <v>7.7</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15174,7 +15179,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 30654-2025</t>
+          <t>A 24861-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15188,10 +15193,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45831</v>
+        <v>45799</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15204,7 +15209,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>2</v>
+        <v>5.6</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15247,7 +15252,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 30669-2025</t>
+          <t>A 25482-2025</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15261,10 +15266,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45831</v>
+        <v>45802</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15277,7 +15282,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15320,7 +15325,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 31228-2025</t>
+          <t>A 15436-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15334,10 +15339,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45832</v>
+        <v>45401</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15350,7 +15355,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15393,7 +15398,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 31235-2025</t>
+          <t>A 7316-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15407,10 +15412,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45832</v>
+        <v>45345</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15423,7 +15428,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15466,7 +15471,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 27675-2025</t>
+          <t>A 30654-2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15480,10 +15485,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45813</v>
+        <v>45831</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15496,7 +15501,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15539,7 +15544,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 36508-2022</t>
+          <t>A 30669-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15553,10 +15558,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44804</v>
+        <v>45831</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15569,7 +15574,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15612,7 +15617,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 37198-2025</t>
+          <t>A 31228-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15626,10 +15631,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45875</v>
+        <v>45832</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15642,7 +15647,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15685,24 +15690,24 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>S 2580-2020</t>
+          <t>A 31235-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44166</v>
+        <v>45832</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15715,7 +15720,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.1</v>
+        <v>4</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -15758,24 +15763,24 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>S 2956-2022</t>
+          <t>A 27675-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44712</v>
+        <v>45813</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15787,13 +15792,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>42.7</v>
+        <v>3.1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -15836,24 +15836,24 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>S 2912-2022</t>
+          <t>A 36508-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44711</v>
+        <v>44804</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15865,13 +15865,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I207" t="n">
-        <v>33.4</v>
+        <v>2.7</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -15914,7 +15909,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>S 1256-2025</t>
+          <t>S 2580-2020</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -15924,14 +15919,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45763</v>
+        <v>44166</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15944,7 +15939,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>9</v>
+        <v>0.1</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -15987,158 +15982,387 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
+          <t>S 2956-2022</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D209" s="1" t="n">
+        <v>44712</v>
+      </c>
+      <c r="E209" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>GNOSJÖ</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I209" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="J209" t="n">
+        <v>0</v>
+      </c>
+      <c r="K209" t="n">
+        <v>0</v>
+      </c>
+      <c r="L209" t="n">
+        <v>0</v>
+      </c>
+      <c r="M209" t="n">
+        <v>0</v>
+      </c>
+      <c r="N209" t="n">
+        <v>0</v>
+      </c>
+      <c r="O209" t="n">
+        <v>0</v>
+      </c>
+      <c r="P209" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>0</v>
+      </c>
+      <c r="R209" t="n">
+        <v>0</v>
+      </c>
+      <c r="S209" t="n">
+        <v>0</v>
+      </c>
+      <c r="T209" t="n">
+        <v>0</v>
+      </c>
+      <c r="U209" t="n">
+        <v>0</v>
+      </c>
+      <c r="V209" s="2" t="inlineStr"/>
+    </row>
+    <row r="210" ht="15" customHeight="1">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>S 2912-2022</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D210" s="1" t="n">
+        <v>44711</v>
+      </c>
+      <c r="E210" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>GNOSJÖ</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I210" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="J210" t="n">
+        <v>0</v>
+      </c>
+      <c r="K210" t="n">
+        <v>0</v>
+      </c>
+      <c r="L210" t="n">
+        <v>0</v>
+      </c>
+      <c r="M210" t="n">
+        <v>0</v>
+      </c>
+      <c r="N210" t="n">
+        <v>0</v>
+      </c>
+      <c r="O210" t="n">
+        <v>0</v>
+      </c>
+      <c r="P210" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>0</v>
+      </c>
+      <c r="R210" t="n">
+        <v>0</v>
+      </c>
+      <c r="S210" t="n">
+        <v>0</v>
+      </c>
+      <c r="T210" t="n">
+        <v>0</v>
+      </c>
+      <c r="U210" t="n">
+        <v>0</v>
+      </c>
+      <c r="V210" s="2" t="inlineStr"/>
+    </row>
+    <row r="211" ht="15" customHeight="1">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>S 1256-2025</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D211" s="1" t="n">
+        <v>45763</v>
+      </c>
+      <c r="E211" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>GNOSJÖ</t>
+        </is>
+      </c>
+      <c r="I211" t="n">
+        <v>9</v>
+      </c>
+      <c r="J211" t="n">
+        <v>0</v>
+      </c>
+      <c r="K211" t="n">
+        <v>0</v>
+      </c>
+      <c r="L211" t="n">
+        <v>0</v>
+      </c>
+      <c r="M211" t="n">
+        <v>0</v>
+      </c>
+      <c r="N211" t="n">
+        <v>0</v>
+      </c>
+      <c r="O211" t="n">
+        <v>0</v>
+      </c>
+      <c r="P211" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>0</v>
+      </c>
+      <c r="R211" t="n">
+        <v>0</v>
+      </c>
+      <c r="S211" t="n">
+        <v>0</v>
+      </c>
+      <c r="T211" t="n">
+        <v>0</v>
+      </c>
+      <c r="U211" t="n">
+        <v>0</v>
+      </c>
+      <c r="V211" s="2" t="inlineStr"/>
+    </row>
+    <row r="212" ht="15" customHeight="1">
+      <c r="A212" t="inlineStr">
+        <is>
           <t>S 1619-2025</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
+      <c r="B212" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr">
+      <c r="C212" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D209" s="1" t="n">
+      <c r="D212" s="1" t="n">
         <v>45798</v>
       </c>
-      <c r="E209" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>GNOSJÖ</t>
-        </is>
-      </c>
-      <c r="H209" t="inlineStr">
+      <c r="E212" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>GNOSJÖ</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
         <is>
           <t>Kyrkan</t>
         </is>
       </c>
-      <c r="I209" t="n">
+      <c r="I212" t="n">
         <v>43.9</v>
       </c>
-      <c r="J209" t="n">
-        <v>0</v>
-      </c>
-      <c r="K209" t="n">
-        <v>0</v>
-      </c>
-      <c r="L209" t="n">
-        <v>0</v>
-      </c>
-      <c r="M209" t="n">
-        <v>0</v>
-      </c>
-      <c r="N209" t="n">
-        <v>0</v>
-      </c>
-      <c r="O209" t="n">
-        <v>0</v>
-      </c>
-      <c r="P209" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
-      <c r="R209" t="n">
-        <v>0</v>
-      </c>
-      <c r="S209" t="n">
-        <v>0</v>
-      </c>
-      <c r="T209" t="n">
-        <v>0</v>
-      </c>
-      <c r="U209" t="n">
-        <v>0</v>
-      </c>
-      <c r="V209" s="2" t="inlineStr"/>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
+      <c r="J212" t="n">
+        <v>0</v>
+      </c>
+      <c r="K212" t="n">
+        <v>0</v>
+      </c>
+      <c r="L212" t="n">
+        <v>0</v>
+      </c>
+      <c r="M212" t="n">
+        <v>0</v>
+      </c>
+      <c r="N212" t="n">
+        <v>0</v>
+      </c>
+      <c r="O212" t="n">
+        <v>0</v>
+      </c>
+      <c r="P212" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>0</v>
+      </c>
+      <c r="R212" t="n">
+        <v>0</v>
+      </c>
+      <c r="S212" t="n">
+        <v>0</v>
+      </c>
+      <c r="T212" t="n">
+        <v>0</v>
+      </c>
+      <c r="U212" t="n">
+        <v>0</v>
+      </c>
+      <c r="V212" s="2" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
         <is>
           <t>S 1452-2026</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr">
+      <c r="B213" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr">
+      <c r="C213" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D210" s="1" t="n">
+      <c r="D213" s="1" t="n">
         <v>46160</v>
       </c>
-      <c r="E210" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>GNOSJÖ</t>
-        </is>
-      </c>
-      <c r="H210" t="inlineStr">
+      <c r="E213" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>GNOSJÖ</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
         <is>
           <t>Kyrkan</t>
         </is>
       </c>
-      <c r="I210" t="n">
+      <c r="I213" t="n">
         <v>43.3</v>
       </c>
-      <c r="J210" t="n">
-        <v>0</v>
-      </c>
-      <c r="K210" t="n">
-        <v>0</v>
-      </c>
-      <c r="L210" t="n">
-        <v>0</v>
-      </c>
-      <c r="M210" t="n">
-        <v>0</v>
-      </c>
-      <c r="N210" t="n">
-        <v>0</v>
-      </c>
-      <c r="O210" t="n">
-        <v>0</v>
-      </c>
-      <c r="P210" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
-      <c r="R210" t="n">
-        <v>0</v>
-      </c>
-      <c r="S210" t="n">
-        <v>0</v>
-      </c>
-      <c r="T210" t="n">
-        <v>0</v>
-      </c>
-      <c r="U210" t="n">
-        <v>0</v>
-      </c>
-      <c r="V210" s="2" t="inlineStr"/>
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" t="n">
+        <v>0</v>
+      </c>
+      <c r="L213" t="n">
+        <v>0</v>
+      </c>
+      <c r="M213" t="n">
+        <v>0</v>
+      </c>
+      <c r="N213" t="n">
+        <v>0</v>
+      </c>
+      <c r="O213" t="n">
+        <v>0</v>
+      </c>
+      <c r="P213" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>0</v>
+      </c>
+      <c r="R213" t="n">
+        <v>0</v>
+      </c>
+      <c r="S213" t="n">
+        <v>0</v>
+      </c>
+      <c r="T213" t="n">
+        <v>0</v>
+      </c>
+      <c r="U213" t="n">
+        <v>0</v>
+      </c>
+      <c r="V213" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt GNOSJÖ.xlsx
+++ b/Översikt GNOSJÖ.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE213"/>
+  <dimension ref="A1:AE214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44757</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46030</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44711</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 23612-2022</t>
+          <t>A 38355-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44721</v>
+        <v>45161</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.4</v>
+        <v>11.4</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -979,248 +979,248 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 38355-2023 artfynd.xlsx", "A 38355-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 38355-2023 karta.png", "A 38355-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 38355-2023 georefererad karta.tif", "A 38355-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 38355-2023 FSC-klagomål.docx", "A 38355-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 38355-2023 FSC-klagomål mail.docx", "A 38355-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 38355-2023 tillsynsbegäran.docx", "A 38355-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 38355-2023 tillsynsbegäran mail.docx", "A 38355-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 28312-2025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45818</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>GNOSJÖ</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 28312-2025 artfynd.xlsx", "A 28312-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 28312-2025 karta.png", "A 28312-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 28312-2025 georefererad karta.tif", "A 28312-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 28312-2025 FSC-klagomål.docx", "A 28312-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 28312-2025 FSC-klagomål mail.docx", "A 28312-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 28312-2025 tillsynsbegäran.docx", "A 28312-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 28312-2025 tillsynsbegäran mail.docx", "A 28312-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 23612-2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>44721</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>GNOSJÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>Kungsfågel</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 23612-2022 artfynd.xlsx", "A 23612-2022")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 23612-2022 karta.png", "A 23612-2022")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 23612-2022 georefererad karta.tif", "A 23612-2022")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 23612-2022 FSC-klagomål.docx", "A 23612-2022")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 23612-2022 FSC-klagomål mail.docx", "A 23612-2022")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 23612-2022 tillsynsbegäran.docx", "A 23612-2022")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 23612-2022 tillsynsbegäran mail.docx", "A 23612-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 38355-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45161</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>GNOSJÖ</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Mattlummer</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 38355-2023 artfynd.xlsx", "A 38355-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 38355-2023 karta.png", "A 38355-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 38355-2023 georefererad karta.tif", "A 38355-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 38355-2023 FSC-klagomål.docx", "A 38355-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 38355-2023 FSC-klagomål mail.docx", "A 38355-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 38355-2023 tillsynsbegäran.docx", "A 38355-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 38355-2023 tillsynsbegäran mail.docx", "A 38355-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 28312-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45818</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>GNOSJÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 28312-2025 artfynd.xlsx", "A 28312-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 28312-2025 karta.png", "A 28312-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 28312-2025 georefererad karta.tif", "A 28312-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 28312-2025 FSC-klagomål.docx", "A 28312-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 28312-2025 FSC-klagomål mail.docx", "A 28312-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 28312-2025 tillsynsbegäran.docx", "A 28312-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 28312-2025 tillsynsbegäran mail.docx", "A 28312-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>44530</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>44837</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>44482</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>44474</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>44866</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>44585</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>44468</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>44503</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>44494</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>44698</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>44470</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>44698</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>44467</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>44568</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>44804</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>44855</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 28372-2022</t>
+          <t>A 29707-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2407,14 +2407,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44747</v>
+        <v>45485</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.3</v>
+        <v>7.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2470,7 +2470,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 4298-2022</t>
+          <t>A 49758-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44588</v>
+        <v>45597</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 48480-2022</t>
+          <t>A 25837-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44858</v>
+        <v>45090</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2633,7 +2633,7 @@
         <v>44470</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 13352-2024</t>
+          <t>A 28372-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45387</v>
+        <v>44747</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2762,7 +2762,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 20948-2024</t>
+          <t>A 23625-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45439</v>
+        <v>44721</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>6.4</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 5089-2024</t>
+          <t>A 47856-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45330</v>
+        <v>44855</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2908,7 +2908,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 62053-2022</t>
+          <t>A 41323-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44918</v>
+        <v>44826</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2981,7 +2981,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 39668-2023</t>
+          <t>A 4298-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2995,10 +2995,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45167</v>
+        <v>44588</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 48188-2022</t>
+          <t>A 16243-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44853</v>
+        <v>45749</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3083,8 +3083,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3127,7 +3132,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 25837-2023</t>
+          <t>A 43758-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3141,10 +3146,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45090</v>
+        <v>45187</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3157,7 +3162,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3200,7 +3205,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 57730-2023</t>
+          <t>A 43784-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3214,10 +3219,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45246</v>
+        <v>45187</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3230,7 +3235,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3273,7 +3278,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 42280-2023</t>
+          <t>A 48480-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3287,10 +3292,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45180</v>
+        <v>44858</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3303,7 +3308,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3346,7 +3351,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 46657-2022</t>
+          <t>A 18314-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3360,10 +3365,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44850</v>
+        <v>45422</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3376,7 +3381,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>7.9</v>
+        <v>1.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3419,7 +3424,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 49758-2024</t>
+          <t>A 16303-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3433,10 +3438,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45597</v>
+        <v>45028</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3449,7 +3454,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.5</v>
+        <v>6.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3492,7 +3497,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 30961-2023</t>
+          <t>A 51901-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3506,10 +3511,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45113</v>
+        <v>44872</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3522,7 +3527,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.7</v>
+        <v>7.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3565,7 +3570,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 13610-2024</t>
+          <t>A 47454-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3579,10 +3584,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45390</v>
+        <v>45202</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3595,7 +3600,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3638,7 +3643,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 48229-2022</t>
+          <t>A 33575-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3652,10 +3657,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44858</v>
+        <v>44789</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3668,7 +3673,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3711,7 +3716,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 16243-2025</t>
+          <t>A 41918-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3725,10 +3730,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45749</v>
+        <v>44830</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3740,13 +3745,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3789,7 +3789,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 5082-2024</t>
+          <t>A 57730-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45330</v>
+        <v>45246</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3862,7 +3862,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 6781-2022</t>
+          <t>A 6763-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3876,10 +3876,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44602</v>
+        <v>45700</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3935,7 +3935,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 41347-2023</t>
+          <t>A 59026-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3949,10 +3949,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45174</v>
+        <v>45252</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>6.2</v>
+        <v>2.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4008,7 +4008,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 50440-2022</t>
+          <t>A 52813-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4022,10 +4022,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44866</v>
+        <v>44467</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>8.699999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 4992-2023</t>
+          <t>A 42280-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44958</v>
+        <v>45180</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 37198-2025</t>
+          <t>A 27258-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4168,10 +4168,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45875</v>
+        <v>45096</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4227,7 +4227,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 38510-2025</t>
+          <t>A 48188-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45884</v>
+        <v>44853</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4300,7 +4300,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 37864-2025</t>
+          <t>A 23254-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45881</v>
+        <v>45075</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4373,7 +4373,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 6415-2025</t>
+          <t>A 26746-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45699</v>
+        <v>45093</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4446,7 +4446,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 30101-2024</t>
+          <t>A 6415-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4456,14 +4456,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45489</v>
+        <v>45699</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4519,7 +4519,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 18337-2026</t>
+          <t>A 8698-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46125</v>
+        <v>45712</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4592,7 +4592,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 54833-2024</t>
+          <t>A 53078-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45618</v>
+        <v>44467</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4621,13 +4621,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4670,7 +4665,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 61532-2023</t>
+          <t>A 64718-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4680,14 +4675,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45265</v>
+        <v>45281</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4699,13 +4694,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4748,7 +4738,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 40863-2025</t>
+          <t>A 40552-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4762,10 +4752,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45897</v>
+        <v>45896</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4778,7 +4768,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4821,7 +4811,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 36905-2024</t>
+          <t>A 40863-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4835,10 +4825,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45538</v>
+        <v>45897</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4851,7 +4841,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4894,7 +4884,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 21076-2025</t>
+          <t>A 46657-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4908,10 +4898,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45777</v>
+        <v>44850</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4924,7 +4914,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.6</v>
+        <v>7.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4967,7 +4957,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 40552-2025</t>
+          <t>A 3504-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4981,10 +4971,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45896</v>
+        <v>44950</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4997,7 +4987,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5040,7 +5030,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 21080-2025</t>
+          <t>A 11157-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5054,10 +5044,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45777</v>
+        <v>45371</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5070,7 +5060,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5113,7 +5103,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 27036-2023</t>
+          <t>A 11163-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5127,10 +5117,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45095</v>
+        <v>45371</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5143,7 +5133,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5186,7 +5176,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 33575-2022</t>
+          <t>A 24861-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5200,10 +5190,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44789</v>
+        <v>45799</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5216,7 +5206,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5259,7 +5249,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 37963-2024</t>
+          <t>A 27264-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5273,10 +5263,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45544</v>
+        <v>45096</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5289,7 +5279,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5.3</v>
+        <v>1.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5332,7 +5322,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 42615-2025</t>
+          <t>A 21080-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5346,10 +5336,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45905</v>
+        <v>45777</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5362,7 +5352,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5405,7 +5395,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 8698-2025</t>
+          <t>A 15776-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5419,10 +5409,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45712</v>
+        <v>45021</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5435,7 +5425,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5478,7 +5468,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 3987-2024</t>
+          <t>A 5082-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5492,10 +5482,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45322</v>
+        <v>45330</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5508,7 +5498,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5551,7 +5541,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 43637-2025</t>
+          <t>A 41347-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5565,10 +5555,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45911</v>
+        <v>45174</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5581,7 +5571,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5624,7 +5614,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 43656-2025</t>
+          <t>A 30091-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5634,14 +5624,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45912</v>
+        <v>45489</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5654,7 +5644,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5697,7 +5687,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 42618-2025</t>
+          <t>A 42615-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5714,7 +5704,7 @@
         <v>45905</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5727,7 +5717,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5770,7 +5760,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 44383-2025</t>
+          <t>A 50440-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5784,10 +5774,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45916</v>
+        <v>44866</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5800,7 +5790,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5843,7 +5833,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 44394-2025</t>
+          <t>A 43637-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5857,10 +5847,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45916</v>
+        <v>45911</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5873,7 +5863,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5916,7 +5906,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 11157-2024</t>
+          <t>A 43656-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5930,10 +5920,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45371</v>
+        <v>45912</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5946,7 +5936,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5989,7 +5979,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 11163-2024</t>
+          <t>A 5707-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6003,10 +5993,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45371</v>
+        <v>44596</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6019,7 +6009,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6062,7 +6052,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 31772-2023</t>
+          <t>A 22650-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6076,10 +6066,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45118</v>
+        <v>45447</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6092,7 +6082,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>7.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6135,7 +6125,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 30314-2024</t>
+          <t>A 44383-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6149,10 +6139,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45490</v>
+        <v>45916</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6165,7 +6155,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6208,7 +6198,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 64481-2023</t>
+          <t>A 44394-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6222,10 +6212,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45280</v>
+        <v>45916</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6238,7 +6228,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>5.5</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6281,7 +6271,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 32177-2024</t>
+          <t>A 26210-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6295,10 +6285,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45511</v>
+        <v>45468</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6311,7 +6301,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6354,7 +6344,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 60859-2024</t>
+          <t>A 25482-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6368,10 +6358,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45644</v>
+        <v>45802</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6384,7 +6374,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6427,7 +6417,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 50728-2025</t>
+          <t>A 15436-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6441,10 +6431,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45946</v>
+        <v>45401</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6457,7 +6447,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>15.2</v>
+        <v>2.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6500,7 +6490,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 23132-2026</t>
+          <t>A 60859-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6514,10 +6504,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46161</v>
+        <v>45644</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6530,7 +6520,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6573,7 +6563,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 55074-2023</t>
+          <t>A 56625-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6587,10 +6577,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45237</v>
+        <v>44893</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6603,7 +6593,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6646,7 +6636,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 5818-2023</t>
+          <t>A 43787-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6660,10 +6650,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44963</v>
+        <v>45187</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6676,7 +6666,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6719,7 +6709,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 62045-2022</t>
+          <t>A 43760-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6733,10 +6723,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44918</v>
+        <v>45187</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6749,7 +6739,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6792,7 +6782,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 40244-2024</t>
+          <t>A 55909-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6806,10 +6796,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45554</v>
+        <v>44889</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6822,7 +6812,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6865,7 +6855,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 55918-2025</t>
+          <t>A 43790-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6879,10 +6869,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45973</v>
+        <v>45187</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6895,7 +6885,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6938,7 +6928,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 41323-2022</t>
+          <t>A 35325-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6952,10 +6942,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44826</v>
+        <v>45146</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6968,7 +6958,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7011,7 +7001,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 56240-2025</t>
+          <t>A 30101-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7021,14 +7011,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45974</v>
+        <v>45489</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7041,7 +7031,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7084,7 +7074,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 56554-2025</t>
+          <t>A 10996-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7098,10 +7088,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45975</v>
+        <v>45370</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7114,7 +7104,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7157,7 +7147,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 4293-2022</t>
+          <t>A 40067-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7171,10 +7161,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44588</v>
+        <v>45168</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7187,7 +7177,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7230,7 +7220,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 57012-2025</t>
+          <t>A 50728-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7244,10 +7234,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45978</v>
+        <v>45946</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7260,7 +7250,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.6</v>
+        <v>15.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7303,7 +7293,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 27264-2023</t>
+          <t>A 73961-2021</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7317,10 +7307,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45096</v>
+        <v>44553</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7332,8 +7322,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>1.4</v>
+        <v>5.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7376,7 +7371,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 58780-2025</t>
+          <t>A 62053-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7390,10 +7385,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45986</v>
+        <v>44918</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7406,7 +7401,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7449,7 +7444,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 53077-2021</t>
+          <t>A 20078-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7463,10 +7458,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44467</v>
+        <v>44698</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7479,7 +7474,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7522,7 +7517,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 61411-2025</t>
+          <t>A 6781-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7536,10 +7531,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46000</v>
+        <v>44602</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7552,7 +7547,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7595,7 +7590,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 61792-2025</t>
+          <t>A 7316-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7609,10 +7604,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46002</v>
+        <v>45345</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7625,7 +7620,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>10.6</v>
+        <v>1.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7668,7 +7663,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 58356-2022</t>
+          <t>A 4293-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7682,10 +7677,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44893</v>
+        <v>44588</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7698,7 +7693,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7741,7 +7736,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 61682-2025</t>
+          <t>A 36406-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7755,10 +7750,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46002</v>
+        <v>44803</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7771,7 +7766,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7814,7 +7809,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 61677-2025</t>
+          <t>A 27036-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7828,10 +7823,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46002</v>
+        <v>45095</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7844,7 +7839,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7887,7 +7882,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 20078-2022</t>
+          <t>A 9828-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7901,10 +7896,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44698</v>
+        <v>45716</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7917,7 +7912,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7960,7 +7955,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 35325-2023</t>
+          <t>A 43786-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7974,10 +7969,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45146</v>
+        <v>45187</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -7990,7 +7985,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8033,7 +8028,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 73961-2021</t>
+          <t>A 50304-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8047,10 +8042,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44553</v>
+        <v>45600</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8062,13 +8057,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>5.1</v>
+        <v>1.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8111,7 +8101,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 63511-2025</t>
+          <t>A 8747-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8125,10 +8115,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46013</v>
+        <v>45356</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8141,7 +8131,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8184,7 +8174,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 63220-2025</t>
+          <t>A 6747-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8198,10 +8188,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46010</v>
+        <v>45700</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8214,7 +8204,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8257,7 +8247,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 27258-2023</t>
+          <t>A 56240-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8271,10 +8261,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45096</v>
+        <v>45974</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8287,7 +8277,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8330,7 +8320,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 29066-2022</t>
+          <t>A 55918-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8344,10 +8334,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44750</v>
+        <v>45973</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8360,7 +8350,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8403,7 +8393,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 3504-2023</t>
+          <t>A 6789-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8417,10 +8407,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44950</v>
+        <v>45700</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8433,7 +8423,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8476,7 +8466,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 1664-2026</t>
+          <t>A 56554-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8490,10 +8480,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46034</v>
+        <v>45975</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8506,7 +8496,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.7</v>
+        <v>7.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8549,7 +8539,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 9828-2025</t>
+          <t>A 59727-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8563,10 +8553,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45716</v>
+        <v>45639</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8579,7 +8569,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8622,7 +8612,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 36653-2022</t>
+          <t>A 57012-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8632,14 +8622,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44804</v>
+        <v>45978</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8652,7 +8642,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8695,7 +8685,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 23254-2023</t>
+          <t>A 4992-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8709,10 +8699,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45075</v>
+        <v>44958</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8725,7 +8715,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8768,7 +8758,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 64718-2023</t>
+          <t>A 58249-2021</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8782,10 +8772,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45281</v>
+        <v>44487</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8798,7 +8788,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8841,7 +8831,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 27954-2026</t>
+          <t>A 30961-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8855,10 +8845,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46193</v>
+        <v>45113</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8871,7 +8861,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8914,7 +8904,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 27951-2026</t>
+          <t>A 58780-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8928,10 +8918,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46193</v>
+        <v>45986</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8943,13 +8933,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -8992,7 +8977,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 27953-2026</t>
+          <t>A 19307-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9006,10 +8991,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46193</v>
+        <v>45049</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9021,13 +9006,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>5.7</v>
+        <v>0.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9070,7 +9050,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 27729-2026</t>
+          <t>A 25487-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9080,14 +9060,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46191</v>
+        <v>44732</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9100,7 +9080,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>5.6</v>
+        <v>7.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9143,7 +9123,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 28026-2026</t>
+          <t>A 16244-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9157,10 +9137,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46195</v>
+        <v>45749</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9172,8 +9152,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9216,7 +9201,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 28018-2026</t>
+          <t>A 58970-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9230,10 +9215,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46195</v>
+        <v>45636</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9246,7 +9231,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9289,7 +9274,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 28058-2026</t>
+          <t>A 29066-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9303,10 +9288,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46195</v>
+        <v>44750</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9319,7 +9304,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9362,7 +9347,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 58779-2025</t>
+          <t>A 34083-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9376,10 +9361,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45986</v>
+        <v>45125</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9392,7 +9377,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9435,7 +9420,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 52813-2021</t>
+          <t>A 30669-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9449,10 +9434,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44467</v>
+        <v>45831</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9465,7 +9450,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9508,7 +9493,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 47454-2023</t>
+          <t>A 30654-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9522,10 +9507,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45202</v>
+        <v>45831</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9538,7 +9523,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9581,7 +9566,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 9641-2026</t>
+          <t>A 31235-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9595,10 +9580,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46070</v>
+        <v>45832</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9610,13 +9595,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9659,7 +9639,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 9624-2026</t>
+          <t>A 61411-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9673,10 +9653,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46070</v>
+        <v>46000</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9688,13 +9668,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9737,7 +9712,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 9627-2026</t>
+          <t>A 31228-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9751,10 +9726,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46070</v>
+        <v>45832</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9766,13 +9741,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9815,7 +9785,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 34083-2023</t>
+          <t>A 61677-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9829,10 +9799,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45125</v>
+        <v>46002</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9845,7 +9815,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9888,7 +9858,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 11667-2026</t>
+          <t>A 1664-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9902,10 +9872,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46084</v>
+        <v>46034</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9918,7 +9888,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9961,7 +9931,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 6785-2025</t>
+          <t>A 61682-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9975,10 +9945,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45700</v>
+        <v>46002</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -9991,7 +9961,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10034,7 +10004,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 6793-2025</t>
+          <t>A 61792-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10048,10 +10018,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45700</v>
+        <v>46002</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10064,7 +10034,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.9</v>
+        <v>10.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10107,7 +10077,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 59727-2024</t>
+          <t>A 48227-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10121,10 +10091,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45639</v>
+        <v>44858</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10180,7 +10150,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 15434-2023</t>
+          <t>A 22846-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10194,10 +10164,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45020</v>
+        <v>45448</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10210,7 +10180,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10253,7 +10223,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 41918-2022</t>
+          <t>A 63220-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10267,10 +10237,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44830</v>
+        <v>46010</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10283,7 +10253,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10326,7 +10296,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 61531-2023</t>
+          <t>A 63511-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10336,14 +10306,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45265</v>
+        <v>46013</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10355,13 +10325,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>0.9</v>
+        <v>4.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10404,7 +10369,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 26746-2023</t>
+          <t>A 61531-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10414,14 +10379,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45093</v>
+        <v>45265</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10433,8 +10398,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10477,7 +10447,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 13600-2026</t>
+          <t>A 38885-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10491,10 +10461,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46097</v>
+        <v>46286</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10506,13 +10476,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10555,7 +10520,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 15776-2023</t>
+          <t>A 58779-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10569,10 +10534,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45021</v>
+        <v>45986</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10585,7 +10550,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10628,7 +10593,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 51901-2022</t>
+          <t>A 39668-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10642,10 +10607,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44872</v>
+        <v>45167</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10658,7 +10623,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>7.3</v>
+        <v>0.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10701,7 +10666,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 26210-2024</t>
+          <t>A 38886-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10715,10 +10680,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45468</v>
+        <v>46286</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10731,7 +10696,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10774,7 +10739,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 16244-2025</t>
+          <t>A 9641-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10788,10 +10753,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45749</v>
+        <v>46070</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10809,7 +10774,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10852,7 +10817,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 41357-2023</t>
+          <t>A 9624-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10866,10 +10831,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45174</v>
+        <v>46070</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10881,8 +10846,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10925,7 +10895,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 17402-2026</t>
+          <t>A 9627-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10939,10 +10909,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46120</v>
+        <v>46070</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10954,8 +10924,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -10998,7 +10973,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 6662-2024</t>
+          <t>A 32903-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11012,10 +10987,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45341</v>
+        <v>46244</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11028,7 +11003,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11071,7 +11046,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 8747-2024</t>
+          <t>A 32913-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11085,10 +11060,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45356</v>
+        <v>46244</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11101,7 +11076,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11144,7 +11119,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 18473-2026</t>
+          <t>A 23138-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11158,10 +11133,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46127</v>
+        <v>46161</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11174,7 +11149,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11217,7 +11192,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 19171-2026</t>
+          <t>A 5818-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11231,10 +11206,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46132</v>
+        <v>44963</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11247,7 +11222,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>22.2</v>
+        <v>0.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11290,7 +11265,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 30160-2026</t>
+          <t>A 39094-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11304,10 +11279,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46206</v>
+        <v>46283</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11319,8 +11294,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>1.6</v>
+        <v>6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11363,7 +11343,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 56393-2023</t>
+          <t>A 11667-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11377,10 +11357,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45243</v>
+        <v>46084</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11393,7 +11373,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11436,7 +11416,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 32826-2023</t>
+          <t>A 39453-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11450,10 +11430,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45124</v>
+        <v>46288</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11466,7 +11446,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11509,7 +11489,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 1450-2024</t>
+          <t>A 5030-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11523,10 +11503,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45303</v>
+        <v>44593</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11539,7 +11519,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11582,7 +11562,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 53078-2021</t>
+          <t>A 40244-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11596,10 +11576,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44467</v>
+        <v>45554</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11612,7 +11592,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11655,7 +11635,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 36406-2022</t>
+          <t>A 64481-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11669,10 +11649,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44803</v>
+        <v>45280</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11685,7 +11665,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.1</v>
+        <v>5.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11728,7 +11708,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 10996-2024</t>
+          <t>A 27675-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11742,10 +11722,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45370</v>
+        <v>45813</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11758,7 +11738,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>5.9</v>
+        <v>3.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11801,7 +11781,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 22846-2024</t>
+          <t>A 13600-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11815,10 +11795,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45448</v>
+        <v>46097</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11830,8 +11810,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11874,7 +11859,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 30091-2024</t>
+          <t>A 36508-2022</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11884,14 +11869,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45489</v>
+        <v>44804</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11904,7 +11889,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11947,7 +11932,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 48227-2022</t>
+          <t>A 55074-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11961,10 +11946,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44858</v>
+        <v>45237</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11977,7 +11962,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12020,7 +12005,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 43758-2023</t>
+          <t>A 58356-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12034,10 +12019,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45187</v>
+        <v>44893</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12050,7 +12035,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12093,7 +12078,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 6747-2025</t>
+          <t>A 14355-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12107,10 +12092,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45700</v>
+        <v>45012</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12123,7 +12108,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12166,7 +12151,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 50304-2024</t>
+          <t>A 13913-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12180,10 +12165,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45600</v>
+        <v>45391</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12196,7 +12181,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12239,7 +12224,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 43786-2023</t>
+          <t>A 46254-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12253,10 +12238,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45187</v>
+        <v>45581</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12269,7 +12254,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12312,7 +12297,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 43787-2023</t>
+          <t>A 13352-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12326,10 +12311,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45187</v>
+        <v>45387</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12342,7 +12327,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12385,7 +12370,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 27498-2026</t>
+          <t>A 13610-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12399,10 +12384,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46185</v>
+        <v>45390</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12414,13 +12399,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12463,7 +12443,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 46254-2024</t>
+          <t>A 56393-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12477,10 +12457,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45581</v>
+        <v>45243</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12493,7 +12473,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12536,7 +12516,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 47856-2022</t>
+          <t>A 36653-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12546,14 +12526,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44855</v>
+        <v>44804</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12566,7 +12546,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.1</v>
+        <v>2.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12609,7 +12589,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 19307-2023</t>
+          <t>A 17402-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12623,10 +12603,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45049</v>
+        <v>46120</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12639,7 +12619,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12682,7 +12662,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 56625-2022</t>
+          <t>A 48229-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12696,10 +12676,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44893</v>
+        <v>44858</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12712,7 +12692,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12755,7 +12735,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 31983-2026</t>
+          <t>A 18473-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12769,10 +12749,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46232</v>
+        <v>46127</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12785,7 +12765,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12828,7 +12808,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 37630-2026</t>
+          <t>A 5089-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12842,10 +12822,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46276</v>
+        <v>45330</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12857,13 +12837,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>13.6</v>
+        <v>0.9</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12906,7 +12881,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 43790-2023</t>
+          <t>A 19171-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12920,10 +12895,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45187</v>
+        <v>46132</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12936,7 +12911,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>3</v>
+        <v>22.2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -12979,7 +12954,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 59026-2023</t>
+          <t>A 58247-2021</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -12993,10 +12968,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45252</v>
+        <v>44487</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13009,7 +12984,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.1</v>
+        <v>8.9</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13052,7 +13027,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 58970-2024</t>
+          <t>A 31772-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13066,10 +13041,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45636</v>
+        <v>45118</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13082,7 +13057,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13125,7 +13100,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 23259-2023</t>
+          <t>A 6662-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13139,10 +13114,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45075</v>
+        <v>45341</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13155,7 +13130,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>2.8</v>
+        <v>0.2</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13198,7 +13173,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 5030-2022</t>
+          <t>A 53077-2021</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13212,10 +13187,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44593</v>
+        <v>44467</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13228,7 +13203,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13271,7 +13246,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 27952-2026</t>
+          <t>A 37198-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13285,10 +13260,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46193</v>
+        <v>45875</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13300,13 +13275,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>8.5</v>
+        <v>3.7</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13349,7 +13319,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 6789-2025</t>
+          <t>A 18337-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13363,10 +13333,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45700</v>
+        <v>46125</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13379,7 +13349,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13422,7 +13392,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 58247-2021</t>
+          <t>A 54833-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13436,10 +13406,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44487</v>
+        <v>45618</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13451,8 +13421,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>8.9</v>
+        <v>1.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13495,7 +13470,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 58249-2021</t>
+          <t>A 1450-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13509,10 +13484,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44487</v>
+        <v>45303</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13525,7 +13500,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13568,7 +13543,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 25487-2022</t>
+          <t>A 38510-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13582,10 +13557,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44732</v>
+        <v>45884</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13598,7 +13573,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>7.1</v>
+        <v>2.1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13641,7 +13616,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 6763-2025</t>
+          <t>A 6785-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13658,7 +13633,7 @@
         <v>45700</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13671,7 +13646,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13714,7 +13689,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 39094-2026</t>
+          <t>A 6793-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13728,10 +13703,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46283</v>
+        <v>45700</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13743,13 +13718,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>6</v>
+        <v>0.9</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13792,7 +13762,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 38885-2026</t>
+          <t>A 21076-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13806,10 +13776,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46286</v>
+        <v>45777</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13822,7 +13792,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -13865,7 +13835,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 13913-2024</t>
+          <t>A 32826-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13879,10 +13849,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45391</v>
+        <v>45124</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13895,7 +13865,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13938,7 +13908,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 23138-2026</t>
+          <t>A 37963-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13952,10 +13922,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46161</v>
+        <v>45544</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -13968,7 +13938,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.3</v>
+        <v>5.3</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14011,7 +13981,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 43760-2023</t>
+          <t>A 36905-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14025,10 +13995,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45187</v>
+        <v>45538</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14041,7 +14011,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14084,7 +14054,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 43784-2023</t>
+          <t>A 3987-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14098,10 +14068,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45187</v>
+        <v>45322</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14114,7 +14084,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14157,7 +14127,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 55909-2022</t>
+          <t>A 61532-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14167,14 +14137,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44889</v>
+        <v>45265</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14186,8 +14156,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14230,7 +14205,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 14355-2023</t>
+          <t>A 32177-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14244,10 +14219,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45012</v>
+        <v>45511</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14260,7 +14235,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14303,7 +14278,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 38886-2026</t>
+          <t>A 41357-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14317,10 +14292,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46286</v>
+        <v>45174</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14333,7 +14308,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14376,7 +14351,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 32913-2026</t>
+          <t>A 42618-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14390,10 +14365,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46244</v>
+        <v>45905</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14406,7 +14381,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14449,7 +14424,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 32903-2026</t>
+          <t>A 37864-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14463,10 +14438,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46244</v>
+        <v>45881</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14479,7 +14454,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14522,7 +14497,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 40067-2023</t>
+          <t>A 62045-2022</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14536,10 +14511,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45168</v>
+        <v>44918</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14552,7 +14527,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14595,7 +14570,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 22650-2024</t>
+          <t>A 15434-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14609,10 +14584,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45447</v>
+        <v>45020</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14625,7 +14600,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>7.9</v>
+        <v>0.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14668,7 +14643,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 23625-2022</t>
+          <t>A 23259-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14682,10 +14657,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44721</v>
+        <v>45075</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14698,7 +14673,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14741,7 +14716,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 16303-2023</t>
+          <t>A 30314-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14755,10 +14730,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45028</v>
+        <v>45490</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14771,7 +14746,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>6.3</v>
+        <v>1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -14814,7 +14789,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 5707-2022</t>
+          <t>A 20948-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14828,10 +14803,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44596</v>
+        <v>45439</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14844,7 +14819,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.5</v>
+        <v>6.4</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -14904,7 +14879,7 @@
         <v>45707</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14977,7 +14952,7 @@
         <v>44928</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15033,7 +15008,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 18314-2024</t>
+          <t>A 23132-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15047,10 +15022,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45422</v>
+        <v>46161</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15063,7 +15038,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15106,7 +15081,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 29707-2024</t>
+          <t>A 27729-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15120,10 +15095,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45485</v>
+        <v>46191</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15136,7 +15111,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>7.7</v>
+        <v>5.6</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15179,7 +15154,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 24861-2025</t>
+          <t>A 28018-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15193,10 +15168,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45799</v>
+        <v>46195</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15209,7 +15184,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15252,7 +15227,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 25482-2025</t>
+          <t>A 27954-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15266,10 +15241,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45802</v>
+        <v>46193</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15282,7 +15257,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>8.300000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15325,7 +15300,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 15436-2024</t>
+          <t>A 27951-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15339,10 +15314,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45401</v>
+        <v>46193</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15354,8 +15329,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15398,7 +15378,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 7316-2024</t>
+          <t>A 28058-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15412,10 +15392,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45345</v>
+        <v>46195</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15428,7 +15408,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15471,7 +15451,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 30654-2025</t>
+          <t>A 27953-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15485,10 +15465,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45831</v>
+        <v>46193</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15500,8 +15480,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I202" t="n">
-        <v>2</v>
+        <v>5.7</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15544,7 +15529,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 30669-2025</t>
+          <t>A 28026-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15558,10 +15543,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45831</v>
+        <v>46195</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15574,7 +15559,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15617,7 +15602,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 31228-2025</t>
+          <t>A 30160-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15631,10 +15616,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45832</v>
+        <v>46206</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15647,7 +15632,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15690,7 +15675,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 31235-2025</t>
+          <t>A 27498-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15704,10 +15689,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45832</v>
+        <v>46185</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15719,8 +15704,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -15763,7 +15753,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 27675-2025</t>
+          <t>A 31983-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -15777,10 +15767,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45813</v>
+        <v>46232</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15793,7 +15783,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -15836,7 +15826,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 36508-2022</t>
+          <t>A 37630-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15850,10 +15840,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44804</v>
+        <v>46276</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15865,8 +15855,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I207" t="n">
-        <v>2.7</v>
+        <v>13.6</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -15909,24 +15904,24 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>S 2580-2020</t>
+          <t>A 27952-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44166</v>
+        <v>46193</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15938,8 +15933,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>0.1</v>
+        <v>8.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -15982,7 +15982,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>S 2956-2022</t>
+          <t>S 2580-2020</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -15992,14 +15992,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44712</v>
+        <v>44166</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16011,13 +16011,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I209" t="n">
-        <v>42.7</v>
+        <v>0.1</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16060,7 +16055,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>S 2912-2022</t>
+          <t>S 2956-2022</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16074,10 +16069,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44711</v>
+        <v>44712</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16095,7 +16090,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>33.4</v>
+        <v>42.7</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16138,7 +16133,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>S 1256-2025</t>
+          <t>S 2912-2022</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16152,10 +16147,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45763</v>
+        <v>44711</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16167,8 +16162,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I211" t="n">
-        <v>9</v>
+        <v>33.4</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16211,158 +16211,231 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
+          <t>S 1256-2025</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D212" s="1" t="n">
+        <v>45763</v>
+      </c>
+      <c r="E212" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>GNOSJÖ</t>
+        </is>
+      </c>
+      <c r="I212" t="n">
+        <v>9</v>
+      </c>
+      <c r="J212" t="n">
+        <v>0</v>
+      </c>
+      <c r="K212" t="n">
+        <v>0</v>
+      </c>
+      <c r="L212" t="n">
+        <v>0</v>
+      </c>
+      <c r="M212" t="n">
+        <v>0</v>
+      </c>
+      <c r="N212" t="n">
+        <v>0</v>
+      </c>
+      <c r="O212" t="n">
+        <v>0</v>
+      </c>
+      <c r="P212" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>0</v>
+      </c>
+      <c r="R212" t="n">
+        <v>0</v>
+      </c>
+      <c r="S212" t="n">
+        <v>0</v>
+      </c>
+      <c r="T212" t="n">
+        <v>0</v>
+      </c>
+      <c r="U212" t="n">
+        <v>0</v>
+      </c>
+      <c r="V212" s="2" t="inlineStr"/>
+    </row>
+    <row r="213" ht="15" customHeight="1">
+      <c r="A213" t="inlineStr">
+        <is>
           <t>S 1619-2025</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
+      <c r="B213" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr">
+      <c r="C213" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D212" s="1" t="n">
+      <c r="D213" s="1" t="n">
         <v>45798</v>
       </c>
-      <c r="E212" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>GNOSJÖ</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr">
+      <c r="E213" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>GNOSJÖ</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
         <is>
           <t>Kyrkan</t>
         </is>
       </c>
-      <c r="I212" t="n">
+      <c r="I213" t="n">
         <v>43.9</v>
       </c>
-      <c r="J212" t="n">
-        <v>0</v>
-      </c>
-      <c r="K212" t="n">
-        <v>0</v>
-      </c>
-      <c r="L212" t="n">
-        <v>0</v>
-      </c>
-      <c r="M212" t="n">
-        <v>0</v>
-      </c>
-      <c r="N212" t="n">
-        <v>0</v>
-      </c>
-      <c r="O212" t="n">
-        <v>0</v>
-      </c>
-      <c r="P212" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
-      <c r="R212" t="n">
-        <v>0</v>
-      </c>
-      <c r="S212" t="n">
-        <v>0</v>
-      </c>
-      <c r="T212" t="n">
-        <v>0</v>
-      </c>
-      <c r="U212" t="n">
-        <v>0</v>
-      </c>
-      <c r="V212" s="2" t="inlineStr"/>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" t="n">
+        <v>0</v>
+      </c>
+      <c r="L213" t="n">
+        <v>0</v>
+      </c>
+      <c r="M213" t="n">
+        <v>0</v>
+      </c>
+      <c r="N213" t="n">
+        <v>0</v>
+      </c>
+      <c r="O213" t="n">
+        <v>0</v>
+      </c>
+      <c r="P213" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>0</v>
+      </c>
+      <c r="R213" t="n">
+        <v>0</v>
+      </c>
+      <c r="S213" t="n">
+        <v>0</v>
+      </c>
+      <c r="T213" t="n">
+        <v>0</v>
+      </c>
+      <c r="U213" t="n">
+        <v>0</v>
+      </c>
+      <c r="V213" s="2" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
         <is>
           <t>S 1452-2026</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
+      <c r="B214" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr">
+      <c r="C214" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D213" s="1" t="n">
+      <c r="D214" s="1" t="n">
         <v>46160</v>
       </c>
-      <c r="E213" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>GNOSJÖ</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr">
+      <c r="E214" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>GNOSJÖ</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
         <is>
           <t>Kyrkan</t>
         </is>
       </c>
-      <c r="I213" t="n">
+      <c r="I214" t="n">
         <v>43.3</v>
       </c>
-      <c r="J213" t="n">
-        <v>0</v>
-      </c>
-      <c r="K213" t="n">
-        <v>0</v>
-      </c>
-      <c r="L213" t="n">
-        <v>0</v>
-      </c>
-      <c r="M213" t="n">
-        <v>0</v>
-      </c>
-      <c r="N213" t="n">
-        <v>0</v>
-      </c>
-      <c r="O213" t="n">
-        <v>0</v>
-      </c>
-      <c r="P213" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
-      <c r="R213" t="n">
-        <v>0</v>
-      </c>
-      <c r="S213" t="n">
-        <v>0</v>
-      </c>
-      <c r="T213" t="n">
-        <v>0</v>
-      </c>
-      <c r="U213" t="n">
-        <v>0</v>
-      </c>
-      <c r="V213" s="2" t="inlineStr"/>
+      <c r="J214" t="n">
+        <v>0</v>
+      </c>
+      <c r="K214" t="n">
+        <v>0</v>
+      </c>
+      <c r="L214" t="n">
+        <v>0</v>
+      </c>
+      <c r="M214" t="n">
+        <v>0</v>
+      </c>
+      <c r="N214" t="n">
+        <v>0</v>
+      </c>
+      <c r="O214" t="n">
+        <v>0</v>
+      </c>
+      <c r="P214" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>0</v>
+      </c>
+      <c r="R214" t="n">
+        <v>0</v>
+      </c>
+      <c r="S214" t="n">
+        <v>0</v>
+      </c>
+      <c r="T214" t="n">
+        <v>0</v>
+      </c>
+      <c r="U214" t="n">
+        <v>0</v>
+      </c>
+      <c r="V214" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt GNOSJÖ.xlsx
+++ b/Översikt GNOSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44757</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46030</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44711</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 38355-2023</t>
+          <t>A 23612-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45161</v>
+        <v>44721</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>11.4</v>
+        <v>4.4</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -979,248 +979,248 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 23612-2022 artfynd.xlsx", "A 23612-2022")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 23612-2022 karta.png", "A 23612-2022")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 23612-2022 georefererad karta.tif", "A 23612-2022")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 23612-2022 FSC-klagomål.docx", "A 23612-2022")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 23612-2022 FSC-klagomål mail.docx", "A 23612-2022")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 23612-2022 tillsynsbegäran.docx", "A 23612-2022")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 23612-2022 tillsynsbegäran mail.docx", "A 23612-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 38355-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45161</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>GNOSJÖ</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
           <t>Mattlummer</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 38355-2023 artfynd.xlsx", "A 38355-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 38355-2023 karta.png", "A 38355-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 38355-2023 georefererad karta.tif", "A 38355-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 38355-2023 FSC-klagomål.docx", "A 38355-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 38355-2023 FSC-klagomål mail.docx", "A 38355-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 38355-2023 tillsynsbegäran.docx", "A 38355-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 38355-2023 tillsynsbegäran mail.docx", "A 38355-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>A 28312-2025</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D7" s="1" t="n">
         <v>45818</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>GNOSJÖ</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="E7" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>GNOSJÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>1</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R7" t="n">
         <v>1</v>
       </c>
-      <c r="S6" t="n">
+      <c r="S7" t="n">
         <v>1</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T7" t="n">
         <v>3</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 28312-2025 artfynd.xlsx", "A 28312-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 28312-2025 karta.png", "A 28312-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 28312-2025 georefererad karta.tif", "A 28312-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 28312-2025 FSC-klagomål.docx", "A 28312-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 28312-2025 FSC-klagomål mail.docx", "A 28312-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 28312-2025 tillsynsbegäran.docx", "A 28312-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 28312-2025 tillsynsbegäran mail.docx", "A 28312-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 23612-2022</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>44721</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>GNOSJÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 23612-2022 artfynd.xlsx", "A 23612-2022")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 23612-2022 karta.png", "A 23612-2022")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 23612-2022 georefererad karta.tif", "A 23612-2022")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 23612-2022 FSC-klagomål.docx", "A 23612-2022")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 23612-2022 FSC-klagomål mail.docx", "A 23612-2022")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 23612-2022 tillsynsbegäran.docx", "A 23612-2022")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 23612-2022 tillsynsbegäran mail.docx", "A 23612-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>44530</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>44837</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>44482</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>44474</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 50444-2022</t>
+          <t>A 3418-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44866</v>
+        <v>44585</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1545,8 +1545,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1589,7 +1594,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 3418-2022</t>
+          <t>A 50444-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1603,10 +1608,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44585</v>
+        <v>44866</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1618,13 +1623,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1684,7 +1684,7 @@
         <v>44468</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>44503</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>44494</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>44698</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>44470</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>44698</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>44467</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>44568</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>44804</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>44855</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 29707-2024</t>
+          <t>A 28372-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2407,14 +2407,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45485</v>
+        <v>44747</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>7.7</v>
+        <v>4.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2470,7 +2470,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 49758-2024</t>
+          <t>A 4298-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45597</v>
+        <v>44588</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 25837-2023</t>
+          <t>A 48480-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45090</v>
+        <v>44858</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2633,7 +2633,7 @@
         <v>44470</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 28372-2022</t>
+          <t>A 42280-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44747</v>
+        <v>45180</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.3</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2762,7 +2762,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 23625-2022</t>
+          <t>A 46657-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44721</v>
+        <v>44850</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>7.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 47856-2022</t>
+          <t>A 20948-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44855</v>
+        <v>45439</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.1</v>
+        <v>6.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2908,7 +2908,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 41323-2022</t>
+          <t>A 13352-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44826</v>
+        <v>45387</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2981,7 +2981,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 4298-2022</t>
+          <t>A 5089-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2995,10 +2995,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44588</v>
+        <v>45330</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 16243-2025</t>
+          <t>A 62053-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45749</v>
+        <v>44918</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3083,13 +3083,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3132,7 +3127,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 43758-2023</t>
+          <t>A 39668-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3146,10 +3141,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45187</v>
+        <v>45167</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3162,7 +3157,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3205,7 +3200,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 43784-2023</t>
+          <t>A 48188-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3219,10 +3214,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45187</v>
+        <v>44853</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3235,7 +3230,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3278,7 +3273,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 48480-2022</t>
+          <t>A 25837-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3292,10 +3287,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44858</v>
+        <v>45090</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3308,7 +3303,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3351,7 +3346,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 18314-2024</t>
+          <t>A 57730-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3365,10 +3360,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45422</v>
+        <v>45246</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3381,7 +3376,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3424,7 +3419,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 16303-2023</t>
+          <t>A 30961-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3438,10 +3433,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45028</v>
+        <v>45113</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3454,7 +3449,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.3</v>
+        <v>2.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3497,7 +3492,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 51901-2022</t>
+          <t>A 13610-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3511,10 +3506,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44872</v>
+        <v>45390</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3527,7 +3522,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>7.3</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3570,7 +3565,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 47454-2023</t>
+          <t>A 49758-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3584,10 +3579,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45202</v>
+        <v>45597</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3600,7 +3595,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3643,7 +3638,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 33575-2022</t>
+          <t>A 48229-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3657,10 +3652,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44789</v>
+        <v>44858</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3673,7 +3668,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3716,7 +3711,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 41918-2022</t>
+          <t>A 16243-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3730,10 +3725,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44830</v>
+        <v>45749</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3745,8 +3740,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3789,7 +3789,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 57730-2023</t>
+          <t>A 5082-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45246</v>
+        <v>45330</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3862,7 +3862,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 6763-2025</t>
+          <t>A 6781-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3876,10 +3876,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45700</v>
+        <v>44602</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3935,7 +3935,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 59026-2023</t>
+          <t>A 41347-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3949,10 +3949,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45252</v>
+        <v>45174</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.1</v>
+        <v>6.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4008,7 +4008,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 52813-2021</t>
+          <t>A 50440-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4022,10 +4022,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44467</v>
+        <v>44866</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 42280-2023</t>
+          <t>A 4992-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45180</v>
+        <v>44958</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 27258-2023</t>
+          <t>A 38510-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4168,10 +4168,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45096</v>
+        <v>45884</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4227,7 +4227,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 48188-2022</t>
+          <t>A 37198-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44853</v>
+        <v>45875</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4300,7 +4300,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 23254-2023</t>
+          <t>A 37864-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45075</v>
+        <v>45881</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4373,7 +4373,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 26746-2023</t>
+          <t>A 18337-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45093</v>
+        <v>46125</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>4.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4446,7 +4446,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 6415-2025</t>
+          <t>A 54833-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4460,10 +4460,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45699</v>
+        <v>45618</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4475,8 +4475,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4519,7 +4524,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8698-2025</t>
+          <t>A 6415-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4533,10 +4538,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45712</v>
+        <v>45699</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4549,7 +4554,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4592,7 +4597,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 53078-2021</t>
+          <t>A 30101-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4602,14 +4607,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44467</v>
+        <v>45489</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4622,7 +4627,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4665,7 +4670,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 64718-2023</t>
+          <t>A 40863-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4679,10 +4684,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45281</v>
+        <v>45897</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4695,7 +4700,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4755,7 +4760,7 @@
         <v>45896</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4811,7 +4816,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 40863-2025</t>
+          <t>A 21080-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4825,10 +4830,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45897</v>
+        <v>45777</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4841,7 +4846,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4884,7 +4889,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 46657-2022</t>
+          <t>A 61532-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4894,14 +4899,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44850</v>
+        <v>45265</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4913,8 +4918,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>7.9</v>
+        <v>1.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4957,7 +4967,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 3504-2023</t>
+          <t>A 42615-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4971,10 +4981,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44950</v>
+        <v>45905</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5030,7 +5040,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 11157-2024</t>
+          <t>A 27036-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5044,10 +5054,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45371</v>
+        <v>45095</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5060,7 +5070,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5103,7 +5113,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 11163-2024</t>
+          <t>A 33575-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5117,10 +5127,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45371</v>
+        <v>44789</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5133,7 +5143,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5176,7 +5186,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 24861-2025</t>
+          <t>A 36905-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5190,10 +5200,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45799</v>
+        <v>45538</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5206,7 +5216,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.6</v>
+        <v>2.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5249,7 +5259,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 27264-2023</t>
+          <t>A 43637-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5263,10 +5273,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45096</v>
+        <v>45911</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5279,7 +5289,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5322,7 +5332,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 21080-2025</t>
+          <t>A 43656-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5336,10 +5346,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45777</v>
+        <v>45912</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5352,7 +5362,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5395,7 +5405,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 15776-2023</t>
+          <t>A 44383-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5409,10 +5419,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45021</v>
+        <v>45916</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5425,7 +5435,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5468,7 +5478,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 5082-2024</t>
+          <t>A 44394-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5482,10 +5492,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45330</v>
+        <v>45916</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5498,7 +5508,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5541,7 +5551,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 41347-2023</t>
+          <t>A 8698-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5555,10 +5565,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45174</v>
+        <v>45712</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5571,7 +5581,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>6.2</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5614,7 +5624,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 30091-2024</t>
+          <t>A 21076-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5624,14 +5634,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45489</v>
+        <v>45777</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5644,7 +5654,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5687,7 +5697,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 42615-2025</t>
+          <t>A 11157-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5701,10 +5711,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45905</v>
+        <v>45371</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5717,7 +5727,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5760,7 +5770,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 50440-2022</t>
+          <t>A 11163-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5774,10 +5784,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44866</v>
+        <v>45371</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5790,7 +5800,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>8.699999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5833,7 +5843,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 43637-2025</t>
+          <t>A 31772-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5847,10 +5857,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45911</v>
+        <v>45118</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5863,7 +5873,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5906,7 +5916,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 43656-2025</t>
+          <t>A 30314-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5920,10 +5930,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45912</v>
+        <v>45490</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5936,7 +5946,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5979,7 +5989,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 5707-2022</t>
+          <t>A 64481-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5993,10 +6003,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44596</v>
+        <v>45280</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6009,7 +6019,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6052,7 +6062,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 22650-2024</t>
+          <t>A 32177-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6066,10 +6076,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45447</v>
+        <v>45511</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6082,7 +6092,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>7.9</v>
+        <v>0.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6125,7 +6135,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 44383-2025</t>
+          <t>A 37963-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6139,10 +6149,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45916</v>
+        <v>45544</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6155,7 +6165,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.3</v>
+        <v>5.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6198,7 +6208,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 44394-2025</t>
+          <t>A 60859-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6212,10 +6222,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45916</v>
+        <v>45644</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6228,7 +6238,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6271,7 +6281,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 26210-2024</t>
+          <t>A 3987-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6285,10 +6295,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45468</v>
+        <v>45322</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6301,7 +6311,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6344,7 +6354,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 25482-2025</t>
+          <t>A 50728-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6358,10 +6368,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45802</v>
+        <v>45946</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6374,7 +6384,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>8.300000000000001</v>
+        <v>15.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6417,7 +6427,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 15436-2024</t>
+          <t>A 42618-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6431,10 +6441,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45401</v>
+        <v>45905</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6447,7 +6457,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6490,7 +6500,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 60859-2024</t>
+          <t>A 55074-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6504,10 +6514,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45644</v>
+        <v>45237</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6520,7 +6530,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6563,7 +6573,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 56625-2022</t>
+          <t>A 5818-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6577,10 +6587,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44893</v>
+        <v>44963</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6636,7 +6646,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 43787-2023</t>
+          <t>A 62045-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6650,10 +6660,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45187</v>
+        <v>44918</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6666,7 +6676,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6709,7 +6719,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 43760-2023</t>
+          <t>A 40244-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6723,10 +6733,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45187</v>
+        <v>45554</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6782,7 +6792,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 55909-2022</t>
+          <t>A 41323-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6796,10 +6806,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44889</v>
+        <v>44826</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6812,7 +6822,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6855,7 +6865,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 43790-2023</t>
+          <t>A 4293-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6869,10 +6879,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45187</v>
+        <v>44588</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6885,7 +6895,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6928,7 +6938,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 35325-2023</t>
+          <t>A 55918-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6942,10 +6952,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45146</v>
+        <v>45973</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6958,7 +6968,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7001,7 +7011,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 30101-2024</t>
+          <t>A 56240-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7011,14 +7021,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45489</v>
+        <v>45974</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7031,7 +7041,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7074,7 +7084,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 10996-2024</t>
+          <t>A 56554-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7088,10 +7098,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45370</v>
+        <v>45975</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7104,7 +7114,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7147,7 +7157,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 40067-2023</t>
+          <t>A 27264-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7161,10 +7171,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45168</v>
+        <v>45096</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7177,7 +7187,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7220,7 +7230,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 50728-2025</t>
+          <t>A 57012-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7234,10 +7244,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45946</v>
+        <v>45978</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7250,7 +7260,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>15.2</v>
+        <v>0.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7293,7 +7303,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 73961-2021</t>
+          <t>A 53077-2021</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7307,10 +7317,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44553</v>
+        <v>44467</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7322,13 +7332,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>5.1</v>
+        <v>1.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7371,7 +7376,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 62053-2022</t>
+          <t>A 58780-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7385,10 +7390,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44918</v>
+        <v>45986</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7401,7 +7406,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7444,7 +7449,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 20078-2022</t>
+          <t>A 58356-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7458,10 +7463,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44698</v>
+        <v>44893</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7474,7 +7479,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7517,7 +7522,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 6781-2022</t>
+          <t>A 20078-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7531,10 +7536,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44602</v>
+        <v>44698</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7547,7 +7552,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7590,7 +7595,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 7316-2024</t>
+          <t>A 61411-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7604,10 +7609,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45345</v>
+        <v>46000</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7620,7 +7625,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7663,7 +7668,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 4293-2022</t>
+          <t>A 61792-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7677,10 +7682,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44588</v>
+        <v>46002</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7693,7 +7698,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2</v>
+        <v>10.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7736,7 +7741,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 36406-2022</t>
+          <t>A 61682-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7750,10 +7755,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44803</v>
+        <v>46002</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7766,7 +7771,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7809,7 +7814,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 27036-2023</t>
+          <t>A 61677-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7823,10 +7828,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45095</v>
+        <v>46002</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7839,7 +7844,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7882,7 +7887,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 9828-2025</t>
+          <t>A 35325-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7896,10 +7901,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45716</v>
+        <v>45146</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7912,7 +7917,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7955,7 +7960,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 43786-2023</t>
+          <t>A 73961-2021</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7969,10 +7974,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45187</v>
+        <v>44553</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -7984,8 +7989,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>0.6</v>
+        <v>5.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8028,7 +8038,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 50304-2024</t>
+          <t>A 27258-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8042,10 +8052,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45600</v>
+        <v>45096</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8058,7 +8068,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8101,7 +8111,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 8747-2024</t>
+          <t>A 29066-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8115,10 +8125,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45356</v>
+        <v>44750</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8131,7 +8141,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8174,7 +8184,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 6747-2025</t>
+          <t>A 23132-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8188,10 +8198,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45700</v>
+        <v>46161</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8204,7 +8214,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8247,7 +8257,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 56240-2025</t>
+          <t>A 63511-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8261,10 +8271,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45974</v>
+        <v>46013</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8277,7 +8287,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8320,7 +8330,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 55918-2025</t>
+          <t>A 63220-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8334,10 +8344,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45973</v>
+        <v>46010</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8350,7 +8360,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8393,7 +8403,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 6789-2025</t>
+          <t>A 3504-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8407,10 +8417,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45700</v>
+        <v>44950</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8423,7 +8433,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8466,7 +8476,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 56554-2025</t>
+          <t>A 9828-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8480,10 +8490,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45975</v>
+        <v>45716</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8496,7 +8506,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>7.2</v>
+        <v>0.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8539,7 +8549,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 59727-2024</t>
+          <t>A 36653-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8549,14 +8559,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45639</v>
+        <v>44804</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8569,7 +8579,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8612,7 +8622,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 57012-2025</t>
+          <t>A 1664-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8626,10 +8636,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45978</v>
+        <v>46034</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8642,7 +8652,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8685,7 +8695,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 4992-2023</t>
+          <t>A 23254-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8699,10 +8709,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44958</v>
+        <v>45075</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8715,7 +8725,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8758,7 +8768,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 58249-2021</t>
+          <t>A 64718-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8772,10 +8782,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44487</v>
+        <v>45281</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8788,7 +8798,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8831,7 +8841,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 30961-2023</t>
+          <t>A 52813-2021</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8845,10 +8855,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45113</v>
+        <v>44467</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8861,7 +8871,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8904,7 +8914,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 58780-2025</t>
+          <t>A 47454-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8918,10 +8928,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45986</v>
+        <v>45202</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8934,7 +8944,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -8977,7 +8987,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 19307-2023</t>
+          <t>A 34083-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -8991,10 +9001,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45049</v>
+        <v>45125</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9007,7 +9017,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9050,7 +9060,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 25487-2022</t>
+          <t>A 58779-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9064,10 +9074,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44732</v>
+        <v>45986</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9080,7 +9090,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>7.1</v>
+        <v>1.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9123,7 +9133,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 16244-2025</t>
+          <t>A 6785-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9137,10 +9147,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45749</v>
+        <v>45700</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9152,13 +9162,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9201,7 +9206,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 58970-2024</t>
+          <t>A 6793-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9215,10 +9220,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45636</v>
+        <v>45700</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9231,7 +9236,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9274,7 +9279,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 29066-2022</t>
+          <t>A 59727-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9288,10 +9293,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44750</v>
+        <v>45639</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9304,7 +9309,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9347,7 +9352,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 34083-2023</t>
+          <t>A 15434-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9361,10 +9366,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45125</v>
+        <v>45020</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9377,7 +9382,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9420,7 +9425,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 30669-2025</t>
+          <t>A 9641-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9434,10 +9439,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45831</v>
+        <v>46070</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9449,8 +9454,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9493,7 +9503,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 30654-2025</t>
+          <t>A 9624-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9507,10 +9517,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45831</v>
+        <v>46070</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9522,8 +9532,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9566,7 +9581,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 31235-2025</t>
+          <t>A 9627-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9580,10 +9595,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45832</v>
+        <v>46070</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9595,8 +9610,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9639,7 +9659,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 61411-2025</t>
+          <t>A 41918-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9653,10 +9673,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46000</v>
+        <v>44830</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9669,7 +9689,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9712,7 +9732,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 31228-2025</t>
+          <t>A 61531-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9722,14 +9742,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45832</v>
+        <v>45265</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9741,8 +9761,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9785,7 +9810,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 61677-2025</t>
+          <t>A 26746-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9799,10 +9824,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46002</v>
+        <v>45093</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9815,7 +9840,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9858,7 +9883,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 1664-2026</t>
+          <t>A 15776-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9872,10 +9897,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46034</v>
+        <v>45021</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9888,7 +9913,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9931,7 +9956,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 61682-2025</t>
+          <t>A 11667-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9945,10 +9970,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46002</v>
+        <v>46084</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -9961,7 +9986,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10004,7 +10029,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 61792-2025</t>
+          <t>A 51901-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10018,10 +10043,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46002</v>
+        <v>44872</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10034,7 +10059,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>10.6</v>
+        <v>7.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10077,7 +10102,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 48227-2022</t>
+          <t>A 13600-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10091,10 +10116,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44858</v>
+        <v>46097</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10106,8 +10131,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10150,7 +10180,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 22846-2024</t>
+          <t>A 26210-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10164,10 +10194,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45448</v>
+        <v>45468</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10180,7 +10210,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10223,7 +10253,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 63220-2025</t>
+          <t>A 16244-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10237,10 +10267,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46010</v>
+        <v>45749</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10252,8 +10282,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10296,7 +10331,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 63511-2025</t>
+          <t>A 41357-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10310,10 +10345,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46013</v>
+        <v>45174</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10326,7 +10361,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10369,7 +10404,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 61531-2023</t>
+          <t>A 6662-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10379,14 +10414,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45265</v>
+        <v>45341</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10398,13 +10433,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10447,7 +10477,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 38885-2026</t>
+          <t>A 17402-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10461,10 +10491,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46286</v>
+        <v>46120</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10477,7 +10507,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10520,7 +10550,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 58779-2025</t>
+          <t>A 8747-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10534,10 +10564,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45986</v>
+        <v>45356</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10550,7 +10580,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10593,7 +10623,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 39668-2023</t>
+          <t>A 27954-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10607,10 +10637,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45167</v>
+        <v>46193</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10623,7 +10653,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.3</v>
+        <v>2.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10666,7 +10696,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 38886-2026</t>
+          <t>A 27951-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10680,10 +10710,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46286</v>
+        <v>46193</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10695,8 +10725,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10739,7 +10774,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 9641-2026</t>
+          <t>A 27953-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10753,10 +10788,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46070</v>
+        <v>46193</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10770,11 +10805,11 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.6</v>
+        <v>5.7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10817,7 +10852,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 9624-2026</t>
+          <t>A 27729-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10827,14 +10862,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46070</v>
+        <v>46191</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10846,13 +10881,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>1.3</v>
+        <v>5.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10895,7 +10925,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 9627-2026</t>
+          <t>A 28026-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10909,10 +10939,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46070</v>
+        <v>46195</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10924,13 +10954,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -10973,7 +10998,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 32903-2026</t>
+          <t>A 18473-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10987,10 +11012,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46244</v>
+        <v>46127</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11003,7 +11028,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11046,7 +11071,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 32913-2026</t>
+          <t>A 28018-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11060,10 +11085,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46244</v>
+        <v>46195</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11076,7 +11101,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11119,7 +11144,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 23138-2026</t>
+          <t>A 19171-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11133,10 +11158,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46161</v>
+        <v>46132</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11149,7 +11174,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.3</v>
+        <v>22.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11192,7 +11217,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 5818-2023</t>
+          <t>A 56393-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11206,10 +11231,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44963</v>
+        <v>45243</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11222,7 +11247,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11265,7 +11290,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 39094-2026</t>
+          <t>A 28058-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11279,10 +11304,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46283</v>
+        <v>46195</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11294,13 +11319,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>6</v>
+        <v>1.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11343,7 +11363,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 11667-2026</t>
+          <t>A 32826-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11357,10 +11377,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46084</v>
+        <v>45124</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11373,7 +11393,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11416,7 +11436,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 39453-2026</t>
+          <t>A 1450-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11430,10 +11450,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46288</v>
+        <v>45303</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11446,7 +11466,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11489,7 +11509,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 5030-2022</t>
+          <t>A 53078-2021</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11503,10 +11523,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44593</v>
+        <v>44467</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11519,7 +11539,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11562,7 +11582,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 40244-2024</t>
+          <t>A 36406-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11576,10 +11596,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45554</v>
+        <v>44803</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11592,7 +11612,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11635,7 +11655,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 64481-2023</t>
+          <t>A 30160-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11649,10 +11669,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45280</v>
+        <v>46206</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11665,7 +11685,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>5.5</v>
+        <v>1.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11708,7 +11728,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 27675-2025</t>
+          <t>A 10996-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11722,10 +11742,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45813</v>
+        <v>45370</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11738,7 +11758,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>3.1</v>
+        <v>5.9</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11781,7 +11801,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 13600-2026</t>
+          <t>A 22846-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11795,10 +11815,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46097</v>
+        <v>45448</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11810,13 +11830,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11859,7 +11874,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 36508-2022</t>
+          <t>A 30091-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11869,14 +11884,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44804</v>
+        <v>45489</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11889,7 +11904,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11932,7 +11947,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 55074-2023</t>
+          <t>A 48227-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11946,10 +11961,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45237</v>
+        <v>44858</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11962,7 +11977,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12005,7 +12020,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 58356-2022</t>
+          <t>A 43758-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12019,10 +12034,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44893</v>
+        <v>45187</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12035,7 +12050,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12078,7 +12093,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 14355-2023</t>
+          <t>A 6747-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12092,10 +12107,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45012</v>
+        <v>45700</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12108,7 +12123,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12151,7 +12166,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 13913-2024</t>
+          <t>A 50304-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12165,10 +12180,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45391</v>
+        <v>45600</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12181,7 +12196,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12224,7 +12239,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 46254-2024</t>
+          <t>A 43786-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12238,10 +12253,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45581</v>
+        <v>45187</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12254,7 +12269,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12297,7 +12312,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 13352-2024</t>
+          <t>A 43787-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12311,10 +12326,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45387</v>
+        <v>45187</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12327,7 +12342,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12370,7 +12385,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 13610-2024</t>
+          <t>A 46254-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12384,10 +12399,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45390</v>
+        <v>45581</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12400,7 +12415,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12443,7 +12458,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 56393-2023</t>
+          <t>A 47856-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12457,10 +12472,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45243</v>
+        <v>44855</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12473,7 +12488,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>4.1</v>
+        <v>0.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12516,7 +12531,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 36653-2022</t>
+          <t>A 19307-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12526,14 +12541,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44804</v>
+        <v>45049</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12546,7 +12561,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12589,7 +12604,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 17402-2026</t>
+          <t>A 56625-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12603,10 +12618,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46120</v>
+        <v>44893</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12619,7 +12634,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12662,7 +12677,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 48229-2022</t>
+          <t>A 43790-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12676,10 +12691,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44858</v>
+        <v>45187</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12692,7 +12707,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12735,7 +12750,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 18473-2026</t>
+          <t>A 59026-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12749,10 +12764,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46127</v>
+        <v>45252</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12765,7 +12780,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12808,7 +12823,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 5089-2024</t>
+          <t>A 58970-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12822,10 +12837,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45330</v>
+        <v>45636</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12838,7 +12853,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12881,7 +12896,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 19171-2026</t>
+          <t>A 23259-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12895,10 +12910,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46132</v>
+        <v>45075</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12911,7 +12926,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>22.2</v>
+        <v>2.8</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -12954,7 +12969,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 58247-2021</t>
+          <t>A 5030-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -12968,10 +12983,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44487</v>
+        <v>44593</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -12984,7 +12999,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>8.9</v>
+        <v>2.3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13027,7 +13042,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 31772-2023</t>
+          <t>A 6789-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13041,10 +13056,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45118</v>
+        <v>45700</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13057,7 +13072,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13100,7 +13115,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 6662-2024</t>
+          <t>A 58247-2021</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13114,10 +13129,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45341</v>
+        <v>44487</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13130,7 +13145,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.2</v>
+        <v>8.9</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13173,7 +13188,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 53077-2021</t>
+          <t>A 58249-2021</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13187,10 +13202,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44467</v>
+        <v>44487</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13203,7 +13218,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13246,7 +13261,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 37198-2025</t>
+          <t>A 25487-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13260,10 +13275,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45875</v>
+        <v>44732</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13276,7 +13291,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>3.7</v>
+        <v>7.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13319,7 +13334,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 18337-2026</t>
+          <t>A 6763-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13333,10 +13348,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46125</v>
+        <v>45700</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13349,7 +13364,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13392,7 +13407,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 54833-2024</t>
+          <t>A 13913-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13406,10 +13421,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45618</v>
+        <v>45391</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13421,13 +13436,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13470,7 +13480,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 1450-2024</t>
+          <t>A 31983-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13484,10 +13494,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45303</v>
+        <v>46232</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13500,7 +13510,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13543,7 +13553,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 38510-2025</t>
+          <t>A 43760-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13557,10 +13567,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45884</v>
+        <v>45187</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13573,7 +13583,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13616,7 +13626,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 6785-2025</t>
+          <t>A 43784-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13630,10 +13640,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45700</v>
+        <v>45187</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13646,7 +13656,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13689,7 +13699,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 6793-2025</t>
+          <t>A 55909-2022</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13703,10 +13713,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45700</v>
+        <v>44889</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13719,7 +13729,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13762,7 +13772,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 21076-2025</t>
+          <t>A 14355-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13776,10 +13786,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45777</v>
+        <v>45012</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13792,7 +13802,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -13835,7 +13845,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 32826-2023</t>
+          <t>A 37630-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13849,10 +13859,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45124</v>
+        <v>46276</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13864,8 +13874,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I180" t="n">
-        <v>0.4</v>
+        <v>13.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13908,7 +13923,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 37963-2024</t>
+          <t>A 40067-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13922,10 +13937,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45544</v>
+        <v>45168</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -13938,7 +13953,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>5.3</v>
+        <v>0.6</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -13981,7 +13996,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 36905-2024</t>
+          <t>A 22650-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -13995,10 +14010,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45538</v>
+        <v>45447</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14011,7 +14026,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.9</v>
+        <v>7.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14054,7 +14069,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 3987-2024</t>
+          <t>A 27952-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14068,10 +14083,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45322</v>
+        <v>46193</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14083,8 +14098,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I183" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14127,7 +14147,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 61532-2023</t>
+          <t>A 23625-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14137,14 +14157,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45265</v>
+        <v>44721</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14156,13 +14176,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14205,7 +14220,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 32177-2024</t>
+          <t>A 16303-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14219,10 +14234,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45511</v>
+        <v>45028</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14235,7 +14250,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.9</v>
+        <v>6.3</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14278,7 +14293,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 41357-2023</t>
+          <t>A 5707-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14292,10 +14307,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45174</v>
+        <v>44596</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14308,7 +14323,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14351,7 +14366,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 42618-2025</t>
+          <t>A 8119-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14365,10 +14380,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45905</v>
+        <v>45707</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14381,7 +14396,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14424,7 +14439,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 37864-2025</t>
+          <t>A 39094-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14438,10 +14453,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45881</v>
+        <v>46283</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14453,8 +14468,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14497,7 +14517,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 62045-2022</t>
+          <t>A 38885-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14511,10 +14531,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44918</v>
+        <v>46286</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14527,7 +14547,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14570,7 +14590,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 15434-2023</t>
+          <t>A 23138-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14584,10 +14604,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45020</v>
+        <v>46161</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14600,7 +14620,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14643,7 +14663,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 23259-2023</t>
+          <t>A 270-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14657,10 +14677,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45075</v>
+        <v>44928</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14673,7 +14693,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14716,7 +14736,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 30314-2024</t>
+          <t>A 38886-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14730,10 +14750,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45490</v>
+        <v>46286</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14746,7 +14766,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -14789,7 +14809,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 20948-2024</t>
+          <t>A 32913-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14803,10 +14823,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45439</v>
+        <v>46244</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14819,7 +14839,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>6.4</v>
+        <v>2.7</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -14862,7 +14882,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 8119-2025</t>
+          <t>A 32903-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14876,10 +14896,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45707</v>
+        <v>46244</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14892,7 +14912,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -14935,7 +14955,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 270-2023</t>
+          <t>A 18314-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -14949,10 +14969,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44928</v>
+        <v>45422</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -14965,7 +14985,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15008,7 +15028,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 23132-2026</t>
+          <t>A 29707-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15018,14 +15038,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46161</v>
+        <v>45485</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15038,7 +15058,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>3.3</v>
+        <v>7.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15081,7 +15101,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 27729-2026</t>
+          <t>A 39453-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15091,14 +15111,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46191</v>
+        <v>46288</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15111,7 +15131,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15154,7 +15174,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 28018-2026</t>
+          <t>A 24861-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15168,10 +15188,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46195</v>
+        <v>45799</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15184,7 +15204,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15227,7 +15247,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 27954-2026</t>
+          <t>A 27498-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15241,10 +15261,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46193</v>
+        <v>46185</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15256,8 +15276,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I199" t="n">
-        <v>2.8</v>
+        <v>38</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15300,7 +15325,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 27951-2026</t>
+          <t>A 25482-2025</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15314,10 +15339,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46193</v>
+        <v>45802</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15329,13 +15354,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>1.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15378,7 +15398,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 28058-2026</t>
+          <t>A 15436-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15392,10 +15412,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46195</v>
+        <v>45401</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15408,7 +15428,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15451,7 +15471,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 27953-2026</t>
+          <t>A 7316-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15465,10 +15485,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46193</v>
+        <v>45345</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15480,13 +15500,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I202" t="n">
-        <v>5.7</v>
+        <v>1.1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15529,7 +15544,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 28026-2026</t>
+          <t>A 30654-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15543,10 +15558,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46195</v>
+        <v>45831</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15559,7 +15574,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15602,7 +15617,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 30160-2026</t>
+          <t>A 30669-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15616,10 +15631,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46206</v>
+        <v>45831</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15632,7 +15647,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15675,7 +15690,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 27498-2026</t>
+          <t>A 31228-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15689,10 +15704,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46185</v>
+        <v>45832</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15704,13 +15719,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>38</v>
+        <v>0.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -15753,7 +15763,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 31983-2026</t>
+          <t>A 31235-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -15767,10 +15777,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46232</v>
+        <v>45832</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15783,7 +15793,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -15826,7 +15836,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 37630-2026</t>
+          <t>A 27675-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15840,10 +15850,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46276</v>
+        <v>45813</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15855,13 +15865,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I207" t="n">
-        <v>13.6</v>
+        <v>3.1</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -15904,7 +15909,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 27952-2026</t>
+          <t>A 36508-2022</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -15918,10 +15923,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46193</v>
+        <v>44804</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15933,13 +15938,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I208" t="n">
-        <v>8.5</v>
+        <v>2.7</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -15999,7 +15999,7 @@
         <v>44166</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
         <v>44712</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>44711</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>45763</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>45798</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>46160</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>

--- a/Översikt GNOSJÖ.xlsx
+++ b/Översikt GNOSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44757</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46030</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44711</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 23612-2022</t>
+          <t>A 28312-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -919,14 +919,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44721</v>
+        <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -939,23 +939,23 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
@@ -963,51 +963,51 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 23612-2022 artfynd.xlsx", "A 23612-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 28312-2025 artfynd.xlsx", "A 28312-2025")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 23612-2022 karta.png", "A 23612-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 28312-2025 karta.png", "A 28312-2025")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 23612-2022 georefererad karta.tif", "A 23612-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 28312-2025 georefererad karta.tif", "A 28312-2025")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 23612-2022 FSC-klagomål.docx", "A 23612-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 28312-2025 FSC-klagomål.docx", "A 28312-2025")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 23612-2022 FSC-klagomål mail.docx", "A 23612-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 28312-2025 FSC-klagomål mail.docx", "A 28312-2025")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 23612-2022 tillsynsbegäran.docx", "A 23612-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 28312-2025 tillsynsbegäran.docx", "A 28312-2025")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 23612-2022 tillsynsbegäran mail.docx", "A 23612-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 28312-2025 tillsynsbegäran mail.docx", "A 28312-2025")</f>
         <v/>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
         <v>45161</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 28312-2025</t>
+          <t>A 23612-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45818</v>
+        <v>44721</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1173,51 +1173,51 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 28312-2025 artfynd.xlsx", "A 28312-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 23612-2022 artfynd.xlsx", "A 23612-2022")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 28312-2025 karta.png", "A 28312-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 23612-2022 karta.png", "A 23612-2022")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 28312-2025 georefererad karta.tif", "A 28312-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 23612-2022 georefererad karta.tif", "A 23612-2022")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 28312-2025 FSC-klagomål.docx", "A 28312-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 23612-2022 FSC-klagomål.docx", "A 23612-2022")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 28312-2025 FSC-klagomål mail.docx", "A 28312-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 23612-2022 FSC-klagomål mail.docx", "A 23612-2022")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 28312-2025 tillsynsbegäran.docx", "A 28312-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 23612-2022 tillsynsbegäran.docx", "A 23612-2022")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 28312-2025 tillsynsbegäran mail.docx", "A 28312-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 23612-2022 tillsynsbegäran mail.docx", "A 23612-2022")</f>
         <v/>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
         <v>44530</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>44837</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>44482</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>44474</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 3418-2022</t>
+          <t>A 50444-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44585</v>
+        <v>44866</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1545,13 +1545,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1594,7 +1589,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 50444-2022</t>
+          <t>A 3418-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1608,10 +1603,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44866</v>
+        <v>44585</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1623,8 +1618,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1684,7 +1684,7 @@
         <v>44468</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>44503</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>44494</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>44698</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>44470</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>44698</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>44467</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>44568</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>44804</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>44855</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>44747</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>44588</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>44858</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>44470</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 42280-2023</t>
+          <t>A 16243-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45180</v>
+        <v>45749</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2718,8 +2718,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2762,7 +2767,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 46657-2022</t>
+          <t>A 47454-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2776,10 +2781,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44850</v>
+        <v>45202</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2792,7 +2797,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>7.9</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2835,7 +2840,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 20948-2024</t>
+          <t>A 43758-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2849,10 +2854,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45439</v>
+        <v>45187</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2865,7 +2870,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>6.4</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2908,7 +2913,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 13352-2024</t>
+          <t>A 43784-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2922,10 +2927,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45387</v>
+        <v>45187</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2938,7 +2943,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2981,7 +2986,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 5089-2024</t>
+          <t>A 33575-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2995,10 +3000,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45330</v>
+        <v>44789</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3011,7 +3016,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3054,7 +3059,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 62053-2022</t>
+          <t>A 59026-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3068,10 +3073,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44918</v>
+        <v>45252</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3084,7 +3089,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3127,7 +3132,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 39668-2023</t>
+          <t>A 23254-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3141,10 +3146,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45167</v>
+        <v>45075</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3157,7 +3162,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3200,7 +3205,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 48188-2022</t>
+          <t>A 53078-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3214,10 +3219,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44853</v>
+        <v>44467</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3230,7 +3235,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3273,7 +3278,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 25837-2023</t>
+          <t>A 64718-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3287,10 +3292,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45090</v>
+        <v>45281</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3303,7 +3308,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3346,7 +3351,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 57730-2023</t>
+          <t>A 63511-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3360,10 +3365,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45246</v>
+        <v>46013</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3376,7 +3381,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.5</v>
+        <v>4.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3419,7 +3424,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 30961-2023</t>
+          <t>A 46657-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3433,10 +3438,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45113</v>
+        <v>44850</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3449,7 +3454,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.7</v>
+        <v>7.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3492,7 +3497,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 13610-2024</t>
+          <t>A 3504-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3506,10 +3511,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45390</v>
+        <v>44950</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3522,7 +3527,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3565,7 +3570,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 49758-2024</t>
+          <t>A 27264-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3579,10 +3584,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45597</v>
+        <v>45096</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3595,7 +3600,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3638,7 +3643,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 48229-2022</t>
+          <t>A 15776-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3652,10 +3657,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44858</v>
+        <v>45021</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3668,7 +3673,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3711,7 +3716,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 16243-2025</t>
+          <t>A 5082-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3725,10 +3730,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45749</v>
+        <v>45330</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3740,13 +3745,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3789,7 +3789,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 5082-2024</t>
+          <t>A 41347-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45330</v>
+        <v>45174</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.3</v>
+        <v>6.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3862,7 +3862,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 6781-2022</t>
+          <t>A 30091-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3872,14 +3872,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44602</v>
+        <v>45489</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3935,7 +3935,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 41347-2023</t>
+          <t>A 1664-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3949,10 +3949,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45174</v>
+        <v>46034</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>6.2</v>
+        <v>1.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
         <v>44866</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 4992-2023</t>
+          <t>A 5707-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44958</v>
+        <v>44596</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 38510-2025</t>
+          <t>A 6415-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4168,10 +4168,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45884</v>
+        <v>45699</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4227,7 +4227,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 37198-2025</t>
+          <t>A 8698-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45875</v>
+        <v>45712</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4300,7 +4300,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 37864-2025</t>
+          <t>A 40552-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45881</v>
+        <v>45896</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4373,7 +4373,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 18337-2026</t>
+          <t>A 24861-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46125</v>
+        <v>45799</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4446,7 +4446,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 54833-2024</t>
+          <t>A 40863-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4460,10 +4460,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45618</v>
+        <v>45897</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4475,13 +4475,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4524,7 +4519,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 6415-2025</t>
+          <t>A 21080-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4538,10 +4533,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45699</v>
+        <v>45777</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4554,7 +4549,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4597,7 +4592,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 30101-2024</t>
+          <t>A 42615-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4607,14 +4602,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45489</v>
+        <v>45905</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4627,7 +4622,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4670,7 +4665,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 40863-2025</t>
+          <t>A 56625-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4684,10 +4679,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45897</v>
+        <v>44893</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4700,7 +4695,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4743,7 +4738,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 40552-2025</t>
+          <t>A 55909-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4757,10 +4752,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45896</v>
+        <v>44889</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4773,7 +4768,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4816,7 +4811,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 21080-2025</t>
+          <t>A 43637-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4830,10 +4825,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45777</v>
+        <v>45911</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4846,7 +4841,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4889,7 +4884,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 61532-2023</t>
+          <t>A 43656-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4899,14 +4894,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45265</v>
+        <v>45912</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4918,13 +4913,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4967,7 +4957,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 42615-2025</t>
+          <t>A 44383-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4981,10 +4971,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45905</v>
+        <v>45916</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4997,7 +4987,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5040,7 +5030,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 27036-2023</t>
+          <t>A 44394-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5054,10 +5044,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45095</v>
+        <v>45916</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5070,7 +5060,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5113,7 +5103,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 33575-2022</t>
+          <t>A 58779-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5127,10 +5117,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44789</v>
+        <v>45986</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5143,7 +5133,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5186,7 +5176,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 36905-2024</t>
+          <t>A 9641-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5200,10 +5190,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45538</v>
+        <v>46070</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5215,8 +5205,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5259,7 +5254,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 43637-2025</t>
+          <t>A 9624-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5273,10 +5268,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45911</v>
+        <v>46070</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5288,8 +5283,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5332,7 +5332,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 43656-2025</t>
+          <t>A 9627-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45912</v>
+        <v>46070</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5361,8 +5361,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5405,7 +5410,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 44383-2025</t>
+          <t>A 30101-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5415,14 +5420,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45916</v>
+        <v>45489</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5435,7 +5440,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5478,7 +5483,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 44394-2025</t>
+          <t>A 25482-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5492,10 +5497,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45916</v>
+        <v>45802</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5508,7 +5513,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5551,7 +5556,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 8698-2025</t>
+          <t>A 15436-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5565,10 +5570,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45712</v>
+        <v>45401</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5581,7 +5586,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5624,7 +5629,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 21076-2025</t>
+          <t>A 11667-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5638,10 +5643,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45777</v>
+        <v>46084</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5654,7 +5659,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5697,7 +5702,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 11157-2024</t>
+          <t>A 62053-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5711,10 +5716,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45371</v>
+        <v>44918</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5727,7 +5732,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5770,7 +5775,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 11163-2024</t>
+          <t>A 4293-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5784,10 +5789,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45371</v>
+        <v>44588</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5800,7 +5805,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5843,7 +5848,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 31772-2023</t>
+          <t>A 13600-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5857,10 +5862,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45118</v>
+        <v>46097</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5872,8 +5877,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5916,7 +5926,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 30314-2024</t>
+          <t>A 50728-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5930,10 +5940,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45490</v>
+        <v>45946</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5946,7 +5956,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>15.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5989,7 +5999,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 64481-2023</t>
+          <t>A 50304-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6003,10 +6013,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45280</v>
+        <v>45600</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6019,7 +6029,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5.5</v>
+        <v>1.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6062,7 +6072,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 32177-2024</t>
+          <t>A 8747-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6076,10 +6086,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45511</v>
+        <v>45356</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6092,7 +6102,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6135,7 +6145,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 37963-2024</t>
+          <t>A 17402-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6149,10 +6159,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45544</v>
+        <v>46120</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6165,7 +6175,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>5.3</v>
+        <v>2.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6208,7 +6218,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 60859-2024</t>
+          <t>A 18473-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6222,10 +6232,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45644</v>
+        <v>46127</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6238,7 +6248,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6281,7 +6291,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 3987-2024</t>
+          <t>A 4992-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6295,10 +6305,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45322</v>
+        <v>44958</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6311,7 +6321,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6354,7 +6364,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 50728-2025</t>
+          <t>A 58249-2021</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6368,10 +6378,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45946</v>
+        <v>44487</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6384,7 +6394,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>15.2</v>
+        <v>3.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6427,7 +6437,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 42618-2025</t>
+          <t>A 56240-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6441,10 +6451,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45905</v>
+        <v>45974</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6457,7 +6467,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6500,7 +6510,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 55074-2023</t>
+          <t>A 55918-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6514,10 +6524,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45237</v>
+        <v>45973</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6530,7 +6540,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6573,7 +6583,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 5818-2023</t>
+          <t>A 56554-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6587,10 +6597,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44963</v>
+        <v>45975</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6603,7 +6613,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>7.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6646,7 +6656,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 62045-2022</t>
+          <t>A 19307-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6660,10 +6670,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44918</v>
+        <v>45049</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6676,7 +6686,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6719,7 +6729,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 40244-2024</t>
+          <t>A 19171-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6733,10 +6743,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45554</v>
+        <v>46132</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6749,7 +6759,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.9</v>
+        <v>22.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6792,7 +6802,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 41323-2022</t>
+          <t>A 57012-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6806,10 +6816,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44826</v>
+        <v>45978</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6822,7 +6832,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6865,7 +6875,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 4293-2022</t>
+          <t>A 25487-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6879,10 +6889,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44588</v>
+        <v>44732</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6895,7 +6905,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>7.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6938,7 +6948,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 55918-2025</t>
+          <t>A 58970-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6952,10 +6962,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45973</v>
+        <v>45636</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6968,7 +6978,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7011,7 +7021,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 56240-2025</t>
+          <t>A 29066-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7025,10 +7035,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45974</v>
+        <v>44750</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7041,7 +7051,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7084,7 +7094,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 56554-2025</t>
+          <t>A 7316-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7098,10 +7108,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45975</v>
+        <v>45345</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7114,7 +7124,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>7.2</v>
+        <v>1.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7157,7 +7167,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 27264-2023</t>
+          <t>A 34083-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7171,10 +7181,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45096</v>
+        <v>45125</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7187,7 +7197,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7230,7 +7240,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 57012-2025</t>
+          <t>A 58780-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7244,10 +7254,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45978</v>
+        <v>45986</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7260,7 +7270,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7303,7 +7313,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 53077-2021</t>
+          <t>A 18337-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7317,10 +7327,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44467</v>
+        <v>46125</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7333,7 +7343,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7376,7 +7386,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 58780-2025</t>
+          <t>A 54833-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7390,10 +7400,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45986</v>
+        <v>45618</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7405,8 +7415,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7449,7 +7464,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 58356-2022</t>
+          <t>A 49758-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7463,10 +7478,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44893</v>
+        <v>45597</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7522,7 +7537,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 20078-2022</t>
+          <t>A 25837-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7536,10 +7551,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44698</v>
+        <v>45090</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7552,7 +7567,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7595,7 +7610,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 61411-2025</t>
+          <t>A 23625-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7609,10 +7624,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46000</v>
+        <v>44721</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7625,7 +7640,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7668,7 +7683,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 61792-2025</t>
+          <t>A 21076-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7682,10 +7697,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46002</v>
+        <v>45777</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7698,7 +7713,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>10.6</v>
+        <v>2.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7741,7 +7756,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 61682-2025</t>
+          <t>A 61411-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7755,10 +7770,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46002</v>
+        <v>46000</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7771,7 +7786,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7814,7 +7829,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 61677-2025</t>
+          <t>A 47856-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7828,10 +7843,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46002</v>
+        <v>44855</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7844,7 +7859,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7887,7 +7902,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 35325-2023</t>
+          <t>A 41323-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7901,10 +7916,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45146</v>
+        <v>44826</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7917,7 +7932,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7960,7 +7975,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 73961-2021</t>
+          <t>A 61677-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7974,10 +7989,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44553</v>
+        <v>46002</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -7989,13 +8004,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>5.1</v>
+        <v>0.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8038,7 +8048,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 27258-2023</t>
+          <t>A 61682-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8052,10 +8062,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45096</v>
+        <v>46002</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8068,7 +8078,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8111,7 +8121,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 29066-2022</t>
+          <t>A 61792-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8125,10 +8135,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44750</v>
+        <v>46002</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8141,7 +8151,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>4.8</v>
+        <v>10.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8184,7 +8194,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 23132-2026</t>
+          <t>A 37963-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8198,10 +8208,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46161</v>
+        <v>45544</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8214,7 +8224,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8257,7 +8267,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 63511-2025</t>
+          <t>A 16303-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8271,10 +8281,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46013</v>
+        <v>45028</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8287,7 +8297,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4.8</v>
+        <v>6.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8347,7 +8357,7 @@
         <v>46010</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8403,7 +8413,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 3504-2023</t>
+          <t>A 36905-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8417,10 +8427,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44950</v>
+        <v>45538</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8433,7 +8443,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8476,7 +8486,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 9828-2025</t>
+          <t>A 3987-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8490,10 +8500,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45716</v>
+        <v>45322</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8506,7 +8516,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8549,7 +8559,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 36653-2022</t>
+          <t>A 51901-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8559,14 +8569,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44804</v>
+        <v>44872</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8579,7 +8589,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.1</v>
+        <v>7.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8622,7 +8632,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 1664-2026</t>
+          <t>A 61532-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8632,14 +8642,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46034</v>
+        <v>45265</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8649,6 +8659,11 @@
       <c r="G109" t="inlineStr">
         <is>
           <t>GNOSJÖ</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I109" t="n">
@@ -8695,7 +8710,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 23254-2023</t>
+          <t>A 42618-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8709,10 +8724,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45075</v>
+        <v>45905</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8725,7 +8740,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8768,7 +8783,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 64718-2023</t>
+          <t>A 37864-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8782,10 +8797,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45281</v>
+        <v>45881</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8798,7 +8813,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8841,7 +8856,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 52813-2021</t>
+          <t>A 41918-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8855,10 +8870,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44467</v>
+        <v>44830</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8871,7 +8886,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8914,7 +8929,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 47454-2023</t>
+          <t>A 57730-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8928,10 +8943,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45202</v>
+        <v>45246</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8944,7 +8959,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -8987,7 +9002,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 34083-2023</t>
+          <t>A 6763-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9001,10 +9016,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45125</v>
+        <v>45700</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9017,7 +9032,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9060,7 +9075,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 58779-2025</t>
+          <t>A 52813-2021</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9074,10 +9089,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45986</v>
+        <v>44467</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9090,7 +9105,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9133,7 +9148,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 6785-2025</t>
+          <t>A 42280-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9147,10 +9162,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45700</v>
+        <v>45180</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9163,7 +9178,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9206,7 +9221,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 6793-2025</t>
+          <t>A 27258-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9220,10 +9235,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45700</v>
+        <v>45096</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9236,7 +9251,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9279,7 +9294,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 59727-2024</t>
+          <t>A 30669-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9293,10 +9308,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45639</v>
+        <v>45831</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9309,7 +9324,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9352,7 +9367,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 15434-2023</t>
+          <t>A 30654-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9366,10 +9381,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45020</v>
+        <v>45831</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9382,7 +9397,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9425,7 +9440,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 9641-2026</t>
+          <t>A 31235-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9439,10 +9454,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46070</v>
+        <v>45832</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9454,13 +9469,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9503,7 +9513,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 9624-2026</t>
+          <t>A 31228-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9517,10 +9527,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46070</v>
+        <v>45832</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9532,13 +9542,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9581,7 +9586,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 9627-2026</t>
+          <t>A 48188-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9595,10 +9600,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46070</v>
+        <v>44853</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9610,13 +9615,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9659,7 +9659,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 41918-2022</t>
+          <t>A 26746-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44830</v>
+        <v>45093</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 61531-2023</t>
+          <t>A 23132-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9742,14 +9742,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45265</v>
+        <v>46161</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9761,13 +9761,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9810,7 +9805,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 26746-2023</t>
+          <t>A 27675-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9824,10 +9819,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45093</v>
+        <v>45813</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9840,7 +9835,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9883,7 +9878,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 15776-2023</t>
+          <t>A 11157-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9897,10 +9892,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45021</v>
+        <v>45371</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9913,7 +9908,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9956,7 +9951,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 11667-2026</t>
+          <t>A 11163-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9970,10 +9965,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46084</v>
+        <v>45371</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -9986,7 +9981,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10029,7 +10024,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 51901-2022</t>
+          <t>A 36508-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10043,10 +10038,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44872</v>
+        <v>44804</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10059,7 +10054,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>7.3</v>
+        <v>2.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10102,7 +10097,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 13600-2026</t>
+          <t>A 22650-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10116,10 +10111,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46097</v>
+        <v>45447</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10131,13 +10126,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>2.9</v>
+        <v>7.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10197,7 +10187,7 @@
         <v>45468</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10253,7 +10243,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 16244-2025</t>
+          <t>A 60859-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10267,10 +10257,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45749</v>
+        <v>45644</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10282,13 +10272,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10331,7 +10316,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 41357-2023</t>
+          <t>A 43787-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10345,10 +10330,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45174</v>
+        <v>45187</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10361,7 +10346,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10404,7 +10389,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 6662-2024</t>
+          <t>A 43760-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10418,10 +10403,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45341</v>
+        <v>45187</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10434,7 +10419,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10477,7 +10462,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 17402-2026</t>
+          <t>A 43790-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10491,10 +10476,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46120</v>
+        <v>45187</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10507,7 +10492,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10550,7 +10535,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 8747-2024</t>
+          <t>A 35325-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10564,10 +10549,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45356</v>
+        <v>45146</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10580,7 +10565,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10623,7 +10608,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 27954-2026</t>
+          <t>A 27729-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10633,14 +10618,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46193</v>
+        <v>46191</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10653,7 +10638,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10696,7 +10681,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 27951-2026</t>
+          <t>A 28018-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10710,10 +10695,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46193</v>
+        <v>46195</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10725,13 +10710,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10774,7 +10754,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 27953-2026</t>
+          <t>A 10996-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10788,10 +10768,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46193</v>
+        <v>45370</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10803,13 +10783,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10852,7 +10827,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 27729-2026</t>
+          <t>A 27954-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10862,14 +10837,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46191</v>
+        <v>46193</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10882,7 +10857,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>5.6</v>
+        <v>2.8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10925,7 +10900,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 28026-2026</t>
+          <t>A 27951-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10939,10 +10914,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46195</v>
+        <v>46193</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10954,8 +10929,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -10998,7 +10978,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 18473-2026</t>
+          <t>A 37198-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11012,10 +10992,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46127</v>
+        <v>45875</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11028,7 +11008,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11071,7 +11051,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 28018-2026</t>
+          <t>A 28058-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11088,7 +11068,7 @@
         <v>46195</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11101,7 +11081,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11144,7 +11124,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 19171-2026</t>
+          <t>A 27953-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11158,10 +11138,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46132</v>
+        <v>46193</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11173,8 +11153,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>22.2</v>
+        <v>5.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11217,7 +11202,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 56393-2023</t>
+          <t>A 28026-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11231,10 +11216,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45243</v>
+        <v>46195</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11247,7 +11232,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11290,7 +11275,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 28058-2026</t>
+          <t>A 40067-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11304,10 +11289,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46195</v>
+        <v>45168</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11320,7 +11305,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11363,7 +11348,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 32826-2023</t>
+          <t>A 73961-2021</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11377,10 +11362,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45124</v>
+        <v>44553</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11392,8 +11377,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>0.4</v>
+        <v>5.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11436,7 +11426,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 1450-2024</t>
+          <t>A 20078-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11450,10 +11440,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45303</v>
+        <v>44698</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11466,7 +11456,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11509,7 +11499,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 53078-2021</t>
+          <t>A 6781-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11523,10 +11513,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44467</v>
+        <v>44602</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11539,7 +11529,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11582,7 +11572,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 36406-2022</t>
+          <t>A 38510-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11596,10 +11586,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44803</v>
+        <v>45884</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11655,7 +11645,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 30160-2026</t>
+          <t>A 36406-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11669,10 +11659,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46206</v>
+        <v>44803</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11685,7 +11675,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11728,7 +11718,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 10996-2024</t>
+          <t>A 27036-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11742,10 +11732,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45370</v>
+        <v>45095</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11758,7 +11748,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>5.9</v>
+        <v>1.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11801,7 +11791,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 22846-2024</t>
+          <t>A 9828-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11815,10 +11805,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45448</v>
+        <v>45716</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11831,7 +11821,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11874,7 +11864,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 30091-2024</t>
+          <t>A 43786-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11884,14 +11874,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45489</v>
+        <v>45187</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11904,7 +11894,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11947,7 +11937,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 48227-2022</t>
+          <t>A 30160-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11961,10 +11951,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44858</v>
+        <v>46206</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11977,7 +11967,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12020,7 +12010,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 43758-2023</t>
+          <t>A 6747-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12034,10 +12024,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45187</v>
+        <v>45700</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12050,7 +12040,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12093,7 +12083,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 6747-2025</t>
+          <t>A 6789-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12110,7 +12100,7 @@
         <v>45700</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12123,7 +12113,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12166,7 +12156,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 50304-2024</t>
+          <t>A 59727-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12180,10 +12170,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45600</v>
+        <v>45639</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12196,7 +12186,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12239,7 +12229,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 43786-2023</t>
+          <t>A 30961-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12253,10 +12243,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45187</v>
+        <v>45113</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12269,7 +12259,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12312,7 +12302,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 43787-2023</t>
+          <t>A 16244-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12326,10 +12316,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45187</v>
+        <v>45749</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12341,8 +12331,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12385,7 +12380,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 46254-2024</t>
+          <t>A 48227-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12399,10 +12394,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45581</v>
+        <v>44858</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12415,7 +12410,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12458,7 +12453,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 47856-2022</t>
+          <t>A 22846-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12472,10 +12467,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44855</v>
+        <v>45448</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12488,7 +12483,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12531,7 +12526,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 19307-2023</t>
+          <t>A 31983-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12545,10 +12540,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45049</v>
+        <v>46232</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12561,7 +12556,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12604,7 +12599,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 56625-2022</t>
+          <t>A 61531-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12614,14 +12609,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44893</v>
+        <v>45265</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12633,8 +12628,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12677,7 +12677,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 43790-2023</t>
+          <t>A 37630-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12691,10 +12691,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45187</v>
+        <v>46276</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12706,8 +12706,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>3</v>
+        <v>13.6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12750,7 +12755,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 59026-2023</t>
+          <t>A 27952-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12764,10 +12769,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45252</v>
+        <v>46193</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12779,8 +12784,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>2.1</v>
+        <v>8.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12823,7 +12833,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 58970-2024</t>
+          <t>A 39668-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12837,10 +12847,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45636</v>
+        <v>45167</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12853,7 +12863,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12896,7 +12906,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 23259-2023</t>
+          <t>A 38885-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12910,10 +12920,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45075</v>
+        <v>46286</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12926,7 +12936,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -12969,7 +12979,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 5030-2022</t>
+          <t>A 5818-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -12983,10 +12993,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44593</v>
+        <v>44963</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -12999,7 +13009,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13042,7 +13052,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 6789-2025</t>
+          <t>A 38886-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13056,10 +13066,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45700</v>
+        <v>46286</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13072,7 +13082,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13115,7 +13125,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 58247-2021</t>
+          <t>A 32903-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13129,10 +13139,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44487</v>
+        <v>46244</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13145,7 +13155,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>8.9</v>
+        <v>0.9</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13188,7 +13198,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 58249-2021</t>
+          <t>A 32913-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13202,10 +13212,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44487</v>
+        <v>46244</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13218,7 +13228,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13261,7 +13271,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 25487-2022</t>
+          <t>A 23138-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13275,10 +13285,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44732</v>
+        <v>46161</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13291,7 +13301,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>7.1</v>
+        <v>2.3</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13334,7 +13344,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 6763-2025</t>
+          <t>A 39094-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13348,10 +13358,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45700</v>
+        <v>46283</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13363,8 +13373,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>1.6</v>
+        <v>6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13407,7 +13422,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 13913-2024</t>
+          <t>A 5030-2022</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13421,10 +13436,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45391</v>
+        <v>44593</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13437,7 +13452,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13480,7 +13495,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 31983-2026</t>
+          <t>A 40244-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13494,10 +13509,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46232</v>
+        <v>45554</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13510,7 +13525,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13553,7 +13568,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 43760-2023</t>
+          <t>A 39453-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13567,10 +13582,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45187</v>
+        <v>46288</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13583,7 +13598,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13626,7 +13641,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 43784-2023</t>
+          <t>A 64481-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13640,10 +13655,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45187</v>
+        <v>45280</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13656,7 +13671,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13699,7 +13714,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 55909-2022</t>
+          <t>A 27498-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13713,10 +13728,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44889</v>
+        <v>46185</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13728,8 +13743,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>1.9</v>
+        <v>38</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13772,7 +13792,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 14355-2023</t>
+          <t>A 55074-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13786,10 +13806,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45012</v>
+        <v>45237</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13802,7 +13822,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -13845,7 +13865,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 37630-2026</t>
+          <t>A 58356-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13859,10 +13879,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46276</v>
+        <v>44893</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13874,13 +13894,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>13.6</v>
+        <v>2.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13923,7 +13938,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 40067-2023</t>
+          <t>A 14355-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13937,10 +13952,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45168</v>
+        <v>45012</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -13953,7 +13968,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -13996,7 +14011,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 22650-2024</t>
+          <t>A 13913-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14010,10 +14025,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45447</v>
+        <v>45391</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14026,7 +14041,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>7.9</v>
+        <v>2.2</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14069,7 +14084,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 27952-2026</t>
+          <t>A 46254-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14083,10 +14098,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46193</v>
+        <v>45581</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14098,13 +14113,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>8.5</v>
+        <v>1.3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14147,7 +14157,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 23625-2022</t>
+          <t>A 13352-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14161,10 +14171,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44721</v>
+        <v>45387</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14177,7 +14187,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14220,7 +14230,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 16303-2023</t>
+          <t>A 13610-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14234,10 +14244,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45028</v>
+        <v>45390</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14250,7 +14260,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>6.3</v>
+        <v>1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14293,7 +14303,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 5707-2022</t>
+          <t>A 56393-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14307,10 +14317,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44596</v>
+        <v>45243</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14323,7 +14333,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14366,7 +14376,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 8119-2025</t>
+          <t>A 36653-2022</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14376,14 +14386,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45707</v>
+        <v>44804</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14396,7 +14406,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14439,7 +14449,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 39094-2026</t>
+          <t>A 48229-2022</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14453,10 +14463,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46283</v>
+        <v>44858</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14468,13 +14478,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14517,7 +14522,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 38885-2026</t>
+          <t>A 5089-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14531,10 +14536,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46286</v>
+        <v>45330</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14547,7 +14552,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14590,7 +14595,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 23138-2026</t>
+          <t>A 58247-2021</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14604,10 +14609,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46161</v>
+        <v>44487</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14620,7 +14625,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.3</v>
+        <v>8.9</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14663,7 +14668,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 270-2023</t>
+          <t>A 31772-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14677,10 +14682,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44928</v>
+        <v>45118</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14693,7 +14698,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14736,7 +14741,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 38886-2026</t>
+          <t>A 6662-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14750,10 +14755,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46286</v>
+        <v>45341</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14766,7 +14771,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -14809,7 +14814,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 32913-2026</t>
+          <t>A 53077-2021</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14823,10 +14828,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46244</v>
+        <v>44467</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14839,7 +14844,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -14882,7 +14887,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 32903-2026</t>
+          <t>A 1450-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14896,10 +14901,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46244</v>
+        <v>45303</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14955,7 +14960,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 18314-2024</t>
+          <t>A 6785-2025</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -14969,10 +14974,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45422</v>
+        <v>45700</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -14985,7 +14990,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15028,7 +15033,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 29707-2024</t>
+          <t>A 6793-2025</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15038,14 +15043,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45485</v>
+        <v>45700</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15058,7 +15063,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>7.7</v>
+        <v>0.9</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15101,7 +15106,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 39453-2026</t>
+          <t>A 32826-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15115,10 +15120,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46288</v>
+        <v>45124</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15131,7 +15136,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15174,7 +15179,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 24861-2025</t>
+          <t>A 32177-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15188,10 +15193,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45799</v>
+        <v>45511</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15204,7 +15209,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>5.6</v>
+        <v>0.9</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15247,7 +15252,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 27498-2026</t>
+          <t>A 41357-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15261,10 +15266,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46185</v>
+        <v>45174</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15276,13 +15281,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I199" t="n">
-        <v>38</v>
+        <v>4.1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15325,7 +15325,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 25482-2025</t>
+          <t>A 62045-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15339,10 +15339,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45802</v>
+        <v>44918</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>8.300000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15398,7 +15398,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 15436-2024</t>
+          <t>A 15434-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15412,10 +15412,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45401</v>
+        <v>45020</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15428,7 +15428,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15471,7 +15471,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 7316-2024</t>
+          <t>A 23259-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15485,10 +15485,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45345</v>
+        <v>45075</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15544,7 +15544,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 30654-2025</t>
+          <t>A 30314-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15558,10 +15558,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45831</v>
+        <v>45490</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 30669-2025</t>
+          <t>A 20948-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15631,10 +15631,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45831</v>
+        <v>45439</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.7</v>
+        <v>6.4</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15690,7 +15690,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 31228-2025</t>
+          <t>A 8119-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15704,10 +15704,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45832</v>
+        <v>45707</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -15763,7 +15763,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 31235-2025</t>
+          <t>A 270-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -15777,10 +15777,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45832</v>
+        <v>44928</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15793,7 +15793,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>4</v>
+        <v>1.9</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -15836,7 +15836,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 27675-2025</t>
+          <t>A 29707-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15846,14 +15846,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45813</v>
+        <v>45485</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>3.1</v>
+        <v>7.7</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -15909,7 +15909,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 36508-2022</t>
+          <t>A 18314-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -15923,10 +15923,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44804</v>
+        <v>45422</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -15999,7 +15999,7 @@
         <v>44166</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
         <v>44712</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>44711</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>45763</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>45798</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>46160</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>

--- a/Översikt GNOSJÖ.xlsx
+++ b/Översikt GNOSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44757</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46030</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44711</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>45161</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>44721</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>44530</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>44837</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>44482</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>44474</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>44866</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>44585</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>44468</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>44503</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>44494</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>44698</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>44470</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>44698</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>44467</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>44568</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>44804</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>44855</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>44747</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>44588</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>44858</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>44470</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>45749</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>45202</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>45187</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>45187</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>44789</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>45252</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>45075</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44467</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>45281</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>46013</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>44850</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>44950</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>45096</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>45021</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>45330</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         <v>45174</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>45489</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>46034</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>44866</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>44596</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>45699</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>45712</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>45896</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>45799</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>45897</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>45777</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>45905</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>44893</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>44889</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>45911</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
         <v>45912</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>45916</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>45916</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>45986</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>46070</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>46070</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>46070</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>45489</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>45802</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         <v>45401</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>46084</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>44918</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>44588</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>46097</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>45946</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>45600</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>45356</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>46120</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>46127</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>44958</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>44487</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>45974</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>45973</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>45975</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>45049</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>46132</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         <v>45978</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>44732</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>45636</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>44750</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>45345</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>45125</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         <v>45986</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>46125</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>45618</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>45597</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>45090</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>44721</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>45777</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>46000</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>44855</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         <v>44826</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>46002</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>46002</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>46002</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>45544</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>45028</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>46010</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>45538</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>45322</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>44872</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
         <v>45265</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>45905</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>45881</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>44830</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         <v>45246</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
         <v>45700</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>44467</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>45180</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9238,7 +9238,7 @@
         <v>45096</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>45831</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>45831</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>45832</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9530,7 +9530,7 @@
         <v>45832</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9603,7 +9603,7 @@
         <v>44853</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>45093</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9749,7 +9749,7 @@
         <v>46161</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9822,7 +9822,7 @@
         <v>45813</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>45371</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9968,7 +9968,7 @@
         <v>45371</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>44804</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>45447</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>45468</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>45644</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>45187</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>45187</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>45187</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>45146</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>46191</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>46195</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>45370</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>46193</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>46193</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>45875</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
         <v>46195</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>46193</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>46195</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>45168</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>44553</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
         <v>44698</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11516,7 +11516,7 @@
         <v>44602</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>45884</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>44803</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>45095</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>45716</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>45187</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         <v>46206</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>45700</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>45700</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>45639</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>45113</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12319,7 +12319,7 @@
         <v>45749</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>44858</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>45448</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>46232</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>45265</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>46276</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>46193</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>45167</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>46286</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>44963</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>46286</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>46244</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>46244</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>46161</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>46283</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         <v>44593</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
         <v>45554</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>46288</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>45280</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>46185</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
         <v>45237</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>44893</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13955,7 +13955,7 @@
         <v>45012</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14028,7 +14028,7 @@
         <v>45391</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14101,7 +14101,7 @@
         <v>45581</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>45387</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>45390</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14320,7 +14320,7 @@
         <v>45243</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>44804</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>44858</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14539,7 +14539,7 @@
         <v>45330</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
         <v>44487</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
         <v>45118</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>45341</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         <v>44467</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         <v>45303</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14977,7 +14977,7 @@
         <v>45700</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>45700</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>45124</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>45511</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>45174</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>44918</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>45020</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>45075</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>45490</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>45439</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>45707</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>44928</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>45485</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>45422</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>44166</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
         <v>44712</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>44711</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>45763</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>45798</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>46160</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>

--- a/Översikt GNOSJÖ.xlsx
+++ b/Översikt GNOSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44757</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46030</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44711</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>45161</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>44721</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>44530</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>44837</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>44482</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>44474</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>44866</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>44585</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>44468</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>44503</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>44494</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>44698</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>44470</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>44698</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>44467</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>44568</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>44804</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>44855</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>44747</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>44588</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>44858</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>44470</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>45749</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>45202</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>45187</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>45187</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>44789</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>45252</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>45075</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44467</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>45281</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>46013</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>44850</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>44950</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>45096</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>45021</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>45330</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         <v>45174</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>45489</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>46034</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>44866</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>44596</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>45699</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>45712</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>45896</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>45799</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>45897</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>45777</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>45905</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>44893</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>44889</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>45911</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
         <v>45912</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>45916</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>45916</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>45986</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>46070</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>46070</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>46070</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>45489</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>45802</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         <v>45401</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>46084</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>44918</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>44588</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>46097</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>45946</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>45600</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>45356</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>46120</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>46127</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>44958</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>44487</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>45974</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>45973</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>45975</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>45049</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>46132</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         <v>45978</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>44732</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>45636</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>44750</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>45345</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>45125</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         <v>45986</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>46125</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>45618</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>45597</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>45090</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>44721</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>45777</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>46000</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>44855</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         <v>44826</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>46002</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>46002</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>46002</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>45544</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>45028</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>46010</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>45538</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>45322</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>44872</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
         <v>45265</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>45905</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>45881</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>44830</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         <v>45246</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
         <v>45700</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>44467</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>45180</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9238,7 +9238,7 @@
         <v>45096</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>45831</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>45831</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>45832</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9530,7 +9530,7 @@
         <v>45832</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9603,7 +9603,7 @@
         <v>44853</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>45093</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9749,7 +9749,7 @@
         <v>46161</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9822,7 +9822,7 @@
         <v>45813</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>45371</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9968,7 +9968,7 @@
         <v>45371</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>44804</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>45447</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>45468</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>45644</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>45187</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>45187</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>45187</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>45146</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>46191</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>46195</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>45370</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>46193</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>46193</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>45875</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
         <v>46195</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>46193</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>46195</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>45168</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>44553</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
         <v>44698</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11516,7 +11516,7 @@
         <v>44602</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>45884</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>44803</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>45095</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>45716</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>45187</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         <v>46206</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>45700</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>45700</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>45639</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>45113</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12319,7 +12319,7 @@
         <v>45749</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>44858</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>45448</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>46232</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>45265</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>46276</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>46193</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>45167</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>46286</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>44963</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>46286</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>46244</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>46244</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>46161</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>46283</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         <v>44593</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
         <v>45554</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>46288</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>45280</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>46185</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
         <v>45237</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>44893</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13955,7 +13955,7 @@
         <v>45012</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14028,7 +14028,7 @@
         <v>45391</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14101,7 +14101,7 @@
         <v>45581</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>45387</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>45390</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14320,7 +14320,7 @@
         <v>45243</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>44804</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>44858</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14539,7 +14539,7 @@
         <v>45330</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
         <v>44487</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
         <v>45118</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>45341</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         <v>44467</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         <v>45303</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14977,7 +14977,7 @@
         <v>45700</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>45700</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>45124</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>45511</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>45174</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>44918</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>45020</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>45075</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>45490</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>45439</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>45707</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>44928</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>45485</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>45422</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>44166</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
         <v>44712</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>44711</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>45763</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>45798</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>46160</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>

--- a/Översikt GNOSJÖ.xlsx
+++ b/Översikt GNOSJÖ.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE214"/>
+  <dimension ref="A1:AE210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44757</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46030</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44711</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 38355-2023</t>
+          <t>A 23612-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45161</v>
+        <v>44721</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>11.4</v>
+        <v>4.4</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1084,143 +1084,143 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 23612-2022 artfynd.xlsx", "A 23612-2022")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 23612-2022 karta.png", "A 23612-2022")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 23612-2022 georefererad karta.tif", "A 23612-2022")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 23612-2022 FSC-klagomål.docx", "A 23612-2022")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 23612-2022 FSC-klagomål mail.docx", "A 23612-2022")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 23612-2022 tillsynsbegäran.docx", "A 23612-2022")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 23612-2022 tillsynsbegäran mail.docx", "A 23612-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 38355-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45161</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>GNOSJÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>Mattlummer</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 38355-2023 artfynd.xlsx", "A 38355-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 38355-2023 karta.png", "A 38355-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 38355-2023 georefererad karta.tif", "A 38355-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 38355-2023 FSC-klagomål.docx", "A 38355-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 38355-2023 FSC-klagomål mail.docx", "A 38355-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 38355-2023 tillsynsbegäran.docx", "A 38355-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 38355-2023 tillsynsbegäran mail.docx", "A 38355-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 23612-2022</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>44721</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>GNOSJÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 23612-2022 artfynd.xlsx", "A 23612-2022")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 23612-2022 karta.png", "A 23612-2022")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 23612-2022 georefererad karta.tif", "A 23612-2022")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 23612-2022 FSC-klagomål.docx", "A 23612-2022")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 23612-2022 FSC-klagomål mail.docx", "A 23612-2022")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 23612-2022 tillsynsbegäran.docx", "A 23612-2022")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 23612-2022 tillsynsbegäran mail.docx", "A 23612-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>44530</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>44837</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>44482</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>44474</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 50444-2022</t>
+          <t>A 3418-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44866</v>
+        <v>44585</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1545,8 +1545,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1589,7 +1594,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 3418-2022</t>
+          <t>A 50444-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1603,10 +1608,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44585</v>
+        <v>44866</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1618,13 +1623,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1684,7 +1684,7 @@
         <v>44468</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>44503</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>44494</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>44698</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>44470</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>44698</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 53064-2021</t>
+          <t>A 704-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44467</v>
+        <v>44568</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2178,7 +2178,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 704-2022</t>
+          <t>A 36525-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2192,10 +2192,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44568</v>
+        <v>44804</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2251,7 +2251,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 36525-2022</t>
+          <t>A 47858-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44804</v>
+        <v>44855</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2324,7 +2324,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 47858-2022</t>
+          <t>A 28372-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44855</v>
+        <v>44747</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2397,7 +2397,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 28372-2022</t>
+          <t>A 4298-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44747</v>
+        <v>44588</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2470,7 +2470,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 4298-2022</t>
+          <t>A 48480-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44588</v>
+        <v>44858</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 48480-2022</t>
+          <t>A 54362-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44858</v>
+        <v>44470</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2616,7 +2616,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 54362-2021</t>
+          <t>A 13352-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2630,10 +2630,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44470</v>
+        <v>45387</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16243-2025</t>
+          <t>A 42280-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45749</v>
+        <v>45180</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2718,13 +2718,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2767,7 +2762,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 47454-2023</t>
+          <t>A 46657-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2781,10 +2776,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45202</v>
+        <v>44850</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2797,7 +2792,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>7.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2840,7 +2835,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 43758-2023</t>
+          <t>A 20948-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2854,10 +2849,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45187</v>
+        <v>45439</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2870,7 +2865,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>6.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2913,7 +2908,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 43784-2023</t>
+          <t>A 5089-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2927,10 +2922,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45187</v>
+        <v>45330</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2943,7 +2938,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2986,7 +2981,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33575-2022</t>
+          <t>A 62053-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3000,10 +2995,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44789</v>
+        <v>44918</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3016,7 +3011,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3059,7 +3054,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 59026-2023</t>
+          <t>A 39668-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3073,10 +3068,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45252</v>
+        <v>45167</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3089,7 +3084,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.1</v>
+        <v>0.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3132,7 +3127,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 23254-2023</t>
+          <t>A 48188-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3146,10 +3141,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45075</v>
+        <v>44853</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3162,7 +3157,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3205,7 +3200,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 53078-2021</t>
+          <t>A 25837-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3219,10 +3214,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44467</v>
+        <v>45090</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3235,7 +3230,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3278,7 +3273,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 64718-2023</t>
+          <t>A 18314-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3292,10 +3287,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45281</v>
+        <v>45422</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3308,7 +3303,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3351,7 +3346,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 63511-2025</t>
+          <t>A 61792-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3365,10 +3360,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46013</v>
+        <v>46002</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3381,7 +3376,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.8</v>
+        <v>10.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3424,7 +3419,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 46657-2022</t>
+          <t>A 29707-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3434,14 +3429,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44850</v>
+        <v>45485</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3454,7 +3449,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3497,7 +3492,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 3504-2023</t>
+          <t>A 8698-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3511,10 +3506,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44950</v>
+        <v>45712</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3527,7 +3522,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3570,7 +3565,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 27264-2023</t>
+          <t>A 61682-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3584,10 +3579,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45096</v>
+        <v>46002</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3600,7 +3595,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3643,7 +3638,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 15776-2023</t>
+          <t>A 57730-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3657,10 +3652,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45021</v>
+        <v>45246</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3673,7 +3668,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3716,7 +3711,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 5082-2024</t>
+          <t>A 61677-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3730,10 +3725,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45330</v>
+        <v>46002</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3746,7 +3741,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3789,7 +3784,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 41347-2023</t>
+          <t>A 38510-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3803,10 +3798,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45174</v>
+        <v>45884</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3819,7 +3814,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6.2</v>
+        <v>2.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3862,7 +3857,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30091-2024</t>
+          <t>A 30961-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3872,14 +3867,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45489</v>
+        <v>45113</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3892,7 +3887,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3935,7 +3930,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 1664-2026</t>
+          <t>A 13610-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3949,10 +3944,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46034</v>
+        <v>45390</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3965,7 +3960,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4008,7 +4003,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 50440-2022</t>
+          <t>A 6415-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4022,10 +4017,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44866</v>
+        <v>45699</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4038,7 +4033,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>8.699999999999999</v>
+        <v>2.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4081,7 +4076,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 5707-2022</t>
+          <t>A 49758-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4095,10 +4090,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44596</v>
+        <v>45597</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4111,7 +4106,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4154,7 +4149,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 6415-2025</t>
+          <t>A 24861-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4168,10 +4163,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45699</v>
+        <v>45799</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4184,7 +4179,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.7</v>
+        <v>5.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4227,7 +4222,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 8698-2025</t>
+          <t>A 25482-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4241,10 +4236,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45712</v>
+        <v>45802</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4257,7 +4252,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4300,7 +4295,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 40552-2025</t>
+          <t>A 40863-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4314,10 +4309,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45896</v>
+        <v>45897</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4330,7 +4325,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4373,7 +4368,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 24861-2025</t>
+          <t>A 40552-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4387,10 +4382,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45799</v>
+        <v>45896</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4403,7 +4398,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5.6</v>
+        <v>1.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4446,7 +4441,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 40863-2025</t>
+          <t>A 21080-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4460,10 +4455,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45897</v>
+        <v>45777</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4476,7 +4471,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4519,7 +4514,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 21080-2025</t>
+          <t>A 48229-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4533,10 +4528,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45777</v>
+        <v>44858</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4549,7 +4544,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4609,7 +4604,7 @@
         <v>45905</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4665,7 +4660,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 56625-2022</t>
+          <t>A 15436-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4679,10 +4674,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44893</v>
+        <v>45401</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4695,7 +4690,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4738,7 +4733,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 55909-2022</t>
+          <t>A 63511-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4752,10 +4747,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44889</v>
+        <v>46013</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4768,7 +4763,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.9</v>
+        <v>4.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4828,7 +4823,7 @@
         <v>45911</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4901,7 +4896,7 @@
         <v>45912</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4957,7 +4952,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 44383-2025</t>
+          <t>A 63220-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4971,10 +4966,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45916</v>
+        <v>46010</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4987,7 +4982,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5030,7 +5025,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 44394-2025</t>
+          <t>A 44383-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5047,7 +5042,7 @@
         <v>45916</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5060,7 +5055,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5103,7 +5098,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 58779-2025</t>
+          <t>A 44394-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5117,10 +5112,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45986</v>
+        <v>45916</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5133,7 +5128,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5176,7 +5171,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 9641-2026</t>
+          <t>A 7316-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5190,10 +5185,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46070</v>
+        <v>45345</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5205,13 +5200,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5254,7 +5244,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 9624-2026</t>
+          <t>A 30654-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5268,10 +5258,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46070</v>
+        <v>45831</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5283,13 +5273,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5332,7 +5317,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 9627-2026</t>
+          <t>A 30669-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5346,10 +5331,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46070</v>
+        <v>45831</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5361,13 +5346,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5410,7 +5390,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 30101-2024</t>
+          <t>A 31228-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5420,14 +5400,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45489</v>
+        <v>45832</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5440,7 +5420,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5483,7 +5463,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 25482-2025</t>
+          <t>A 31235-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5497,10 +5477,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45802</v>
+        <v>45832</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5513,7 +5493,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>8.300000000000001</v>
+        <v>4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5556,7 +5536,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 15436-2024</t>
+          <t>A 16243-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5570,10 +5550,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45401</v>
+        <v>45749</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5585,8 +5565,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5629,7 +5614,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 11667-2026</t>
+          <t>A 27675-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5643,10 +5628,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46084</v>
+        <v>45813</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5659,7 +5644,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5702,7 +5687,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 62053-2022</t>
+          <t>A 50728-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5716,10 +5701,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44918</v>
+        <v>45946</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5732,7 +5717,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>15.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5775,7 +5760,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 4293-2022</t>
+          <t>A 36508-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5789,10 +5774,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44588</v>
+        <v>44804</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5805,7 +5790,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5848,7 +5833,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 13600-2026</t>
+          <t>A 5082-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5862,10 +5847,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46097</v>
+        <v>45330</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5877,13 +5862,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5926,7 +5906,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 50728-2025</t>
+          <t>A 1664-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5940,10 +5920,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45946</v>
+        <v>46034</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5956,7 +5936,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>15.2</v>
+        <v>1.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5999,7 +5979,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 50304-2024</t>
+          <t>A 37198-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6013,10 +5993,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45600</v>
+        <v>45875</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6029,7 +6009,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6072,7 +6052,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 8747-2024</t>
+          <t>A 6781-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6086,10 +6066,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45356</v>
+        <v>44602</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6102,7 +6082,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6145,7 +6125,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 17402-2026</t>
+          <t>A 41347-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6159,10 +6139,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46120</v>
+        <v>45174</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6175,7 +6155,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.3</v>
+        <v>6.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6218,7 +6198,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 18473-2026</t>
+          <t>A 55918-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6232,10 +6212,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46127</v>
+        <v>45973</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6248,7 +6228,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6291,7 +6271,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 4992-2023</t>
+          <t>A 50440-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6305,10 +6285,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44958</v>
+        <v>44866</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6321,7 +6301,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6364,7 +6344,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 58249-2021</t>
+          <t>A 4992-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6378,10 +6358,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44487</v>
+        <v>44958</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6394,7 +6374,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6454,7 +6434,7 @@
         <v>45974</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6510,7 +6490,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 55918-2025</t>
+          <t>A 56554-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6524,10 +6504,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45973</v>
+        <v>45975</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6540,7 +6520,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.1</v>
+        <v>7.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6583,7 +6563,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 56554-2025</t>
+          <t>A 57012-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6597,10 +6577,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6613,7 +6593,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>7.2</v>
+        <v>0.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6656,7 +6636,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 19307-2023</t>
+          <t>A 58780-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6670,10 +6650,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45049</v>
+        <v>45986</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6686,7 +6666,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6729,7 +6709,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 19171-2026</t>
+          <t>A 30101-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6739,14 +6719,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46132</v>
+        <v>45489</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6759,7 +6739,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>22.2</v>
+        <v>1.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6802,7 +6782,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 57012-2025</t>
+          <t>A 61411-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6816,10 +6796,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45978</v>
+        <v>46000</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6832,7 +6812,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6875,7 +6855,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 25487-2022</t>
+          <t>A 27036-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6889,10 +6869,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44732</v>
+        <v>45095</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6905,7 +6885,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>7.1</v>
+        <v>1.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6948,7 +6928,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 58970-2024</t>
+          <t>A 33575-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6962,10 +6942,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45636</v>
+        <v>44789</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6978,7 +6958,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7021,7 +7001,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 29066-2022</t>
+          <t>A 58779-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7035,10 +7015,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44750</v>
+        <v>45986</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7051,7 +7031,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7094,7 +7074,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 7316-2024</t>
+          <t>A 11157-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7108,10 +7088,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45345</v>
+        <v>45371</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7124,7 +7104,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7167,7 +7147,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 34083-2023</t>
+          <t>A 11163-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7181,10 +7161,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45125</v>
+        <v>45371</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7197,7 +7177,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7240,7 +7220,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 58780-2025</t>
+          <t>A 9641-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7254,10 +7234,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45986</v>
+        <v>46070</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7269,8 +7249,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7313,7 +7298,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 18337-2026</t>
+          <t>A 9624-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7327,10 +7312,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46125</v>
+        <v>46070</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7342,8 +7327,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7386,7 +7376,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 54833-2024</t>
+          <t>A 9627-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7400,10 +7390,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45618</v>
+        <v>46070</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7464,7 +7454,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 49758-2024</t>
+          <t>A 31772-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7478,10 +7468,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45597</v>
+        <v>45118</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7494,7 +7484,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7537,7 +7527,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 25837-2023</t>
+          <t>A 30314-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7551,10 +7541,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45090</v>
+        <v>45490</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7567,7 +7557,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7610,7 +7600,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 23625-2022</t>
+          <t>A 11667-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7624,10 +7614,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44721</v>
+        <v>46084</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7640,7 +7630,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7683,7 +7673,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 21076-2025</t>
+          <t>A 64481-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7697,10 +7687,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45777</v>
+        <v>45280</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7713,7 +7703,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7756,7 +7746,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 61411-2025</t>
+          <t>A 32177-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7770,10 +7760,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46000</v>
+        <v>45511</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7786,7 +7776,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7829,7 +7819,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 47856-2022</t>
+          <t>A 60859-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7843,10 +7833,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44855</v>
+        <v>45644</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7859,7 +7849,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.1</v>
+        <v>3.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7902,7 +7892,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 41323-2022</t>
+          <t>A 13600-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7916,10 +7906,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44826</v>
+        <v>46097</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7931,8 +7921,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7975,7 +7970,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 61677-2025</t>
+          <t>A 55074-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7989,10 +7984,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46002</v>
+        <v>45237</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8005,7 +8000,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8048,7 +8043,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 61682-2025</t>
+          <t>A 5818-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8062,10 +8057,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46002</v>
+        <v>44963</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8078,7 +8073,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8121,7 +8116,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 61792-2025</t>
+          <t>A 62045-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8135,10 +8130,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46002</v>
+        <v>44918</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8151,7 +8146,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>10.6</v>
+        <v>2.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8194,7 +8189,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 37963-2024</t>
+          <t>A 40244-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8208,10 +8203,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45544</v>
+        <v>45554</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8224,7 +8219,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>5.3</v>
+        <v>0.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8267,7 +8262,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 16303-2023</t>
+          <t>A 41323-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8281,10 +8276,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45028</v>
+        <v>44826</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8297,7 +8292,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>6.3</v>
+        <v>1.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8340,7 +8335,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 63220-2025</t>
+          <t>A 4293-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8354,10 +8349,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46010</v>
+        <v>44588</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8370,7 +8365,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8413,7 +8408,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 36905-2024</t>
+          <t>A 17402-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8427,10 +8422,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45538</v>
+        <v>46120</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8443,7 +8438,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8486,7 +8481,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 3987-2024</t>
+          <t>A 27264-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8500,10 +8495,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45322</v>
+        <v>45096</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8516,7 +8511,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8559,7 +8554,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 51901-2022</t>
+          <t>A 18473-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8573,10 +8568,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44872</v>
+        <v>46127</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8589,7 +8584,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>7.3</v>
+        <v>1.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8632,7 +8627,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 61532-2023</t>
+          <t>A 19171-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8642,14 +8637,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45265</v>
+        <v>46132</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8661,13 +8656,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>1.7</v>
+        <v>22.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8710,7 +8700,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 42618-2025</t>
+          <t>A 37864-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8724,10 +8714,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45905</v>
+        <v>45881</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8740,7 +8730,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8783,7 +8773,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 37864-2025</t>
+          <t>A 18337-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8797,10 +8787,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45881</v>
+        <v>46125</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8813,7 +8803,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8856,7 +8846,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 41918-2022</t>
+          <t>A 54833-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8870,10 +8860,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44830</v>
+        <v>45618</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8885,8 +8875,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8929,7 +8924,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 57730-2023</t>
+          <t>A 58356-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8943,10 +8938,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45246</v>
+        <v>44893</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8959,7 +8954,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9002,7 +8997,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 6763-2025</t>
+          <t>A 20078-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9016,10 +9011,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45700</v>
+        <v>44698</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9032,7 +9027,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9075,7 +9070,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 52813-2021</t>
+          <t>A 61532-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9085,14 +9080,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44467</v>
+        <v>45265</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9104,8 +9099,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9148,7 +9148,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 42280-2023</t>
+          <t>A 36905-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9162,10 +9162,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45180</v>
+        <v>45538</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9221,7 +9221,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 27258-2023</t>
+          <t>A 21076-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9235,10 +9235,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45096</v>
+        <v>45777</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9294,7 +9294,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 30669-2025</t>
+          <t>A 35325-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9308,10 +9308,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45831</v>
+        <v>45146</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 30654-2025</t>
+          <t>A 73961-2021</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9381,10 +9381,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45831</v>
+        <v>44553</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9396,8 +9396,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>2</v>
+        <v>5.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9440,7 +9445,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 31235-2025</t>
+          <t>A 27258-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9454,10 +9459,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45832</v>
+        <v>45096</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9470,7 +9475,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9513,7 +9518,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 31228-2025</t>
+          <t>A 29066-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9527,10 +9532,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45832</v>
+        <v>44750</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9543,7 +9548,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9586,7 +9591,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 48188-2022</t>
+          <t>A 37963-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9600,10 +9605,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44853</v>
+        <v>45544</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9616,7 +9621,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9659,7 +9664,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 26746-2023</t>
+          <t>A 3987-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9673,10 +9678,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45093</v>
+        <v>45322</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9689,7 +9694,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9732,7 +9737,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 23132-2026</t>
+          <t>A 42618-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9746,10 +9751,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46161</v>
+        <v>45905</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9762,7 +9767,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9805,7 +9810,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 27675-2025</t>
+          <t>A 3504-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9819,10 +9824,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45813</v>
+        <v>44950</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9835,7 +9840,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9878,7 +9883,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 11157-2024</t>
+          <t>A 9828-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9892,10 +9897,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45371</v>
+        <v>45716</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9908,7 +9913,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9951,7 +9956,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 11163-2024</t>
+          <t>A 36653-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9961,14 +9966,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45371</v>
+        <v>44804</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -9981,7 +9986,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10024,7 +10029,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 36508-2022</t>
+          <t>A 23254-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10038,10 +10043,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44804</v>
+        <v>45075</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10054,7 +10059,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10097,7 +10102,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 22650-2024</t>
+          <t>A 64718-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10111,10 +10116,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45447</v>
+        <v>45281</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10127,7 +10132,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>7.9</v>
+        <v>4.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10170,7 +10175,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 26210-2024</t>
+          <t>A 47454-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10184,10 +10189,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45468</v>
+        <v>45202</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10200,7 +10205,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10243,7 +10248,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 60859-2024</t>
+          <t>A 34083-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10257,10 +10262,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45644</v>
+        <v>45125</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10273,7 +10278,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10316,7 +10321,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 43787-2023</t>
+          <t>A 6785-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10330,10 +10335,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45187</v>
+        <v>45700</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10389,7 +10394,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 43760-2023</t>
+          <t>A 6793-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10403,10 +10408,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45187</v>
+        <v>45700</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10462,7 +10467,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 43790-2023</t>
+          <t>A 59727-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10476,10 +10481,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45187</v>
+        <v>45639</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10492,7 +10497,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10535,7 +10540,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 35325-2023</t>
+          <t>A 23132-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10549,10 +10554,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45146</v>
+        <v>46161</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10565,7 +10570,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10608,7 +10613,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 27729-2026</t>
+          <t>A 15434-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10618,14 +10623,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46191</v>
+        <v>45020</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10638,7 +10643,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10681,7 +10686,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 28018-2026</t>
+          <t>A 41918-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10695,10 +10700,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46195</v>
+        <v>44830</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10711,7 +10716,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10754,7 +10759,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 10996-2024</t>
+          <t>A 61531-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10764,14 +10769,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45370</v>
+        <v>45265</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10783,8 +10788,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>5.9</v>
+        <v>0.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10827,7 +10837,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 27954-2026</t>
+          <t>A 26746-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10841,10 +10851,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46193</v>
+        <v>45093</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10857,7 +10867,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10900,7 +10910,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 27951-2026</t>
+          <t>A 15776-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10914,10 +10924,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46193</v>
+        <v>45021</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10929,13 +10939,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -10978,7 +10983,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 37198-2025</t>
+          <t>A 51901-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10992,10 +10997,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45875</v>
+        <v>44872</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11008,7 +11013,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>3.7</v>
+        <v>7.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11051,7 +11056,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 28058-2026</t>
+          <t>A 26210-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11065,10 +11070,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46195</v>
+        <v>45468</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11124,7 +11129,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 27953-2026</t>
+          <t>A 16244-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11138,10 +11143,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46193</v>
+        <v>45749</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11155,11 +11160,11 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>5.7</v>
+        <v>2.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11202,7 +11207,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 28026-2026</t>
+          <t>A 41357-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11216,10 +11221,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46195</v>
+        <v>45174</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11232,7 +11237,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11275,7 +11280,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 40067-2023</t>
+          <t>A 6662-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11289,10 +11294,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45168</v>
+        <v>45341</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11305,7 +11310,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11348,7 +11353,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 73961-2021</t>
+          <t>A 8747-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11362,10 +11367,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44553</v>
+        <v>45356</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11377,13 +11382,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11426,7 +11426,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 20078-2022</t>
+          <t>A 56393-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11440,10 +11440,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44698</v>
+        <v>45243</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11499,7 +11499,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 6781-2022</t>
+          <t>A 32826-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11513,10 +11513,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44602</v>
+        <v>45124</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11572,7 +11572,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 38510-2025</t>
+          <t>A 1450-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11586,10 +11586,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45884</v>
+        <v>45303</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11645,7 +11645,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 36406-2022</t>
+          <t>A 27954-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11659,10 +11659,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44803</v>
+        <v>46193</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11718,7 +11718,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 27036-2023</t>
+          <t>A 27951-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11732,10 +11732,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45095</v>
+        <v>46193</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11745,6 +11745,11 @@
       <c r="G151" t="inlineStr">
         <is>
           <t>GNOSJÖ</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I151" t="n">
@@ -11791,7 +11796,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 9828-2025</t>
+          <t>A 27953-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11805,10 +11810,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45716</v>
+        <v>46193</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11820,8 +11825,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>0.4</v>
+        <v>5.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11864,7 +11874,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 43786-2023</t>
+          <t>A 27729-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11874,14 +11884,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45187</v>
+        <v>46191</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11894,7 +11904,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.6</v>
+        <v>5.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11937,7 +11947,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 30160-2026</t>
+          <t>A 28026-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11951,10 +11961,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46206</v>
+        <v>46195</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11967,7 +11977,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12010,7 +12020,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 6747-2025</t>
+          <t>A 28018-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12024,10 +12034,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45700</v>
+        <v>46195</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12040,7 +12050,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12083,7 +12093,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 6789-2025</t>
+          <t>A 28058-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12097,10 +12107,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45700</v>
+        <v>46195</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12113,7 +12123,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12156,7 +12166,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 59727-2024</t>
+          <t>A 36406-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12170,10 +12180,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45639</v>
+        <v>44803</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12186,7 +12196,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12229,7 +12239,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 30961-2023</t>
+          <t>A 10996-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12243,10 +12253,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45113</v>
+        <v>45370</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12259,7 +12269,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2.7</v>
+        <v>5.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12302,7 +12312,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 16244-2025</t>
+          <t>A 22846-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12316,10 +12326,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45749</v>
+        <v>45448</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12331,13 +12341,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12380,7 +12385,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 48227-2022</t>
+          <t>A 30091-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12390,14 +12395,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44858</v>
+        <v>45489</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12410,7 +12415,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12453,7 +12458,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 22846-2024</t>
+          <t>A 30160-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12467,10 +12472,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45448</v>
+        <v>46206</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12483,7 +12488,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12526,7 +12531,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 31983-2026</t>
+          <t>A 48227-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12540,10 +12545,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46232</v>
+        <v>44858</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12556,7 +12561,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12599,7 +12604,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 61531-2023</t>
+          <t>A 43758-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12609,14 +12614,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45265</v>
+        <v>45187</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12628,13 +12633,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12677,7 +12677,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 37630-2026</t>
+          <t>A 6747-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12691,10 +12691,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46276</v>
+        <v>45700</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12706,13 +12706,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>13.6</v>
+        <v>0.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12755,7 +12750,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 27952-2026</t>
+          <t>A 50304-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12769,10 +12764,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46193</v>
+        <v>45600</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12784,13 +12779,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>8.5</v>
+        <v>1.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12833,7 +12823,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 39668-2023</t>
+          <t>A 43786-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12847,10 +12837,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45167</v>
+        <v>45187</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12863,7 +12853,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12906,7 +12896,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 38885-2026</t>
+          <t>A 43787-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12920,10 +12910,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46286</v>
+        <v>45187</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12936,7 +12926,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -12979,7 +12969,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 5818-2023</t>
+          <t>A 46254-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -12993,10 +12983,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44963</v>
+        <v>45581</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13009,7 +12999,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13052,7 +13042,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 38886-2026</t>
+          <t>A 47856-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13066,10 +13056,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46286</v>
+        <v>44855</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13082,7 +13072,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13125,7 +13115,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 32903-2026</t>
+          <t>A 19307-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13139,10 +13129,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46244</v>
+        <v>45049</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13155,7 +13145,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13198,7 +13188,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 32913-2026</t>
+          <t>A 56625-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13212,10 +13202,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46244</v>
+        <v>44893</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13228,7 +13218,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13271,7 +13261,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 23138-2026</t>
+          <t>A 43790-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13285,10 +13275,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46161</v>
+        <v>45187</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13301,7 +13291,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13344,7 +13334,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 39094-2026</t>
+          <t>A 59026-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13358,10 +13348,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46283</v>
+        <v>45252</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13373,13 +13363,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>6</v>
+        <v>2.1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13422,7 +13407,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 5030-2022</t>
+          <t>A 58970-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13436,10 +13421,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44593</v>
+        <v>45636</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13452,7 +13437,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13495,7 +13480,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 40244-2024</t>
+          <t>A 23259-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13509,10 +13494,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45554</v>
+        <v>45075</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13525,7 +13510,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13568,7 +13553,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 39453-2026</t>
+          <t>A 5030-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13582,10 +13567,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46288</v>
+        <v>44593</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13598,7 +13583,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13641,7 +13626,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 64481-2023</t>
+          <t>A 6789-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13655,10 +13640,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45280</v>
+        <v>45700</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13671,7 +13656,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>5.5</v>
+        <v>1.4</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13714,7 +13699,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 27498-2026</t>
+          <t>A 58247-2021</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13728,10 +13713,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46185</v>
+        <v>44487</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13743,13 +13728,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>38</v>
+        <v>8.9</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13792,7 +13772,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 55074-2023</t>
+          <t>A 58249-2021</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13806,10 +13786,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45237</v>
+        <v>44487</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13822,7 +13802,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -13865,7 +13845,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 58356-2022</t>
+          <t>A 25487-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13879,10 +13859,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44893</v>
+        <v>44732</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13895,7 +13875,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.5</v>
+        <v>7.1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13938,7 +13918,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 14355-2023</t>
+          <t>A 6763-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13952,10 +13932,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45012</v>
+        <v>45700</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14028,7 +14008,7 @@
         <v>45391</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14084,7 +14064,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 46254-2024</t>
+          <t>A 43760-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14098,10 +14078,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45581</v>
+        <v>45187</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14114,7 +14094,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14157,7 +14137,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 13352-2024</t>
+          <t>A 43784-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14171,10 +14151,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45387</v>
+        <v>45187</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14187,7 +14167,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14230,7 +14210,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 13610-2024</t>
+          <t>A 55909-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14244,10 +14224,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45390</v>
+        <v>44889</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14260,7 +14240,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14303,7 +14283,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 56393-2023</t>
+          <t>A 14355-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14317,10 +14297,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45243</v>
+        <v>45012</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14333,7 +14313,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14376,7 +14356,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 36653-2022</t>
+          <t>A 40067-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14386,14 +14366,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44804</v>
+        <v>45168</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14406,7 +14386,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14449,7 +14429,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 48229-2022</t>
+          <t>A 22650-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14463,10 +14443,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44858</v>
+        <v>45447</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14479,7 +14459,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>3.6</v>
+        <v>7.9</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14522,7 +14502,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 5089-2024</t>
+          <t>A 31983-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14536,10 +14516,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45330</v>
+        <v>46232</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14552,7 +14532,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14595,7 +14575,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 58247-2021</t>
+          <t>A 37630-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14609,10 +14589,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44487</v>
+        <v>46276</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14624,8 +14604,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>8.9</v>
+        <v>13.6</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14668,7 +14653,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 31772-2023</t>
+          <t>A 23625-2022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14682,10 +14667,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45118</v>
+        <v>44721</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14698,7 +14683,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14741,7 +14726,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 6662-2024</t>
+          <t>A 16303-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14755,10 +14740,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45341</v>
+        <v>45028</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14771,7 +14756,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.2</v>
+        <v>6.3</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -14814,7 +14799,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 53077-2021</t>
+          <t>A 5707-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14828,10 +14813,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44467</v>
+        <v>44596</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14844,7 +14829,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -14887,7 +14872,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 1450-2024</t>
+          <t>A 27952-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14901,10 +14886,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45303</v>
+        <v>46193</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14916,8 +14901,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>0.9</v>
+        <v>8.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -14960,7 +14950,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 6785-2025</t>
+          <t>A 8119-2025</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -14974,10 +14964,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45700</v>
+        <v>45707</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -14990,7 +14980,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15033,7 +15023,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 6793-2025</t>
+          <t>A 270-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15047,10 +15037,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45700</v>
+        <v>44928</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15063,7 +15053,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15106,7 +15096,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 32826-2023</t>
+          <t>A 39094-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15120,10 +15110,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45124</v>
+        <v>46283</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15135,8 +15125,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>0.4</v>
+        <v>6</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15179,7 +15174,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 32177-2024</t>
+          <t>A 38885-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15193,10 +15188,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45511</v>
+        <v>46286</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15209,7 +15204,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15252,7 +15247,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 41357-2023</t>
+          <t>A 23138-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15266,10 +15261,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45174</v>
+        <v>46161</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15282,7 +15277,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15325,7 +15320,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 62045-2022</t>
+          <t>A 38886-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15339,10 +15334,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44918</v>
+        <v>46286</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15355,7 +15350,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15398,7 +15393,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 15434-2023</t>
+          <t>A 32913-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15412,10 +15407,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45020</v>
+        <v>46244</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15428,7 +15423,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15471,7 +15466,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 23259-2023</t>
+          <t>A 32903-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15485,10 +15480,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45075</v>
+        <v>46244</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15501,7 +15496,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15544,7 +15539,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 30314-2024</t>
+          <t>A 39453-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15558,10 +15553,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45490</v>
+        <v>46288</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15574,7 +15569,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15617,7 +15612,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 20948-2024</t>
+          <t>A 27498-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15631,10 +15626,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45439</v>
+        <v>46185</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15646,8 +15641,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>6.4</v>
+        <v>38</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15690,24 +15690,24 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 8119-2025</t>
+          <t>S 2580-2020</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45707</v>
+        <v>44166</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.8</v>
+        <v>0.1</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -15763,24 +15763,24 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 270-2023</t>
+          <t>S 2956-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44928</v>
+        <v>44712</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15792,8 +15792,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>1.9</v>
+        <v>42.7</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -15836,24 +15841,24 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 29707-2024</t>
+          <t>S 2912-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45485</v>
+        <v>44711</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15865,8 +15870,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I207" t="n">
-        <v>7.7</v>
+        <v>33.4</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -15909,24 +15919,24 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 18314-2024</t>
+          <t>S 1256-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45422</v>
+        <v>45763</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15939,7 +15949,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.3</v>
+        <v>9</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -15982,7 +15992,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>S 2580-2020</t>
+          <t>S 1619-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -15992,14 +16002,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44166</v>
+        <v>45798</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16011,8 +16021,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I209" t="n">
-        <v>0.1</v>
+        <v>43.9</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16052,10 +16067,10 @@
       </c>
       <c r="V209" s="2" t="inlineStr"/>
     </row>
-    <row r="210" ht="15" customHeight="1">
+    <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>S 2956-2022</t>
+          <t>S 1452-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16069,10 +16084,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44712</v>
+        <v>46160</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16090,7 +16105,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>42.7</v>
+        <v>43.3</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16129,313 +16144,6 @@
         <v>0</v>
       </c>
       <c r="V210" s="2" t="inlineStr"/>
-    </row>
-    <row r="211" ht="15" customHeight="1">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>S 2912-2022</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D211" s="1" t="n">
-        <v>44711</v>
-      </c>
-      <c r="E211" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>GNOSJÖ</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I211" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="J211" t="n">
-        <v>0</v>
-      </c>
-      <c r="K211" t="n">
-        <v>0</v>
-      </c>
-      <c r="L211" t="n">
-        <v>0</v>
-      </c>
-      <c r="M211" t="n">
-        <v>0</v>
-      </c>
-      <c r="N211" t="n">
-        <v>0</v>
-      </c>
-      <c r="O211" t="n">
-        <v>0</v>
-      </c>
-      <c r="P211" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
-      <c r="R211" t="n">
-        <v>0</v>
-      </c>
-      <c r="S211" t="n">
-        <v>0</v>
-      </c>
-      <c r="T211" t="n">
-        <v>0</v>
-      </c>
-      <c r="U211" t="n">
-        <v>0</v>
-      </c>
-      <c r="V211" s="2" t="inlineStr"/>
-    </row>
-    <row r="212" ht="15" customHeight="1">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>S 1256-2025</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D212" s="1" t="n">
-        <v>45763</v>
-      </c>
-      <c r="E212" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>GNOSJÖ</t>
-        </is>
-      </c>
-      <c r="I212" t="n">
-        <v>9</v>
-      </c>
-      <c r="J212" t="n">
-        <v>0</v>
-      </c>
-      <c r="K212" t="n">
-        <v>0</v>
-      </c>
-      <c r="L212" t="n">
-        <v>0</v>
-      </c>
-      <c r="M212" t="n">
-        <v>0</v>
-      </c>
-      <c r="N212" t="n">
-        <v>0</v>
-      </c>
-      <c r="O212" t="n">
-        <v>0</v>
-      </c>
-      <c r="P212" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
-      <c r="R212" t="n">
-        <v>0</v>
-      </c>
-      <c r="S212" t="n">
-        <v>0</v>
-      </c>
-      <c r="T212" t="n">
-        <v>0</v>
-      </c>
-      <c r="U212" t="n">
-        <v>0</v>
-      </c>
-      <c r="V212" s="2" t="inlineStr"/>
-    </row>
-    <row r="213" ht="15" customHeight="1">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>S 1619-2025</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D213" s="1" t="n">
-        <v>45798</v>
-      </c>
-      <c r="E213" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>GNOSJÖ</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I213" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="J213" t="n">
-        <v>0</v>
-      </c>
-      <c r="K213" t="n">
-        <v>0</v>
-      </c>
-      <c r="L213" t="n">
-        <v>0</v>
-      </c>
-      <c r="M213" t="n">
-        <v>0</v>
-      </c>
-      <c r="N213" t="n">
-        <v>0</v>
-      </c>
-      <c r="O213" t="n">
-        <v>0</v>
-      </c>
-      <c r="P213" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
-      <c r="R213" t="n">
-        <v>0</v>
-      </c>
-      <c r="S213" t="n">
-        <v>0</v>
-      </c>
-      <c r="T213" t="n">
-        <v>0</v>
-      </c>
-      <c r="U213" t="n">
-        <v>0</v>
-      </c>
-      <c r="V213" s="2" t="inlineStr"/>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>S 1452-2026</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D214" s="1" t="n">
-        <v>46160</v>
-      </c>
-      <c r="E214" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>GNOSJÖ</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I214" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="J214" t="n">
-        <v>0</v>
-      </c>
-      <c r="K214" t="n">
-        <v>0</v>
-      </c>
-      <c r="L214" t="n">
-        <v>0</v>
-      </c>
-      <c r="M214" t="n">
-        <v>0</v>
-      </c>
-      <c r="N214" t="n">
-        <v>0</v>
-      </c>
-      <c r="O214" t="n">
-        <v>0</v>
-      </c>
-      <c r="P214" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
-      <c r="R214" t="n">
-        <v>0</v>
-      </c>
-      <c r="S214" t="n">
-        <v>0</v>
-      </c>
-      <c r="T214" t="n">
-        <v>0</v>
-      </c>
-      <c r="U214" t="n">
-        <v>0</v>
-      </c>
-      <c r="V214" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt GNOSJÖ.xlsx
+++ b/Översikt GNOSJÖ.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE210"/>
+  <dimension ref="A1:AE209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44757</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46030</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44711</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 23612-2022</t>
+          <t>A 38355-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44721</v>
+        <v>45161</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.4</v>
+        <v>11.4</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1084,143 +1084,143 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 38355-2023 artfynd.xlsx", "A 38355-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 38355-2023 karta.png", "A 38355-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 38355-2023 georefererad karta.tif", "A 38355-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 38355-2023 FSC-klagomål.docx", "A 38355-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 38355-2023 FSC-klagomål mail.docx", "A 38355-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 38355-2023 tillsynsbegäran.docx", "A 38355-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 38355-2023 tillsynsbegäran mail.docx", "A 38355-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 23612-2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>44721</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>GNOSJÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>Kungsfågel</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 23612-2022 artfynd.xlsx", "A 23612-2022")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 23612-2022 karta.png", "A 23612-2022")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 23612-2022 georefererad karta.tif", "A 23612-2022")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 23612-2022 FSC-klagomål.docx", "A 23612-2022")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 23612-2022 FSC-klagomål mail.docx", "A 23612-2022")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 23612-2022 tillsynsbegäran.docx", "A 23612-2022")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 23612-2022 tillsynsbegäran mail.docx", "A 23612-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 38355-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45161</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>GNOSJÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Mattlummer</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 38355-2023 artfynd.xlsx", "A 38355-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 38355-2023 karta.png", "A 38355-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 38355-2023 georefererad karta.tif", "A 38355-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 38355-2023 FSC-klagomål.docx", "A 38355-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 38355-2023 FSC-klagomål mail.docx", "A 38355-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 38355-2023 tillsynsbegäran.docx", "A 38355-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 38355-2023 tillsynsbegäran mail.docx", "A 38355-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>44530</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>44837</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>44482</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>44474</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 3418-2022</t>
+          <t>A 50444-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44585</v>
+        <v>44866</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1545,13 +1545,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1594,7 +1589,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 50444-2022</t>
+          <t>A 3418-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1608,10 +1603,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44866</v>
+        <v>44585</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1623,8 +1618,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1667,7 +1667,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 53196-2021</t>
+          <t>A 62615-2021</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44468</v>
+        <v>44503</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1740,7 +1740,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 62615-2021</t>
+          <t>A 59855-2021</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44503</v>
+        <v>44494</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 59855-2021</t>
+          <t>A 20077-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1827,10 +1827,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44494</v>
+        <v>44698</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1886,7 +1886,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 20077-2022</t>
+          <t>A 54376-2021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44698</v>
+        <v>44470</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1959,7 +1959,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 54376-2021</t>
+          <t>A 20080-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44470</v>
+        <v>44698</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2032,7 +2032,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 20080-2022</t>
+          <t>A 704-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44698</v>
+        <v>44568</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2105,7 +2105,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 704-2022</t>
+          <t>A 36525-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44568</v>
+        <v>44804</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2178,7 +2178,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 36525-2022</t>
+          <t>A 47858-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2192,10 +2192,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44804</v>
+        <v>44855</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2251,7 +2251,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 47858-2022</t>
+          <t>A 28372-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44855</v>
+        <v>44747</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2324,7 +2324,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 28372-2022</t>
+          <t>A 4298-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44747</v>
+        <v>44588</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2397,7 +2397,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 4298-2022</t>
+          <t>A 48480-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44588</v>
+        <v>44858</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2470,7 +2470,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 48480-2022</t>
+          <t>A 54362-2021</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44858</v>
+        <v>44470</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 54362-2021</t>
+          <t>A 16243-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44470</v>
+        <v>45749</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2572,8 +2572,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2616,7 +2621,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 13352-2024</t>
+          <t>A 47454-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2630,10 +2635,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45387</v>
+        <v>45202</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2646,7 +2651,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2689,7 +2694,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 42280-2023</t>
+          <t>A 33575-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2703,10 +2708,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45180</v>
+        <v>44789</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2719,7 +2724,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2762,7 +2767,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 46657-2022</t>
+          <t>A 59026-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2776,10 +2781,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44850</v>
+        <v>45252</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2792,7 +2797,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>7.9</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2835,7 +2840,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 20948-2024</t>
+          <t>A 43758-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2849,10 +2854,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45439</v>
+        <v>45187</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2865,7 +2870,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>6.4</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2908,7 +2913,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 5089-2024</t>
+          <t>A 43784-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2922,10 +2927,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45330</v>
+        <v>45187</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2938,7 +2943,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2981,7 +2986,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 62053-2022</t>
+          <t>A 23254-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2995,10 +3000,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44918</v>
+        <v>45075</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3011,7 +3016,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3054,7 +3059,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 39668-2023</t>
+          <t>A 63511-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3068,10 +3073,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45167</v>
+        <v>46013</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3084,7 +3089,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.3</v>
+        <v>4.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3127,7 +3132,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 48188-2022</t>
+          <t>A 64718-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3141,10 +3146,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44853</v>
+        <v>45281</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3157,7 +3162,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3200,7 +3205,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 25837-2023</t>
+          <t>A 46657-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3214,10 +3219,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45090</v>
+        <v>44850</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3230,7 +3235,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.3</v>
+        <v>7.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3273,7 +3278,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 18314-2024</t>
+          <t>A 3504-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3287,10 +3292,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45422</v>
+        <v>44950</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3303,7 +3308,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3346,7 +3351,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 61792-2025</t>
+          <t>A 27264-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3360,10 +3365,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46002</v>
+        <v>45096</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3376,7 +3381,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>10.6</v>
+        <v>1.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3419,7 +3424,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 29707-2024</t>
+          <t>A 15776-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3429,14 +3434,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45485</v>
+        <v>45021</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3449,7 +3454,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>7.7</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3492,7 +3497,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 8698-2025</t>
+          <t>A 5082-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3506,10 +3511,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45712</v>
+        <v>45330</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3522,7 +3527,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3565,7 +3570,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 61682-2025</t>
+          <t>A 41347-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3579,10 +3584,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46002</v>
+        <v>45174</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3595,7 +3600,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>6.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3638,7 +3643,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 57730-2023</t>
+          <t>A 30091-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3648,14 +3653,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45246</v>
+        <v>45489</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3711,7 +3716,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 61677-2025</t>
+          <t>A 6415-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3725,10 +3730,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46002</v>
+        <v>45699</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3741,7 +3746,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3784,7 +3789,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 38510-2025</t>
+          <t>A 8698-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3798,10 +3803,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45884</v>
+        <v>45712</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3814,7 +3819,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3857,7 +3862,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30961-2023</t>
+          <t>A 50440-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3871,10 +3876,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45113</v>
+        <v>44866</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3887,7 +3892,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3930,7 +3935,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 13610-2024</t>
+          <t>A 5707-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3944,10 +3949,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45390</v>
+        <v>44596</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3960,7 +3965,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4003,7 +4008,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 6415-2025</t>
+          <t>A 24861-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4017,10 +4022,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45699</v>
+        <v>45799</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4033,7 +4038,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.7</v>
+        <v>5.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4076,7 +4081,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 49758-2024</t>
+          <t>A 40552-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4090,10 +4095,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45597</v>
+        <v>45896</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4106,7 +4111,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4149,7 +4154,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 24861-2025</t>
+          <t>A 40863-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4163,10 +4168,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45799</v>
+        <v>45897</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4179,7 +4184,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5.6</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4239,7 +4244,7 @@
         <v>45802</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4295,7 +4300,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 40863-2025</t>
+          <t>A 21080-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4309,10 +4314,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45897</v>
+        <v>45777</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4325,7 +4330,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4368,7 +4373,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 40552-2025</t>
+          <t>A 15436-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4382,10 +4387,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45896</v>
+        <v>45401</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4398,7 +4403,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4441,7 +4446,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 21080-2025</t>
+          <t>A 1664-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4455,10 +4460,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45777</v>
+        <v>46034</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4471,7 +4476,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4514,7 +4519,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 48229-2022</t>
+          <t>A 42615-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4528,10 +4533,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44858</v>
+        <v>45905</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4544,7 +4549,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4587,7 +4592,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 42615-2025</t>
+          <t>A 43637-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4601,10 +4606,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45905</v>
+        <v>45911</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4617,7 +4622,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4660,7 +4665,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 15436-2024</t>
+          <t>A 43656-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4674,10 +4679,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45401</v>
+        <v>45912</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4690,7 +4695,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4733,7 +4738,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 63511-2025</t>
+          <t>A 56625-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4747,10 +4752,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46013</v>
+        <v>44893</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4763,7 +4768,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4806,7 +4811,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 43637-2025</t>
+          <t>A 55909-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4820,10 +4825,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45911</v>
+        <v>44889</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4836,7 +4841,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4879,7 +4884,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 43656-2025</t>
+          <t>A 7316-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4893,10 +4898,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45912</v>
+        <v>45345</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4909,7 +4914,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4952,7 +4957,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 63220-2025</t>
+          <t>A 44383-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4966,10 +4971,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46010</v>
+        <v>45916</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4982,7 +4987,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5025,7 +5030,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 44383-2025</t>
+          <t>A 44394-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5042,7 +5047,7 @@
         <v>45916</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5055,7 +5060,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5098,7 +5103,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 44394-2025</t>
+          <t>A 30101-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5108,14 +5113,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45916</v>
+        <v>45489</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5128,7 +5133,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5171,7 +5176,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 7316-2024</t>
+          <t>A 30669-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5185,10 +5190,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45345</v>
+        <v>45831</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5201,7 +5206,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5261,7 +5266,7 @@
         <v>45831</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5317,7 +5322,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 30669-2025</t>
+          <t>A 31235-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5331,10 +5336,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45831</v>
+        <v>45832</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5347,7 +5352,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5407,7 +5412,7 @@
         <v>45832</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5463,7 +5468,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 31235-2025</t>
+          <t>A 62053-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5477,10 +5482,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45832</v>
+        <v>44918</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5493,7 +5498,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5536,7 +5541,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 16243-2025</t>
+          <t>A 4293-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5550,10 +5555,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45749</v>
+        <v>44588</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5565,13 +5570,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5631,7 +5631,7 @@
         <v>45813</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 50728-2025</t>
+          <t>A 36508-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5701,10 +5701,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45946</v>
+        <v>44804</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>15.2</v>
+        <v>2.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5760,7 +5760,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 36508-2022</t>
+          <t>A 50728-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5774,10 +5774,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44804</v>
+        <v>45946</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.7</v>
+        <v>15.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5833,7 +5833,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 5082-2024</t>
+          <t>A 50304-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5847,10 +5847,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45330</v>
+        <v>45600</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 1664-2026</t>
+          <t>A 8747-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5920,10 +5920,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46034</v>
+        <v>45356</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5996,7 +5996,7 @@
         <v>45875</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 6781-2022</t>
+          <t>A 38510-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6066,10 +6066,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44602</v>
+        <v>45884</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6125,7 +6125,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 41347-2023</t>
+          <t>A 58779-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6139,10 +6139,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45174</v>
+        <v>45986</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>6.2</v>
+        <v>1.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6198,7 +6198,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 55918-2025</t>
+          <t>A 4992-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6212,10 +6212,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45973</v>
+        <v>44958</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6271,7 +6271,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 50440-2022</t>
+          <t>A 56240-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6285,10 +6285,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44866</v>
+        <v>45974</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>8.699999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6344,7 +6344,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 4992-2023</t>
+          <t>A 58249-2021</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6358,10 +6358,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44958</v>
+        <v>44487</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6417,7 +6417,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 56240-2025</t>
+          <t>A 55918-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6431,10 +6431,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45974</v>
+        <v>45973</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6447,7 +6447,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6490,7 +6490,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 56554-2025</t>
+          <t>A 9641-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6504,10 +6504,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45975</v>
+        <v>46070</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6519,8 +6519,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>7.2</v>
+        <v>0.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6563,7 +6568,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 57012-2025</t>
+          <t>A 9624-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6577,10 +6582,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45978</v>
+        <v>46070</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6592,8 +6597,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6636,7 +6646,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 58780-2025</t>
+          <t>A 9627-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6650,10 +6660,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45986</v>
+        <v>46070</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6665,8 +6675,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6709,7 +6724,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 30101-2024</t>
+          <t>A 56554-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6719,14 +6734,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45489</v>
+        <v>45975</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6739,7 +6754,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.7</v>
+        <v>7.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6782,7 +6797,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 61411-2025</t>
+          <t>A 19307-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6796,10 +6811,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46000</v>
+        <v>45049</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6812,7 +6827,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6855,7 +6870,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 27036-2023</t>
+          <t>A 57012-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6869,10 +6884,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45095</v>
+        <v>45978</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6885,7 +6900,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6928,7 +6943,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 33575-2022</t>
+          <t>A 25487-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6942,10 +6957,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44789</v>
+        <v>44732</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6958,7 +6973,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.4</v>
+        <v>7.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7001,7 +7016,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 58779-2025</t>
+          <t>A 58970-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7015,10 +7030,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45986</v>
+        <v>45636</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7031,7 +7046,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7074,7 +7089,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 11157-2024</t>
+          <t>A 29066-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7088,10 +7103,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45371</v>
+        <v>44750</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7104,7 +7119,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7147,7 +7162,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 11163-2024</t>
+          <t>A 34083-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7161,10 +7176,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45371</v>
+        <v>45125</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7177,7 +7192,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7220,7 +7235,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 9641-2026</t>
+          <t>A 58780-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7234,10 +7249,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46070</v>
+        <v>45986</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7249,13 +7264,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7298,7 +7308,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 9624-2026</t>
+          <t>A 49758-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7312,10 +7322,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46070</v>
+        <v>45597</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7327,13 +7337,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7376,7 +7381,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 9627-2026</t>
+          <t>A 25837-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7390,10 +7395,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46070</v>
+        <v>45090</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7405,13 +7410,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7454,7 +7454,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 31772-2023</t>
+          <t>A 23625-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7468,10 +7468,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45118</v>
+        <v>44721</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7527,7 +7527,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 30314-2024</t>
+          <t>A 47856-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7541,10 +7541,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45490</v>
+        <v>44855</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7600,7 +7600,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 11667-2026</t>
+          <t>A 41323-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7614,10 +7614,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46084</v>
+        <v>44826</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7673,7 +7673,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 64481-2023</t>
+          <t>A 11667-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7687,10 +7687,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45280</v>
+        <v>46084</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>5.5</v>
+        <v>1.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7746,7 +7746,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 32177-2024</t>
+          <t>A 61411-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7760,10 +7760,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45511</v>
+        <v>46000</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7819,7 +7819,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 60859-2024</t>
+          <t>A 61677-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7833,10 +7833,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45644</v>
+        <v>46002</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7892,7 +7892,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 13600-2026</t>
+          <t>A 61682-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7906,10 +7906,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46097</v>
+        <v>46002</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7921,13 +7921,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7970,7 +7965,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 55074-2023</t>
+          <t>A 61792-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7984,10 +7979,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45237</v>
+        <v>46002</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8000,7 +7995,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.9</v>
+        <v>10.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8043,7 +8038,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 5818-2023</t>
+          <t>A 13600-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8057,10 +8052,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44963</v>
+        <v>46097</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8072,8 +8067,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8116,7 +8116,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 62045-2022</t>
+          <t>A 63220-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8130,10 +8130,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44918</v>
+        <v>46010</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8189,7 +8189,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 40244-2024</t>
+          <t>A 16303-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45554</v>
+        <v>45028</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.9</v>
+        <v>6.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8262,7 +8262,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 41323-2022</t>
+          <t>A 51901-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8276,10 +8276,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44826</v>
+        <v>44872</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.1</v>
+        <v>7.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8335,7 +8335,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 4293-2022</t>
+          <t>A 41918-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8349,10 +8349,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44588</v>
+        <v>44830</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 17402-2026</t>
+          <t>A 57730-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8422,10 +8422,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46120</v>
+        <v>45246</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8481,7 +8481,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 27264-2023</t>
+          <t>A 6763-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8495,10 +8495,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45096</v>
+        <v>45700</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8554,7 +8554,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 18473-2026</t>
+          <t>A 42280-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8568,10 +8568,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46127</v>
+        <v>45180</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8627,7 +8627,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 19171-2026</t>
+          <t>A 17402-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8641,10 +8641,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46132</v>
+        <v>46120</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>22.2</v>
+        <v>2.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 37864-2025</t>
+          <t>A 27258-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8714,10 +8714,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45881</v>
+        <v>45096</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8773,7 +8773,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 18337-2026</t>
+          <t>A 18473-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8787,10 +8787,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8803,7 +8803,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>4.1</v>
+        <v>1.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8846,7 +8846,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 54833-2024</t>
+          <t>A 48188-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8860,10 +8860,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45618</v>
+        <v>44853</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8875,13 +8875,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8924,7 +8919,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 58356-2022</t>
+          <t>A 19171-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8938,10 +8933,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44893</v>
+        <v>46132</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8954,7 +8949,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.5</v>
+        <v>22.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -8997,7 +8992,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 20078-2022</t>
+          <t>A 26746-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9011,10 +9006,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44698</v>
+        <v>45093</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9027,7 +9022,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9070,7 +9065,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 61532-2023</t>
+          <t>A 18337-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9080,14 +9075,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45265</v>
+        <v>46125</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9099,13 +9094,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9148,7 +9138,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 36905-2024</t>
+          <t>A 54833-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9162,10 +9152,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45538</v>
+        <v>45618</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9177,8 +9167,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9221,7 +9216,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 21076-2025</t>
+          <t>A 11157-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9235,10 +9230,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45777</v>
+        <v>45371</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9251,7 +9246,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9294,7 +9289,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 35325-2023</t>
+          <t>A 11163-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9308,10 +9303,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45146</v>
+        <v>45371</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9324,7 +9319,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9367,7 +9362,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 73961-2021</t>
+          <t>A 21076-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9381,10 +9376,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44553</v>
+        <v>45777</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9396,13 +9391,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>5.1</v>
+        <v>2.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9445,7 +9435,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 27258-2023</t>
+          <t>A 22650-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9459,10 +9449,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45096</v>
+        <v>45447</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9475,7 +9465,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.5</v>
+        <v>7.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9518,7 +9508,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 29066-2022</t>
+          <t>A 37963-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9532,10 +9522,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44750</v>
+        <v>45544</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9548,7 +9538,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9591,7 +9581,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 37963-2024</t>
+          <t>A 36905-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9605,10 +9595,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45544</v>
+        <v>45538</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9621,7 +9611,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>5.3</v>
+        <v>2.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9681,7 +9671,7 @@
         <v>45322</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9737,7 +9727,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 42618-2025</t>
+          <t>A 61532-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9747,14 +9737,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45905</v>
+        <v>45265</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9766,8 +9756,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9810,7 +9805,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 3504-2023</t>
+          <t>A 26210-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9824,10 +9819,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44950</v>
+        <v>45468</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9840,7 +9835,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9883,7 +9878,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 9828-2025</t>
+          <t>A 42618-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9897,10 +9892,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45716</v>
+        <v>45905</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9913,7 +9908,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9956,7 +9951,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 36653-2022</t>
+          <t>A 60859-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9966,14 +9961,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44804</v>
+        <v>45644</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -9986,7 +9981,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10029,7 +10024,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 23254-2023</t>
+          <t>A 37864-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10043,10 +10038,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45075</v>
+        <v>45881</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10059,7 +10054,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10102,7 +10097,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 64718-2023</t>
+          <t>A 43787-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10116,10 +10111,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45281</v>
+        <v>45187</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10132,7 +10127,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>4.4</v>
+        <v>0.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10175,7 +10170,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 47454-2023</t>
+          <t>A 43760-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10189,10 +10184,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45202</v>
+        <v>45187</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10205,7 +10200,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10248,7 +10243,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 34083-2023</t>
+          <t>A 43790-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10262,10 +10257,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45125</v>
+        <v>45187</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10278,7 +10273,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10321,7 +10316,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 6785-2025</t>
+          <t>A 35325-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10335,10 +10330,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45700</v>
+        <v>45146</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10351,7 +10346,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10394,7 +10389,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 6793-2025</t>
+          <t>A 10996-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10408,10 +10403,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45700</v>
+        <v>45370</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10424,7 +10419,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.9</v>
+        <v>5.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10467,7 +10462,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 59727-2024</t>
+          <t>A 40067-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10481,10 +10476,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45639</v>
+        <v>45168</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10497,7 +10492,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10540,7 +10535,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 23132-2026</t>
+          <t>A 73961-2021</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10554,10 +10549,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46161</v>
+        <v>44553</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10569,8 +10564,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10613,7 +10613,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 15434-2023</t>
+          <t>A 20078-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10627,10 +10627,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45020</v>
+        <v>44698</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10686,7 +10686,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 41918-2022</t>
+          <t>A 6781-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10700,10 +10700,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44830</v>
+        <v>44602</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10759,7 +10759,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 61531-2023</t>
+          <t>A 36406-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10769,14 +10769,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45265</v>
+        <v>44803</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10788,13 +10788,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10837,7 +10832,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 26746-2023</t>
+          <t>A 27036-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10851,10 +10846,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45093</v>
+        <v>45095</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10867,7 +10862,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10910,7 +10905,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 15776-2023</t>
+          <t>A 9828-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10924,10 +10919,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45021</v>
+        <v>45716</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10940,7 +10935,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -10983,7 +10978,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 51901-2022</t>
+          <t>A 43786-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10997,10 +10992,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44872</v>
+        <v>45187</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11013,7 +11008,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>7.3</v>
+        <v>0.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11056,7 +11051,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 26210-2024</t>
+          <t>A 23132-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11070,10 +11065,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45468</v>
+        <v>46161</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11086,7 +11081,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11129,7 +11124,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 16244-2025</t>
+          <t>A 6747-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11143,10 +11138,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45749</v>
+        <v>45700</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11158,13 +11153,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11207,7 +11197,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 41357-2023</t>
+          <t>A 6789-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11221,10 +11211,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45174</v>
+        <v>45700</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11237,7 +11227,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11280,7 +11270,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 6662-2024</t>
+          <t>A 59727-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11294,10 +11284,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45341</v>
+        <v>45639</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11310,7 +11300,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11353,7 +11343,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 8747-2024</t>
+          <t>A 30961-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11367,10 +11357,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45356</v>
+        <v>45113</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11383,7 +11373,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11426,7 +11416,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 56393-2023</t>
+          <t>A 16244-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11440,10 +11430,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45243</v>
+        <v>45749</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11455,8 +11445,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11499,7 +11494,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 32826-2023</t>
+          <t>A 48227-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11513,10 +11508,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45124</v>
+        <v>44858</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11529,7 +11524,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11572,7 +11567,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 1450-2024</t>
+          <t>A 22846-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11586,10 +11581,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45303</v>
+        <v>45448</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11602,7 +11597,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11645,7 +11640,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 27954-2026</t>
+          <t>A 27729-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11655,14 +11650,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46193</v>
+        <v>46191</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11675,7 +11670,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11718,7 +11713,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 27951-2026</t>
+          <t>A 28018-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11732,10 +11727,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46193</v>
+        <v>46195</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11747,13 +11742,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11796,7 +11786,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 27953-2026</t>
+          <t>A 27954-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11813,7 +11803,7 @@
         <v>46193</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11825,13 +11815,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>5.7</v>
+        <v>2.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11874,7 +11859,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 27729-2026</t>
+          <t>A 27951-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11884,14 +11869,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46191</v>
+        <v>46193</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11903,8 +11888,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>5.6</v>
+        <v>1.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11947,7 +11937,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 28026-2026</t>
+          <t>A 61531-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11957,14 +11947,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46195</v>
+        <v>45265</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11976,8 +11966,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12020,7 +12015,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 28018-2026</t>
+          <t>A 28058-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12037,7 +12032,7 @@
         <v>46195</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12050,7 +12045,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12093,7 +12088,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 28058-2026</t>
+          <t>A 27953-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12107,10 +12102,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46195</v>
+        <v>46193</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12122,8 +12117,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>1.3</v>
+        <v>5.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 36406-2022</t>
+          <t>A 28026-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12180,10 +12180,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44803</v>
+        <v>46195</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12239,7 +12239,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 10996-2024</t>
+          <t>A 39668-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12253,10 +12253,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45370</v>
+        <v>45167</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>5.9</v>
+        <v>0.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12312,7 +12312,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 22846-2024</t>
+          <t>A 5818-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12326,10 +12326,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45448</v>
+        <v>44963</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 30091-2024</t>
+          <t>A 5030-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12395,14 +12395,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45489</v>
+        <v>44593</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12458,7 +12458,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 30160-2026</t>
+          <t>A 40244-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12472,10 +12472,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46206</v>
+        <v>45554</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12531,7 +12531,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 48227-2022</t>
+          <t>A 64481-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12545,10 +12545,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44858</v>
+        <v>45280</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12604,7 +12604,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 43758-2023</t>
+          <t>A 30160-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12618,10 +12618,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45187</v>
+        <v>46206</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12677,7 +12677,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 6747-2025</t>
+          <t>A 55074-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12691,10 +12691,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45700</v>
+        <v>45237</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12707,7 +12707,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12750,7 +12750,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 50304-2024</t>
+          <t>A 58356-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12764,10 +12764,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45600</v>
+        <v>44893</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12823,7 +12823,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 43786-2023</t>
+          <t>A 14355-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12837,10 +12837,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45187</v>
+        <v>45012</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12896,7 +12896,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 43787-2023</t>
+          <t>A 13913-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12910,10 +12910,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45187</v>
+        <v>45391</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -12986,7 +12986,7 @@
         <v>45581</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 47856-2022</t>
+          <t>A 13352-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13056,10 +13056,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44855</v>
+        <v>45387</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.1</v>
+        <v>2.1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13115,7 +13115,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 19307-2023</t>
+          <t>A 13610-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13129,10 +13129,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45049</v>
+        <v>45390</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13188,7 +13188,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 56625-2022</t>
+          <t>A 56393-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13202,10 +13202,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44893</v>
+        <v>45243</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13261,7 +13261,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 43790-2023</t>
+          <t>A 36653-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13271,14 +13271,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45187</v>
+        <v>44804</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13334,7 +13334,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 59026-2023</t>
+          <t>A 48229-2022</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13348,10 +13348,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45252</v>
+        <v>44858</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13407,7 +13407,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 58970-2024</t>
+          <t>A 5089-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13421,10 +13421,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45636</v>
+        <v>45330</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13480,7 +13480,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 23259-2023</t>
+          <t>A 58247-2021</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13494,10 +13494,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45075</v>
+        <v>44487</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2.8</v>
+        <v>8.9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13553,7 +13553,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 5030-2022</t>
+          <t>A 31772-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13567,10 +13567,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44593</v>
+        <v>45118</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13626,7 +13626,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 6789-2025</t>
+          <t>A 6662-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13640,10 +13640,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45700</v>
+        <v>45341</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13699,7 +13699,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 58247-2021</t>
+          <t>A 1450-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13713,10 +13713,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44487</v>
+        <v>45303</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>8.9</v>
+        <v>0.9</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13772,7 +13772,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 58249-2021</t>
+          <t>A 31983-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13786,10 +13786,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44487</v>
+        <v>46232</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13802,7 +13802,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -13845,7 +13845,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 25487-2022</t>
+          <t>A 6785-2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13859,10 +13859,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44732</v>
+        <v>45700</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>7.1</v>
+        <v>0.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13918,7 +13918,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 6763-2025</t>
+          <t>A 6793-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13935,7 +13935,7 @@
         <v>45700</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -13948,7 +13948,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -13991,7 +13991,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 13913-2024</t>
+          <t>A 37630-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14005,10 +14005,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45391</v>
+        <v>46276</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14020,8 +14020,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>2.2</v>
+        <v>13.6</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14064,7 +14069,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 43760-2023</t>
+          <t>A 32826-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14078,10 +14083,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45187</v>
+        <v>45124</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14094,7 +14099,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14137,7 +14142,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 43784-2023</t>
+          <t>A 27952-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14151,10 +14156,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45187</v>
+        <v>46193</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14166,8 +14171,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>3.8</v>
+        <v>8.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14210,7 +14220,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 55909-2022</t>
+          <t>A 32177-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14224,10 +14234,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44889</v>
+        <v>45511</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14240,7 +14250,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14283,7 +14293,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 14355-2023</t>
+          <t>A 41357-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14297,10 +14307,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45012</v>
+        <v>45174</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14313,7 +14323,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.6</v>
+        <v>4.1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14356,7 +14366,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 40067-2023</t>
+          <t>A 38885-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14370,10 +14380,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45168</v>
+        <v>46286</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14386,7 +14396,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14429,7 +14439,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 22650-2024</t>
+          <t>A 62045-2022</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14443,10 +14453,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45447</v>
+        <v>44918</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14459,7 +14469,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>7.9</v>
+        <v>2.4</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14502,7 +14512,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 31983-2026</t>
+          <t>A 15434-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14516,10 +14526,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46232</v>
+        <v>45020</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14532,7 +14542,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14575,7 +14585,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 37630-2026</t>
+          <t>A 38886-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14589,10 +14599,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46276</v>
+        <v>46286</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14604,13 +14614,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>13.6</v>
+        <v>1.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14653,7 +14658,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 23625-2022</t>
+          <t>A 23259-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14667,10 +14672,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44721</v>
+        <v>45075</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14683,7 +14688,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14726,7 +14731,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 16303-2023</t>
+          <t>A 32903-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14740,10 +14745,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45028</v>
+        <v>46244</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14756,7 +14761,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>6.3</v>
+        <v>0.9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -14799,7 +14804,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 5707-2022</t>
+          <t>A 32913-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14813,10 +14818,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44596</v>
+        <v>46244</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14829,7 +14834,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -14872,7 +14877,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 27952-2026</t>
+          <t>A 23138-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14886,10 +14891,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46193</v>
+        <v>46161</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14901,13 +14906,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I194" t="n">
-        <v>8.5</v>
+        <v>2.3</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -14950,7 +14950,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 8119-2025</t>
+          <t>A 30314-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -14964,10 +14964,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45707</v>
+        <v>45490</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -14980,7 +14980,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15023,7 +15023,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 270-2023</t>
+          <t>A 20948-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15037,10 +15037,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44928</v>
+        <v>45439</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.9</v>
+        <v>6.4</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15113,7 +15113,7 @@
         <v>46283</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 38885-2026</t>
+          <t>A 39453-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15188,10 +15188,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15247,7 +15247,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 23138-2026</t>
+          <t>A 8119-2025</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15261,10 +15261,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46161</v>
+        <v>45707</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15320,7 +15320,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 38886-2026</t>
+          <t>A 270-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15334,10 +15334,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46286</v>
+        <v>44928</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15393,7 +15393,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 32913-2026</t>
+          <t>A 29707-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15403,14 +15403,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46244</v>
+        <v>45485</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2.7</v>
+        <v>7.7</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15466,7 +15466,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 32903-2026</t>
+          <t>A 18314-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15480,10 +15480,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46244</v>
+        <v>45422</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15496,7 +15496,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15539,7 +15539,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 39453-2026</t>
+          <t>A 27498-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15553,10 +15553,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46288</v>
+        <v>46185</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15568,8 +15568,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I203" t="n">
-        <v>0.5</v>
+        <v>38</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15612,24 +15617,24 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 27498-2026</t>
+          <t>S 2580-2020</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46185</v>
+        <v>44166</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15641,13 +15646,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I204" t="n">
-        <v>38</v>
+        <v>0.1</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15690,7 +15690,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>S 2580-2020</t>
+          <t>S 2956-2022</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15700,14 +15700,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44166</v>
+        <v>44712</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15719,8 +15719,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>0.1</v>
+        <v>42.7</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -15763,7 +15768,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>S 2956-2022</t>
+          <t>S 2912-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -15777,10 +15782,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44712</v>
+        <v>44711</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15798,7 +15803,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>42.7</v>
+        <v>33.4</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -15841,7 +15846,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>S 2912-2022</t>
+          <t>S 1256-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15855,10 +15860,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44711</v>
+        <v>45763</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15870,13 +15875,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I207" t="n">
-        <v>33.4</v>
+        <v>9</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -15919,7 +15919,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>S 1256-2025</t>
+          <t>S 1619-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -15933,10 +15933,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45763</v>
+        <v>45798</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15948,8 +15948,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>9</v>
+        <v>43.9</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -15989,10 +15994,10 @@
       </c>
       <c r="V208" s="2" t="inlineStr"/>
     </row>
-    <row r="209" ht="15" customHeight="1">
+    <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>S 1619-2025</t>
+          <t>S 1452-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16006,10 +16011,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45798</v>
+        <v>46160</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16027,7 +16032,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>43.9</v>
+        <v>43.3</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16066,84 +16071,6 @@
         <v>0</v>
       </c>
       <c r="V209" s="2" t="inlineStr"/>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>S 1452-2026</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D210" s="1" t="n">
-        <v>46160</v>
-      </c>
-      <c r="E210" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>GNOSJÖ</t>
-        </is>
-      </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I210" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="J210" t="n">
-        <v>0</v>
-      </c>
-      <c r="K210" t="n">
-        <v>0</v>
-      </c>
-      <c r="L210" t="n">
-        <v>0</v>
-      </c>
-      <c r="M210" t="n">
-        <v>0</v>
-      </c>
-      <c r="N210" t="n">
-        <v>0</v>
-      </c>
-      <c r="O210" t="n">
-        <v>0</v>
-      </c>
-      <c r="P210" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
-      <c r="R210" t="n">
-        <v>0</v>
-      </c>
-      <c r="S210" t="n">
-        <v>0</v>
-      </c>
-      <c r="T210" t="n">
-        <v>0</v>
-      </c>
-      <c r="U210" t="n">
-        <v>0</v>
-      </c>
-      <c r="V210" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt GNOSJÖ.xlsx
+++ b/Översikt GNOSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44757</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46030</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44711</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 28312-2025</t>
+          <t>A 38355-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -919,14 +919,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45818</v>
+        <v>45161</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -954,7 +954,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -963,264 +963,264 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 38355-2023 artfynd.xlsx", "A 38355-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 38355-2023 karta.png", "A 38355-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 38355-2023 georefererad karta.tif", "A 38355-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 38355-2023 FSC-klagomål.docx", "A 38355-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 38355-2023 FSC-klagomål mail.docx", "A 38355-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 38355-2023 tillsynsbegäran.docx", "A 38355-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 38355-2023 tillsynsbegäran mail.docx", "A 38355-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 23612-2022</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>44721</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>GNOSJÖ</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 23612-2022 artfynd.xlsx", "A 23612-2022")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 23612-2022 karta.png", "A 23612-2022")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 23612-2022 georefererad karta.tif", "A 23612-2022")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 23612-2022 FSC-klagomål.docx", "A 23612-2022")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 23612-2022 FSC-klagomål mail.docx", "A 23612-2022")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 23612-2022 tillsynsbegäran.docx", "A 23612-2022")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 23612-2022 tillsynsbegäran mail.docx", "A 23612-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 28312-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45818</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>GNOSJÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
         <v>3</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 28312-2025 artfynd.xlsx", "A 28312-2025")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 28312-2025 karta.png", "A 28312-2025")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 28312-2025 georefererad karta.tif", "A 28312-2025")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 28312-2025 FSC-klagomål.docx", "A 28312-2025")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 28312-2025 FSC-klagomål mail.docx", "A 28312-2025")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 28312-2025 tillsynsbegäran.docx", "A 28312-2025")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 28312-2025 tillsynsbegäran mail.docx", "A 28312-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 38355-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45161</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>GNOSJÖ</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Mattlummer</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 38355-2023 artfynd.xlsx", "A 38355-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 38355-2023 karta.png", "A 38355-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 38355-2023 georefererad karta.tif", "A 38355-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 38355-2023 FSC-klagomål.docx", "A 38355-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 38355-2023 FSC-klagomål mail.docx", "A 38355-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 38355-2023 tillsynsbegäran.docx", "A 38355-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 38355-2023 tillsynsbegäran mail.docx", "A 38355-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 23612-2022</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>44721</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>GNOSJÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 23612-2022 artfynd.xlsx", "A 23612-2022")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 23612-2022 karta.png", "A 23612-2022")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 23612-2022 georefererad karta.tif", "A 23612-2022")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 23612-2022 FSC-klagomål.docx", "A 23612-2022")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 23612-2022 FSC-klagomål mail.docx", "A 23612-2022")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 23612-2022 tillsynsbegäran.docx", "A 23612-2022")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 23612-2022 tillsynsbegäran mail.docx", "A 23612-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>44530</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>44837</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>44482</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>44474</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 50444-2022</t>
+          <t>A 3418-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44866</v>
+        <v>44585</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1545,8 +1545,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1589,7 +1594,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 3418-2022</t>
+          <t>A 50444-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1603,10 +1608,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44585</v>
+        <v>44866</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1618,13 +1623,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1684,7 +1684,7 @@
         <v>44503</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 59855-2021</t>
+          <t>A 54376-2021</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44494</v>
+        <v>44470</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 20077-2022</t>
+          <t>A 704-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1827,10 +1827,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44698</v>
+        <v>44568</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1886,7 +1886,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 54376-2021</t>
+          <t>A 20080-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44470</v>
+        <v>44698</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1959,7 +1959,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 20080-2022</t>
+          <t>A 59855-2021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44698</v>
+        <v>44494</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2032,7 +2032,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 704-2022</t>
+          <t>A 20077-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44568</v>
+        <v>44698</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2105,7 +2105,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 36525-2022</t>
+          <t>A 28372-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44804</v>
+        <v>44747</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2178,7 +2178,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 47858-2022</t>
+          <t>A 36525-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2192,10 +2192,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44855</v>
+        <v>44804</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2251,7 +2251,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 28372-2022</t>
+          <t>A 4298-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44747</v>
+        <v>44588</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2324,7 +2324,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 4298-2022</t>
+          <t>A 47858-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44588</v>
+        <v>44855</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2397,7 +2397,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 48480-2022</t>
+          <t>A 13352-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44858</v>
+        <v>45387</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2470,7 +2470,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 54362-2021</t>
+          <t>A 42280-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44470</v>
+        <v>45180</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 16243-2025</t>
+          <t>A 46657-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45749</v>
+        <v>44850</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2572,13 +2572,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>2.1</v>
+        <v>7.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2621,7 +2616,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 47454-2023</t>
+          <t>A 48480-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2635,10 +2630,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45202</v>
+        <v>44858</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2651,7 +2646,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2694,7 +2689,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33575-2022</t>
+          <t>A 54362-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2708,10 +2703,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44789</v>
+        <v>44470</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2724,7 +2719,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2767,7 +2762,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 59026-2023</t>
+          <t>A 6781-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2781,10 +2776,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45252</v>
+        <v>44602</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2797,7 +2792,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2840,7 +2835,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 43758-2023</t>
+          <t>A 41347-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2854,10 +2849,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45187</v>
+        <v>45174</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2870,7 +2865,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>6.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2913,7 +2908,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 43784-2023</t>
+          <t>A 20948-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2927,10 +2922,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45187</v>
+        <v>45439</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2943,7 +2938,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.8</v>
+        <v>6.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2986,7 +2981,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 23254-2023</t>
+          <t>A 5089-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3000,10 +2995,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45075</v>
+        <v>45330</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3016,7 +3011,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3059,7 +3054,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 63511-2025</t>
+          <t>A 50440-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3073,10 +3068,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46013</v>
+        <v>44866</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3089,7 +3084,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3132,7 +3127,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 64718-2023</t>
+          <t>A 4992-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3146,10 +3141,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45281</v>
+        <v>44958</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3162,7 +3157,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3205,7 +3200,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 46657-2022</t>
+          <t>A 43790-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3219,10 +3214,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44850</v>
+        <v>45187</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3235,7 +3230,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>7.9</v>
+        <v>3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3278,7 +3273,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 3504-2023</t>
+          <t>A 47454-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3292,10 +3287,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44950</v>
+        <v>45202</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3308,7 +3303,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3351,7 +3346,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 27264-2023</t>
+          <t>A 59026-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3365,10 +3360,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45096</v>
+        <v>45252</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3381,7 +3376,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3424,7 +3419,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 15776-2023</t>
+          <t>A 58970-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3438,10 +3433,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45021</v>
+        <v>45636</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3454,7 +3449,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3497,7 +3492,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 5082-2024</t>
+          <t>A 23259-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3511,10 +3506,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45330</v>
+        <v>45075</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3527,7 +3522,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3570,7 +3565,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 41347-2023</t>
+          <t>A 34083-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3584,10 +3579,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45174</v>
+        <v>45125</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3600,7 +3595,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>6.2</v>
+        <v>2.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3643,7 +3638,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 30091-2024</t>
+          <t>A 5030-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3653,14 +3648,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45489</v>
+        <v>44593</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3673,7 +3668,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3716,7 +3711,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 6415-2025</t>
+          <t>A 62053-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3730,10 +3725,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45699</v>
+        <v>44918</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3746,7 +3741,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3789,7 +3784,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 8698-2025</t>
+          <t>A 6785-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3803,10 +3798,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45712</v>
+        <v>45700</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3819,7 +3814,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3862,7 +3857,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 50440-2022</t>
+          <t>A 6793-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3876,10 +3871,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44866</v>
+        <v>45700</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3892,7 +3887,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>8.699999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3935,7 +3930,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 5707-2022</t>
+          <t>A 59727-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3949,10 +3944,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44596</v>
+        <v>45639</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3965,7 +3960,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4008,7 +4003,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 24861-2025</t>
+          <t>A 15434-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4022,10 +4017,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45799</v>
+        <v>45020</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4038,7 +4033,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4081,7 +4076,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 40552-2025</t>
+          <t>A 30101-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4091,14 +4086,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45896</v>
+        <v>45489</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4154,7 +4149,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 40863-2025</t>
+          <t>A 6789-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4168,10 +4163,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45897</v>
+        <v>45700</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4184,7 +4179,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4227,7 +4222,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 25482-2025</t>
+          <t>A 58247-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4241,10 +4236,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45802</v>
+        <v>44487</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4257,7 +4252,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>8.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4300,7 +4295,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 21080-2025</t>
+          <t>A 58249-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4314,10 +4309,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45777</v>
+        <v>44487</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4330,7 +4325,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4373,7 +4368,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 15436-2024</t>
+          <t>A 25487-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4387,10 +4382,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45401</v>
+        <v>44732</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4403,7 +4398,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.2</v>
+        <v>7.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4446,7 +4441,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 1664-2026</t>
+          <t>A 6763-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4460,10 +4455,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46034</v>
+        <v>45700</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4476,7 +4471,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4519,7 +4514,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 42615-2025</t>
+          <t>A 41918-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4533,10 +4528,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45905</v>
+        <v>44830</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4549,7 +4544,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4592,7 +4587,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 43637-2025</t>
+          <t>A 61531-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4602,14 +4597,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45911</v>
+        <v>45265</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4621,8 +4616,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>4.6</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4665,7 +4665,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 43656-2025</t>
+          <t>A 26746-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4679,10 +4679,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45912</v>
+        <v>45093</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4738,7 +4738,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 56625-2022</t>
+          <t>A 15776-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4752,10 +4752,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44893</v>
+        <v>45021</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4811,7 +4811,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 55909-2022</t>
+          <t>A 13913-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44889</v>
+        <v>45391</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4884,7 +4884,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 7316-2024</t>
+          <t>A 27036-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45345</v>
+        <v>45095</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4957,7 +4957,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 44383-2025</t>
+          <t>A 33575-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4971,10 +4971,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45916</v>
+        <v>44789</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5030,7 +5030,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 44394-2025</t>
+          <t>A 43760-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5044,10 +5044,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45916</v>
+        <v>45187</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5103,7 +5103,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 30101-2024</t>
+          <t>A 43784-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5113,14 +5113,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45489</v>
+        <v>45187</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5176,7 +5176,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 30669-2025</t>
+          <t>A 55909-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5190,10 +5190,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45831</v>
+        <v>44889</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5249,7 +5249,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 30654-2025</t>
+          <t>A 51901-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5263,10 +5263,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45831</v>
+        <v>44872</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>7.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5322,7 +5322,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 31235-2025</t>
+          <t>A 14355-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5336,10 +5336,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45832</v>
+        <v>45012</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5395,7 +5395,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 31228-2025</t>
+          <t>A 26210-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45832</v>
+        <v>45468</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5468,7 +5468,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 62053-2022</t>
+          <t>A 16244-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5482,10 +5482,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44918</v>
+        <v>45749</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5497,8 +5497,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5541,7 +5546,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 4293-2022</t>
+          <t>A 11157-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5555,10 +5560,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44588</v>
+        <v>45371</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5571,7 +5576,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5614,7 +5619,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 27675-2025</t>
+          <t>A 39668-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5628,10 +5633,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45813</v>
+        <v>45167</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5644,7 +5649,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.1</v>
+        <v>0.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5687,7 +5692,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 36508-2022</t>
+          <t>A 11163-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5701,10 +5706,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44804</v>
+        <v>45371</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5717,7 +5722,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5760,7 +5765,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 50728-2025</t>
+          <t>A 40067-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5774,10 +5779,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45946</v>
+        <v>45168</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5790,7 +5795,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>15.2</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5833,7 +5838,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 50304-2024</t>
+          <t>A 22650-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5847,10 +5852,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45600</v>
+        <v>45447</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5863,7 +5868,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.6</v>
+        <v>7.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5906,7 +5911,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 8747-2024</t>
+          <t>A 41357-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5920,10 +5925,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45356</v>
+        <v>45174</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5936,7 +5941,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5979,7 +5984,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 37198-2025</t>
+          <t>A 48188-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5993,10 +5998,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45875</v>
+        <v>44853</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6009,7 +6014,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6052,7 +6057,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 38510-2025</t>
+          <t>A 25837-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6066,10 +6071,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45884</v>
+        <v>45090</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6082,7 +6087,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6125,7 +6130,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 58779-2025</t>
+          <t>A 57730-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6139,10 +6144,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45986</v>
+        <v>45246</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6155,7 +6160,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6198,7 +6203,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 4992-2023</t>
+          <t>A 23625-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6212,10 +6217,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44958</v>
+        <v>44721</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6228,7 +6233,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6271,7 +6276,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 56240-2025</t>
+          <t>A 16303-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6285,10 +6290,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45974</v>
+        <v>45028</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6301,7 +6306,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.5</v>
+        <v>6.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6344,7 +6349,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 58249-2021</t>
+          <t>A 31772-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6358,10 +6363,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44487</v>
+        <v>45118</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6374,7 +6379,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6417,7 +6422,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 55918-2025</t>
+          <t>A 6662-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6431,10 +6436,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45973</v>
+        <v>45341</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6447,7 +6452,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6490,7 +6495,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 9641-2026</t>
+          <t>A 30314-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6504,10 +6509,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46070</v>
+        <v>45490</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6519,13 +6524,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6568,7 +6568,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 9624-2026</t>
+          <t>A 5707-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6582,10 +6582,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46070</v>
+        <v>44596</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6597,13 +6597,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6646,7 +6641,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 9627-2026</t>
+          <t>A 8747-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6660,10 +6655,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46070</v>
+        <v>45356</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6675,13 +6670,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6724,7 +6714,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 56554-2025</t>
+          <t>A 64481-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6738,10 +6728,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45975</v>
+        <v>45280</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6754,7 +6744,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6797,7 +6787,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 19307-2023</t>
+          <t>A 32177-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6811,10 +6801,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45049</v>
+        <v>45511</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6827,7 +6817,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6870,7 +6860,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 57012-2025</t>
+          <t>A 8119-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6884,10 +6874,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45978</v>
+        <v>45707</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6900,7 +6890,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6943,7 +6933,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 25487-2022</t>
+          <t>A 60859-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6957,10 +6947,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44732</v>
+        <v>45644</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6973,7 +6963,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>7.1</v>
+        <v>3.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7016,7 +7006,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 58970-2024</t>
+          <t>A 270-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7030,10 +7020,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45636</v>
+        <v>44928</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7046,7 +7036,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7089,7 +7079,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 29066-2022</t>
+          <t>A 56393-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7103,10 +7093,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44750</v>
+        <v>45243</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7119,7 +7109,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7162,7 +7152,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 34083-2023</t>
+          <t>A 32826-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7176,10 +7166,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45125</v>
+        <v>45124</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7192,7 +7182,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7235,7 +7225,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 58780-2025</t>
+          <t>A 55074-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7249,10 +7239,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45986</v>
+        <v>45237</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7265,7 +7255,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7308,7 +7298,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 49758-2024</t>
+          <t>A 1450-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7322,10 +7312,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45597</v>
+        <v>45303</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7338,7 +7328,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7381,7 +7371,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 25837-2023</t>
+          <t>A 18314-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7395,10 +7385,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45090</v>
+        <v>45422</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7411,7 +7401,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7454,7 +7444,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 23625-2022</t>
+          <t>A 29707-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7464,14 +7454,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44721</v>
+        <v>45485</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7484,7 +7474,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>7.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7527,7 +7517,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 47856-2022</t>
+          <t>A 5818-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7541,10 +7531,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44855</v>
+        <v>44963</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7557,7 +7547,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7600,7 +7590,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 41323-2022</t>
+          <t>A 62045-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7614,10 +7604,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44826</v>
+        <v>44918</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7630,7 +7620,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7673,7 +7663,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 11667-2026</t>
+          <t>A 40244-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7687,10 +7677,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46084</v>
+        <v>45554</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7703,7 +7693,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7746,7 +7736,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 61411-2025</t>
+          <t>A 30961-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7760,10 +7750,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46000</v>
+        <v>45113</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7776,7 +7766,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7819,7 +7809,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 61677-2025</t>
+          <t>A 13610-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7833,10 +7823,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46002</v>
+        <v>45390</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7849,7 +7839,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7892,7 +7882,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 61682-2025</t>
+          <t>A 49758-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7906,10 +7896,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46002</v>
+        <v>45597</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7922,7 +7912,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7965,7 +7955,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 61792-2025</t>
+          <t>A 48229-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7979,10 +7969,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46002</v>
+        <v>44858</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -7995,7 +7985,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>10.6</v>
+        <v>3.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8038,7 +8028,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 13600-2026</t>
+          <t>A 41323-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8052,10 +8042,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46097</v>
+        <v>44826</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8067,13 +8057,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8116,7 +8101,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 63220-2025</t>
+          <t>A 4293-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8130,10 +8115,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46010</v>
+        <v>44588</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8146,7 +8131,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8189,7 +8174,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 16303-2023</t>
+          <t>A 24861-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8203,10 +8188,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45028</v>
+        <v>45799</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8219,7 +8204,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8262,7 +8247,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 51901-2022</t>
+          <t>A 25482-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8276,10 +8261,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44872</v>
+        <v>45802</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8292,7 +8277,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8335,7 +8320,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 41918-2022</t>
+          <t>A 36406-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8349,10 +8334,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44830</v>
+        <v>44803</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8365,7 +8350,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8408,7 +8393,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 57730-2023</t>
+          <t>A 27264-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8422,10 +8407,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45246</v>
+        <v>45096</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8438,7 +8423,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8481,7 +8466,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 6763-2025</t>
+          <t>A 15436-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8495,10 +8480,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45700</v>
+        <v>45401</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8511,7 +8496,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8554,7 +8539,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 42280-2023</t>
+          <t>A 10996-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8568,10 +8553,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45180</v>
+        <v>45370</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8584,7 +8569,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.9</v>
+        <v>5.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8627,7 +8612,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 17402-2026</t>
+          <t>A 22846-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8641,10 +8626,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46120</v>
+        <v>45448</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8657,7 +8642,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8700,7 +8685,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 27258-2023</t>
+          <t>A 30091-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8710,14 +8695,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45096</v>
+        <v>45489</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8730,7 +8715,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8773,7 +8758,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 18473-2026</t>
+          <t>A 7316-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8787,10 +8772,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46127</v>
+        <v>45345</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8803,7 +8788,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8846,7 +8831,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 48188-2022</t>
+          <t>A 48227-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8860,10 +8845,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44853</v>
+        <v>44858</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8876,7 +8861,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8919,7 +8904,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 19171-2026</t>
+          <t>A 58356-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8933,10 +8918,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46132</v>
+        <v>44893</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8949,7 +8934,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>22.2</v>
+        <v>2.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -8992,7 +8977,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 26746-2023</t>
+          <t>A 43758-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9006,10 +8991,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45093</v>
+        <v>45187</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9022,7 +9007,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9065,7 +9050,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 18337-2026</t>
+          <t>A 6747-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9079,10 +9064,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46125</v>
+        <v>45700</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9095,7 +9080,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9138,7 +9123,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 54833-2024</t>
+          <t>A 20078-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9152,10 +9137,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45618</v>
+        <v>44698</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9167,13 +9152,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9216,7 +9196,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 11157-2024</t>
+          <t>A 50304-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9230,10 +9210,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45371</v>
+        <v>45600</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9246,7 +9226,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9289,7 +9269,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 11163-2024</t>
+          <t>A 30654-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9303,10 +9283,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45371</v>
+        <v>45831</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9319,7 +9299,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9362,7 +9342,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 21076-2025</t>
+          <t>A 30669-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9376,10 +9356,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45777</v>
+        <v>45831</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9392,7 +9372,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9435,7 +9415,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 22650-2024</t>
+          <t>A 31228-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9449,10 +9429,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45447</v>
+        <v>45832</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9465,7 +9445,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>7.9</v>
+        <v>0.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9508,7 +9488,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 37963-2024</t>
+          <t>A 31235-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9522,10 +9502,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45544</v>
+        <v>45832</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9538,7 +9518,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9581,7 +9561,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 36905-2024</t>
+          <t>A 16243-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9595,10 +9575,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45538</v>
+        <v>45749</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9610,8 +9590,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9654,7 +9639,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 3987-2024</t>
+          <t>A 43786-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9668,10 +9653,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45322</v>
+        <v>45187</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9684,7 +9669,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9727,7 +9712,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 61532-2023</t>
+          <t>A 43787-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9737,14 +9722,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45265</v>
+        <v>45187</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9756,13 +9741,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9805,7 +9785,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 26210-2024</t>
+          <t>A 35325-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9819,10 +9799,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45468</v>
+        <v>45146</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9835,7 +9815,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9878,7 +9858,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 42618-2025</t>
+          <t>A 73961-2021</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9892,10 +9872,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45905</v>
+        <v>44553</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9907,8 +9887,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9951,7 +9936,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 60859-2024</t>
+          <t>A 46254-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9965,10 +9950,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45644</v>
+        <v>45581</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -9981,7 +9966,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10024,7 +10009,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 37864-2025</t>
+          <t>A 27258-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10038,10 +10023,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45881</v>
+        <v>45096</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10054,7 +10039,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10097,7 +10082,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 43787-2023</t>
+          <t>A 47856-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10111,10 +10096,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45187</v>
+        <v>44855</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10127,7 +10112,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10170,7 +10155,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 43760-2023</t>
+          <t>A 29066-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10184,10 +10169,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45187</v>
+        <v>44750</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10200,7 +10185,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.9</v>
+        <v>4.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10243,7 +10228,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 43790-2023</t>
+          <t>A 19307-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10257,10 +10242,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45187</v>
+        <v>45049</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10273,7 +10258,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10316,7 +10301,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 35325-2023</t>
+          <t>A 27675-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10330,10 +10315,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45146</v>
+        <v>45813</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10346,7 +10331,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10389,7 +10374,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 10996-2024</t>
+          <t>A 56625-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10403,10 +10388,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45370</v>
+        <v>44893</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10419,7 +10404,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>5.9</v>
+        <v>0.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10462,7 +10447,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 40067-2023</t>
+          <t>A 3504-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10476,10 +10461,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45168</v>
+        <v>44950</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10535,7 +10520,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 73961-2021</t>
+          <t>A 36508-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10549,10 +10534,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44553</v>
+        <v>44804</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10564,13 +10549,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>5.1</v>
+        <v>2.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10613,7 +10593,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 20078-2022</t>
+          <t>A 9828-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10627,10 +10607,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44698</v>
+        <v>45716</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10643,7 +10623,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10686,7 +10666,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 6781-2022</t>
+          <t>A 36653-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10696,14 +10676,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44602</v>
+        <v>44804</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10716,7 +10696,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10759,7 +10739,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 36406-2022</t>
+          <t>A 8698-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10773,10 +10753,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44803</v>
+        <v>45712</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10789,7 +10769,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10832,7 +10812,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 27036-2023</t>
+          <t>A 23254-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10846,10 +10826,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45095</v>
+        <v>45075</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10862,7 +10842,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10905,7 +10885,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 9828-2025</t>
+          <t>A 64718-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10919,10 +10899,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45716</v>
+        <v>45281</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10935,7 +10915,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.4</v>
+        <v>4.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -10978,7 +10958,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 43786-2023</t>
+          <t>A 5082-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10992,10 +10972,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45187</v>
+        <v>45330</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11008,7 +10988,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11051,7 +11031,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 23132-2026</t>
+          <t>A 38510-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11065,10 +11045,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46161</v>
+        <v>45884</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11081,7 +11061,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11124,7 +11104,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 6747-2025</t>
+          <t>A 37198-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11138,10 +11118,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45700</v>
+        <v>45875</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11154,7 +11134,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11197,7 +11177,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 6789-2025</t>
+          <t>A 6415-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11211,10 +11191,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45700</v>
+        <v>45699</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11227,7 +11207,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11270,7 +11250,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 59727-2024</t>
+          <t>A 50728-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11284,10 +11264,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45639</v>
+        <v>45946</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11300,7 +11280,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.3</v>
+        <v>15.2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11343,7 +11323,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 30961-2023</t>
+          <t>A 40863-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11357,10 +11337,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45113</v>
+        <v>45897</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11373,7 +11353,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11416,7 +11396,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 16244-2025</t>
+          <t>A 40552-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11430,10 +11410,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45749</v>
+        <v>45896</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11445,13 +11425,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11494,7 +11469,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 48227-2022</t>
+          <t>A 21080-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11508,10 +11483,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44858</v>
+        <v>45777</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11524,7 +11499,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11567,7 +11542,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 22846-2024</t>
+          <t>A 42615-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11581,10 +11556,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45448</v>
+        <v>45905</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11597,7 +11572,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11640,7 +11615,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 27729-2026</t>
+          <t>A 43637-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11650,14 +11625,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46191</v>
+        <v>45911</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11670,7 +11645,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11713,7 +11688,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 28018-2026</t>
+          <t>A 43656-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11727,10 +11702,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46195</v>
+        <v>45912</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11786,7 +11761,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 27954-2026</t>
+          <t>A 44383-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11800,10 +11775,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46193</v>
+        <v>45916</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11816,7 +11791,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11859,7 +11834,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 27951-2026</t>
+          <t>A 44394-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11873,10 +11848,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46193</v>
+        <v>45916</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11888,13 +11863,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11937,7 +11907,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 61531-2023</t>
+          <t>A 55918-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11947,14 +11917,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45265</v>
+        <v>45973</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11966,13 +11936,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12015,7 +11980,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 28058-2026</t>
+          <t>A 56240-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12029,10 +11994,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46195</v>
+        <v>45974</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12045,7 +12010,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12088,7 +12053,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 27953-2026</t>
+          <t>A 56554-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12102,10 +12067,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46193</v>
+        <v>45975</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12117,13 +12082,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12166,7 +12126,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 28026-2026</t>
+          <t>A 57012-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12180,10 +12140,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46195</v>
+        <v>45978</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12196,7 +12156,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12239,7 +12199,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 39668-2023</t>
+          <t>A 58780-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12253,10 +12213,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45167</v>
+        <v>45986</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12269,7 +12229,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12312,7 +12272,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 5818-2023</t>
+          <t>A 61411-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12326,10 +12286,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44963</v>
+        <v>46000</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12342,7 +12302,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12385,7 +12345,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 5030-2022</t>
+          <t>A 61792-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12399,10 +12359,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44593</v>
+        <v>46002</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12415,7 +12375,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.3</v>
+        <v>10.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12458,7 +12418,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 40244-2024</t>
+          <t>A 61682-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12472,10 +12432,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45554</v>
+        <v>46002</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12531,7 +12491,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 64481-2023</t>
+          <t>A 61677-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12545,10 +12505,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45280</v>
+        <v>46002</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12561,7 +12521,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12604,7 +12564,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 30160-2026</t>
+          <t>A 63511-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12618,10 +12578,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46206</v>
+        <v>46013</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12634,7 +12594,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12677,7 +12637,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 55074-2023</t>
+          <t>A 63220-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12691,10 +12651,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45237</v>
+        <v>46010</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12707,7 +12667,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12750,7 +12710,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 58356-2022</t>
+          <t>A 1664-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12764,10 +12724,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44893</v>
+        <v>46034</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12780,7 +12740,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12823,7 +12783,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 14355-2023</t>
+          <t>A 58779-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12837,10 +12797,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45012</v>
+        <v>45986</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12853,7 +12813,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12896,7 +12856,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 13913-2024</t>
+          <t>A 9641-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12910,10 +12870,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45391</v>
+        <v>46070</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12925,8 +12885,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -12969,7 +12934,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 46254-2024</t>
+          <t>A 9624-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -12983,10 +12948,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45581</v>
+        <v>46070</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -12996,6 +12961,11 @@
       <c r="G168" t="inlineStr">
         <is>
           <t>GNOSJÖ</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I168" t="n">
@@ -13042,7 +13012,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 13352-2024</t>
+          <t>A 9627-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13056,10 +13026,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45387</v>
+        <v>46070</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13071,8 +13041,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I169" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13115,7 +13090,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 13610-2024</t>
+          <t>A 11667-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13129,10 +13104,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45390</v>
+        <v>46084</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13145,7 +13120,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13188,7 +13163,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 56393-2023</t>
+          <t>A 13600-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13202,10 +13177,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45243</v>
+        <v>46097</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13217,8 +13192,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13261,7 +13241,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 36653-2022</t>
+          <t>A 17402-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13271,14 +13251,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44804</v>
+        <v>46120</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13291,7 +13271,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13334,7 +13314,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 48229-2022</t>
+          <t>A 18473-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13348,10 +13328,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44858</v>
+        <v>46127</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13364,7 +13344,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13407,7 +13387,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 5089-2024</t>
+          <t>A 19171-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13421,10 +13401,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45330</v>
+        <v>46132</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13437,7 +13417,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.9</v>
+        <v>22.2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13480,7 +13460,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 58247-2021</t>
+          <t>A 37864-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13494,10 +13474,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44487</v>
+        <v>45881</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13510,7 +13490,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>8.9</v>
+        <v>3.8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13553,7 +13533,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 31772-2023</t>
+          <t>A 18337-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13567,10 +13547,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45118</v>
+        <v>46125</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13583,7 +13563,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13626,7 +13606,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 6662-2024</t>
+          <t>A 54833-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13640,10 +13620,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45341</v>
+        <v>45618</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13655,8 +13635,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I177" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13699,7 +13684,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 1450-2024</t>
+          <t>A 61532-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13709,14 +13694,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45303</v>
+        <v>45265</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13728,8 +13713,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13772,7 +13762,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 31983-2026</t>
+          <t>A 36905-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13786,10 +13776,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46232</v>
+        <v>45538</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13802,7 +13792,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -13845,7 +13835,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 6785-2025</t>
+          <t>A 21076-2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13859,10 +13849,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45700</v>
+        <v>45777</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13875,7 +13865,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13918,7 +13908,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 6793-2025</t>
+          <t>A 37963-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13932,10 +13922,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45700</v>
+        <v>45544</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -13948,7 +13938,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.9</v>
+        <v>5.3</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -13991,7 +13981,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 37630-2026</t>
+          <t>A 3987-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14005,10 +13995,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46276</v>
+        <v>45322</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14020,13 +14010,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>13.6</v>
+        <v>2.5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14069,7 +14054,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 32826-2023</t>
+          <t>A 42618-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14083,10 +14068,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45124</v>
+        <v>45905</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14099,7 +14084,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14142,7 +14127,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 27952-2026</t>
+          <t>A 23132-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14156,10 +14141,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46193</v>
+        <v>46161</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14171,13 +14156,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>8.5</v>
+        <v>3.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14220,7 +14200,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 32177-2024</t>
+          <t>A 27954-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14234,10 +14214,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45511</v>
+        <v>46193</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14250,7 +14230,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14293,7 +14273,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 41357-2023</t>
+          <t>A 27951-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14307,10 +14287,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45174</v>
+        <v>46193</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14322,8 +14302,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14366,7 +14351,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 38885-2026</t>
+          <t>A 27953-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14380,10 +14365,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46286</v>
+        <v>46193</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14395,8 +14380,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>3.5</v>
+        <v>5.7</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14439,7 +14429,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 62045-2022</t>
+          <t>A 27729-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14449,14 +14439,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44918</v>
+        <v>46191</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14469,7 +14459,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14512,7 +14502,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 15434-2023</t>
+          <t>A 28026-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14526,10 +14516,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45020</v>
+        <v>46195</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14542,7 +14532,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14585,7 +14575,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 38886-2026</t>
+          <t>A 28018-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14599,10 +14589,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46286</v>
+        <v>46195</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14615,7 +14605,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14658,7 +14648,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 23259-2023</t>
+          <t>A 28058-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14672,10 +14662,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45075</v>
+        <v>46195</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14688,7 +14678,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14731,7 +14721,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 32903-2026</t>
+          <t>A 30160-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14745,10 +14735,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46244</v>
+        <v>46206</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14761,7 +14751,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -14804,7 +14794,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 32913-2026</t>
+          <t>A 31983-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14818,10 +14808,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46244</v>
+        <v>46232</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14834,7 +14824,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -14877,7 +14867,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 23138-2026</t>
+          <t>A 37630-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14891,10 +14881,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46161</v>
+        <v>46276</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14906,8 +14896,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>2.3</v>
+        <v>13.6</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -14950,7 +14945,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 30314-2024</t>
+          <t>A 27952-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -14964,10 +14959,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45490</v>
+        <v>46193</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -14979,8 +14974,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I195" t="n">
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15023,7 +15023,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 20948-2024</t>
+          <t>A 39094-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15037,10 +15037,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45439</v>
+        <v>46283</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15052,8 +15052,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15096,7 +15101,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 39094-2026</t>
+          <t>A 38885-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15110,10 +15115,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15125,13 +15130,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15174,7 +15174,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 39453-2026</t>
+          <t>A 23138-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15188,10 +15188,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46288</v>
+        <v>46161</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15247,7 +15247,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 8119-2025</t>
+          <t>A 38886-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15261,10 +15261,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45707</v>
+        <v>46286</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15320,7 +15320,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 270-2023</t>
+          <t>A 32913-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15334,10 +15334,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44928</v>
+        <v>46244</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15393,7 +15393,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 29707-2024</t>
+          <t>A 32903-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15403,14 +15403,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45485</v>
+        <v>46244</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>7.7</v>
+        <v>0.9</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15466,7 +15466,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 18314-2024</t>
+          <t>A 39453-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15480,10 +15480,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45422</v>
+        <v>46288</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15496,7 +15496,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15556,7 +15556,7 @@
         <v>46185</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>44166</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>44712</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>44711</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>45763</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>45798</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16014,7 +16014,7 @@
         <v>46160</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>

--- a/Översikt GNOSJÖ.xlsx
+++ b/Översikt GNOSJÖ.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE209"/>
+  <dimension ref="A1:AE212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44757</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46030</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44711</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 38355-2023</t>
+          <t>A 28312-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -919,14 +919,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45161</v>
+        <v>45818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -939,23 +939,23 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
@@ -963,264 +963,264 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 28312-2025 artfynd.xlsx", "A 28312-2025")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 28312-2025 karta.png", "A 28312-2025")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 28312-2025 georefererad karta.tif", "A 28312-2025")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 28312-2025 FSC-klagomål.docx", "A 28312-2025")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 28312-2025 FSC-klagomål mail.docx", "A 28312-2025")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 28312-2025 tillsynsbegäran.docx", "A 28312-2025")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 28312-2025 tillsynsbegäran mail.docx", "A 28312-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 38355-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45161</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>GNOSJÖ</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Mattlummer</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 38355-2023 artfynd.xlsx", "A 38355-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 38355-2023 karta.png", "A 38355-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 38355-2023 georefererad karta.tif", "A 38355-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 38355-2023 FSC-klagomål.docx", "A 38355-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 38355-2023 FSC-klagomål mail.docx", "A 38355-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 38355-2023 tillsynsbegäran.docx", "A 38355-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 38355-2023 tillsynsbegäran mail.docx", "A 38355-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>A 23612-2022</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
         <v>44721</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>GNOSJÖ</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
+      <c r="E7" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>GNOSJÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>4.4</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>1</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T7" t="n">
         <v>1</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Kungsfågel</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 23612-2022 artfynd.xlsx", "A 23612-2022")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 23612-2022 karta.png", "A 23612-2022")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 23612-2022 georefererad karta.tif", "A 23612-2022")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 23612-2022 FSC-klagomål.docx", "A 23612-2022")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 23612-2022 FSC-klagomål mail.docx", "A 23612-2022")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 23612-2022 tillsynsbegäran.docx", "A 23612-2022")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 23612-2022 tillsynsbegäran mail.docx", "A 23612-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 28312-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45818</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>GNOSJÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/artfynd/A 28312-2025 artfynd.xlsx", "A 28312-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor/A 28312-2025 karta.png", "A 28312-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/kartor_geotiff/A 28312-2025 georefererad karta.tif", "A 28312-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomål/A 28312-2025 FSC-klagomål.docx", "A 28312-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/klagomålsmail/A 28312-2025 FSC-klagomål mail.docx", "A 28312-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsyn/A 28312-2025 tillsynsbegäran.docx", "A 28312-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0617/tillsynsmail/A 28312-2025 tillsynsbegäran mail.docx", "A 28312-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>44530</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>44837</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>44482</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>44474</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>44585</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>44866</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>44503</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 54376-2021</t>
+          <t>A 59855-2021</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44470</v>
+        <v>44494</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 704-2022</t>
+          <t>A 20077-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1827,10 +1827,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44568</v>
+        <v>44698</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
         <v>44698</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 59855-2021</t>
+          <t>A 704-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44494</v>
+        <v>44568</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2032,7 +2032,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 20077-2022</t>
+          <t>A 36525-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44698</v>
+        <v>44804</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2105,7 +2105,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 28372-2022</t>
+          <t>A 47858-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44747</v>
+        <v>44855</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2178,7 +2178,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 36525-2022</t>
+          <t>A 28372-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2192,10 +2192,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44804</v>
+        <v>44747</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>44588</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 47858-2022</t>
+          <t>A 48480-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44855</v>
+        <v>44858</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2397,7 +2397,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 13352-2024</t>
+          <t>A 16243-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45387</v>
+        <v>45749</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2424,6 +2424,11 @@
       <c r="G24" t="inlineStr">
         <is>
           <t>GNOSJÖ</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -2470,7 +2475,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 42280-2023</t>
+          <t>A 43758-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2484,10 +2489,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45180</v>
+        <v>45187</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2500,7 +2505,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2543,7 +2548,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 46657-2022</t>
+          <t>A 43784-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2557,10 +2562,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44850</v>
+        <v>45187</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2573,7 +2578,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>7.9</v>
+        <v>3.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2616,7 +2621,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 48480-2022</t>
+          <t>A 47454-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2630,10 +2635,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44858</v>
+        <v>45202</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2646,7 +2651,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2689,7 +2694,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 54362-2021</t>
+          <t>A 59026-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2703,10 +2708,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44470</v>
+        <v>45252</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2719,7 +2724,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2762,7 +2767,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 6781-2022</t>
+          <t>A 33575-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2776,10 +2781,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44602</v>
+        <v>44789</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2792,7 +2797,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2835,7 +2840,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 41347-2023</t>
+          <t>A 23254-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2849,10 +2854,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45174</v>
+        <v>45075</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2865,7 +2870,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>6.2</v>
+        <v>1.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2908,7 +2913,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 20948-2024</t>
+          <t>A 63511-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2922,10 +2927,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45439</v>
+        <v>46013</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2938,7 +2943,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2981,7 +2986,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 5089-2024</t>
+          <t>A 64718-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2995,10 +3000,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45330</v>
+        <v>45281</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3011,7 +3016,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3054,7 +3059,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 50440-2022</t>
+          <t>A 1664-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3068,10 +3073,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44866</v>
+        <v>46034</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3084,7 +3089,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>8.699999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3127,7 +3132,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 4992-2023</t>
+          <t>A 46657-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3141,10 +3146,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44958</v>
+        <v>44850</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3157,7 +3162,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.9</v>
+        <v>7.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3200,7 +3205,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 43790-2023</t>
+          <t>A 3504-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3214,10 +3219,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45187</v>
+        <v>44950</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3230,7 +3235,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3273,7 +3278,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 47454-2023</t>
+          <t>A 27264-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3287,10 +3292,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45202</v>
+        <v>45096</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3303,7 +3308,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3346,7 +3351,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 59026-2023</t>
+          <t>A 15776-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3360,10 +3365,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45252</v>
+        <v>45021</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3376,7 +3381,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3419,7 +3424,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 58970-2024</t>
+          <t>A 5082-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3433,10 +3438,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45636</v>
+        <v>45330</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3449,7 +3454,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3492,7 +3497,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 23259-2023</t>
+          <t>A 6415-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3506,10 +3511,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45075</v>
+        <v>45699</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3522,7 +3527,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3565,7 +3570,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 34083-2023</t>
+          <t>A 8698-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3579,10 +3584,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45125</v>
+        <v>45712</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3595,7 +3600,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3638,7 +3643,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 5030-2022</t>
+          <t>A 41347-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3652,10 +3657,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44593</v>
+        <v>45174</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3668,7 +3673,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.3</v>
+        <v>6.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3711,7 +3716,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62053-2022</t>
+          <t>A 30091-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3721,14 +3726,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44918</v>
+        <v>45489</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3741,7 +3746,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3784,7 +3789,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 6785-2025</t>
+          <t>A 40552-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3798,10 +3803,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45700</v>
+        <v>45896</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3814,7 +3819,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3857,7 +3862,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 6793-2025</t>
+          <t>A 50440-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3871,10 +3876,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45700</v>
+        <v>44866</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3887,7 +3892,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3930,7 +3935,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 59727-2024</t>
+          <t>A 5707-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3944,10 +3949,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45639</v>
+        <v>44596</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3960,7 +3965,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4003,7 +4008,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 15434-2023</t>
+          <t>A 40863-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4017,10 +4022,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45020</v>
+        <v>45897</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4033,7 +4038,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4076,7 +4081,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 30101-2024</t>
+          <t>A 21080-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4086,14 +4091,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45489</v>
+        <v>45777</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4106,7 +4111,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4149,7 +4154,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 6789-2025</t>
+          <t>A 42615-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4163,10 +4168,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45700</v>
+        <v>45905</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4179,7 +4184,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4222,7 +4227,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 58247-2021</t>
+          <t>A 43637-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4236,10 +4241,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44487</v>
+        <v>45911</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4252,7 +4257,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>8.9</v>
+        <v>4.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4295,7 +4300,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 58249-2021</t>
+          <t>A 43656-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4309,10 +4314,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44487</v>
+        <v>45912</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4325,7 +4330,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4368,7 +4373,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 25487-2022</t>
+          <t>A 58779-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4382,10 +4387,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44732</v>
+        <v>45986</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4398,7 +4403,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>7.1</v>
+        <v>1.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4441,7 +4446,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 6763-2025</t>
+          <t>A 24861-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4455,10 +4460,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45700</v>
+        <v>45799</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4471,7 +4476,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.6</v>
+        <v>5.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4514,7 +4519,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 41918-2022</t>
+          <t>A 44383-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4528,10 +4533,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44830</v>
+        <v>45916</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4544,7 +4549,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4587,7 +4592,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 61531-2023</t>
+          <t>A 44394-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4597,14 +4602,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45265</v>
+        <v>45916</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4616,13 +4621,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4665,7 +4665,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 26746-2023</t>
+          <t>A 9641-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4679,10 +4679,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45093</v>
+        <v>46070</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4694,8 +4694,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4738,7 +4743,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 15776-2023</t>
+          <t>A 9624-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4752,10 +4757,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45021</v>
+        <v>46070</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4767,8 +4772,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4811,7 +4821,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 13913-2024</t>
+          <t>A 9627-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4825,10 +4835,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45391</v>
+        <v>46070</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4840,8 +4850,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4884,7 +4899,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 27036-2023</t>
+          <t>A 56625-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4898,10 +4913,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45095</v>
+        <v>44893</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4914,7 +4929,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4957,7 +4972,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 33575-2022</t>
+          <t>A 55909-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4971,10 +4986,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44789</v>
+        <v>44889</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4987,7 +5002,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5030,7 +5045,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 43760-2023</t>
+          <t>A 25482-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5044,10 +5059,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45187</v>
+        <v>45802</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5060,7 +5075,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5103,7 +5118,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 43784-2023</t>
+          <t>A 30101-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5113,14 +5128,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45187</v>
+        <v>45489</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5133,7 +5148,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5176,7 +5191,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 55909-2022</t>
+          <t>A 11667-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5190,10 +5205,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44889</v>
+        <v>46084</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5206,7 +5221,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5249,7 +5264,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 51901-2022</t>
+          <t>A 15436-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5263,10 +5278,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44872</v>
+        <v>45401</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5279,7 +5294,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>7.3</v>
+        <v>2.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5322,7 +5337,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 14355-2023</t>
+          <t>A 50728-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5336,10 +5351,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45012</v>
+        <v>45946</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5352,7 +5367,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.6</v>
+        <v>15.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5395,7 +5410,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 26210-2024</t>
+          <t>A 13600-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5409,10 +5424,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45468</v>
+        <v>46097</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5424,8 +5439,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5468,7 +5488,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 16244-2025</t>
+          <t>A 62053-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5482,10 +5502,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45749</v>
+        <v>44918</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5497,13 +5517,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5546,7 +5561,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 11157-2024</t>
+          <t>A 4293-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5560,10 +5575,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45371</v>
+        <v>44588</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5576,7 +5591,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5619,7 +5634,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 39668-2023</t>
+          <t>A 50304-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5633,10 +5648,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45167</v>
+        <v>45600</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5649,7 +5664,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5692,7 +5707,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 11163-2024</t>
+          <t>A 8747-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5706,10 +5721,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45371</v>
+        <v>45356</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5722,7 +5737,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5765,7 +5780,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 40067-2023</t>
+          <t>A 17402-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5779,10 +5794,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45168</v>
+        <v>46120</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5795,7 +5810,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5838,7 +5853,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 22650-2024</t>
+          <t>A 56240-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5852,10 +5867,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45447</v>
+        <v>45974</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5868,7 +5883,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>7.9</v>
+        <v>3.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5911,7 +5926,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 41357-2023</t>
+          <t>A 55918-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5925,10 +5940,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45174</v>
+        <v>45973</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5941,7 +5956,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5984,7 +5999,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 48188-2022</t>
+          <t>A 56554-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5998,10 +6013,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44853</v>
+        <v>45975</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6014,7 +6029,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.3</v>
+        <v>7.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6057,7 +6072,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 25837-2023</t>
+          <t>A 18473-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6071,10 +6086,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45090</v>
+        <v>46127</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6087,7 +6102,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6130,7 +6145,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 57730-2023</t>
+          <t>A 7316-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6144,10 +6159,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45246</v>
+        <v>45345</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6160,7 +6175,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6203,7 +6218,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 23625-2022</t>
+          <t>A 57012-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6217,10 +6232,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44721</v>
+        <v>45978</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6233,7 +6248,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6276,7 +6291,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 16303-2023</t>
+          <t>A 19171-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6290,10 +6305,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45028</v>
+        <v>46132</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6306,7 +6321,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>6.3</v>
+        <v>22.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6349,7 +6364,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 31772-2023</t>
+          <t>A 4992-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6363,10 +6378,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45118</v>
+        <v>44958</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6379,7 +6394,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6422,7 +6437,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 6662-2024</t>
+          <t>A 58249-2021</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6436,10 +6451,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45341</v>
+        <v>44487</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6452,7 +6467,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.2</v>
+        <v>3.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6495,7 +6510,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 30314-2024</t>
+          <t>A 58780-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6509,10 +6524,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45490</v>
+        <v>45986</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6525,7 +6540,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6568,7 +6583,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 5707-2022</t>
+          <t>A 19307-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6582,10 +6597,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44596</v>
+        <v>45049</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6598,7 +6613,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6641,7 +6656,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 8747-2024</t>
+          <t>A 18337-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6655,10 +6670,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45356</v>
+        <v>46125</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6671,7 +6686,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6714,7 +6729,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 64481-2023</t>
+          <t>A 54833-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6728,10 +6743,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45280</v>
+        <v>45618</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6743,8 +6758,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>5.5</v>
+        <v>1.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6787,7 +6807,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 32177-2024</t>
+          <t>A 25487-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6801,10 +6821,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45511</v>
+        <v>44732</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6817,7 +6837,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.9</v>
+        <v>7.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6860,7 +6880,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 8119-2025</t>
+          <t>A 58970-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6874,10 +6894,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45707</v>
+        <v>45636</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6890,7 +6910,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6933,7 +6953,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 60859-2024</t>
+          <t>A 29066-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6947,10 +6967,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45644</v>
+        <v>44750</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6963,7 +6983,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7006,7 +7026,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 270-2023</t>
+          <t>A 34083-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7020,10 +7040,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44928</v>
+        <v>45125</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7036,7 +7056,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7079,7 +7099,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 56393-2023</t>
+          <t>A 21076-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7093,10 +7113,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45243</v>
+        <v>45777</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7109,7 +7129,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7152,7 +7172,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 32826-2023</t>
+          <t>A 49758-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7166,10 +7186,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45124</v>
+        <v>45597</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7182,7 +7202,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7225,7 +7245,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 55074-2023</t>
+          <t>A 25837-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7239,10 +7259,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45237</v>
+        <v>45090</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7255,7 +7275,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7298,7 +7318,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 1450-2024</t>
+          <t>A 61411-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7312,10 +7332,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45303</v>
+        <v>46000</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7328,7 +7348,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7371,7 +7391,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 18314-2024</t>
+          <t>A 23625-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7385,10 +7405,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45422</v>
+        <v>44721</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7401,7 +7421,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7444,7 +7464,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 29707-2024</t>
+          <t>A 61677-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7454,14 +7474,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45485</v>
+        <v>46002</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7474,7 +7494,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>7.7</v>
+        <v>0.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7517,7 +7537,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 5818-2023</t>
+          <t>A 61682-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7531,10 +7551,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44963</v>
+        <v>46002</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7547,7 +7567,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7590,7 +7610,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 62045-2022</t>
+          <t>A 61792-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7604,10 +7624,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44918</v>
+        <v>46002</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7620,7 +7640,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.4</v>
+        <v>10.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7663,7 +7683,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 40244-2024</t>
+          <t>A 47856-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7677,10 +7697,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45554</v>
+        <v>44855</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7693,7 +7713,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7736,7 +7756,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 30961-2023</t>
+          <t>A 41323-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7750,10 +7770,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45113</v>
+        <v>44826</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7766,7 +7786,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7809,7 +7829,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 13610-2024</t>
+          <t>A 37963-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7823,10 +7843,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45390</v>
+        <v>45544</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7839,7 +7859,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>5.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7882,7 +7902,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 49758-2024</t>
+          <t>A 36905-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7896,10 +7916,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45597</v>
+        <v>45538</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7912,7 +7932,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7955,7 +7975,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 48229-2022</t>
+          <t>A 63220-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7969,10 +7989,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44858</v>
+        <v>46010</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -7985,7 +8005,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8028,7 +8048,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 41323-2022</t>
+          <t>A 30669-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8042,10 +8062,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44826</v>
+        <v>45831</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8058,7 +8078,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8101,7 +8121,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 4293-2022</t>
+          <t>A 30654-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8115,10 +8135,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44588</v>
+        <v>45831</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8174,7 +8194,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 24861-2025</t>
+          <t>A 31235-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8188,10 +8208,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45799</v>
+        <v>45832</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8204,7 +8224,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8247,7 +8267,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 25482-2025</t>
+          <t>A 31228-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8261,10 +8281,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45802</v>
+        <v>45832</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8277,7 +8297,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>8.300000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8320,7 +8340,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 36406-2022</t>
+          <t>A 3987-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8334,10 +8354,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44803</v>
+        <v>45322</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8350,7 +8370,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8393,7 +8413,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 27264-2023</t>
+          <t>A 16303-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8407,10 +8427,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45096</v>
+        <v>45028</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8423,7 +8443,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.4</v>
+        <v>6.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8466,7 +8486,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 15436-2024</t>
+          <t>A 27675-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8480,10 +8500,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45401</v>
+        <v>45813</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8496,7 +8516,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8539,7 +8559,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 10996-2024</t>
+          <t>A 61532-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8549,14 +8569,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45370</v>
+        <v>45265</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8568,8 +8588,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>5.9</v>
+        <v>1.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8612,7 +8637,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 22846-2024</t>
+          <t>A 36508-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8626,10 +8651,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45448</v>
+        <v>44804</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8642,7 +8667,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8685,7 +8710,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 30091-2024</t>
+          <t>A 51901-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8695,14 +8720,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45489</v>
+        <v>44872</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8715,7 +8740,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.5</v>
+        <v>7.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8758,7 +8783,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 7316-2024</t>
+          <t>A 42618-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8772,10 +8797,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45345</v>
+        <v>45905</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8831,7 +8856,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 48227-2022</t>
+          <t>A 41918-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8845,10 +8870,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44858</v>
+        <v>44830</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8861,7 +8886,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8904,7 +8929,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 58356-2022</t>
+          <t>A 37864-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8918,10 +8943,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44893</v>
+        <v>45881</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8934,7 +8959,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -8977,7 +9002,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 43758-2023</t>
+          <t>A 57730-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -8991,10 +9016,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45187</v>
+        <v>45246</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9050,7 +9075,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 6747-2025</t>
+          <t>A 6763-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9067,7 +9092,7 @@
         <v>45700</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9080,7 +9105,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9123,7 +9148,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 20078-2022</t>
+          <t>A 37198-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9137,10 +9162,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44698</v>
+        <v>45875</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9153,7 +9178,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9196,7 +9221,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 50304-2024</t>
+          <t>A 42280-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9210,10 +9235,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45600</v>
+        <v>45180</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9226,7 +9251,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9269,7 +9294,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 30654-2025</t>
+          <t>A 38510-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9283,10 +9308,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45831</v>
+        <v>45884</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9299,7 +9324,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9342,7 +9367,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 30669-2025</t>
+          <t>A 27258-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9356,10 +9381,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45831</v>
+        <v>45096</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9372,7 +9397,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9415,7 +9440,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 31228-2025</t>
+          <t>A 48188-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9429,10 +9454,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45832</v>
+        <v>44853</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9445,7 +9470,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9488,7 +9513,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 31235-2025</t>
+          <t>A 26746-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9502,10 +9527,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45832</v>
+        <v>45093</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9518,7 +9543,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9561,7 +9586,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 16243-2025</t>
+          <t>A 11157-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9575,10 +9600,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45749</v>
+        <v>45371</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9590,13 +9615,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9639,7 +9659,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 43786-2023</t>
+          <t>A 11163-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9653,10 +9673,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45187</v>
+        <v>45371</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9669,7 +9689,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9712,7 +9732,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 43787-2023</t>
+          <t>A 23132-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9726,10 +9746,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45187</v>
+        <v>46161</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9742,7 +9762,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9785,7 +9805,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 35325-2023</t>
+          <t>A 22650-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9799,10 +9819,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45146</v>
+        <v>45447</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9815,7 +9835,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.7</v>
+        <v>7.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9858,7 +9878,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 73961-2021</t>
+          <t>A 26210-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9872,10 +9892,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44553</v>
+        <v>45468</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9887,13 +9907,8 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>5.1</v>
+        <v>1.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -9936,7 +9951,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 46254-2024</t>
+          <t>A 60859-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9950,10 +9965,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45581</v>
+        <v>45644</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -9966,7 +9981,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10009,7 +10024,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 27258-2023</t>
+          <t>A 43787-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10023,10 +10038,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45096</v>
+        <v>45187</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10039,7 +10054,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10082,7 +10097,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 47856-2022</t>
+          <t>A 43760-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10096,10 +10111,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44855</v>
+        <v>45187</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10112,7 +10127,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10155,7 +10170,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 29066-2022</t>
+          <t>A 43790-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10169,10 +10184,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44750</v>
+        <v>45187</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10185,7 +10200,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10228,7 +10243,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 19307-2023</t>
+          <t>A 35325-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10242,10 +10257,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45049</v>
+        <v>45146</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10258,7 +10273,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10301,7 +10316,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 27675-2025</t>
+          <t>A 10996-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10315,10 +10330,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45813</v>
+        <v>45370</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10331,7 +10346,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.1</v>
+        <v>5.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10374,7 +10389,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 56625-2022</t>
+          <t>A 40067-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10388,10 +10403,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44893</v>
+        <v>45168</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10404,7 +10419,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10447,7 +10462,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 3504-2023</t>
+          <t>A 73961-2021</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10461,10 +10476,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44950</v>
+        <v>44553</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10476,8 +10491,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>0.6</v>
+        <v>5.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10520,7 +10540,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 36508-2022</t>
+          <t>A 20078-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10534,10 +10554,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44804</v>
+        <v>44698</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10550,7 +10570,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10593,7 +10613,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 9828-2025</t>
+          <t>A 6781-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10607,10 +10627,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45716</v>
+        <v>44602</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10623,7 +10643,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10666,7 +10686,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 36653-2022</t>
+          <t>A 36406-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10676,14 +10696,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44804</v>
+        <v>44803</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10739,7 +10759,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 8698-2025</t>
+          <t>A 27036-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10753,10 +10773,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45712</v>
+        <v>45095</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10769,7 +10789,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10812,7 +10832,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 23254-2023</t>
+          <t>A 27729-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10822,14 +10842,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45075</v>
+        <v>46191</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10842,7 +10862,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.4</v>
+        <v>5.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10885,7 +10905,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 64718-2023</t>
+          <t>A 9828-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10899,10 +10919,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45281</v>
+        <v>45716</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10915,7 +10935,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>4.4</v>
+        <v>0.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -10958,7 +10978,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 5082-2024</t>
+          <t>A 43786-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10972,10 +10992,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45330</v>
+        <v>45187</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -10988,7 +11008,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11031,7 +11051,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 38510-2025</t>
+          <t>A 28018-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11045,10 +11065,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45884</v>
+        <v>46195</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11061,7 +11081,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11104,7 +11124,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 37198-2025</t>
+          <t>A 27954-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11118,10 +11138,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45875</v>
+        <v>46193</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11134,7 +11154,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11177,7 +11197,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 6415-2025</t>
+          <t>A 27951-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11191,10 +11211,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45699</v>
+        <v>46193</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11206,8 +11226,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11250,7 +11275,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 50728-2025</t>
+          <t>A 28058-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11264,10 +11289,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45946</v>
+        <v>46195</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11280,7 +11305,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>15.2</v>
+        <v>1.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11323,7 +11348,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 40863-2025</t>
+          <t>A 27953-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11337,10 +11362,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45897</v>
+        <v>46193</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11352,8 +11377,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>1.3</v>
+        <v>5.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11396,7 +11426,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 40552-2025</t>
+          <t>A 28026-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11410,10 +11440,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45896</v>
+        <v>46195</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11426,7 +11456,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11469,7 +11499,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 21080-2025</t>
+          <t>A 6747-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11483,10 +11513,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45777</v>
+        <v>45700</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11499,7 +11529,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11542,7 +11572,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 42615-2025</t>
+          <t>A 6789-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11556,10 +11586,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45905</v>
+        <v>45700</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11572,7 +11602,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11615,7 +11645,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 43637-2025</t>
+          <t>A 59727-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11629,10 +11659,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45911</v>
+        <v>45639</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11645,7 +11675,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11688,7 +11718,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 43656-2025</t>
+          <t>A 30961-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11702,10 +11732,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45912</v>
+        <v>45113</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11718,7 +11748,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11761,7 +11791,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 44383-2025</t>
+          <t>A 30160-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11775,10 +11805,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45916</v>
+        <v>46206</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11791,7 +11821,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11834,7 +11864,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 44394-2025</t>
+          <t>A 16244-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11848,10 +11878,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45916</v>
+        <v>45749</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11863,8 +11893,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11907,7 +11942,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 55918-2025</t>
+          <t>A 48227-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11921,10 +11956,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45973</v>
+        <v>44858</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11937,7 +11972,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -11980,7 +12015,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 56240-2025</t>
+          <t>A 22846-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11994,10 +12029,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45974</v>
+        <v>45448</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12010,7 +12045,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12053,7 +12088,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 56554-2025</t>
+          <t>A 61531-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12063,14 +12098,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45975</v>
+        <v>45265</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12082,8 +12117,13 @@
           <t>GNOSJÖ</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>7.2</v>
+        <v>0.9</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12126,7 +12166,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 57012-2025</t>
+          <t>A 39668-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12140,10 +12180,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45978</v>
+        <v>45167</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12156,7 +12196,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12199,7 +12239,7 @@
     <row r="158" ht="15" customHeight=